--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/England EFL League Two_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/England EFL League Two_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2018" uniqueCount="417">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2090" uniqueCount="427">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -889,6 +889,24 @@
     <t>['45+5']</t>
   </si>
   <si>
+    <t>['80']</t>
+  </si>
+  <si>
+    <t>['78', '87']</t>
+  </si>
+  <si>
+    <t>['7', '56']</t>
+  </si>
+  <si>
+    <t>['13', '52', '59', '86']</t>
+  </si>
+  <si>
+    <t>['88']</t>
+  </si>
+  <si>
+    <t>['31', '73']</t>
+  </si>
+  <si>
     <t>['1', '9']</t>
   </si>
   <si>
@@ -995,9 +1013,6 @@
   </si>
   <si>
     <t>['35', '45+2', '45+4', '87', '90']</t>
-  </si>
-  <si>
-    <t>['88']</t>
   </si>
   <si>
     <t>['25', '51', '57', '67', '85', '90+4']</t>
@@ -1255,9 +1270,6 @@
     <t>['90+5']</t>
   </si>
   <si>
-    <t>['80']</t>
-  </si>
-  <si>
     <t>['19', '85']</t>
   </si>
   <si>
@@ -1265,6 +1277,24 @@
   </si>
   <si>
     <t>['28', '29', '78']</t>
+  </si>
+  <si>
+    <t>['17', '20']</t>
+  </si>
+  <si>
+    <t>['4', '75']</t>
+  </si>
+  <si>
+    <t>['9', '33', '63']</t>
+  </si>
+  <si>
+    <t>['41', '75']</t>
+  </si>
+  <si>
+    <t>['45+2', '47', '83', '90', '90+6']</t>
+  </si>
+  <si>
+    <t>['46', '70']</t>
   </si>
 </sst>
 </file>
@@ -1626,7 +1656,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP326"/>
+  <dimension ref="A1:BP338"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1963,7 +1993,7 @@
         <v>1.57</v>
       </c>
       <c r="AQ2">
-        <v>0.87</v>
+        <v>1</v>
       </c>
       <c r="AR2">
         <v>0</v>
@@ -2088,7 +2118,7 @@
         <v>95</v>
       </c>
       <c r="P3" t="s">
-        <v>291</v>
+        <v>297</v>
       </c>
       <c r="Q3">
         <v>2.5</v>
@@ -2166,10 +2196,10 @@
         <v>0</v>
       </c>
       <c r="AP3">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="AQ3">
-        <v>1.08</v>
+        <v>1.21</v>
       </c>
       <c r="AR3">
         <v>0</v>
@@ -2375,7 +2405,7 @@
         <v>1.57</v>
       </c>
       <c r="AQ4">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="AR4">
         <v>0</v>
@@ -2500,7 +2530,7 @@
         <v>97</v>
       </c>
       <c r="P5" t="s">
-        <v>292</v>
+        <v>298</v>
       </c>
       <c r="Q5">
         <v>2.4</v>
@@ -2578,7 +2608,7 @@
         <v>0</v>
       </c>
       <c r="AP5">
-        <v>1.71</v>
+        <v>1.8</v>
       </c>
       <c r="AQ5">
         <v>0.67</v>
@@ -2784,10 +2814,10 @@
         <v>0</v>
       </c>
       <c r="AP6">
-        <v>1.79</v>
+        <v>1.87</v>
       </c>
       <c r="AQ6">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR6">
         <v>0</v>
@@ -2993,7 +3023,7 @@
         <v>1.47</v>
       </c>
       <c r="AQ7">
-        <v>1.36</v>
+        <v>1.47</v>
       </c>
       <c r="AR7">
         <v>0</v>
@@ -3196,7 +3226,7 @@
         <v>0</v>
       </c>
       <c r="AP8">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="AQ8">
         <v>0.86</v>
@@ -3324,7 +3354,7 @@
         <v>101</v>
       </c>
       <c r="P9" t="s">
-        <v>293</v>
+        <v>299</v>
       </c>
       <c r="Q9">
         <v>2.75</v>
@@ -3402,7 +3432,7 @@
         <v>0</v>
       </c>
       <c r="AP9">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AQ9">
         <v>1.43</v>
@@ -3530,7 +3560,7 @@
         <v>102</v>
       </c>
       <c r="P10" t="s">
-        <v>294</v>
+        <v>300</v>
       </c>
       <c r="Q10">
         <v>2.63</v>
@@ -3611,7 +3641,7 @@
         <v>1.56</v>
       </c>
       <c r="AQ10">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR10">
         <v>0</v>
@@ -3736,7 +3766,7 @@
         <v>101</v>
       </c>
       <c r="P11" t="s">
-        <v>295</v>
+        <v>301</v>
       </c>
       <c r="Q11">
         <v>2.88</v>
@@ -4020,10 +4050,10 @@
         <v>0</v>
       </c>
       <c r="AP12">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="AQ12">
-        <v>1.64</v>
+        <v>1.73</v>
       </c>
       <c r="AR12">
         <v>0</v>
@@ -4226,7 +4256,7 @@
         <v>0</v>
       </c>
       <c r="AP13">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="AQ13">
         <v>0.93</v>
@@ -4432,10 +4462,10 @@
         <v>0</v>
       </c>
       <c r="AP14">
-        <v>0.6899999999999999</v>
+        <v>0.64</v>
       </c>
       <c r="AQ14">
-        <v>0.6899999999999999</v>
+        <v>0.64</v>
       </c>
       <c r="AR14">
         <v>0</v>
@@ -4638,7 +4668,7 @@
         <v>0</v>
       </c>
       <c r="AP15">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="AQ15">
         <v>1.38</v>
@@ -4766,7 +4796,7 @@
         <v>105</v>
       </c>
       <c r="P16" t="s">
-        <v>296</v>
+        <v>302</v>
       </c>
       <c r="Q16">
         <v>2.88</v>
@@ -5053,7 +5083,7 @@
         <v>1.43</v>
       </c>
       <c r="AQ17">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AR17">
         <v>0</v>
@@ -5178,7 +5208,7 @@
         <v>101</v>
       </c>
       <c r="P18" t="s">
-        <v>297</v>
+        <v>303</v>
       </c>
       <c r="Q18">
         <v>3.4</v>
@@ -5259,7 +5289,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ18">
-        <v>1.31</v>
+        <v>1.21</v>
       </c>
       <c r="AR18">
         <v>0</v>
@@ -5384,7 +5414,7 @@
         <v>107</v>
       </c>
       <c r="P19" t="s">
-        <v>298</v>
+        <v>304</v>
       </c>
       <c r="Q19">
         <v>3</v>
@@ -5668,7 +5698,7 @@
         <v>0</v>
       </c>
       <c r="AP20">
-        <v>0.5</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AQ20">
         <v>1</v>
@@ -5874,7 +5904,7 @@
         <v>0</v>
       </c>
       <c r="AP21">
-        <v>1.55</v>
+        <v>1.67</v>
       </c>
       <c r="AQ21">
         <v>1.71</v>
@@ -6080,7 +6110,7 @@
         <v>0</v>
       </c>
       <c r="AP22">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="AQ22">
         <v>0.57</v>
@@ -6208,7 +6238,7 @@
         <v>101</v>
       </c>
       <c r="P23" t="s">
-        <v>299</v>
+        <v>305</v>
       </c>
       <c r="Q23">
         <v>3</v>
@@ -6495,7 +6525,7 @@
         <v>2.36</v>
       </c>
       <c r="AQ24">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="AR24">
         <v>0</v>
@@ -6620,7 +6650,7 @@
         <v>109</v>
       </c>
       <c r="P25" t="s">
-        <v>300</v>
+        <v>306</v>
       </c>
       <c r="Q25">
         <v>2.63</v>
@@ -6701,7 +6731,7 @@
         <v>1.85</v>
       </c>
       <c r="AQ25">
-        <v>1.27</v>
+        <v>1.17</v>
       </c>
       <c r="AR25">
         <v>0</v>
@@ -6826,7 +6856,7 @@
         <v>110</v>
       </c>
       <c r="P26" t="s">
-        <v>301</v>
+        <v>307</v>
       </c>
       <c r="Q26">
         <v>2.38</v>
@@ -6907,7 +6937,7 @@
         <v>1.85</v>
       </c>
       <c r="AQ26">
-        <v>1.36</v>
+        <v>1.47</v>
       </c>
       <c r="AR26">
         <v>1.83</v>
@@ -7110,7 +7140,7 @@
         <v>3</v>
       </c>
       <c r="AP27">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="AQ27">
         <v>1.77</v>
@@ -7319,7 +7349,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ28">
-        <v>0.87</v>
+        <v>1</v>
       </c>
       <c r="AR28">
         <v>1.35</v>
@@ -7522,7 +7552,7 @@
         <v>0</v>
       </c>
       <c r="AP29">
-        <v>1.79</v>
+        <v>1.87</v>
       </c>
       <c r="AQ29">
         <v>0.93</v>
@@ -7650,7 +7680,7 @@
         <v>112</v>
       </c>
       <c r="P30" t="s">
-        <v>302</v>
+        <v>308</v>
       </c>
       <c r="Q30">
         <v>3</v>
@@ -7728,10 +7758,10 @@
         <v>0</v>
       </c>
       <c r="AP30">
-        <v>1.55</v>
+        <v>1.67</v>
       </c>
       <c r="AQ30">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR30">
         <v>0</v>
@@ -8349,7 +8379,7 @@
         <v>1.57</v>
       </c>
       <c r="AQ33">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="AR33">
         <v>1.27</v>
@@ -8552,7 +8582,7 @@
         <v>0</v>
       </c>
       <c r="AP34">
-        <v>1.71</v>
+        <v>1.8</v>
       </c>
       <c r="AQ34">
         <v>1.38</v>
@@ -9092,7 +9122,7 @@
         <v>101</v>
       </c>
       <c r="P37" t="s">
-        <v>303</v>
+        <v>309</v>
       </c>
       <c r="Q37">
         <v>2.6</v>
@@ -9298,7 +9328,7 @@
         <v>117</v>
       </c>
       <c r="P38" t="s">
-        <v>304</v>
+        <v>310</v>
       </c>
       <c r="Q38">
         <v>2.88</v>
@@ -9376,7 +9406,7 @@
         <v>0</v>
       </c>
       <c r="AP38">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="AQ38">
         <v>1.71</v>
@@ -9582,10 +9612,10 @@
         <v>3</v>
       </c>
       <c r="AP39">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="AQ39">
-        <v>1.31</v>
+        <v>1.21</v>
       </c>
       <c r="AR39">
         <v>1.62</v>
@@ -9710,7 +9740,7 @@
         <v>119</v>
       </c>
       <c r="P40" t="s">
-        <v>305</v>
+        <v>311</v>
       </c>
       <c r="Q40">
         <v>3</v>
@@ -9791,7 +9821,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ40">
-        <v>1.64</v>
+        <v>1.73</v>
       </c>
       <c r="AR40">
         <v>0</v>
@@ -9994,7 +10024,7 @@
         <v>0</v>
       </c>
       <c r="AP41">
-        <v>0.5</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AQ41">
         <v>0.67</v>
@@ -10122,7 +10152,7 @@
         <v>101</v>
       </c>
       <c r="P42" t="s">
-        <v>306</v>
+        <v>312</v>
       </c>
       <c r="Q42">
         <v>3.75</v>
@@ -10200,10 +10230,10 @@
         <v>0</v>
       </c>
       <c r="AP42">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AQ42">
-        <v>0.6899999999999999</v>
+        <v>0.64</v>
       </c>
       <c r="AR42">
         <v>1.15</v>
@@ -10406,7 +10436,7 @@
         <v>0</v>
       </c>
       <c r="AP43">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="AQ43">
         <v>0.85</v>
@@ -10534,7 +10564,7 @@
         <v>121</v>
       </c>
       <c r="P44" t="s">
-        <v>307</v>
+        <v>313</v>
       </c>
       <c r="Q44">
         <v>2.75</v>
@@ -10612,7 +10642,7 @@
         <v>1</v>
       </c>
       <c r="AP44">
-        <v>0.6899999999999999</v>
+        <v>0.64</v>
       </c>
       <c r="AQ44">
         <v>0.57</v>
@@ -10740,7 +10770,7 @@
         <v>122</v>
       </c>
       <c r="P45" t="s">
-        <v>308</v>
+        <v>314</v>
       </c>
       <c r="Q45">
         <v>2.63</v>
@@ -10818,10 +10848,10 @@
         <v>0</v>
       </c>
       <c r="AP45">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="AQ45">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="AR45">
         <v>1.02</v>
@@ -11027,7 +11057,7 @@
         <v>1.15</v>
       </c>
       <c r="AQ46">
-        <v>1.08</v>
+        <v>1.21</v>
       </c>
       <c r="AR46">
         <v>2.58</v>
@@ -11230,10 +11260,10 @@
         <v>1</v>
       </c>
       <c r="AP47">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="AQ47">
-        <v>1.27</v>
+        <v>1.17</v>
       </c>
       <c r="AR47">
         <v>1.5</v>
@@ -11358,7 +11388,7 @@
         <v>125</v>
       </c>
       <c r="P48" t="s">
-        <v>309</v>
+        <v>315</v>
       </c>
       <c r="Q48">
         <v>3.5</v>
@@ -11439,7 +11469,7 @@
         <v>1.43</v>
       </c>
       <c r="AQ48">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR48">
         <v>1.43</v>
@@ -11645,7 +11675,7 @@
         <v>1.79</v>
       </c>
       <c r="AQ49">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AR49">
         <v>1.1</v>
@@ -11770,7 +11800,7 @@
         <v>127</v>
       </c>
       <c r="P50" t="s">
-        <v>310</v>
+        <v>316</v>
       </c>
       <c r="Q50">
         <v>3.6</v>
@@ -11848,7 +11878,7 @@
         <v>1.5</v>
       </c>
       <c r="AP50">
-        <v>1.55</v>
+        <v>1.67</v>
       </c>
       <c r="AQ50">
         <v>1.67</v>
@@ -11976,7 +12006,7 @@
         <v>103</v>
       </c>
       <c r="P51" t="s">
-        <v>311</v>
+        <v>317</v>
       </c>
       <c r="Q51">
         <v>2.5</v>
@@ -12057,7 +12087,7 @@
         <v>1.57</v>
       </c>
       <c r="AQ51">
-        <v>0.87</v>
+        <v>1</v>
       </c>
       <c r="AR51">
         <v>1.28</v>
@@ -12260,7 +12290,7 @@
         <v>2</v>
       </c>
       <c r="AP52">
-        <v>1.71</v>
+        <v>1.8</v>
       </c>
       <c r="AQ52">
         <v>0.87</v>
@@ -12469,7 +12499,7 @@
         <v>1.57</v>
       </c>
       <c r="AQ53">
-        <v>1.36</v>
+        <v>1.47</v>
       </c>
       <c r="AR53">
         <v>1.25</v>
@@ -13084,7 +13114,7 @@
         <v>2</v>
       </c>
       <c r="AP56">
-        <v>1.79</v>
+        <v>1.87</v>
       </c>
       <c r="AQ56">
         <v>1</v>
@@ -13705,7 +13735,7 @@
         <v>1.85</v>
       </c>
       <c r="AQ59">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR59">
         <v>1.79</v>
@@ -13908,7 +13938,7 @@
         <v>1.5</v>
       </c>
       <c r="AP60">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AQ60">
         <v>1.71</v>
@@ -14114,10 +14144,10 @@
         <v>0</v>
       </c>
       <c r="AP61">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="AQ61">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AR61">
         <v>1.47</v>
@@ -14654,7 +14684,7 @@
         <v>139</v>
       </c>
       <c r="P64" t="s">
-        <v>302</v>
+        <v>308</v>
       </c>
       <c r="Q64">
         <v>3</v>
@@ -14732,10 +14762,10 @@
         <v>1.5</v>
       </c>
       <c r="AP64">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="AQ64">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR64">
         <v>1.57</v>
@@ -14938,10 +14968,10 @@
         <v>1.5</v>
       </c>
       <c r="AP65">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="AQ65">
-        <v>1.31</v>
+        <v>1.21</v>
       </c>
       <c r="AR65">
         <v>1.4</v>
@@ -15066,7 +15096,7 @@
         <v>141</v>
       </c>
       <c r="P66" t="s">
-        <v>312</v>
+        <v>318</v>
       </c>
       <c r="Q66">
         <v>3.75</v>
@@ -15144,10 +15174,10 @@
         <v>0.5</v>
       </c>
       <c r="AP66">
-        <v>0.5</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AQ66">
-        <v>1.08</v>
+        <v>1.21</v>
       </c>
       <c r="AR66">
         <v>1.41</v>
@@ -15350,7 +15380,7 @@
         <v>2</v>
       </c>
       <c r="AP67">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="AQ67">
         <v>0.57</v>
@@ -15559,7 +15589,7 @@
         <v>1.15</v>
       </c>
       <c r="AQ68">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="AR68">
         <v>1.88</v>
@@ -15684,7 +15714,7 @@
         <v>143</v>
       </c>
       <c r="P69" t="s">
-        <v>313</v>
+        <v>319</v>
       </c>
       <c r="Q69">
         <v>3.2</v>
@@ -15762,10 +15792,10 @@
         <v>2</v>
       </c>
       <c r="AP69">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="AQ69">
-        <v>1.64</v>
+        <v>1.73</v>
       </c>
       <c r="AR69">
         <v>1.03</v>
@@ -15890,7 +15920,7 @@
         <v>144</v>
       </c>
       <c r="P70" t="s">
-        <v>314</v>
+        <v>320</v>
       </c>
       <c r="Q70">
         <v>3.25</v>
@@ -15971,7 +16001,7 @@
         <v>1.43</v>
       </c>
       <c r="AQ70">
-        <v>0.6899999999999999</v>
+        <v>0.64</v>
       </c>
       <c r="AR70">
         <v>1.23</v>
@@ -16096,7 +16126,7 @@
         <v>145</v>
       </c>
       <c r="P71" t="s">
-        <v>315</v>
+        <v>321</v>
       </c>
       <c r="Q71">
         <v>3</v>
@@ -16174,10 +16204,10 @@
         <v>0.5</v>
       </c>
       <c r="AP71">
-        <v>0.6899999999999999</v>
+        <v>0.64</v>
       </c>
       <c r="AQ71">
-        <v>1.27</v>
+        <v>1.17</v>
       </c>
       <c r="AR71">
         <v>1.35</v>
@@ -16302,7 +16332,7 @@
         <v>146</v>
       </c>
       <c r="P72" t="s">
-        <v>316</v>
+        <v>322</v>
       </c>
       <c r="Q72">
         <v>4</v>
@@ -16714,7 +16744,7 @@
         <v>101</v>
       </c>
       <c r="P74" t="s">
-        <v>317</v>
+        <v>323</v>
       </c>
       <c r="Q74">
         <v>2.63</v>
@@ -16920,7 +16950,7 @@
         <v>101</v>
       </c>
       <c r="P75" t="s">
-        <v>318</v>
+        <v>324</v>
       </c>
       <c r="Q75">
         <v>3.4</v>
@@ -17126,7 +17156,7 @@
         <v>101</v>
       </c>
       <c r="P76" t="s">
-        <v>302</v>
+        <v>308</v>
       </c>
       <c r="Q76">
         <v>2.6</v>
@@ -17538,7 +17568,7 @@
         <v>149</v>
       </c>
       <c r="P78" t="s">
-        <v>319</v>
+        <v>325</v>
       </c>
       <c r="Q78">
         <v>2.88</v>
@@ -18568,7 +18598,7 @@
         <v>153</v>
       </c>
       <c r="P83" t="s">
-        <v>320</v>
+        <v>326</v>
       </c>
       <c r="Q83">
         <v>2.2</v>
@@ -18852,10 +18882,10 @@
         <v>1</v>
       </c>
       <c r="AP84">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="AQ84">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="AR84">
         <v>0.73</v>
@@ -19058,10 +19088,10 @@
         <v>0.67</v>
       </c>
       <c r="AP85">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="AQ85">
-        <v>1.08</v>
+        <v>1.21</v>
       </c>
       <c r="AR85">
         <v>1.6</v>
@@ -19264,10 +19294,10 @@
         <v>1</v>
       </c>
       <c r="AP86">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AQ86">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR86">
         <v>1.1</v>
@@ -19470,10 +19500,10 @@
         <v>2.33</v>
       </c>
       <c r="AP87">
-        <v>0.5</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AQ87">
-        <v>1.64</v>
+        <v>1.73</v>
       </c>
       <c r="AR87">
         <v>1.28</v>
@@ -19676,10 +19706,10 @@
         <v>1</v>
       </c>
       <c r="AP88">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="AQ88">
-        <v>0.87</v>
+        <v>1</v>
       </c>
       <c r="AR88">
         <v>1.3</v>
@@ -19804,7 +19834,7 @@
         <v>157</v>
       </c>
       <c r="P89" t="s">
-        <v>321</v>
+        <v>327</v>
       </c>
       <c r="Q89">
         <v>3.75</v>
@@ -19882,10 +19912,10 @@
         <v>2</v>
       </c>
       <c r="AP89">
-        <v>1.55</v>
+        <v>1.67</v>
       </c>
       <c r="AQ89">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="AR89">
         <v>0.82</v>
@@ -20088,10 +20118,10 @@
         <v>0</v>
       </c>
       <c r="AP90">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="AQ90">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AR90">
         <v>1.27</v>
@@ -20216,7 +20246,7 @@
         <v>101</v>
       </c>
       <c r="P91" t="s">
-        <v>322</v>
+        <v>328</v>
       </c>
       <c r="Q91">
         <v>2.75</v>
@@ -20294,10 +20324,10 @@
         <v>1</v>
       </c>
       <c r="AP91">
-        <v>1.79</v>
+        <v>1.87</v>
       </c>
       <c r="AQ91">
-        <v>1.31</v>
+        <v>1.21</v>
       </c>
       <c r="AR91">
         <v>1.18</v>
@@ -20422,7 +20452,7 @@
         <v>101</v>
       </c>
       <c r="P92" t="s">
-        <v>323</v>
+        <v>329</v>
       </c>
       <c r="Q92">
         <v>3.4</v>
@@ -20500,10 +20530,10 @@
         <v>1.33</v>
       </c>
       <c r="AP92">
-        <v>1.71</v>
+        <v>1.8</v>
       </c>
       <c r="AQ92">
-        <v>1.27</v>
+        <v>1.17</v>
       </c>
       <c r="AR92">
         <v>1.26</v>
@@ -20628,7 +20658,7 @@
         <v>159</v>
       </c>
       <c r="P93" t="s">
-        <v>324</v>
+        <v>330</v>
       </c>
       <c r="Q93">
         <v>2.75</v>
@@ -20706,10 +20736,10 @@
         <v>0</v>
       </c>
       <c r="AP93">
-        <v>0.6899999999999999</v>
+        <v>0.64</v>
       </c>
       <c r="AQ93">
-        <v>1.36</v>
+        <v>1.47</v>
       </c>
       <c r="AR93">
         <v>1.37</v>
@@ -20912,10 +20942,10 @@
         <v>2</v>
       </c>
       <c r="AP94">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="AQ94">
-        <v>0.6899999999999999</v>
+        <v>0.64</v>
       </c>
       <c r="AR94">
         <v>1.4</v>
@@ -21040,7 +21070,7 @@
         <v>161</v>
       </c>
       <c r="P95" t="s">
-        <v>325</v>
+        <v>331</v>
       </c>
       <c r="Q95">
         <v>2.5</v>
@@ -21118,10 +21148,10 @@
         <v>0.5</v>
       </c>
       <c r="AP95">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="AQ95">
-        <v>1.08</v>
+        <v>1.21</v>
       </c>
       <c r="AR95">
         <v>1.55</v>
@@ -21246,7 +21276,7 @@
         <v>162</v>
       </c>
       <c r="P96" t="s">
-        <v>326</v>
+        <v>332</v>
       </c>
       <c r="Q96">
         <v>4.5</v>
@@ -21324,10 +21354,10 @@
         <v>0.25</v>
       </c>
       <c r="AP96">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AQ96">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AR96">
         <v>1.14</v>
@@ -21530,10 +21560,10 @@
         <v>0.75</v>
       </c>
       <c r="AP97">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="AQ97">
-        <v>0.87</v>
+        <v>1</v>
       </c>
       <c r="AR97">
         <v>1.07</v>
@@ -21736,10 +21766,10 @@
         <v>1</v>
       </c>
       <c r="AP98">
-        <v>1.55</v>
+        <v>1.67</v>
       </c>
       <c r="AQ98">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="AR98">
         <v>0.92</v>
@@ -21864,7 +21894,7 @@
         <v>165</v>
       </c>
       <c r="P99" t="s">
-        <v>327</v>
+        <v>295</v>
       </c>
       <c r="Q99">
         <v>4.5</v>
@@ -21942,10 +21972,10 @@
         <v>0.75</v>
       </c>
       <c r="AP99">
-        <v>0.5</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AQ99">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR99">
         <v>1.37</v>
@@ -22070,7 +22100,7 @@
         <v>166</v>
       </c>
       <c r="P100" t="s">
-        <v>328</v>
+        <v>333</v>
       </c>
       <c r="Q100">
         <v>2.75</v>
@@ -22148,10 +22178,10 @@
         <v>1.75</v>
       </c>
       <c r="AP100">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="AQ100">
-        <v>1.27</v>
+        <v>1.17</v>
       </c>
       <c r="AR100">
         <v>1.61</v>
@@ -22354,10 +22384,10 @@
         <v>0.75</v>
       </c>
       <c r="AP101">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="AQ101">
-        <v>1.36</v>
+        <v>1.47</v>
       </c>
       <c r="AR101">
         <v>1.31</v>
@@ -22482,7 +22512,7 @@
         <v>167</v>
       </c>
       <c r="P102" t="s">
-        <v>329</v>
+        <v>334</v>
       </c>
       <c r="Q102">
         <v>2.88</v>
@@ -22560,10 +22590,10 @@
         <v>0</v>
       </c>
       <c r="AP102">
-        <v>1.71</v>
+        <v>1.8</v>
       </c>
       <c r="AQ102">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR102">
         <v>1.14</v>
@@ -22688,7 +22718,7 @@
         <v>101</v>
       </c>
       <c r="P103" t="s">
-        <v>330</v>
+        <v>335</v>
       </c>
       <c r="Q103">
         <v>3</v>
@@ -22766,10 +22796,10 @@
         <v>2</v>
       </c>
       <c r="AP103">
-        <v>0.6899999999999999</v>
+        <v>0.64</v>
       </c>
       <c r="AQ103">
-        <v>1.64</v>
+        <v>1.73</v>
       </c>
       <c r="AR103">
         <v>1.32</v>
@@ -22894,7 +22924,7 @@
         <v>168</v>
       </c>
       <c r="P104" t="s">
-        <v>331</v>
+        <v>336</v>
       </c>
       <c r="Q104">
         <v>4</v>
@@ -22972,10 +23002,10 @@
         <v>1.5</v>
       </c>
       <c r="AP104">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="AQ104">
-        <v>1.31</v>
+        <v>1.21</v>
       </c>
       <c r="AR104">
         <v>1.27</v>
@@ -23178,10 +23208,10 @@
         <v>1.5</v>
       </c>
       <c r="AP105">
-        <v>1.79</v>
+        <v>1.87</v>
       </c>
       <c r="AQ105">
-        <v>0.6899999999999999</v>
+        <v>0.64</v>
       </c>
       <c r="AR105">
         <v>1</v>
@@ -23306,7 +23336,7 @@
         <v>101</v>
       </c>
       <c r="P106" t="s">
-        <v>332</v>
+        <v>337</v>
       </c>
       <c r="Q106">
         <v>3.6</v>
@@ -24748,7 +24778,7 @@
         <v>172</v>
       </c>
       <c r="P113" t="s">
-        <v>333</v>
+        <v>338</v>
       </c>
       <c r="Q113">
         <v>2.6</v>
@@ -24954,7 +24984,7 @@
         <v>173</v>
       </c>
       <c r="P114" t="s">
-        <v>334</v>
+        <v>339</v>
       </c>
       <c r="Q114">
         <v>2.4</v>
@@ -25778,7 +25808,7 @@
         <v>176</v>
       </c>
       <c r="P118" t="s">
-        <v>335</v>
+        <v>340</v>
       </c>
       <c r="Q118">
         <v>2.5</v>
@@ -25859,7 +25889,7 @@
         <v>1.57</v>
       </c>
       <c r="AQ118">
-        <v>1.64</v>
+        <v>1.73</v>
       </c>
       <c r="AR118">
         <v>1.26</v>
@@ -25984,7 +26014,7 @@
         <v>101</v>
       </c>
       <c r="P119" t="s">
-        <v>336</v>
+        <v>341</v>
       </c>
       <c r="Q119">
         <v>3.4</v>
@@ -26062,10 +26092,10 @@
         <v>0.8</v>
       </c>
       <c r="AP119">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="AQ119">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR119">
         <v>1.15</v>
@@ -26190,7 +26220,7 @@
         <v>94</v>
       </c>
       <c r="P120" t="s">
-        <v>337</v>
+        <v>342</v>
       </c>
       <c r="Q120">
         <v>2.88</v>
@@ -26271,7 +26301,7 @@
         <v>1.79</v>
       </c>
       <c r="AQ120">
-        <v>1.36</v>
+        <v>1.47</v>
       </c>
       <c r="AR120">
         <v>1.19</v>
@@ -26680,7 +26710,7 @@
         <v>0.6</v>
       </c>
       <c r="AP122">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AQ122">
         <v>0.67</v>
@@ -26808,7 +26838,7 @@
         <v>178</v>
       </c>
       <c r="P123" t="s">
-        <v>338</v>
+        <v>343</v>
       </c>
       <c r="Q123">
         <v>2.38</v>
@@ -26886,10 +26916,10 @@
         <v>0</v>
       </c>
       <c r="AP123">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="AQ123">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR123">
         <v>1.25</v>
@@ -27092,10 +27122,10 @@
         <v>1.5</v>
       </c>
       <c r="AP124">
-        <v>1.79</v>
+        <v>1.87</v>
       </c>
       <c r="AQ124">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="AR124">
         <v>1.08</v>
@@ -27220,7 +27250,7 @@
         <v>101</v>
       </c>
       <c r="P125" t="s">
-        <v>319</v>
+        <v>325</v>
       </c>
       <c r="Q125">
         <v>2.1</v>
@@ -27504,7 +27534,7 @@
         <v>0.8</v>
       </c>
       <c r="AP126">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="AQ126">
         <v>0.86</v>
@@ -27632,7 +27662,7 @@
         <v>180</v>
       </c>
       <c r="P127" t="s">
-        <v>339</v>
+        <v>344</v>
       </c>
       <c r="Q127">
         <v>3.25</v>
@@ -27710,10 +27740,10 @@
         <v>0.8</v>
       </c>
       <c r="AP127">
-        <v>1.71</v>
+        <v>1.8</v>
       </c>
       <c r="AQ127">
-        <v>0.87</v>
+        <v>1</v>
       </c>
       <c r="AR127">
         <v>1.2</v>
@@ -27838,7 +27868,7 @@
         <v>101</v>
       </c>
       <c r="P128" t="s">
-        <v>340</v>
+        <v>345</v>
       </c>
       <c r="Q128">
         <v>4.75</v>
@@ -27916,10 +27946,10 @@
         <v>1.4</v>
       </c>
       <c r="AP128">
-        <v>1.55</v>
+        <v>1.67</v>
       </c>
       <c r="AQ128">
-        <v>1.31</v>
+        <v>1.21</v>
       </c>
       <c r="AR128">
         <v>1.07</v>
@@ -28125,7 +28155,7 @@
         <v>1.15</v>
       </c>
       <c r="AQ129">
-        <v>0.6899999999999999</v>
+        <v>0.64</v>
       </c>
       <c r="AR129">
         <v>1.45</v>
@@ -28456,7 +28486,7 @@
         <v>182</v>
       </c>
       <c r="P131" t="s">
-        <v>341</v>
+        <v>346</v>
       </c>
       <c r="Q131">
         <v>2.63</v>
@@ -28534,10 +28564,10 @@
         <v>2</v>
       </c>
       <c r="AP131">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="AQ131">
-        <v>1.27</v>
+        <v>1.17</v>
       </c>
       <c r="AR131">
         <v>1.51</v>
@@ -28662,7 +28692,7 @@
         <v>183</v>
       </c>
       <c r="P132" t="s">
-        <v>342</v>
+        <v>347</v>
       </c>
       <c r="Q132">
         <v>3.5</v>
@@ -28949,7 +28979,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ133">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="AR133">
         <v>1.2</v>
@@ -29074,7 +29104,7 @@
         <v>185</v>
       </c>
       <c r="P134" t="s">
-        <v>343</v>
+        <v>348</v>
       </c>
       <c r="Q134">
         <v>4</v>
@@ -29152,10 +29182,10 @@
         <v>0.8</v>
       </c>
       <c r="AP134">
-        <v>0.5</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AQ134">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AR134">
         <v>1.35</v>
@@ -29280,7 +29310,7 @@
         <v>147</v>
       </c>
       <c r="P135" t="s">
-        <v>344</v>
+        <v>349</v>
       </c>
       <c r="Q135">
         <v>2.6</v>
@@ -29486,7 +29516,7 @@
         <v>186</v>
       </c>
       <c r="P136" t="s">
-        <v>345</v>
+        <v>350</v>
       </c>
       <c r="Q136">
         <v>3.6</v>
@@ -29692,7 +29722,7 @@
         <v>187</v>
       </c>
       <c r="P137" t="s">
-        <v>346</v>
+        <v>351</v>
       </c>
       <c r="Q137">
         <v>3</v>
@@ -29770,7 +29800,7 @@
         <v>1</v>
       </c>
       <c r="AP137">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="AQ137">
         <v>0.57</v>
@@ -30104,7 +30134,7 @@
         <v>185</v>
       </c>
       <c r="P139" t="s">
-        <v>329</v>
+        <v>334</v>
       </c>
       <c r="Q139">
         <v>2.5</v>
@@ -30182,7 +30212,7 @@
         <v>1</v>
       </c>
       <c r="AP139">
-        <v>0.6899999999999999</v>
+        <v>0.64</v>
       </c>
       <c r="AQ139">
         <v>0.87</v>
@@ -30310,7 +30340,7 @@
         <v>189</v>
       </c>
       <c r="P140" t="s">
-        <v>319</v>
+        <v>325</v>
       </c>
       <c r="Q140">
         <v>2.25</v>
@@ -30388,7 +30418,7 @@
         <v>0.67</v>
       </c>
       <c r="AP140">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="AQ140">
         <v>0.86</v>
@@ -30597,7 +30627,7 @@
         <v>1.79</v>
       </c>
       <c r="AQ141">
-        <v>0.87</v>
+        <v>1</v>
       </c>
       <c r="AR141">
         <v>1.41</v>
@@ -30803,7 +30833,7 @@
         <v>1.56</v>
       </c>
       <c r="AQ142">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR142">
         <v>1.27</v>
@@ -31006,7 +31036,7 @@
         <v>2.17</v>
       </c>
       <c r="AP143">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AQ143">
         <v>1.67</v>
@@ -31134,7 +31164,7 @@
         <v>101</v>
       </c>
       <c r="P144" t="s">
-        <v>347</v>
+        <v>352</v>
       </c>
       <c r="Q144">
         <v>2.25</v>
@@ -31212,7 +31242,7 @@
         <v>0.5</v>
       </c>
       <c r="AP144">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="AQ144">
         <v>0.67</v>
@@ -31421,7 +31451,7 @@
         <v>1.47</v>
       </c>
       <c r="AQ145">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="AR145">
         <v>1.61</v>
@@ -31624,7 +31654,7 @@
         <v>1</v>
       </c>
       <c r="AP146">
-        <v>1.79</v>
+        <v>1.87</v>
       </c>
       <c r="AQ146">
         <v>1.43</v>
@@ -31752,7 +31782,7 @@
         <v>101</v>
       </c>
       <c r="P147" t="s">
-        <v>348</v>
+        <v>353</v>
       </c>
       <c r="Q147">
         <v>3</v>
@@ -31830,10 +31860,10 @@
         <v>1.5</v>
       </c>
       <c r="AP147">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="AQ147">
-        <v>1.36</v>
+        <v>1.47</v>
       </c>
       <c r="AR147">
         <v>1.19</v>
@@ -32036,10 +32066,10 @@
         <v>1.17</v>
       </c>
       <c r="AP148">
-        <v>1.71</v>
+        <v>1.8</v>
       </c>
       <c r="AQ148">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR148">
         <v>1.26</v>
@@ -32245,7 +32275,7 @@
         <v>1.57</v>
       </c>
       <c r="AQ149">
-        <v>1.64</v>
+        <v>1.73</v>
       </c>
       <c r="AR149">
         <v>1.45</v>
@@ -32448,7 +32478,7 @@
         <v>0.67</v>
       </c>
       <c r="AP150">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="AQ150">
         <v>0.93</v>
@@ -32576,7 +32606,7 @@
         <v>193</v>
       </c>
       <c r="P151" t="s">
-        <v>349</v>
+        <v>354</v>
       </c>
       <c r="Q151">
         <v>2.4</v>
@@ -32657,7 +32687,7 @@
         <v>1.57</v>
       </c>
       <c r="AQ151">
-        <v>1.08</v>
+        <v>1.21</v>
       </c>
       <c r="AR151">
         <v>1.31</v>
@@ -32782,7 +32812,7 @@
         <v>194</v>
       </c>
       <c r="P152" t="s">
-        <v>350</v>
+        <v>355</v>
       </c>
       <c r="Q152">
         <v>4.5</v>
@@ -32860,10 +32890,10 @@
         <v>1.67</v>
       </c>
       <c r="AP152">
-        <v>0.5</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AQ152">
-        <v>1.31</v>
+        <v>1.21</v>
       </c>
       <c r="AR152">
         <v>1.38</v>
@@ -32988,7 +33018,7 @@
         <v>195</v>
       </c>
       <c r="P153" t="s">
-        <v>351</v>
+        <v>356</v>
       </c>
       <c r="Q153">
         <v>2.75</v>
@@ -33069,7 +33099,7 @@
         <v>1.43</v>
       </c>
       <c r="AQ153">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="AR153">
         <v>1.74</v>
@@ -33400,7 +33430,7 @@
         <v>197</v>
       </c>
       <c r="P155" t="s">
-        <v>352</v>
+        <v>357</v>
       </c>
       <c r="Q155">
         <v>3</v>
@@ -33478,7 +33508,7 @@
         <v>0.8</v>
       </c>
       <c r="AP155">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="AQ155">
         <v>1.38</v>
@@ -33684,10 +33714,10 @@
         <v>1.67</v>
       </c>
       <c r="AP156">
-        <v>1.55</v>
+        <v>1.67</v>
       </c>
       <c r="AQ156">
-        <v>1.27</v>
+        <v>1.17</v>
       </c>
       <c r="AR156">
         <v>1.14</v>
@@ -33812,7 +33842,7 @@
         <v>198</v>
       </c>
       <c r="P157" t="s">
-        <v>353</v>
+        <v>358</v>
       </c>
       <c r="Q157">
         <v>3.4</v>
@@ -33893,7 +33923,7 @@
         <v>1.43</v>
       </c>
       <c r="AQ157">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AR157">
         <v>1.15</v>
@@ -34302,7 +34332,7 @@
         <v>0.67</v>
       </c>
       <c r="AP159">
-        <v>0.6899999999999999</v>
+        <v>0.64</v>
       </c>
       <c r="AQ159">
         <v>0.85</v>
@@ -34430,7 +34460,7 @@
         <v>200</v>
       </c>
       <c r="P160" t="s">
-        <v>354</v>
+        <v>359</v>
       </c>
       <c r="Q160">
         <v>3.2</v>
@@ -35126,10 +35156,10 @@
         <v>1</v>
       </c>
       <c r="AP163">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="AQ163">
-        <v>0.6899999999999999</v>
+        <v>0.64</v>
       </c>
       <c r="AR163">
         <v>1.49</v>
@@ -35254,7 +35284,7 @@
         <v>203</v>
       </c>
       <c r="P164" t="s">
-        <v>355</v>
+        <v>360</v>
       </c>
       <c r="Q164">
         <v>2.4</v>
@@ -35335,7 +35365,7 @@
         <v>1.47</v>
       </c>
       <c r="AQ164">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="AR164">
         <v>1.63</v>
@@ -35460,7 +35490,7 @@
         <v>101</v>
       </c>
       <c r="P165" t="s">
-        <v>327</v>
+        <v>295</v>
       </c>
       <c r="Q165">
         <v>2.63</v>
@@ -35666,7 +35696,7 @@
         <v>204</v>
       </c>
       <c r="P166" t="s">
-        <v>356</v>
+        <v>361</v>
       </c>
       <c r="Q166">
         <v>2.88</v>
@@ -35744,7 +35774,7 @@
         <v>0.57</v>
       </c>
       <c r="AP166">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AQ166">
         <v>0.93</v>
@@ -35950,7 +35980,7 @@
         <v>2.29</v>
       </c>
       <c r="AP167">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="AQ167">
         <v>1.67</v>
@@ -36078,7 +36108,7 @@
         <v>206</v>
       </c>
       <c r="P168" t="s">
-        <v>357</v>
+        <v>362</v>
       </c>
       <c r="Q168">
         <v>2.3</v>
@@ -36156,10 +36186,10 @@
         <v>1.67</v>
       </c>
       <c r="AP168">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="AQ168">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="AR168">
         <v>1.52</v>
@@ -36362,7 +36392,7 @@
         <v>0.86</v>
       </c>
       <c r="AP169">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="AQ169">
         <v>0.67</v>
@@ -36490,7 +36520,7 @@
         <v>208</v>
       </c>
       <c r="P170" t="s">
-        <v>358</v>
+        <v>363</v>
       </c>
       <c r="Q170">
         <v>2.5</v>
@@ -36571,7 +36601,7 @@
         <v>1.56</v>
       </c>
       <c r="AQ170">
-        <v>0.87</v>
+        <v>1</v>
       </c>
       <c r="AR170">
         <v>1.18</v>
@@ -36777,7 +36807,7 @@
         <v>1.47</v>
       </c>
       <c r="AQ171">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR171">
         <v>1.56</v>
@@ -36980,10 +37010,10 @@
         <v>1.71</v>
       </c>
       <c r="AP172">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="AQ172">
-        <v>1.36</v>
+        <v>1.47</v>
       </c>
       <c r="AR172">
         <v>1.56</v>
@@ -37108,7 +37138,7 @@
         <v>101</v>
       </c>
       <c r="P173" t="s">
-        <v>359</v>
+        <v>364</v>
       </c>
       <c r="Q173">
         <v>2.1</v>
@@ -37189,7 +37219,7 @@
         <v>1.57</v>
       </c>
       <c r="AQ173">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR173">
         <v>1.48</v>
@@ -37314,7 +37344,7 @@
         <v>148</v>
       </c>
       <c r="P174" t="s">
-        <v>319</v>
+        <v>325</v>
       </c>
       <c r="Q174">
         <v>3.2</v>
@@ -37392,7 +37422,7 @@
         <v>1.33</v>
       </c>
       <c r="AP174">
-        <v>1.71</v>
+        <v>1.8</v>
       </c>
       <c r="AQ174">
         <v>1.43</v>
@@ -37601,7 +37631,7 @@
         <v>1.57</v>
       </c>
       <c r="AQ175">
-        <v>1.08</v>
+        <v>1.21</v>
       </c>
       <c r="AR175">
         <v>1.45</v>
@@ -37804,10 +37834,10 @@
         <v>1.86</v>
       </c>
       <c r="AP176">
-        <v>1.79</v>
+        <v>1.87</v>
       </c>
       <c r="AQ176">
-        <v>1.64</v>
+        <v>1.73</v>
       </c>
       <c r="AR176">
         <v>1.32</v>
@@ -38010,10 +38040,10 @@
         <v>1.88</v>
       </c>
       <c r="AP177">
-        <v>1.55</v>
+        <v>1.67</v>
       </c>
       <c r="AQ177">
-        <v>1.36</v>
+        <v>1.47</v>
       </c>
       <c r="AR177">
         <v>1.11</v>
@@ -38216,7 +38246,7 @@
         <v>2</v>
       </c>
       <c r="AP178">
-        <v>0.5</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AQ178">
         <v>1.67</v>
@@ -38344,7 +38374,7 @@
         <v>210</v>
       </c>
       <c r="P179" t="s">
-        <v>360</v>
+        <v>365</v>
       </c>
       <c r="Q179">
         <v>2.3</v>
@@ -38628,10 +38658,10 @@
         <v>1.14</v>
       </c>
       <c r="AP180">
-        <v>1.79</v>
+        <v>1.87</v>
       </c>
       <c r="AQ180">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="AR180">
         <v>1.38</v>
@@ -38837,7 +38867,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ181">
-        <v>1.64</v>
+        <v>1.73</v>
       </c>
       <c r="AR181">
         <v>1.19</v>
@@ -39040,10 +39070,10 @@
         <v>1.86</v>
       </c>
       <c r="AP182">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AQ182">
-        <v>1.31</v>
+        <v>1.21</v>
       </c>
       <c r="AR182">
         <v>1.26</v>
@@ -39246,7 +39276,7 @@
         <v>0.88</v>
       </c>
       <c r="AP183">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="AQ183">
         <v>0.86</v>
@@ -39374,7 +39404,7 @@
         <v>185</v>
       </c>
       <c r="P184" t="s">
-        <v>361</v>
+        <v>366</v>
       </c>
       <c r="Q184">
         <v>3.4</v>
@@ -39580,7 +39610,7 @@
         <v>215</v>
       </c>
       <c r="P185" t="s">
-        <v>362</v>
+        <v>367</v>
       </c>
       <c r="Q185">
         <v>3.2</v>
@@ -39661,7 +39691,7 @@
         <v>1.15</v>
       </c>
       <c r="AQ185">
-        <v>0.87</v>
+        <v>1</v>
       </c>
       <c r="AR185">
         <v>1.27</v>
@@ -39867,7 +39897,7 @@
         <v>1.43</v>
       </c>
       <c r="AQ186">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR186">
         <v>1.66</v>
@@ -39992,7 +40022,7 @@
         <v>217</v>
       </c>
       <c r="P187" t="s">
-        <v>363</v>
+        <v>368</v>
       </c>
       <c r="Q187">
         <v>2.2</v>
@@ -40070,10 +40100,10 @@
         <v>0.86</v>
       </c>
       <c r="AP187">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="AQ187">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR187">
         <v>1.62</v>
@@ -40276,7 +40306,7 @@
         <v>1.14</v>
       </c>
       <c r="AP188">
-        <v>1.71</v>
+        <v>1.8</v>
       </c>
       <c r="AQ188">
         <v>0.57</v>
@@ -40610,7 +40640,7 @@
         <v>101</v>
       </c>
       <c r="P190" t="s">
-        <v>309</v>
+        <v>315</v>
       </c>
       <c r="Q190">
         <v>3.25</v>
@@ -40691,7 +40721,7 @@
         <v>1.43</v>
       </c>
       <c r="AQ190">
-        <v>1.08</v>
+        <v>1.21</v>
       </c>
       <c r="AR190">
         <v>1.22</v>
@@ -40816,7 +40846,7 @@
         <v>148</v>
       </c>
       <c r="P191" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="Q191">
         <v>2.3</v>
@@ -40894,7 +40924,7 @@
         <v>0.86</v>
       </c>
       <c r="AP191">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="AQ191">
         <v>0.87</v>
@@ -41022,7 +41052,7 @@
         <v>219</v>
       </c>
       <c r="P192" t="s">
-        <v>365</v>
+        <v>370</v>
       </c>
       <c r="Q192">
         <v>2.4</v>
@@ -41306,7 +41336,7 @@
         <v>1.57</v>
       </c>
       <c r="AP193">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="AQ193">
         <v>1.77</v>
@@ -41512,7 +41542,7 @@
         <v>1.86</v>
       </c>
       <c r="AP194">
-        <v>0.6899999999999999</v>
+        <v>0.64</v>
       </c>
       <c r="AQ194">
         <v>1.71</v>
@@ -41721,7 +41751,7 @@
         <v>1.57</v>
       </c>
       <c r="AQ195">
-        <v>0.6899999999999999</v>
+        <v>0.64</v>
       </c>
       <c r="AR195">
         <v>1.49</v>
@@ -41924,10 +41954,10 @@
         <v>1.57</v>
       </c>
       <c r="AP196">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="AQ196">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="AR196">
         <v>1.37</v>
@@ -42052,7 +42082,7 @@
         <v>101</v>
       </c>
       <c r="P197" t="s">
-        <v>366</v>
+        <v>371</v>
       </c>
       <c r="Q197">
         <v>3.75</v>
@@ -42130,7 +42160,7 @@
         <v>1</v>
       </c>
       <c r="AP197">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="AQ197">
         <v>1.38</v>
@@ -42258,7 +42288,7 @@
         <v>221</v>
       </c>
       <c r="P198" t="s">
-        <v>367</v>
+        <v>372</v>
       </c>
       <c r="Q198">
         <v>2.2</v>
@@ -42336,7 +42366,7 @@
         <v>1.29</v>
       </c>
       <c r="AP198">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="AQ198">
         <v>1.43</v>
@@ -42464,7 +42494,7 @@
         <v>122</v>
       </c>
       <c r="P199" t="s">
-        <v>319</v>
+        <v>325</v>
       </c>
       <c r="Q199">
         <v>3.4</v>
@@ -42542,10 +42572,10 @@
         <v>1.5</v>
       </c>
       <c r="AP199">
-        <v>0.6899999999999999</v>
+        <v>0.64</v>
       </c>
       <c r="AQ199">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="AR199">
         <v>1.51</v>
@@ -42751,7 +42781,7 @@
         <v>1.47</v>
       </c>
       <c r="AQ200">
-        <v>1.08</v>
+        <v>1.21</v>
       </c>
       <c r="AR200">
         <v>1.45</v>
@@ -42876,7 +42906,7 @@
         <v>222</v>
       </c>
       <c r="P201" t="s">
-        <v>368</v>
+        <v>373</v>
       </c>
       <c r="Q201">
         <v>2.85</v>
@@ -42957,7 +42987,7 @@
         <v>1.43</v>
       </c>
       <c r="AQ201">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR201">
         <v>1.24</v>
@@ -43082,7 +43112,7 @@
         <v>223</v>
       </c>
       <c r="P202" t="s">
-        <v>369</v>
+        <v>374</v>
       </c>
       <c r="Q202">
         <v>1.8</v>
@@ -43160,7 +43190,7 @@
         <v>0.78</v>
       </c>
       <c r="AP202">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="AQ202">
         <v>0.67</v>
@@ -43288,7 +43318,7 @@
         <v>205</v>
       </c>
       <c r="P203" t="s">
-        <v>370</v>
+        <v>375</v>
       </c>
       <c r="Q203">
         <v>2.75</v>
@@ -43369,7 +43399,7 @@
         <v>2.36</v>
       </c>
       <c r="AQ203">
-        <v>0.6899999999999999</v>
+        <v>0.64</v>
       </c>
       <c r="AR203">
         <v>1.53</v>
@@ -43494,7 +43524,7 @@
         <v>224</v>
       </c>
       <c r="P204" t="s">
-        <v>371</v>
+        <v>376</v>
       </c>
       <c r="Q204">
         <v>3.55</v>
@@ -43572,7 +43602,7 @@
         <v>2.11</v>
       </c>
       <c r="AP204">
-        <v>1.71</v>
+        <v>1.8</v>
       </c>
       <c r="AQ204">
         <v>1.67</v>
@@ -43781,7 +43811,7 @@
         <v>1.43</v>
       </c>
       <c r="AQ205">
-        <v>0.87</v>
+        <v>1</v>
       </c>
       <c r="AR205">
         <v>1.62</v>
@@ -43987,7 +44017,7 @@
         <v>1.56</v>
       </c>
       <c r="AQ206">
-        <v>1.31</v>
+        <v>1.21</v>
       </c>
       <c r="AR206">
         <v>1.27</v>
@@ -44318,7 +44348,7 @@
         <v>228</v>
       </c>
       <c r="P208" t="s">
-        <v>372</v>
+        <v>377</v>
       </c>
       <c r="Q208">
         <v>2.4</v>
@@ -44396,7 +44426,7 @@
         <v>1.11</v>
       </c>
       <c r="AP208">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="AQ208">
         <v>0.93</v>
@@ -44524,7 +44554,7 @@
         <v>229</v>
       </c>
       <c r="P209" t="s">
-        <v>373</v>
+        <v>378</v>
       </c>
       <c r="Q209">
         <v>2.5</v>
@@ -44602,10 +44632,10 @@
         <v>1.56</v>
       </c>
       <c r="AP209">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="AQ209">
-        <v>1.64</v>
+        <v>1.73</v>
       </c>
       <c r="AR209">
         <v>1.49</v>
@@ -44808,7 +44838,7 @@
         <v>1.14</v>
       </c>
       <c r="AP210">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="AQ210">
         <v>1</v>
@@ -44936,7 +44966,7 @@
         <v>231</v>
       </c>
       <c r="P211" t="s">
-        <v>374</v>
+        <v>379</v>
       </c>
       <c r="Q211">
         <v>3.5</v>
@@ -45223,7 +45253,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ212">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR212">
         <v>1.19</v>
@@ -45426,7 +45456,7 @@
         <v>1.75</v>
       </c>
       <c r="AP213">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="AQ213">
         <v>1.77</v>
@@ -45760,7 +45790,7 @@
         <v>101</v>
       </c>
       <c r="P215" t="s">
-        <v>375</v>
+        <v>380</v>
       </c>
       <c r="Q215">
         <v>4.33</v>
@@ -45838,7 +45868,7 @@
         <v>1.25</v>
       </c>
       <c r="AP215">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AQ215">
         <v>1.38</v>
@@ -45966,7 +45996,7 @@
         <v>234</v>
       </c>
       <c r="P216" t="s">
-        <v>376</v>
+        <v>381</v>
       </c>
       <c r="Q216">
         <v>3</v>
@@ -46172,7 +46202,7 @@
         <v>235</v>
       </c>
       <c r="P217" t="s">
-        <v>377</v>
+        <v>382</v>
       </c>
       <c r="Q217">
         <v>0</v>
@@ -46250,7 +46280,7 @@
         <v>0.88</v>
       </c>
       <c r="AP217">
-        <v>1.79</v>
+        <v>1.87</v>
       </c>
       <c r="AQ217">
         <v>0.85</v>
@@ -46459,7 +46489,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ218">
-        <v>1.27</v>
+        <v>1.17</v>
       </c>
       <c r="AR218">
         <v>1.22</v>
@@ -46584,7 +46614,7 @@
         <v>101</v>
       </c>
       <c r="P219" t="s">
-        <v>378</v>
+        <v>383</v>
       </c>
       <c r="Q219">
         <v>3.2</v>
@@ -46662,10 +46692,10 @@
         <v>1.78</v>
       </c>
       <c r="AP219">
-        <v>0.5</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AQ219">
-        <v>1.36</v>
+        <v>1.47</v>
       </c>
       <c r="AR219">
         <v>1.32</v>
@@ -46868,10 +46898,10 @@
         <v>1.13</v>
       </c>
       <c r="AP220">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="AQ220">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="AR220">
         <v>1.25</v>
@@ -47074,7 +47104,7 @@
         <v>1</v>
       </c>
       <c r="AP221">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="AQ221">
         <v>0.87</v>
@@ -47283,7 +47313,7 @@
         <v>1.79</v>
       </c>
       <c r="AQ222">
-        <v>1.64</v>
+        <v>1.73</v>
       </c>
       <c r="AR222">
         <v>1.41</v>
@@ -47408,7 +47438,7 @@
         <v>101</v>
       </c>
       <c r="P223" t="s">
-        <v>379</v>
+        <v>384</v>
       </c>
       <c r="Q223">
         <v>3.75</v>
@@ -47486,10 +47516,10 @@
         <v>1.44</v>
       </c>
       <c r="AP223">
-        <v>0.6899999999999999</v>
+        <v>0.64</v>
       </c>
       <c r="AQ223">
-        <v>1.31</v>
+        <v>1.21</v>
       </c>
       <c r="AR223">
         <v>1.42</v>
@@ -47614,7 +47644,7 @@
         <v>101</v>
       </c>
       <c r="P224" t="s">
-        <v>380</v>
+        <v>385</v>
       </c>
       <c r="Q224">
         <v>3.4</v>
@@ -47695,7 +47725,7 @@
         <v>1.43</v>
       </c>
       <c r="AQ224">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="AR224">
         <v>1.28</v>
@@ -48104,10 +48134,10 @@
         <v>0.89</v>
       </c>
       <c r="AP226">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="AQ226">
-        <v>0.6899999999999999</v>
+        <v>0.64</v>
       </c>
       <c r="AR226">
         <v>1.56</v>
@@ -48310,7 +48340,7 @@
         <v>1.89</v>
       </c>
       <c r="AP227">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="AQ227">
         <v>1.71</v>
@@ -48519,7 +48549,7 @@
         <v>2.36</v>
       </c>
       <c r="AQ228">
-        <v>0.87</v>
+        <v>1</v>
       </c>
       <c r="AR228">
         <v>1.48</v>
@@ -48722,7 +48752,7 @@
         <v>2</v>
       </c>
       <c r="AP229">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="AQ229">
         <v>1.67</v>
@@ -48850,7 +48880,7 @@
         <v>101</v>
       </c>
       <c r="P230" t="s">
-        <v>348</v>
+        <v>353</v>
       </c>
       <c r="Q230">
         <v>2.5</v>
@@ -49134,7 +49164,7 @@
         <v>1.1</v>
       </c>
       <c r="AP231">
-        <v>1.71</v>
+        <v>1.8</v>
       </c>
       <c r="AQ231">
         <v>0.93</v>
@@ -49262,7 +49292,7 @@
         <v>240</v>
       </c>
       <c r="P232" t="s">
-        <v>381</v>
+        <v>386</v>
       </c>
       <c r="Q232">
         <v>2.4</v>
@@ -49343,7 +49373,7 @@
         <v>1.47</v>
       </c>
       <c r="AQ232">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR232">
         <v>1.34</v>
@@ -49468,7 +49498,7 @@
         <v>241</v>
       </c>
       <c r="P233" t="s">
-        <v>382</v>
+        <v>387</v>
       </c>
       <c r="Q233">
         <v>2.88</v>
@@ -49546,7 +49576,7 @@
         <v>0.89</v>
       </c>
       <c r="AP233">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="AQ233">
         <v>0.85</v>
@@ -49755,7 +49785,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ234">
-        <v>1.08</v>
+        <v>1.21</v>
       </c>
       <c r="AR234">
         <v>1.16</v>
@@ -49958,7 +49988,7 @@
         <v>0.89</v>
       </c>
       <c r="AP235">
-        <v>1.79</v>
+        <v>1.87</v>
       </c>
       <c r="AQ235">
         <v>0.57</v>
@@ -50167,7 +50197,7 @@
         <v>1.57</v>
       </c>
       <c r="AQ236">
-        <v>1.27</v>
+        <v>1.17</v>
       </c>
       <c r="AR236">
         <v>1.41</v>
@@ -50370,7 +50400,7 @@
         <v>0.89</v>
       </c>
       <c r="AP237">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="AQ237">
         <v>0.86</v>
@@ -50579,7 +50609,7 @@
         <v>1.85</v>
       </c>
       <c r="AQ238">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR238">
         <v>1.85</v>
@@ -50704,7 +50734,7 @@
         <v>245</v>
       </c>
       <c r="P239" t="s">
-        <v>383</v>
+        <v>388</v>
       </c>
       <c r="Q239">
         <v>4.5</v>
@@ -50782,10 +50812,10 @@
         <v>1.43</v>
       </c>
       <c r="AP239">
-        <v>1.55</v>
+        <v>1.67</v>
       </c>
       <c r="AQ239">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AR239">
         <v>1.15</v>
@@ -50910,7 +50940,7 @@
         <v>101</v>
       </c>
       <c r="P240" t="s">
-        <v>384</v>
+        <v>389</v>
       </c>
       <c r="Q240">
         <v>3.75</v>
@@ -50988,7 +51018,7 @@
         <v>1.44</v>
       </c>
       <c r="AP240">
-        <v>0.5</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AQ240">
         <v>1.43</v>
@@ -51116,7 +51146,7 @@
         <v>101</v>
       </c>
       <c r="P241" t="s">
-        <v>385</v>
+        <v>390</v>
       </c>
       <c r="Q241">
         <v>5.5</v>
@@ -51194,7 +51224,7 @@
         <v>1.89</v>
       </c>
       <c r="AP241">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AQ241">
         <v>1.77</v>
@@ -51322,7 +51352,7 @@
         <v>246</v>
       </c>
       <c r="P242" t="s">
-        <v>386</v>
+        <v>391</v>
       </c>
       <c r="Q242">
         <v>2.88</v>
@@ -51403,7 +51433,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ242">
-        <v>1.36</v>
+        <v>1.47</v>
       </c>
       <c r="AR242">
         <v>1.23</v>
@@ -51528,7 +51558,7 @@
         <v>101</v>
       </c>
       <c r="P243" t="s">
-        <v>387</v>
+        <v>392</v>
       </c>
       <c r="Q243">
         <v>3.5</v>
@@ -51609,7 +51639,7 @@
         <v>1.15</v>
       </c>
       <c r="AQ243">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="AR243">
         <v>1.3</v>
@@ -52018,10 +52048,10 @@
         <v>1.6</v>
       </c>
       <c r="AP245">
-        <v>1.71</v>
+        <v>1.8</v>
       </c>
       <c r="AQ245">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="AR245">
         <v>1.29</v>
@@ -52146,7 +52176,7 @@
         <v>248</v>
       </c>
       <c r="P246" t="s">
-        <v>319</v>
+        <v>325</v>
       </c>
       <c r="Q246">
         <v>2.38</v>
@@ -52352,7 +52382,7 @@
         <v>101</v>
       </c>
       <c r="P247" t="s">
-        <v>388</v>
+        <v>393</v>
       </c>
       <c r="Q247">
         <v>2.6</v>
@@ -52433,7 +52463,7 @@
         <v>1.56</v>
       </c>
       <c r="AQ247">
-        <v>1.64</v>
+        <v>1.73</v>
       </c>
       <c r="AR247">
         <v>1.35</v>
@@ -52639,7 +52669,7 @@
         <v>1.79</v>
       </c>
       <c r="AQ248">
-        <v>0.6899999999999999</v>
+        <v>0.64</v>
       </c>
       <c r="AR248">
         <v>1.42</v>
@@ -52842,7 +52872,7 @@
         <v>1.7</v>
       </c>
       <c r="AP249">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="AQ249">
         <v>1.71</v>
@@ -53051,7 +53081,7 @@
         <v>1.47</v>
       </c>
       <c r="AQ250">
-        <v>1.31</v>
+        <v>1.21</v>
       </c>
       <c r="AR250">
         <v>1.32</v>
@@ -53176,7 +53206,7 @@
         <v>252</v>
       </c>
       <c r="P251" t="s">
-        <v>389</v>
+        <v>394</v>
       </c>
       <c r="Q251">
         <v>2.25</v>
@@ -53254,10 +53284,10 @@
         <v>0.73</v>
       </c>
       <c r="AP251">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="AQ251">
-        <v>0.87</v>
+        <v>1</v>
       </c>
       <c r="AR251">
         <v>1.49</v>
@@ -53588,7 +53618,7 @@
         <v>254</v>
       </c>
       <c r="P253" t="s">
-        <v>390</v>
+        <v>395</v>
       </c>
       <c r="Q253">
         <v>2.1</v>
@@ -53666,7 +53696,7 @@
         <v>0.82</v>
       </c>
       <c r="AP253">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="AQ253">
         <v>0.67</v>
@@ -53794,7 +53824,7 @@
         <v>101</v>
       </c>
       <c r="P254" t="s">
-        <v>391</v>
+        <v>396</v>
       </c>
       <c r="Q254">
         <v>2.5</v>
@@ -53872,7 +53902,7 @@
         <v>1</v>
       </c>
       <c r="AP254">
-        <v>0.6899999999999999</v>
+        <v>0.64</v>
       </c>
       <c r="AQ254">
         <v>0.93</v>
@@ -54206,7 +54236,7 @@
         <v>114</v>
       </c>
       <c r="P256" t="s">
-        <v>386</v>
+        <v>391</v>
       </c>
       <c r="Q256">
         <v>2.88</v>
@@ -54284,10 +54314,10 @@
         <v>0.75</v>
       </c>
       <c r="AP256">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="AQ256">
-        <v>0.87</v>
+        <v>1</v>
       </c>
       <c r="AR256">
         <v>1.49</v>
@@ -54490,10 +54520,10 @@
         <v>0.8</v>
       </c>
       <c r="AP257">
-        <v>0.6899999999999999</v>
+        <v>0.64</v>
       </c>
       <c r="AQ257">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR257">
         <v>1.34</v>
@@ -54696,10 +54726,10 @@
         <v>0.73</v>
       </c>
       <c r="AP258">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="AQ258">
-        <v>0.6899999999999999</v>
+        <v>0.64</v>
       </c>
       <c r="AR258">
         <v>1.44</v>
@@ -55314,7 +55344,7 @@
         <v>0.75</v>
       </c>
       <c r="AP261">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="AQ261">
         <v>0.67</v>
@@ -55523,7 +55553,7 @@
         <v>1.56</v>
       </c>
       <c r="AQ262">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="AR262">
         <v>1.35</v>
@@ -55729,7 +55759,7 @@
         <v>2.36</v>
       </c>
       <c r="AQ263">
-        <v>1.31</v>
+        <v>1.21</v>
       </c>
       <c r="AR263">
         <v>1.41</v>
@@ -56266,7 +56296,7 @@
         <v>259</v>
       </c>
       <c r="P266" t="s">
-        <v>392</v>
+        <v>397</v>
       </c>
       <c r="Q266">
         <v>3.6</v>
@@ -56344,10 +56374,10 @@
         <v>1.42</v>
       </c>
       <c r="AP266">
-        <v>1.71</v>
+        <v>1.8</v>
       </c>
       <c r="AQ266">
-        <v>1.64</v>
+        <v>1.73</v>
       </c>
       <c r="AR266">
         <v>1.31</v>
@@ -56550,7 +56580,7 @@
         <v>1.1</v>
       </c>
       <c r="AP267">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="AQ267">
         <v>1</v>
@@ -56756,7 +56786,7 @@
         <v>0.9</v>
       </c>
       <c r="AP268">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="AQ268">
         <v>0.85</v>
@@ -56884,7 +56914,7 @@
         <v>261</v>
       </c>
       <c r="P269" t="s">
-        <v>393</v>
+        <v>398</v>
       </c>
       <c r="Q269">
         <v>2.75</v>
@@ -57090,7 +57120,7 @@
         <v>262</v>
       </c>
       <c r="P270" t="s">
-        <v>394</v>
+        <v>399</v>
       </c>
       <c r="Q270">
         <v>2.4</v>
@@ -57168,10 +57198,10 @@
         <v>1.22</v>
       </c>
       <c r="AP270">
-        <v>1.79</v>
+        <v>1.87</v>
       </c>
       <c r="AQ270">
-        <v>1.27</v>
+        <v>1.17</v>
       </c>
       <c r="AR270">
         <v>1.45</v>
@@ -57296,7 +57326,7 @@
         <v>101</v>
       </c>
       <c r="P271" t="s">
-        <v>395</v>
+        <v>400</v>
       </c>
       <c r="Q271">
         <v>4</v>
@@ -57374,10 +57404,10 @@
         <v>1.2</v>
       </c>
       <c r="AP271">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AQ271">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="AR271">
         <v>1.11</v>
@@ -57502,7 +57532,7 @@
         <v>263</v>
       </c>
       <c r="P272" t="s">
-        <v>396</v>
+        <v>401</v>
       </c>
       <c r="Q272">
         <v>3.1</v>
@@ -57583,7 +57613,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ272">
-        <v>1.08</v>
+        <v>1.21</v>
       </c>
       <c r="AR272">
         <v>1.26</v>
@@ -57786,7 +57816,7 @@
         <v>0.8</v>
       </c>
       <c r="AP273">
-        <v>0.5</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AQ273">
         <v>0.57</v>
@@ -57914,7 +57944,7 @@
         <v>184</v>
       </c>
       <c r="P274" t="s">
-        <v>397</v>
+        <v>402</v>
       </c>
       <c r="Q274">
         <v>3.25</v>
@@ -58120,7 +58150,7 @@
         <v>265</v>
       </c>
       <c r="P275" t="s">
-        <v>398</v>
+        <v>403</v>
       </c>
       <c r="Q275">
         <v>3.4</v>
@@ -58201,7 +58231,7 @@
         <v>1.57</v>
       </c>
       <c r="AQ275">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR275">
         <v>1.43</v>
@@ -58326,7 +58356,7 @@
         <v>266</v>
       </c>
       <c r="P276" t="s">
-        <v>399</v>
+        <v>404</v>
       </c>
       <c r="Q276">
         <v>2.88</v>
@@ -58407,7 +58437,7 @@
         <v>1.57</v>
       </c>
       <c r="AQ276">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AR276">
         <v>1.46</v>
@@ -58532,7 +58562,7 @@
         <v>267</v>
       </c>
       <c r="P277" t="s">
-        <v>400</v>
+        <v>405</v>
       </c>
       <c r="Q277">
         <v>3.1</v>
@@ -58613,7 +58643,7 @@
         <v>1.15</v>
       </c>
       <c r="AQ277">
-        <v>1.36</v>
+        <v>1.47</v>
       </c>
       <c r="AR277">
         <v>1.27</v>
@@ -58738,7 +58768,7 @@
         <v>101</v>
       </c>
       <c r="P278" t="s">
-        <v>401</v>
+        <v>406</v>
       </c>
       <c r="Q278">
         <v>3.1</v>
@@ -58816,7 +58846,7 @@
         <v>1.6</v>
       </c>
       <c r="AP278">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="AQ278">
         <v>1.43</v>
@@ -58944,7 +58974,7 @@
         <v>128</v>
       </c>
       <c r="P279" t="s">
-        <v>402</v>
+        <v>407</v>
       </c>
       <c r="Q279">
         <v>5</v>
@@ -59022,7 +59052,7 @@
         <v>1.3</v>
       </c>
       <c r="AP279">
-        <v>1.55</v>
+        <v>1.67</v>
       </c>
       <c r="AQ279">
         <v>1.38</v>
@@ -59231,7 +59261,7 @@
         <v>1.85</v>
       </c>
       <c r="AQ280">
-        <v>0.87</v>
+        <v>1</v>
       </c>
       <c r="AR280">
         <v>1.76</v>
@@ -59437,7 +59467,7 @@
         <v>2.36</v>
       </c>
       <c r="AQ281">
-        <v>1.36</v>
+        <v>1.47</v>
       </c>
       <c r="AR281">
         <v>1.35</v>
@@ -59562,7 +59592,7 @@
         <v>101</v>
       </c>
       <c r="P282" t="s">
-        <v>403</v>
+        <v>408</v>
       </c>
       <c r="Q282">
         <v>2.5</v>
@@ -59849,7 +59879,7 @@
         <v>1.56</v>
       </c>
       <c r="AQ283">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="AR283">
         <v>1.32</v>
@@ -60052,7 +60082,7 @@
         <v>1.62</v>
       </c>
       <c r="AP284">
-        <v>1.79</v>
+        <v>1.87</v>
       </c>
       <c r="AQ284">
         <v>1.67</v>
@@ -60180,7 +60210,7 @@
         <v>101</v>
       </c>
       <c r="P285" t="s">
-        <v>404</v>
+        <v>409</v>
       </c>
       <c r="Q285">
         <v>2.6</v>
@@ -60261,7 +60291,7 @@
         <v>1.43</v>
       </c>
       <c r="AQ285">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR285">
         <v>1.6</v>
@@ -60464,7 +60494,7 @@
         <v>0.82</v>
       </c>
       <c r="AP286">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="AQ286">
         <v>0.86</v>
@@ -60592,7 +60622,7 @@
         <v>270</v>
       </c>
       <c r="P287" t="s">
-        <v>341</v>
+        <v>346</v>
       </c>
       <c r="Q287">
         <v>2.75</v>
@@ -60876,7 +60906,7 @@
         <v>0.73</v>
       </c>
       <c r="AP288">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="AQ288">
         <v>0.57</v>
@@ -61085,7 +61115,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ289">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="AR289">
         <v>1.31</v>
@@ -61288,7 +61318,7 @@
         <v>0.91</v>
       </c>
       <c r="AP290">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AQ290">
         <v>0.85</v>
@@ -61416,7 +61446,7 @@
         <v>101</v>
       </c>
       <c r="P291" t="s">
-        <v>405</v>
+        <v>410</v>
       </c>
       <c r="Q291">
         <v>4</v>
@@ -61494,7 +61524,7 @@
         <v>1.5</v>
       </c>
       <c r="AP291">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="AQ291">
         <v>1.71</v>
@@ -61700,10 +61730,10 @@
         <v>0.92</v>
       </c>
       <c r="AP292">
-        <v>0.6899999999999999</v>
+        <v>0.64</v>
       </c>
       <c r="AQ292">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR292">
         <v>1.32</v>
@@ -61828,7 +61858,7 @@
         <v>101</v>
       </c>
       <c r="P293" t="s">
-        <v>406</v>
+        <v>411</v>
       </c>
       <c r="Q293">
         <v>2.88</v>
@@ -61906,10 +61936,10 @@
         <v>0.91</v>
       </c>
       <c r="AP293">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="AQ293">
-        <v>1.08</v>
+        <v>1.21</v>
       </c>
       <c r="AR293">
         <v>1.46</v>
@@ -62034,7 +62064,7 @@
         <v>101</v>
       </c>
       <c r="P294" t="s">
-        <v>407</v>
+        <v>412</v>
       </c>
       <c r="Q294">
         <v>3.6</v>
@@ -62115,7 +62145,7 @@
         <v>1.15</v>
       </c>
       <c r="AQ294">
-        <v>1.64</v>
+        <v>1.73</v>
       </c>
       <c r="AR294">
         <v>1.29</v>
@@ -62321,7 +62351,7 @@
         <v>1.43</v>
       </c>
       <c r="AQ295">
-        <v>1.31</v>
+        <v>1.21</v>
       </c>
       <c r="AR295">
         <v>1.29</v>
@@ -62446,7 +62476,7 @@
         <v>273</v>
       </c>
       <c r="P296" t="s">
-        <v>408</v>
+        <v>413</v>
       </c>
       <c r="Q296">
         <v>2</v>
@@ -62524,7 +62554,7 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="AP296">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="AQ296">
         <v>0.67</v>
@@ -62652,7 +62682,7 @@
         <v>101</v>
       </c>
       <c r="P297" t="s">
-        <v>409</v>
+        <v>414</v>
       </c>
       <c r="Q297">
         <v>2.75</v>
@@ -62733,7 +62763,7 @@
         <v>1.79</v>
       </c>
       <c r="AQ297">
-        <v>1.27</v>
+        <v>1.17</v>
       </c>
       <c r="AR297">
         <v>1.45</v>
@@ -62939,7 +62969,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ298">
-        <v>0.6899999999999999</v>
+        <v>0.64</v>
       </c>
       <c r="AR298">
         <v>1.32</v>
@@ -63064,7 +63094,7 @@
         <v>275</v>
       </c>
       <c r="P299" t="s">
-        <v>410</v>
+        <v>415</v>
       </c>
       <c r="Q299">
         <v>2.38</v>
@@ -63142,10 +63172,10 @@
         <v>1.44</v>
       </c>
       <c r="AP299">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="AQ299">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AR299">
         <v>1.58</v>
@@ -63270,7 +63300,7 @@
         <v>101</v>
       </c>
       <c r="P300" t="s">
-        <v>303</v>
+        <v>309</v>
       </c>
       <c r="Q300">
         <v>4</v>
@@ -63348,10 +63378,10 @@
         <v>1.38</v>
       </c>
       <c r="AP300">
-        <v>0.5</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AQ300">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="AR300">
         <v>1.31</v>
@@ -63554,7 +63584,7 @@
         <v>0.67</v>
       </c>
       <c r="AP301">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="AQ301">
         <v>0.57</v>
@@ -63763,7 +63793,7 @@
         <v>1.47</v>
       </c>
       <c r="AQ302">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AR302">
         <v>1.31</v>
@@ -63966,10 +63996,10 @@
         <v>1.08</v>
       </c>
       <c r="AP303">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AQ303">
-        <v>1.08</v>
+        <v>1.21</v>
       </c>
       <c r="AR303">
         <v>1.08</v>
@@ -64094,7 +64124,7 @@
         <v>278</v>
       </c>
       <c r="P304" t="s">
-        <v>411</v>
+        <v>416</v>
       </c>
       <c r="Q304">
         <v>4</v>
@@ -64172,10 +64202,10 @@
         <v>0.71</v>
       </c>
       <c r="AP304">
-        <v>1.55</v>
+        <v>1.67</v>
       </c>
       <c r="AQ304">
-        <v>0.87</v>
+        <v>1</v>
       </c>
       <c r="AR304">
         <v>1.29</v>
@@ -64793,7 +64823,7 @@
         <v>1.57</v>
       </c>
       <c r="AQ307">
-        <v>1.36</v>
+        <v>1.47</v>
       </c>
       <c r="AR307">
         <v>1.39</v>
@@ -64918,7 +64948,7 @@
         <v>281</v>
       </c>
       <c r="P308" t="s">
-        <v>412</v>
+        <v>417</v>
       </c>
       <c r="Q308">
         <v>3.75</v>
@@ -64996,10 +65026,10 @@
         <v>1.5</v>
       </c>
       <c r="AP308">
-        <v>1.71</v>
+        <v>1.8</v>
       </c>
       <c r="AQ308">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="AR308">
         <v>1.34</v>
@@ -65124,7 +65154,7 @@
         <v>252</v>
       </c>
       <c r="P309" t="s">
-        <v>413</v>
+        <v>291</v>
       </c>
       <c r="Q309">
         <v>2.5</v>
@@ -65408,7 +65438,7 @@
         <v>1</v>
       </c>
       <c r="AP310">
-        <v>1.79</v>
+        <v>1.87</v>
       </c>
       <c r="AQ310">
         <v>0.87</v>
@@ -65536,7 +65566,7 @@
         <v>195</v>
       </c>
       <c r="P311" t="s">
-        <v>414</v>
+        <v>418</v>
       </c>
       <c r="Q311">
         <v>2.63</v>
@@ -66026,7 +66056,7 @@
         <v>1</v>
       </c>
       <c r="AP313">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="AQ313">
         <v>1</v>
@@ -66235,7 +66265,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ314">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR314">
         <v>1.21</v>
@@ -67184,7 +67214,7 @@
         <v>284</v>
       </c>
       <c r="P319" t="s">
-        <v>415</v>
+        <v>419</v>
       </c>
       <c r="Q319">
         <v>3.4</v>
@@ -68626,7 +68656,7 @@
         <v>290</v>
       </c>
       <c r="P326" t="s">
-        <v>416</v>
+        <v>420</v>
       </c>
       <c r="Q326">
         <v>3.75</v>
@@ -68783,6 +68813,2478 @@
       </c>
       <c r="BP326">
         <v>1.39</v>
+      </c>
+    </row>
+    <row r="327" spans="1:68">
+      <c r="A327" s="1">
+        <v>326</v>
+      </c>
+      <c r="B327">
+        <v>7476896</v>
+      </c>
+      <c r="C327" t="s">
+        <v>68</v>
+      </c>
+      <c r="D327" t="s">
+        <v>69</v>
+      </c>
+      <c r="E327" s="2">
+        <v>45689.39583333334</v>
+      </c>
+      <c r="F327">
+        <v>30</v>
+      </c>
+      <c r="G327" t="s">
+        <v>76</v>
+      </c>
+      <c r="H327" t="s">
+        <v>93</v>
+      </c>
+      <c r="I327">
+        <v>0</v>
+      </c>
+      <c r="J327">
+        <v>2</v>
+      </c>
+      <c r="K327">
+        <v>2</v>
+      </c>
+      <c r="L327">
+        <v>1</v>
+      </c>
+      <c r="M327">
+        <v>2</v>
+      </c>
+      <c r="N327">
+        <v>3</v>
+      </c>
+      <c r="O327" t="s">
+        <v>291</v>
+      </c>
+      <c r="P327" t="s">
+        <v>421</v>
+      </c>
+      <c r="Q327">
+        <v>3.75</v>
+      </c>
+      <c r="R327">
+        <v>2</v>
+      </c>
+      <c r="S327">
+        <v>3.2</v>
+      </c>
+      <c r="T327">
+        <v>1.5</v>
+      </c>
+      <c r="U327">
+        <v>2.5</v>
+      </c>
+      <c r="V327">
+        <v>3.4</v>
+      </c>
+      <c r="W327">
+        <v>1.3</v>
+      </c>
+      <c r="X327">
+        <v>10</v>
+      </c>
+      <c r="Y327">
+        <v>1.06</v>
+      </c>
+      <c r="Z327">
+        <v>2.88</v>
+      </c>
+      <c r="AA327">
+        <v>3.31</v>
+      </c>
+      <c r="AB327">
+        <v>2.38</v>
+      </c>
+      <c r="AC327">
+        <v>1.07</v>
+      </c>
+      <c r="AD327">
+        <v>8</v>
+      </c>
+      <c r="AE327">
+        <v>1.38</v>
+      </c>
+      <c r="AF327">
+        <v>2.95</v>
+      </c>
+      <c r="AG327">
+        <v>2</v>
+      </c>
+      <c r="AH327">
+        <v>1.75</v>
+      </c>
+      <c r="AI327">
+        <v>1.91</v>
+      </c>
+      <c r="AJ327">
+        <v>1.8</v>
+      </c>
+      <c r="AK327">
+        <v>1.55</v>
+      </c>
+      <c r="AL327">
+        <v>1.28</v>
+      </c>
+      <c r="AM327">
+        <v>1.38</v>
+      </c>
+      <c r="AN327">
+        <v>1.46</v>
+      </c>
+      <c r="AO327">
+        <v>1.64</v>
+      </c>
+      <c r="AP327">
+        <v>1.36</v>
+      </c>
+      <c r="AQ327">
+        <v>1.73</v>
+      </c>
+      <c r="AR327">
+        <v>1.28</v>
+      </c>
+      <c r="AS327">
+        <v>1.3</v>
+      </c>
+      <c r="AT327">
+        <v>2.58</v>
+      </c>
+      <c r="AU327">
+        <v>7</v>
+      </c>
+      <c r="AV327">
+        <v>5</v>
+      </c>
+      <c r="AW327">
+        <v>9</v>
+      </c>
+      <c r="AX327">
+        <v>7</v>
+      </c>
+      <c r="AY327">
+        <v>20</v>
+      </c>
+      <c r="AZ327">
+        <v>13</v>
+      </c>
+      <c r="BA327">
+        <v>2</v>
+      </c>
+      <c r="BB327">
+        <v>4</v>
+      </c>
+      <c r="BC327">
+        <v>6</v>
+      </c>
+      <c r="BD327">
+        <v>2.23</v>
+      </c>
+      <c r="BE327">
+        <v>6.4</v>
+      </c>
+      <c r="BF327">
+        <v>1.8</v>
+      </c>
+      <c r="BG327">
+        <v>1.3</v>
+      </c>
+      <c r="BH327">
+        <v>3.05</v>
+      </c>
+      <c r="BI327">
+        <v>1.52</v>
+      </c>
+      <c r="BJ327">
+        <v>2.32</v>
+      </c>
+      <c r="BK327">
+        <v>1.84</v>
+      </c>
+      <c r="BL327">
+        <v>1.84</v>
+      </c>
+      <c r="BM327">
+        <v>2.32</v>
+      </c>
+      <c r="BN327">
+        <v>1.53</v>
+      </c>
+      <c r="BO327">
+        <v>2.95</v>
+      </c>
+      <c r="BP327">
+        <v>1.33</v>
+      </c>
+    </row>
+    <row r="328" spans="1:68">
+      <c r="A328" s="1">
+        <v>327</v>
+      </c>
+      <c r="B328">
+        <v>7476894</v>
+      </c>
+      <c r="C328" t="s">
+        <v>68</v>
+      </c>
+      <c r="D328" t="s">
+        <v>69</v>
+      </c>
+      <c r="E328" s="2">
+        <v>45689.39583333334</v>
+      </c>
+      <c r="F328">
+        <v>30</v>
+      </c>
+      <c r="G328" t="s">
+        <v>73</v>
+      </c>
+      <c r="H328" t="s">
+        <v>70</v>
+      </c>
+      <c r="I328">
+        <v>0</v>
+      </c>
+      <c r="J328">
+        <v>0</v>
+      </c>
+      <c r="K328">
+        <v>0</v>
+      </c>
+      <c r="L328">
+        <v>1</v>
+      </c>
+      <c r="M328">
+        <v>0</v>
+      </c>
+      <c r="N328">
+        <v>1</v>
+      </c>
+      <c r="O328" t="s">
+        <v>128</v>
+      </c>
+      <c r="P328" t="s">
+        <v>101</v>
+      </c>
+      <c r="Q328">
+        <v>3.4</v>
+      </c>
+      <c r="R328">
+        <v>2.2</v>
+      </c>
+      <c r="S328">
+        <v>3.1</v>
+      </c>
+      <c r="T328">
+        <v>1.36</v>
+      </c>
+      <c r="U328">
+        <v>3</v>
+      </c>
+      <c r="V328">
+        <v>2.75</v>
+      </c>
+      <c r="W328">
+        <v>1.4</v>
+      </c>
+      <c r="X328">
+        <v>7</v>
+      </c>
+      <c r="Y328">
+        <v>1.1</v>
+      </c>
+      <c r="Z328">
+        <v>2.85</v>
+      </c>
+      <c r="AA328">
+        <v>3.17</v>
+      </c>
+      <c r="AB328">
+        <v>2.48</v>
+      </c>
+      <c r="AC328">
+        <v>1.06</v>
+      </c>
+      <c r="AD328">
+        <v>8.5</v>
+      </c>
+      <c r="AE328">
+        <v>1.28</v>
+      </c>
+      <c r="AF328">
+        <v>3.6</v>
+      </c>
+      <c r="AG328">
+        <v>1.82</v>
+      </c>
+      <c r="AH328">
+        <v>1.92</v>
+      </c>
+      <c r="AI328">
+        <v>1.62</v>
+      </c>
+      <c r="AJ328">
+        <v>2.2</v>
+      </c>
+      <c r="AK328">
+        <v>1.53</v>
+      </c>
+      <c r="AL328">
+        <v>1.28</v>
+      </c>
+      <c r="AM328">
+        <v>1.4</v>
+      </c>
+      <c r="AN328">
+        <v>1.71</v>
+      </c>
+      <c r="AO328">
+        <v>1.31</v>
+      </c>
+      <c r="AP328">
+        <v>1.8</v>
+      </c>
+      <c r="AQ328">
+        <v>1.21</v>
+      </c>
+      <c r="AR328">
+        <v>1.38</v>
+      </c>
+      <c r="AS328">
+        <v>1.26</v>
+      </c>
+      <c r="AT328">
+        <v>2.64</v>
+      </c>
+      <c r="AU328">
+        <v>3</v>
+      </c>
+      <c r="AV328">
+        <v>4</v>
+      </c>
+      <c r="AW328">
+        <v>6</v>
+      </c>
+      <c r="AX328">
+        <v>16</v>
+      </c>
+      <c r="AY328">
+        <v>10</v>
+      </c>
+      <c r="AZ328">
+        <v>24</v>
+      </c>
+      <c r="BA328">
+        <v>2</v>
+      </c>
+      <c r="BB328">
+        <v>8</v>
+      </c>
+      <c r="BC328">
+        <v>10</v>
+      </c>
+      <c r="BD328">
+        <v>2.05</v>
+      </c>
+      <c r="BE328">
+        <v>6.4</v>
+      </c>
+      <c r="BF328">
+        <v>1.95</v>
+      </c>
+      <c r="BG328">
+        <v>1.38</v>
+      </c>
+      <c r="BH328">
+        <v>2.75</v>
+      </c>
+      <c r="BI328">
+        <v>1.65</v>
+      </c>
+      <c r="BJ328">
+        <v>2.08</v>
+      </c>
+      <c r="BK328">
+        <v>2.05</v>
+      </c>
+      <c r="BL328">
+        <v>1.68</v>
+      </c>
+      <c r="BM328">
+        <v>2.6</v>
+      </c>
+      <c r="BN328">
+        <v>1.43</v>
+      </c>
+      <c r="BO328">
+        <v>3.4</v>
+      </c>
+      <c r="BP328">
+        <v>1.26</v>
+      </c>
+    </row>
+    <row r="329" spans="1:68">
+      <c r="A329" s="1">
+        <v>328</v>
+      </c>
+      <c r="B329">
+        <v>7476902</v>
+      </c>
+      <c r="C329" t="s">
+        <v>68</v>
+      </c>
+      <c r="D329" t="s">
+        <v>69</v>
+      </c>
+      <c r="E329" s="2">
+        <v>45689.5</v>
+      </c>
+      <c r="F329">
+        <v>30</v>
+      </c>
+      <c r="G329" t="s">
+        <v>81</v>
+      </c>
+      <c r="H329" t="s">
+        <v>79</v>
+      </c>
+      <c r="I329">
+        <v>0</v>
+      </c>
+      <c r="J329">
+        <v>1</v>
+      </c>
+      <c r="K329">
+        <v>1</v>
+      </c>
+      <c r="L329">
+        <v>2</v>
+      </c>
+      <c r="M329">
+        <v>2</v>
+      </c>
+      <c r="N329">
+        <v>4</v>
+      </c>
+      <c r="O329" t="s">
+        <v>292</v>
+      </c>
+      <c r="P329" t="s">
+        <v>422</v>
+      </c>
+      <c r="Q329">
+        <v>2.63</v>
+      </c>
+      <c r="R329">
+        <v>2.1</v>
+      </c>
+      <c r="S329">
+        <v>4.33</v>
+      </c>
+      <c r="T329">
+        <v>1.4</v>
+      </c>
+      <c r="U329">
+        <v>2.75</v>
+      </c>
+      <c r="V329">
+        <v>3</v>
+      </c>
+      <c r="W329">
+        <v>1.36</v>
+      </c>
+      <c r="X329">
+        <v>8</v>
+      </c>
+      <c r="Y329">
+        <v>1.08</v>
+      </c>
+      <c r="Z329">
+        <v>1.94</v>
+      </c>
+      <c r="AA329">
+        <v>3.47</v>
+      </c>
+      <c r="AB329">
+        <v>3.77</v>
+      </c>
+      <c r="AC329">
+        <v>1.07</v>
+      </c>
+      <c r="AD329">
+        <v>9</v>
+      </c>
+      <c r="AE329">
+        <v>1.38</v>
+      </c>
+      <c r="AF329">
+        <v>3</v>
+      </c>
+      <c r="AG329">
+        <v>1.92</v>
+      </c>
+      <c r="AH329">
+        <v>1.82</v>
+      </c>
+      <c r="AI329">
+        <v>1.8</v>
+      </c>
+      <c r="AJ329">
+        <v>1.91</v>
+      </c>
+      <c r="AK329">
+        <v>1.24</v>
+      </c>
+      <c r="AL329">
+        <v>1.29</v>
+      </c>
+      <c r="AM329">
+        <v>1.83</v>
+      </c>
+      <c r="AN329">
+        <v>2.5</v>
+      </c>
+      <c r="AO329">
+        <v>1.38</v>
+      </c>
+      <c r="AP329">
+        <v>2.4</v>
+      </c>
+      <c r="AQ329">
+        <v>1.36</v>
+      </c>
+      <c r="AR329">
+        <v>1.67</v>
+      </c>
+      <c r="AS329">
+        <v>1.25</v>
+      </c>
+      <c r="AT329">
+        <v>2.92</v>
+      </c>
+      <c r="AU329">
+        <v>5</v>
+      </c>
+      <c r="AV329">
+        <v>5</v>
+      </c>
+      <c r="AW329">
+        <v>13</v>
+      </c>
+      <c r="AX329">
+        <v>1</v>
+      </c>
+      <c r="AY329">
+        <v>20</v>
+      </c>
+      <c r="AZ329">
+        <v>6</v>
+      </c>
+      <c r="BA329">
+        <v>15</v>
+      </c>
+      <c r="BB329">
+        <v>1</v>
+      </c>
+      <c r="BC329">
+        <v>16</v>
+      </c>
+      <c r="BD329">
+        <v>1.68</v>
+      </c>
+      <c r="BE329">
+        <v>6.25</v>
+      </c>
+      <c r="BF329">
+        <v>2.43</v>
+      </c>
+      <c r="BG329">
+        <v>1.34</v>
+      </c>
+      <c r="BH329">
+        <v>2.9</v>
+      </c>
+      <c r="BI329">
+        <v>1.58</v>
+      </c>
+      <c r="BJ329">
+        <v>2.18</v>
+      </c>
+      <c r="BK329">
+        <v>1.97</v>
+      </c>
+      <c r="BL329">
+        <v>1.74</v>
+      </c>
+      <c r="BM329">
+        <v>2.48</v>
+      </c>
+      <c r="BN329">
+        <v>1.47</v>
+      </c>
+      <c r="BO329">
+        <v>3.15</v>
+      </c>
+      <c r="BP329">
+        <v>1.29</v>
+      </c>
+    </row>
+    <row r="330" spans="1:68">
+      <c r="A330" s="1">
+        <v>329</v>
+      </c>
+      <c r="B330">
+        <v>7476901</v>
+      </c>
+      <c r="C330" t="s">
+        <v>68</v>
+      </c>
+      <c r="D330" t="s">
+        <v>69</v>
+      </c>
+      <c r="E330" s="2">
+        <v>45689.5</v>
+      </c>
+      <c r="F330">
+        <v>30</v>
+      </c>
+      <c r="G330" t="s">
+        <v>80</v>
+      </c>
+      <c r="H330" t="s">
+        <v>85</v>
+      </c>
+      <c r="I330">
+        <v>0</v>
+      </c>
+      <c r="J330">
+        <v>2</v>
+      </c>
+      <c r="K330">
+        <v>2</v>
+      </c>
+      <c r="L330">
+        <v>1</v>
+      </c>
+      <c r="M330">
+        <v>3</v>
+      </c>
+      <c r="N330">
+        <v>4</v>
+      </c>
+      <c r="O330" t="s">
+        <v>260</v>
+      </c>
+      <c r="P330" t="s">
+        <v>423</v>
+      </c>
+      <c r="Q330">
+        <v>3.5</v>
+      </c>
+      <c r="R330">
+        <v>1.95</v>
+      </c>
+      <c r="S330">
+        <v>3.5</v>
+      </c>
+      <c r="T330">
+        <v>1.53</v>
+      </c>
+      <c r="U330">
+        <v>2.38</v>
+      </c>
+      <c r="V330">
+        <v>3.5</v>
+      </c>
+      <c r="W330">
+        <v>1.29</v>
+      </c>
+      <c r="X330">
+        <v>11</v>
+      </c>
+      <c r="Y330">
+        <v>1.05</v>
+      </c>
+      <c r="Z330">
+        <v>2.64</v>
+      </c>
+      <c r="AA330">
+        <v>3.21</v>
+      </c>
+      <c r="AB330">
+        <v>2.64</v>
+      </c>
+      <c r="AC330">
+        <v>1.08</v>
+      </c>
+      <c r="AD330">
+        <v>8.5</v>
+      </c>
+      <c r="AE330">
+        <v>1.44</v>
+      </c>
+      <c r="AF330">
+        <v>2.75</v>
+      </c>
+      <c r="AG330">
+        <v>2.3</v>
+      </c>
+      <c r="AH330">
+        <v>1.57</v>
+      </c>
+      <c r="AI330">
+        <v>2</v>
+      </c>
+      <c r="AJ330">
+        <v>1.73</v>
+      </c>
+      <c r="AK330">
+        <v>1.55</v>
+      </c>
+      <c r="AL330">
+        <v>1.33</v>
+      </c>
+      <c r="AM330">
+        <v>1.37</v>
+      </c>
+      <c r="AN330">
+        <v>1.38</v>
+      </c>
+      <c r="AO330">
+        <v>1.08</v>
+      </c>
+      <c r="AP330">
+        <v>1.29</v>
+      </c>
+      <c r="AQ330">
+        <v>1.21</v>
+      </c>
+      <c r="AR330">
+        <v>1.52</v>
+      </c>
+      <c r="AS330">
+        <v>1.12</v>
+      </c>
+      <c r="AT330">
+        <v>2.64</v>
+      </c>
+      <c r="AU330">
+        <v>3</v>
+      </c>
+      <c r="AV330">
+        <v>4</v>
+      </c>
+      <c r="AW330">
+        <v>8</v>
+      </c>
+      <c r="AX330">
+        <v>11</v>
+      </c>
+      <c r="AY330">
+        <v>16</v>
+      </c>
+      <c r="AZ330">
+        <v>24</v>
+      </c>
+      <c r="BA330">
+        <v>5</v>
+      </c>
+      <c r="BB330">
+        <v>2</v>
+      </c>
+      <c r="BC330">
+        <v>7</v>
+      </c>
+      <c r="BD330">
+        <v>2.07</v>
+      </c>
+      <c r="BE330">
+        <v>6.75</v>
+      </c>
+      <c r="BF330">
+        <v>1.9</v>
+      </c>
+      <c r="BG330">
+        <v>1.19</v>
+      </c>
+      <c r="BH330">
+        <v>4.1</v>
+      </c>
+      <c r="BI330">
+        <v>1.34</v>
+      </c>
+      <c r="BJ330">
+        <v>2.9</v>
+      </c>
+      <c r="BK330">
+        <v>1.57</v>
+      </c>
+      <c r="BL330">
+        <v>2.23</v>
+      </c>
+      <c r="BM330">
+        <v>1.9</v>
+      </c>
+      <c r="BN330">
+        <v>1.79</v>
+      </c>
+      <c r="BO330">
+        <v>2.38</v>
+      </c>
+      <c r="BP330">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="331" spans="1:68">
+      <c r="A331" s="1">
+        <v>330</v>
+      </c>
+      <c r="B331">
+        <v>7476900</v>
+      </c>
+      <c r="C331" t="s">
+        <v>68</v>
+      </c>
+      <c r="D331" t="s">
+        <v>69</v>
+      </c>
+      <c r="E331" s="2">
+        <v>45689.5</v>
+      </c>
+      <c r="F331">
+        <v>30</v>
+      </c>
+      <c r="G331" t="s">
+        <v>90</v>
+      </c>
+      <c r="H331" t="s">
+        <v>84</v>
+      </c>
+      <c r="I331">
+        <v>1</v>
+      </c>
+      <c r="J331">
+        <v>0</v>
+      </c>
+      <c r="K331">
+        <v>1</v>
+      </c>
+      <c r="L331">
+        <v>2</v>
+      </c>
+      <c r="M331">
+        <v>1</v>
+      </c>
+      <c r="N331">
+        <v>3</v>
+      </c>
+      <c r="O331" t="s">
+        <v>293</v>
+      </c>
+      <c r="P331" t="s">
+        <v>148</v>
+      </c>
+      <c r="Q331">
+        <v>2.38</v>
+      </c>
+      <c r="R331">
+        <v>2.2</v>
+      </c>
+      <c r="S331">
+        <v>5</v>
+      </c>
+      <c r="T331">
+        <v>1.4</v>
+      </c>
+      <c r="U331">
+        <v>2.75</v>
+      </c>
+      <c r="V331">
+        <v>3</v>
+      </c>
+      <c r="W331">
+        <v>1.36</v>
+      </c>
+      <c r="X331">
+        <v>8</v>
+      </c>
+      <c r="Y331">
+        <v>1.08</v>
+      </c>
+      <c r="Z331">
+        <v>1.75</v>
+      </c>
+      <c r="AA331">
+        <v>3.5</v>
+      </c>
+      <c r="AB331">
+        <v>4.75</v>
+      </c>
+      <c r="AC331">
+        <v>1.05</v>
+      </c>
+      <c r="AD331">
+        <v>11</v>
+      </c>
+      <c r="AE331">
+        <v>1.33</v>
+      </c>
+      <c r="AF331">
+        <v>3.3</v>
+      </c>
+      <c r="AG331">
+        <v>1.92</v>
+      </c>
+      <c r="AH331">
+        <v>1.82</v>
+      </c>
+      <c r="AI331">
+        <v>1.83</v>
+      </c>
+      <c r="AJ331">
+        <v>1.83</v>
+      </c>
+      <c r="AK331">
+        <v>1.2</v>
+      </c>
+      <c r="AL331">
+        <v>1.28</v>
+      </c>
+      <c r="AM331">
+        <v>1.98</v>
+      </c>
+      <c r="AN331">
+        <v>1.67</v>
+      </c>
+      <c r="AO331">
+        <v>1.08</v>
+      </c>
+      <c r="AP331">
+        <v>1.77</v>
+      </c>
+      <c r="AQ331">
+        <v>1</v>
+      </c>
+      <c r="AR331">
+        <v>1.33</v>
+      </c>
+      <c r="AS331">
+        <v>1.32</v>
+      </c>
+      <c r="AT331">
+        <v>2.65</v>
+      </c>
+      <c r="AU331">
+        <v>4</v>
+      </c>
+      <c r="AV331">
+        <v>5</v>
+      </c>
+      <c r="AW331">
+        <v>6</v>
+      </c>
+      <c r="AX331">
+        <v>12</v>
+      </c>
+      <c r="AY331">
+        <v>14</v>
+      </c>
+      <c r="AZ331">
+        <v>22</v>
+      </c>
+      <c r="BA331">
+        <v>4</v>
+      </c>
+      <c r="BB331">
+        <v>5</v>
+      </c>
+      <c r="BC331">
+        <v>9</v>
+      </c>
+      <c r="BD331">
+        <v>1.52</v>
+      </c>
+      <c r="BE331">
+        <v>6.75</v>
+      </c>
+      <c r="BF331">
+        <v>2.8</v>
+      </c>
+      <c r="BG331">
+        <v>1.27</v>
+      </c>
+      <c r="BH331">
+        <v>3.3</v>
+      </c>
+      <c r="BI331">
+        <v>1.48</v>
+      </c>
+      <c r="BJ331">
+        <v>2.45</v>
+      </c>
+      <c r="BK331">
+        <v>1.76</v>
+      </c>
+      <c r="BL331">
+        <v>1.94</v>
+      </c>
+      <c r="BM331">
+        <v>2.18</v>
+      </c>
+      <c r="BN331">
+        <v>1.58</v>
+      </c>
+      <c r="BO331">
+        <v>2.7</v>
+      </c>
+      <c r="BP331">
+        <v>1.38</v>
+      </c>
+    </row>
+    <row r="332" spans="1:68">
+      <c r="A332" s="1">
+        <v>331</v>
+      </c>
+      <c r="B332">
+        <v>7476899</v>
+      </c>
+      <c r="C332" t="s">
+        <v>68</v>
+      </c>
+      <c r="D332" t="s">
+        <v>69</v>
+      </c>
+      <c r="E332" s="2">
+        <v>45689.5</v>
+      </c>
+      <c r="F332">
+        <v>30</v>
+      </c>
+      <c r="G332" t="s">
+        <v>89</v>
+      </c>
+      <c r="H332" t="s">
+        <v>72</v>
+      </c>
+      <c r="I332">
+        <v>0</v>
+      </c>
+      <c r="J332">
+        <v>0</v>
+      </c>
+      <c r="K332">
+        <v>0</v>
+      </c>
+      <c r="L332">
+        <v>1</v>
+      </c>
+      <c r="M332">
+        <v>0</v>
+      </c>
+      <c r="N332">
+        <v>1</v>
+      </c>
+      <c r="O332" t="s">
+        <v>195</v>
+      </c>
+      <c r="P332" t="s">
+        <v>101</v>
+      </c>
+      <c r="Q332">
+        <v>3.75</v>
+      </c>
+      <c r="R332">
+        <v>2.1</v>
+      </c>
+      <c r="S332">
+        <v>2.88</v>
+      </c>
+      <c r="T332">
+        <v>1.4</v>
+      </c>
+      <c r="U332">
+        <v>2.75</v>
+      </c>
+      <c r="V332">
+        <v>3</v>
+      </c>
+      <c r="W332">
+        <v>1.36</v>
+      </c>
+      <c r="X332">
+        <v>8</v>
+      </c>
+      <c r="Y332">
+        <v>1.08</v>
+      </c>
+      <c r="Z332">
+        <v>3.35</v>
+      </c>
+      <c r="AA332">
+        <v>3.45</v>
+      </c>
+      <c r="AB332">
+        <v>2.08</v>
+      </c>
+      <c r="AC332">
+        <v>1.05</v>
+      </c>
+      <c r="AD332">
+        <v>11</v>
+      </c>
+      <c r="AE332">
+        <v>1.3</v>
+      </c>
+      <c r="AF332">
+        <v>3.4</v>
+      </c>
+      <c r="AG332">
+        <v>1.91</v>
+      </c>
+      <c r="AH332">
+        <v>1.83</v>
+      </c>
+      <c r="AI332">
+        <v>1.73</v>
+      </c>
+      <c r="AJ332">
+        <v>2</v>
+      </c>
+      <c r="AK332">
+        <v>1.68</v>
+      </c>
+      <c r="AL332">
+        <v>1.3</v>
+      </c>
+      <c r="AM332">
+        <v>1.32</v>
+      </c>
+      <c r="AN332">
+        <v>1.55</v>
+      </c>
+      <c r="AO332">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="AP332">
+        <v>1.67</v>
+      </c>
+      <c r="AQ332">
+        <v>0.64</v>
+      </c>
+      <c r="AR332">
+        <v>1.27</v>
+      </c>
+      <c r="AS332">
+        <v>1.13</v>
+      </c>
+      <c r="AT332">
+        <v>2.4</v>
+      </c>
+      <c r="AU332">
+        <v>4</v>
+      </c>
+      <c r="AV332">
+        <v>4</v>
+      </c>
+      <c r="AW332">
+        <v>1</v>
+      </c>
+      <c r="AX332">
+        <v>11</v>
+      </c>
+      <c r="AY332">
+        <v>5</v>
+      </c>
+      <c r="AZ332">
+        <v>19</v>
+      </c>
+      <c r="BA332">
+        <v>0</v>
+      </c>
+      <c r="BB332">
+        <v>9</v>
+      </c>
+      <c r="BC332">
+        <v>9</v>
+      </c>
+      <c r="BD332">
+        <v>2.32</v>
+      </c>
+      <c r="BE332">
+        <v>6.75</v>
+      </c>
+      <c r="BF332">
+        <v>1.75</v>
+      </c>
+      <c r="BG332">
+        <v>1.26</v>
+      </c>
+      <c r="BH332">
+        <v>3.4</v>
+      </c>
+      <c r="BI332">
+        <v>1.46</v>
+      </c>
+      <c r="BJ332">
+        <v>2.5</v>
+      </c>
+      <c r="BK332">
+        <v>1.73</v>
+      </c>
+      <c r="BL332">
+        <v>1.98</v>
+      </c>
+      <c r="BM332">
+        <v>2.12</v>
+      </c>
+      <c r="BN332">
+        <v>1.64</v>
+      </c>
+      <c r="BO332">
+        <v>2.65</v>
+      </c>
+      <c r="BP332">
+        <v>1.4</v>
+      </c>
+    </row>
+    <row r="333" spans="1:68">
+      <c r="A333" s="1">
+        <v>332</v>
+      </c>
+      <c r="B333">
+        <v>7476898</v>
+      </c>
+      <c r="C333" t="s">
+        <v>68</v>
+      </c>
+      <c r="D333" t="s">
+        <v>69</v>
+      </c>
+      <c r="E333" s="2">
+        <v>45689.5</v>
+      </c>
+      <c r="F333">
+        <v>30</v>
+      </c>
+      <c r="G333" t="s">
+        <v>88</v>
+      </c>
+      <c r="H333" t="s">
+        <v>75</v>
+      </c>
+      <c r="I333">
+        <v>1</v>
+      </c>
+      <c r="J333">
+        <v>1</v>
+      </c>
+      <c r="K333">
+        <v>2</v>
+      </c>
+      <c r="L333">
+        <v>4</v>
+      </c>
+      <c r="M333">
+        <v>2</v>
+      </c>
+      <c r="N333">
+        <v>6</v>
+      </c>
+      <c r="O333" t="s">
+        <v>294</v>
+      </c>
+      <c r="P333" t="s">
+        <v>424</v>
+      </c>
+      <c r="Q333">
+        <v>4</v>
+      </c>
+      <c r="R333">
+        <v>2.1</v>
+      </c>
+      <c r="S333">
+        <v>2.75</v>
+      </c>
+      <c r="T333">
+        <v>1.4</v>
+      </c>
+      <c r="U333">
+        <v>2.75</v>
+      </c>
+      <c r="V333">
+        <v>3</v>
+      </c>
+      <c r="W333">
+        <v>1.36</v>
+      </c>
+      <c r="X333">
+        <v>8</v>
+      </c>
+      <c r="Y333">
+        <v>1.08</v>
+      </c>
+      <c r="Z333">
+        <v>3.38</v>
+      </c>
+      <c r="AA333">
+        <v>3.38</v>
+      </c>
+      <c r="AB333">
+        <v>2.09</v>
+      </c>
+      <c r="AC333">
+        <v>1.06</v>
+      </c>
+      <c r="AD333">
+        <v>8.5</v>
+      </c>
+      <c r="AE333">
+        <v>1.3</v>
+      </c>
+      <c r="AF333">
+        <v>3.35</v>
+      </c>
+      <c r="AG333">
+        <v>1.92</v>
+      </c>
+      <c r="AH333">
+        <v>1.82</v>
+      </c>
+      <c r="AI333">
+        <v>1.73</v>
+      </c>
+      <c r="AJ333">
+        <v>2</v>
+      </c>
+      <c r="AK333">
+        <v>1.7</v>
+      </c>
+      <c r="AL333">
+        <v>1.25</v>
+      </c>
+      <c r="AM333">
+        <v>1.3</v>
+      </c>
+      <c r="AN333">
+        <v>0.5</v>
+      </c>
+      <c r="AO333">
+        <v>1.27</v>
+      </c>
+      <c r="AP333">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="AQ333">
+        <v>1.17</v>
+      </c>
+      <c r="AR333">
+        <v>1.34</v>
+      </c>
+      <c r="AS333">
+        <v>1.15</v>
+      </c>
+      <c r="AT333">
+        <v>2.49</v>
+      </c>
+      <c r="AU333">
+        <v>7</v>
+      </c>
+      <c r="AV333">
+        <v>7</v>
+      </c>
+      <c r="AW333">
+        <v>11</v>
+      </c>
+      <c r="AX333">
+        <v>6</v>
+      </c>
+      <c r="AY333">
+        <v>18</v>
+      </c>
+      <c r="AZ333">
+        <v>13</v>
+      </c>
+      <c r="BA333">
+        <v>1</v>
+      </c>
+      <c r="BB333">
+        <v>3</v>
+      </c>
+      <c r="BC333">
+        <v>4</v>
+      </c>
+      <c r="BD333">
+        <v>2.3</v>
+      </c>
+      <c r="BE333">
+        <v>6.75</v>
+      </c>
+      <c r="BF333">
+        <v>1.75</v>
+      </c>
+      <c r="BG333">
+        <v>1.2</v>
+      </c>
+      <c r="BH333">
+        <v>3.95</v>
+      </c>
+      <c r="BI333">
+        <v>1.36</v>
+      </c>
+      <c r="BJ333">
+        <v>2.85</v>
+      </c>
+      <c r="BK333">
+        <v>1.58</v>
+      </c>
+      <c r="BL333">
+        <v>2.18</v>
+      </c>
+      <c r="BM333">
+        <v>1.92</v>
+      </c>
+      <c r="BN333">
+        <v>1.88</v>
+      </c>
+      <c r="BO333">
+        <v>2.4</v>
+      </c>
+      <c r="BP333">
+        <v>1.49</v>
+      </c>
+    </row>
+    <row r="334" spans="1:68">
+      <c r="A334" s="1">
+        <v>333</v>
+      </c>
+      <c r="B334">
+        <v>7476897</v>
+      </c>
+      <c r="C334" t="s">
+        <v>68</v>
+      </c>
+      <c r="D334" t="s">
+        <v>69</v>
+      </c>
+      <c r="E334" s="2">
+        <v>45689.5</v>
+      </c>
+      <c r="F334">
+        <v>30</v>
+      </c>
+      <c r="G334" t="s">
+        <v>77</v>
+      </c>
+      <c r="H334" t="s">
+        <v>86</v>
+      </c>
+      <c r="I334">
+        <v>1</v>
+      </c>
+      <c r="J334">
+        <v>0</v>
+      </c>
+      <c r="K334">
+        <v>1</v>
+      </c>
+      <c r="L334">
+        <v>1</v>
+      </c>
+      <c r="M334">
+        <v>1</v>
+      </c>
+      <c r="N334">
+        <v>2</v>
+      </c>
+      <c r="O334" t="s">
+        <v>124</v>
+      </c>
+      <c r="P334" t="s">
+        <v>201</v>
+      </c>
+      <c r="Q334">
+        <v>4.5</v>
+      </c>
+      <c r="R334">
+        <v>2.05</v>
+      </c>
+      <c r="S334">
+        <v>2.75</v>
+      </c>
+      <c r="T334">
+        <v>1.5</v>
+      </c>
+      <c r="U334">
+        <v>2.5</v>
+      </c>
+      <c r="V334">
+        <v>3.4</v>
+      </c>
+      <c r="W334">
+        <v>1.3</v>
+      </c>
+      <c r="X334">
+        <v>10</v>
+      </c>
+      <c r="Y334">
+        <v>1.06</v>
+      </c>
+      <c r="Z334">
+        <v>3.56</v>
+      </c>
+      <c r="AA334">
+        <v>3.36</v>
+      </c>
+      <c r="AB334">
+        <v>2.03</v>
+      </c>
+      <c r="AC334">
+        <v>1.07</v>
+      </c>
+      <c r="AD334">
+        <v>8</v>
+      </c>
+      <c r="AE334">
+        <v>1.4</v>
+      </c>
+      <c r="AF334">
+        <v>2.88</v>
+      </c>
+      <c r="AG334">
+        <v>2.2</v>
+      </c>
+      <c r="AH334">
+        <v>1.6</v>
+      </c>
+      <c r="AI334">
+        <v>2</v>
+      </c>
+      <c r="AJ334">
+        <v>1.73</v>
+      </c>
+      <c r="AK334">
+        <v>1.7</v>
+      </c>
+      <c r="AL334">
+        <v>1.25</v>
+      </c>
+      <c r="AM334">
+        <v>1.28</v>
+      </c>
+      <c r="AN334">
+        <v>1.14</v>
+      </c>
+      <c r="AO334">
+        <v>1.5</v>
+      </c>
+      <c r="AP334">
+        <v>1.13</v>
+      </c>
+      <c r="AQ334">
+        <v>1.47</v>
+      </c>
+      <c r="AR334">
+        <v>1.08</v>
+      </c>
+      <c r="AS334">
+        <v>1.12</v>
+      </c>
+      <c r="AT334">
+        <v>2.2</v>
+      </c>
+      <c r="AU334">
+        <v>3</v>
+      </c>
+      <c r="AV334">
+        <v>4</v>
+      </c>
+      <c r="AW334">
+        <v>9</v>
+      </c>
+      <c r="AX334">
+        <v>5</v>
+      </c>
+      <c r="AY334">
+        <v>14</v>
+      </c>
+      <c r="AZ334">
+        <v>13</v>
+      </c>
+      <c r="BA334">
+        <v>4</v>
+      </c>
+      <c r="BB334">
+        <v>4</v>
+      </c>
+      <c r="BC334">
+        <v>8</v>
+      </c>
+      <c r="BD334">
+        <v>2.32</v>
+      </c>
+      <c r="BE334">
+        <v>6.75</v>
+      </c>
+      <c r="BF334">
+        <v>1.72</v>
+      </c>
+      <c r="BG334">
+        <v>1.24</v>
+      </c>
+      <c r="BH334">
+        <v>3.55</v>
+      </c>
+      <c r="BI334">
+        <v>1.44</v>
+      </c>
+      <c r="BJ334">
+        <v>2.55</v>
+      </c>
+      <c r="BK334">
+        <v>1.71</v>
+      </c>
+      <c r="BL334">
+        <v>2</v>
+      </c>
+      <c r="BM334">
+        <v>2.08</v>
+      </c>
+      <c r="BN334">
+        <v>1.65</v>
+      </c>
+      <c r="BO334">
+        <v>2.65</v>
+      </c>
+      <c r="BP334">
+        <v>1.42</v>
+      </c>
+    </row>
+    <row r="335" spans="1:68">
+      <c r="A335" s="1">
+        <v>334</v>
+      </c>
+      <c r="B335">
+        <v>7476893</v>
+      </c>
+      <c r="C335" t="s">
+        <v>68</v>
+      </c>
+      <c r="D335" t="s">
+        <v>69</v>
+      </c>
+      <c r="E335" s="2">
+        <v>45689.5</v>
+      </c>
+      <c r="F335">
+        <v>30</v>
+      </c>
+      <c r="G335" t="s">
+        <v>82</v>
+      </c>
+      <c r="H335" t="s">
+        <v>91</v>
+      </c>
+      <c r="I335">
+        <v>0</v>
+      </c>
+      <c r="J335">
+        <v>1</v>
+      </c>
+      <c r="K335">
+        <v>1</v>
+      </c>
+      <c r="L335">
+        <v>1</v>
+      </c>
+      <c r="M335">
+        <v>5</v>
+      </c>
+      <c r="N335">
+        <v>6</v>
+      </c>
+      <c r="O335" t="s">
+        <v>295</v>
+      </c>
+      <c r="P335" t="s">
+        <v>425</v>
+      </c>
+      <c r="Q335">
+        <v>3.1</v>
+      </c>
+      <c r="R335">
+        <v>2.1</v>
+      </c>
+      <c r="S335">
+        <v>3.4</v>
+      </c>
+      <c r="T335">
+        <v>1.4</v>
+      </c>
+      <c r="U335">
+        <v>2.75</v>
+      </c>
+      <c r="V335">
+        <v>3</v>
+      </c>
+      <c r="W335">
+        <v>1.36</v>
+      </c>
+      <c r="X335">
+        <v>8</v>
+      </c>
+      <c r="Y335">
+        <v>1.08</v>
+      </c>
+      <c r="Z335">
+        <v>2.25</v>
+      </c>
+      <c r="AA335">
+        <v>3.3</v>
+      </c>
+      <c r="AB335">
+        <v>3.1</v>
+      </c>
+      <c r="AC335">
+        <v>1.06</v>
+      </c>
+      <c r="AD335">
+        <v>8.5</v>
+      </c>
+      <c r="AE335">
+        <v>1.3</v>
+      </c>
+      <c r="AF335">
+        <v>3.4</v>
+      </c>
+      <c r="AG335">
+        <v>1.92</v>
+      </c>
+      <c r="AH335">
+        <v>1.82</v>
+      </c>
+      <c r="AI335">
+        <v>1.73</v>
+      </c>
+      <c r="AJ335">
+        <v>2</v>
+      </c>
+      <c r="AK335">
+        <v>1.38</v>
+      </c>
+      <c r="AL335">
+        <v>1.25</v>
+      </c>
+      <c r="AM335">
+        <v>1.55</v>
+      </c>
+      <c r="AN335">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="AO335">
+        <v>0.87</v>
+      </c>
+      <c r="AP335">
+        <v>0.64</v>
+      </c>
+      <c r="AQ335">
+        <v>1</v>
+      </c>
+      <c r="AR335">
+        <v>1.3</v>
+      </c>
+      <c r="AS335">
+        <v>1.09</v>
+      </c>
+      <c r="AT335">
+        <v>2.39</v>
+      </c>
+      <c r="AU335">
+        <v>6</v>
+      </c>
+      <c r="AV335">
+        <v>9</v>
+      </c>
+      <c r="AW335">
+        <v>10</v>
+      </c>
+      <c r="AX335">
+        <v>6</v>
+      </c>
+      <c r="AY335">
+        <v>21</v>
+      </c>
+      <c r="AZ335">
+        <v>19</v>
+      </c>
+      <c r="BA335">
+        <v>11</v>
+      </c>
+      <c r="BB335">
+        <v>7</v>
+      </c>
+      <c r="BC335">
+        <v>18</v>
+      </c>
+      <c r="BD335">
+        <v>1.97</v>
+      </c>
+      <c r="BE335">
+        <v>6.4</v>
+      </c>
+      <c r="BF335">
+        <v>2.05</v>
+      </c>
+      <c r="BG335">
+        <v>1.26</v>
+      </c>
+      <c r="BH335">
+        <v>3.4</v>
+      </c>
+      <c r="BI335">
+        <v>1.46</v>
+      </c>
+      <c r="BJ335">
+        <v>2.48</v>
+      </c>
+      <c r="BK335">
+        <v>1.8</v>
+      </c>
+      <c r="BL335">
+        <v>2</v>
+      </c>
+      <c r="BM335">
+        <v>2.15</v>
+      </c>
+      <c r="BN335">
+        <v>1.61</v>
+      </c>
+      <c r="BO335">
+        <v>2.7</v>
+      </c>
+      <c r="BP335">
+        <v>1.38</v>
+      </c>
+    </row>
+    <row r="336" spans="1:68">
+      <c r="A336" s="1">
+        <v>335</v>
+      </c>
+      <c r="B336">
+        <v>7476892</v>
+      </c>
+      <c r="C336" t="s">
+        <v>68</v>
+      </c>
+      <c r="D336" t="s">
+        <v>69</v>
+      </c>
+      <c r="E336" s="2">
+        <v>45689.5</v>
+      </c>
+      <c r="F336">
+        <v>30</v>
+      </c>
+      <c r="G336" t="s">
+        <v>83</v>
+      </c>
+      <c r="H336" t="s">
+        <v>87</v>
+      </c>
+      <c r="I336">
+        <v>0</v>
+      </c>
+      <c r="J336">
+        <v>0</v>
+      </c>
+      <c r="K336">
+        <v>0</v>
+      </c>
+      <c r="L336">
+        <v>0</v>
+      </c>
+      <c r="M336">
+        <v>2</v>
+      </c>
+      <c r="N336">
+        <v>2</v>
+      </c>
+      <c r="O336" t="s">
+        <v>101</v>
+      </c>
+      <c r="P336" t="s">
+        <v>426</v>
+      </c>
+      <c r="Q336">
+        <v>2.63</v>
+      </c>
+      <c r="R336">
+        <v>2.25</v>
+      </c>
+      <c r="S336">
+        <v>3.75</v>
+      </c>
+      <c r="T336">
+        <v>1.36</v>
+      </c>
+      <c r="U336">
+        <v>3</v>
+      </c>
+      <c r="V336">
+        <v>2.63</v>
+      </c>
+      <c r="W336">
+        <v>1.44</v>
+      </c>
+      <c r="X336">
+        <v>7</v>
+      </c>
+      <c r="Y336">
+        <v>1.1</v>
+      </c>
+      <c r="Z336">
+        <v>2.05</v>
+      </c>
+      <c r="AA336">
+        <v>3.3</v>
+      </c>
+      <c r="AB336">
+        <v>3.59</v>
+      </c>
+      <c r="AC336">
+        <v>1.05</v>
+      </c>
+      <c r="AD336">
+        <v>9</v>
+      </c>
+      <c r="AE336">
+        <v>1.25</v>
+      </c>
+      <c r="AF336">
+        <v>3.7</v>
+      </c>
+      <c r="AG336">
+        <v>1.77</v>
+      </c>
+      <c r="AH336">
+        <v>1.98</v>
+      </c>
+      <c r="AI336">
+        <v>1.62</v>
+      </c>
+      <c r="AJ336">
+        <v>2.2</v>
+      </c>
+      <c r="AK336">
+        <v>1.28</v>
+      </c>
+      <c r="AL336">
+        <v>1.25</v>
+      </c>
+      <c r="AM336">
+        <v>1.73</v>
+      </c>
+      <c r="AN336">
+        <v>1.15</v>
+      </c>
+      <c r="AO336">
+        <v>1.36</v>
+      </c>
+      <c r="AP336">
+        <v>1.07</v>
+      </c>
+      <c r="AQ336">
+        <v>1.47</v>
+      </c>
+      <c r="AR336">
+        <v>1.49</v>
+      </c>
+      <c r="AS336">
+        <v>1.2</v>
+      </c>
+      <c r="AT336">
+        <v>2.69</v>
+      </c>
+      <c r="AU336">
+        <v>3</v>
+      </c>
+      <c r="AV336">
+        <v>5</v>
+      </c>
+      <c r="AW336">
+        <v>14</v>
+      </c>
+      <c r="AX336">
+        <v>8</v>
+      </c>
+      <c r="AY336">
+        <v>23</v>
+      </c>
+      <c r="AZ336">
+        <v>17</v>
+      </c>
+      <c r="BA336">
+        <v>12</v>
+      </c>
+      <c r="BB336">
+        <v>4</v>
+      </c>
+      <c r="BC336">
+        <v>16</v>
+      </c>
+      <c r="BD336">
+        <v>1.74</v>
+      </c>
+      <c r="BE336">
+        <v>6.75</v>
+      </c>
+      <c r="BF336">
+        <v>2.32</v>
+      </c>
+      <c r="BG336">
+        <v>1.29</v>
+      </c>
+      <c r="BH336">
+        <v>3.2</v>
+      </c>
+      <c r="BI336">
+        <v>1.5</v>
+      </c>
+      <c r="BJ336">
+        <v>2.4</v>
+      </c>
+      <c r="BK336">
+        <v>1.8</v>
+      </c>
+      <c r="BL336">
+        <v>1.89</v>
+      </c>
+      <c r="BM336">
+        <v>2.25</v>
+      </c>
+      <c r="BN336">
+        <v>1.55</v>
+      </c>
+      <c r="BO336">
+        <v>2.9</v>
+      </c>
+      <c r="BP336">
+        <v>1.34</v>
+      </c>
+    </row>
+    <row r="337" spans="1:68">
+      <c r="A337" s="1">
+        <v>336</v>
+      </c>
+      <c r="B337">
+        <v>7476891</v>
+      </c>
+      <c r="C337" t="s">
+        <v>68</v>
+      </c>
+      <c r="D337" t="s">
+        <v>69</v>
+      </c>
+      <c r="E337" s="2">
+        <v>45689.5</v>
+      </c>
+      <c r="F337">
+        <v>30</v>
+      </c>
+      <c r="G337" t="s">
+        <v>71</v>
+      </c>
+      <c r="H337" t="s">
+        <v>92</v>
+      </c>
+      <c r="I337">
+        <v>1</v>
+      </c>
+      <c r="J337">
+        <v>0</v>
+      </c>
+      <c r="K337">
+        <v>1</v>
+      </c>
+      <c r="L337">
+        <v>1</v>
+      </c>
+      <c r="M337">
+        <v>0</v>
+      </c>
+      <c r="N337">
+        <v>1</v>
+      </c>
+      <c r="O337" t="s">
+        <v>111</v>
+      </c>
+      <c r="P337" t="s">
+        <v>101</v>
+      </c>
+      <c r="Q337">
+        <v>3</v>
+      </c>
+      <c r="R337">
+        <v>2.05</v>
+      </c>
+      <c r="S337">
+        <v>4</v>
+      </c>
+      <c r="T337">
+        <v>1.44</v>
+      </c>
+      <c r="U337">
+        <v>2.63</v>
+      </c>
+      <c r="V337">
+        <v>3.4</v>
+      </c>
+      <c r="W337">
+        <v>1.3</v>
+      </c>
+      <c r="X337">
+        <v>10</v>
+      </c>
+      <c r="Y337">
+        <v>1.06</v>
+      </c>
+      <c r="Z337">
+        <v>2.23</v>
+      </c>
+      <c r="AA337">
+        <v>3.27</v>
+      </c>
+      <c r="AB337">
+        <v>3.17</v>
+      </c>
+      <c r="AC337">
+        <v>1.07</v>
+      </c>
+      <c r="AD337">
+        <v>8</v>
+      </c>
+      <c r="AE337">
+        <v>1.38</v>
+      </c>
+      <c r="AF337">
+        <v>3</v>
+      </c>
+      <c r="AG337">
+        <v>2.13</v>
+      </c>
+      <c r="AH337">
+        <v>1.65</v>
+      </c>
+      <c r="AI337">
+        <v>1.83</v>
+      </c>
+      <c r="AJ337">
+        <v>1.83</v>
+      </c>
+      <c r="AK337">
+        <v>1.33</v>
+      </c>
+      <c r="AL337">
+        <v>1.28</v>
+      </c>
+      <c r="AM337">
+        <v>1.62</v>
+      </c>
+      <c r="AN337">
+        <v>2.08</v>
+      </c>
+      <c r="AO337">
+        <v>1.08</v>
+      </c>
+      <c r="AP337">
+        <v>2.14</v>
+      </c>
+      <c r="AQ337">
+        <v>1</v>
+      </c>
+      <c r="AR337">
+        <v>1.4</v>
+      </c>
+      <c r="AS337">
+        <v>1.26</v>
+      </c>
+      <c r="AT337">
+        <v>2.66</v>
+      </c>
+      <c r="AU337">
+        <v>4</v>
+      </c>
+      <c r="AV337">
+        <v>3</v>
+      </c>
+      <c r="AW337">
+        <v>10</v>
+      </c>
+      <c r="AX337">
+        <v>3</v>
+      </c>
+      <c r="AY337">
+        <v>16</v>
+      </c>
+      <c r="AZ337">
+        <v>10</v>
+      </c>
+      <c r="BA337">
+        <v>3</v>
+      </c>
+      <c r="BB337">
+        <v>5</v>
+      </c>
+      <c r="BC337">
+        <v>8</v>
+      </c>
+      <c r="BD337">
+        <v>1.78</v>
+      </c>
+      <c r="BE337">
+        <v>6.5</v>
+      </c>
+      <c r="BF337">
+        <v>2.23</v>
+      </c>
+      <c r="BG337">
+        <v>1.3</v>
+      </c>
+      <c r="BH337">
+        <v>3.05</v>
+      </c>
+      <c r="BI337">
+        <v>1.53</v>
+      </c>
+      <c r="BJ337">
+        <v>2.3</v>
+      </c>
+      <c r="BK337">
+        <v>1.8</v>
+      </c>
+      <c r="BL337">
+        <v>2</v>
+      </c>
+      <c r="BM337">
+        <v>2.35</v>
+      </c>
+      <c r="BN337">
+        <v>1.5</v>
+      </c>
+      <c r="BO337">
+        <v>3.05</v>
+      </c>
+      <c r="BP337">
+        <v>1.32</v>
+      </c>
+    </row>
+    <row r="338" spans="1:68">
+      <c r="A338" s="1">
+        <v>337</v>
+      </c>
+      <c r="B338">
+        <v>7476895</v>
+      </c>
+      <c r="C338" t="s">
+        <v>68</v>
+      </c>
+      <c r="D338" t="s">
+        <v>69</v>
+      </c>
+      <c r="E338" s="2">
+        <v>45689.5</v>
+      </c>
+      <c r="F338">
+        <v>30</v>
+      </c>
+      <c r="G338" t="s">
+        <v>74</v>
+      </c>
+      <c r="H338" t="s">
+        <v>78</v>
+      </c>
+      <c r="I338">
+        <v>1</v>
+      </c>
+      <c r="J338">
+        <v>0</v>
+      </c>
+      <c r="K338">
+        <v>1</v>
+      </c>
+      <c r="L338">
+        <v>2</v>
+      </c>
+      <c r="M338">
+        <v>1</v>
+      </c>
+      <c r="N338">
+        <v>3</v>
+      </c>
+      <c r="O338" t="s">
+        <v>296</v>
+      </c>
+      <c r="P338" t="s">
+        <v>201</v>
+      </c>
+      <c r="Q338">
+        <v>2.75</v>
+      </c>
+      <c r="R338">
+        <v>2.25</v>
+      </c>
+      <c r="S338">
+        <v>3.75</v>
+      </c>
+      <c r="T338">
+        <v>1.36</v>
+      </c>
+      <c r="U338">
+        <v>3</v>
+      </c>
+      <c r="V338">
+        <v>2.63</v>
+      </c>
+      <c r="W338">
+        <v>1.44</v>
+      </c>
+      <c r="X338">
+        <v>7</v>
+      </c>
+      <c r="Y338">
+        <v>1.1</v>
+      </c>
+      <c r="Z338">
+        <v>2.09</v>
+      </c>
+      <c r="AA338">
+        <v>3.38</v>
+      </c>
+      <c r="AB338">
+        <v>3.38</v>
+      </c>
+      <c r="AC338">
+        <v>1.05</v>
+      </c>
+      <c r="AD338">
+        <v>9</v>
+      </c>
+      <c r="AE338">
+        <v>1.25</v>
+      </c>
+      <c r="AF338">
+        <v>3.7</v>
+      </c>
+      <c r="AG338">
+        <v>1.77</v>
+      </c>
+      <c r="AH338">
+        <v>1.98</v>
+      </c>
+      <c r="AI338">
+        <v>1.62</v>
+      </c>
+      <c r="AJ338">
+        <v>2.2</v>
+      </c>
+      <c r="AK338">
+        <v>1.3</v>
+      </c>
+      <c r="AL338">
+        <v>1.25</v>
+      </c>
+      <c r="AM338">
+        <v>1.7</v>
+      </c>
+      <c r="AN338">
+        <v>1.79</v>
+      </c>
+      <c r="AO338">
+        <v>1.18</v>
+      </c>
+      <c r="AP338">
+        <v>1.87</v>
+      </c>
+      <c r="AQ338">
+        <v>1.08</v>
+      </c>
+      <c r="AR338">
+        <v>1.49</v>
+      </c>
+      <c r="AS338">
+        <v>1.4</v>
+      </c>
+      <c r="AT338">
+        <v>2.89</v>
+      </c>
+      <c r="AU338">
+        <v>8</v>
+      </c>
+      <c r="AV338">
+        <v>5</v>
+      </c>
+      <c r="AW338">
+        <v>8</v>
+      </c>
+      <c r="AX338">
+        <v>5</v>
+      </c>
+      <c r="AY338">
+        <v>18</v>
+      </c>
+      <c r="AZ338">
+        <v>11</v>
+      </c>
+      <c r="BA338">
+        <v>5</v>
+      </c>
+      <c r="BB338">
+        <v>4</v>
+      </c>
+      <c r="BC338">
+        <v>9</v>
+      </c>
+      <c r="BD338">
+        <v>1.72</v>
+      </c>
+      <c r="BE338">
+        <v>6.75</v>
+      </c>
+      <c r="BF338">
+        <v>2.35</v>
+      </c>
+      <c r="BG338">
+        <v>1.3</v>
+      </c>
+      <c r="BH338">
+        <v>3.15</v>
+      </c>
+      <c r="BI338">
+        <v>1.52</v>
+      </c>
+      <c r="BJ338">
+        <v>2.33</v>
+      </c>
+      <c r="BK338">
+        <v>1.82</v>
+      </c>
+      <c r="BL338">
+        <v>1.98</v>
+      </c>
+      <c r="BM338">
+        <v>2.32</v>
+      </c>
+      <c r="BN338">
+        <v>1.52</v>
+      </c>
+      <c r="BO338">
+        <v>2.95</v>
+      </c>
+      <c r="BP338">
+        <v>1.33</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/England EFL League Two_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/England EFL League Two_20242025.xlsx
@@ -70209,13 +70209,13 @@
         <v>13</v>
       </c>
       <c r="BA333">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BB333">
         <v>3</v>
       </c>
       <c r="BC333">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="BD333">
         <v>2.3</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/England EFL League Two_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/England EFL League Two_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2102" uniqueCount="430">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2108" uniqueCount="432">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -913,6 +913,9 @@
     <t>['8', '82']</t>
   </si>
   <si>
+    <t>['11', '37', '54', '59', '90+4']</t>
+  </si>
+  <si>
     <t>['1', '9']</t>
   </si>
   <si>
@@ -1305,6 +1308,9 @@
   <si>
     <t>['13', '38', '51']</t>
   </si>
+  <si>
+    <t>['45+4', '90+3']</t>
+  </si>
 </sst>
 </file>
 
@@ -1665,7 +1671,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP340"/>
+  <dimension ref="A1:BP341"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1999,7 +2005,7 @@
         <v>0</v>
       </c>
       <c r="AP2">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AQ2">
         <v>1</v>
@@ -2127,7 +2133,7 @@
         <v>95</v>
       </c>
       <c r="P3" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="Q3">
         <v>2.5</v>
@@ -2539,7 +2545,7 @@
         <v>97</v>
       </c>
       <c r="P5" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="Q5">
         <v>2.4</v>
@@ -3363,7 +3369,7 @@
         <v>101</v>
       </c>
       <c r="P9" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="Q9">
         <v>2.75</v>
@@ -3569,7 +3575,7 @@
         <v>102</v>
       </c>
       <c r="P10" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="Q10">
         <v>2.63</v>
@@ -3775,7 +3781,7 @@
         <v>101</v>
       </c>
       <c r="P11" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="Q11">
         <v>2.88</v>
@@ -4805,7 +4811,7 @@
         <v>105</v>
       </c>
       <c r="P16" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="Q16">
         <v>2.88</v>
@@ -5217,7 +5223,7 @@
         <v>101</v>
       </c>
       <c r="P18" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="Q18">
         <v>3.4</v>
@@ -5423,7 +5429,7 @@
         <v>107</v>
       </c>
       <c r="P19" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="Q19">
         <v>3</v>
@@ -5916,7 +5922,7 @@
         <v>1.77</v>
       </c>
       <c r="AQ21">
-        <v>1.71</v>
+        <v>1.6</v>
       </c>
       <c r="AR21">
         <v>0</v>
@@ -6247,7 +6253,7 @@
         <v>101</v>
       </c>
       <c r="P23" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="Q23">
         <v>3</v>
@@ -6659,7 +6665,7 @@
         <v>109</v>
       </c>
       <c r="P25" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="Q25">
         <v>2.63</v>
@@ -6865,7 +6871,7 @@
         <v>110</v>
       </c>
       <c r="P26" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="Q26">
         <v>2.38</v>
@@ -7689,7 +7695,7 @@
         <v>112</v>
       </c>
       <c r="P30" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="Q30">
         <v>3</v>
@@ -8385,7 +8391,7 @@
         <v>1</v>
       </c>
       <c r="AP33">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AQ33">
         <v>1.36</v>
@@ -9131,7 +9137,7 @@
         <v>101</v>
       </c>
       <c r="P37" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="Q37">
         <v>2.6</v>
@@ -9337,7 +9343,7 @@
         <v>117</v>
       </c>
       <c r="P38" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="Q38">
         <v>2.88</v>
@@ -9418,7 +9424,7 @@
         <v>1.77</v>
       </c>
       <c r="AQ38">
-        <v>1.71</v>
+        <v>1.6</v>
       </c>
       <c r="AR38">
         <v>0</v>
@@ -9749,7 +9755,7 @@
         <v>119</v>
       </c>
       <c r="P40" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="Q40">
         <v>3</v>
@@ -10161,7 +10167,7 @@
         <v>101</v>
       </c>
       <c r="P42" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="Q42">
         <v>3.75</v>
@@ -10573,7 +10579,7 @@
         <v>121</v>
       </c>
       <c r="P44" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="Q44">
         <v>2.75</v>
@@ -10779,7 +10785,7 @@
         <v>122</v>
       </c>
       <c r="P45" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="Q45">
         <v>2.63</v>
@@ -11397,7 +11403,7 @@
         <v>125</v>
       </c>
       <c r="P48" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="Q48">
         <v>3.5</v>
@@ -11809,7 +11815,7 @@
         <v>127</v>
       </c>
       <c r="P50" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="Q50">
         <v>3.6</v>
@@ -12015,7 +12021,7 @@
         <v>103</v>
       </c>
       <c r="P51" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="Q51">
         <v>2.5</v>
@@ -12505,7 +12511,7 @@
         <v>0</v>
       </c>
       <c r="AP53">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AQ53">
         <v>1.47</v>
@@ -13950,7 +13956,7 @@
         <v>1.13</v>
       </c>
       <c r="AQ60">
-        <v>1.71</v>
+        <v>1.6</v>
       </c>
       <c r="AR60">
         <v>1.11</v>
@@ -14693,7 +14699,7 @@
         <v>139</v>
       </c>
       <c r="P64" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="Q64">
         <v>3</v>
@@ -15105,7 +15111,7 @@
         <v>141</v>
       </c>
       <c r="P66" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="Q66">
         <v>3.75</v>
@@ -15723,7 +15729,7 @@
         <v>143</v>
       </c>
       <c r="P69" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="Q69">
         <v>3.2</v>
@@ -15929,7 +15935,7 @@
         <v>144</v>
       </c>
       <c r="P70" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="Q70">
         <v>3.25</v>
@@ -16135,7 +16141,7 @@
         <v>145</v>
       </c>
       <c r="P71" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="Q71">
         <v>3</v>
@@ -16341,7 +16347,7 @@
         <v>146</v>
       </c>
       <c r="P72" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="Q72">
         <v>4</v>
@@ -16625,7 +16631,7 @@
         <v>0</v>
       </c>
       <c r="AP73">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AQ73">
         <v>0.85</v>
@@ -16753,7 +16759,7 @@
         <v>101</v>
       </c>
       <c r="P74" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="Q74">
         <v>2.63</v>
@@ -16959,7 +16965,7 @@
         <v>101</v>
       </c>
       <c r="P75" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="Q75">
         <v>3.4</v>
@@ -17165,7 +17171,7 @@
         <v>101</v>
       </c>
       <c r="P76" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="Q76">
         <v>2.6</v>
@@ -17577,7 +17583,7 @@
         <v>149</v>
       </c>
       <c r="P78" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="Q78">
         <v>2.88</v>
@@ -17658,7 +17664,7 @@
         <v>1.56</v>
       </c>
       <c r="AQ78">
-        <v>1.71</v>
+        <v>1.6</v>
       </c>
       <c r="AR78">
         <v>1.48</v>
@@ -18607,7 +18613,7 @@
         <v>153</v>
       </c>
       <c r="P83" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="Q83">
         <v>2.2</v>
@@ -19843,7 +19849,7 @@
         <v>157</v>
       </c>
       <c r="P89" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="Q89">
         <v>3.75</v>
@@ -20255,7 +20261,7 @@
         <v>101</v>
       </c>
       <c r="P91" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="Q91">
         <v>2.75</v>
@@ -20461,7 +20467,7 @@
         <v>101</v>
       </c>
       <c r="P92" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="Q92">
         <v>3.4</v>
@@ -20667,7 +20673,7 @@
         <v>159</v>
       </c>
       <c r="P93" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="Q93">
         <v>2.75</v>
@@ -21079,7 +21085,7 @@
         <v>161</v>
       </c>
       <c r="P95" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="Q95">
         <v>2.5</v>
@@ -21285,7 +21291,7 @@
         <v>162</v>
       </c>
       <c r="P96" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="Q96">
         <v>4.5</v>
@@ -22109,7 +22115,7 @@
         <v>166</v>
       </c>
       <c r="P100" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="Q100">
         <v>2.75</v>
@@ -22521,7 +22527,7 @@
         <v>167</v>
       </c>
       <c r="P102" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="Q102">
         <v>2.88</v>
@@ -22727,7 +22733,7 @@
         <v>101</v>
       </c>
       <c r="P103" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="Q103">
         <v>3</v>
@@ -22933,7 +22939,7 @@
         <v>168</v>
       </c>
       <c r="P104" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="Q104">
         <v>4</v>
@@ -23345,7 +23351,7 @@
         <v>101</v>
       </c>
       <c r="P106" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="Q106">
         <v>3.6</v>
@@ -23426,7 +23432,7 @@
         <v>1.43</v>
       </c>
       <c r="AQ106">
-        <v>1.71</v>
+        <v>1.6</v>
       </c>
       <c r="AR106">
         <v>1.16</v>
@@ -24787,7 +24793,7 @@
         <v>172</v>
       </c>
       <c r="P113" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="Q113">
         <v>2.6</v>
@@ -24865,7 +24871,7 @@
         <v>1.5</v>
       </c>
       <c r="AP113">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AQ113">
         <v>1.77</v>
@@ -24993,7 +24999,7 @@
         <v>173</v>
       </c>
       <c r="P114" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="Q114">
         <v>2.4</v>
@@ -25817,7 +25823,7 @@
         <v>176</v>
       </c>
       <c r="P118" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="Q118">
         <v>2.5</v>
@@ -25895,7 +25901,7 @@
         <v>2.2</v>
       </c>
       <c r="AP118">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AQ118">
         <v>1.73</v>
@@ -26023,7 +26029,7 @@
         <v>101</v>
       </c>
       <c r="P119" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="Q119">
         <v>3.4</v>
@@ -26229,7 +26235,7 @@
         <v>94</v>
       </c>
       <c r="P120" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="Q120">
         <v>2.88</v>
@@ -26847,7 +26853,7 @@
         <v>178</v>
       </c>
       <c r="P123" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="Q123">
         <v>2.38</v>
@@ -27259,7 +27265,7 @@
         <v>101</v>
       </c>
       <c r="P125" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="Q125">
         <v>2.1</v>
@@ -27671,7 +27677,7 @@
         <v>180</v>
       </c>
       <c r="P127" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="Q127">
         <v>3.25</v>
@@ -27877,7 +27883,7 @@
         <v>101</v>
       </c>
       <c r="P128" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="Q128">
         <v>4.75</v>
@@ -28495,7 +28501,7 @@
         <v>182</v>
       </c>
       <c r="P131" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="Q131">
         <v>2.63</v>
@@ -28701,7 +28707,7 @@
         <v>183</v>
       </c>
       <c r="P132" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="Q132">
         <v>3.5</v>
@@ -28782,7 +28788,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ132">
-        <v>1.71</v>
+        <v>1.6</v>
       </c>
       <c r="AR132">
         <v>1.44</v>
@@ -29113,7 +29119,7 @@
         <v>185</v>
       </c>
       <c r="P134" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="Q134">
         <v>4</v>
@@ -29319,7 +29325,7 @@
         <v>147</v>
       </c>
       <c r="P135" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="Q135">
         <v>2.6</v>
@@ -29525,7 +29531,7 @@
         <v>186</v>
       </c>
       <c r="P136" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="Q136">
         <v>3.6</v>
@@ -29731,7 +29737,7 @@
         <v>187</v>
       </c>
       <c r="P137" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="Q137">
         <v>3</v>
@@ -30143,7 +30149,7 @@
         <v>185</v>
       </c>
       <c r="P139" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="Q139">
         <v>2.5</v>
@@ -30349,7 +30355,7 @@
         <v>189</v>
       </c>
       <c r="P140" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="Q140">
         <v>2.25</v>
@@ -31173,7 +31179,7 @@
         <v>101</v>
       </c>
       <c r="P144" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="Q144">
         <v>2.25</v>
@@ -31791,7 +31797,7 @@
         <v>101</v>
       </c>
       <c r="P147" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="Q147">
         <v>3</v>
@@ -32615,7 +32621,7 @@
         <v>193</v>
       </c>
       <c r="P151" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="Q151">
         <v>2.4</v>
@@ -32693,7 +32699,7 @@
         <v>0.6</v>
       </c>
       <c r="AP151">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AQ151">
         <v>1.21</v>
@@ -32821,7 +32827,7 @@
         <v>194</v>
       </c>
       <c r="P152" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="Q152">
         <v>4.5</v>
@@ -33027,7 +33033,7 @@
         <v>195</v>
       </c>
       <c r="P153" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="Q153">
         <v>2.75</v>
@@ -33439,7 +33445,7 @@
         <v>197</v>
       </c>
       <c r="P155" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="Q155">
         <v>3</v>
@@ -33851,7 +33857,7 @@
         <v>198</v>
       </c>
       <c r="P157" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="Q157">
         <v>3.4</v>
@@ -34469,7 +34475,7 @@
         <v>200</v>
       </c>
       <c r="P160" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="Q160">
         <v>3.2</v>
@@ -34550,7 +34556,7 @@
         <v>2.36</v>
       </c>
       <c r="AQ160">
-        <v>1.71</v>
+        <v>1.6</v>
       </c>
       <c r="AR160">
         <v>1.54</v>
@@ -35293,7 +35299,7 @@
         <v>203</v>
       </c>
       <c r="P164" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="Q164">
         <v>2.4</v>
@@ -35705,7 +35711,7 @@
         <v>204</v>
       </c>
       <c r="P166" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="Q166">
         <v>2.88</v>
@@ -36117,7 +36123,7 @@
         <v>206</v>
       </c>
       <c r="P168" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="Q168">
         <v>2.3</v>
@@ -36529,7 +36535,7 @@
         <v>208</v>
       </c>
       <c r="P170" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="Q170">
         <v>2.5</v>
@@ -37147,7 +37153,7 @@
         <v>101</v>
       </c>
       <c r="P173" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="Q173">
         <v>2.1</v>
@@ -37225,7 +37231,7 @@
         <v>0.5</v>
       </c>
       <c r="AP173">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AQ173">
         <v>1</v>
@@ -37353,7 +37359,7 @@
         <v>148</v>
       </c>
       <c r="P174" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="Q174">
         <v>3.2</v>
@@ -38383,7 +38389,7 @@
         <v>210</v>
       </c>
       <c r="P179" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="Q179">
         <v>2.3</v>
@@ -39413,7 +39419,7 @@
         <v>185</v>
       </c>
       <c r="P184" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="Q184">
         <v>3.4</v>
@@ -39619,7 +39625,7 @@
         <v>215</v>
       </c>
       <c r="P185" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="Q185">
         <v>3.2</v>
@@ -40031,7 +40037,7 @@
         <v>217</v>
       </c>
       <c r="P187" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="Q187">
         <v>2.2</v>
@@ -40649,7 +40655,7 @@
         <v>101</v>
       </c>
       <c r="P190" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="Q190">
         <v>3.25</v>
@@ -40855,7 +40861,7 @@
         <v>148</v>
       </c>
       <c r="P191" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="Q191">
         <v>2.3</v>
@@ -41061,7 +41067,7 @@
         <v>219</v>
       </c>
       <c r="P192" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="Q192">
         <v>2.4</v>
@@ -41554,7 +41560,7 @@
         <v>0.64</v>
       </c>
       <c r="AQ194">
-        <v>1.71</v>
+        <v>1.6</v>
       </c>
       <c r="AR194">
         <v>1.51</v>
@@ -41757,7 +41763,7 @@
         <v>1</v>
       </c>
       <c r="AP195">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AQ195">
         <v>0.64</v>
@@ -42091,7 +42097,7 @@
         <v>101</v>
       </c>
       <c r="P197" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="Q197">
         <v>3.75</v>
@@ -42297,7 +42303,7 @@
         <v>221</v>
       </c>
       <c r="P198" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="Q198">
         <v>2.2</v>
@@ -42503,7 +42509,7 @@
         <v>122</v>
       </c>
       <c r="P199" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="Q199">
         <v>3.4</v>
@@ -42915,7 +42921,7 @@
         <v>222</v>
       </c>
       <c r="P201" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="Q201">
         <v>2.85</v>
@@ -43121,7 +43127,7 @@
         <v>223</v>
       </c>
       <c r="P202" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="Q202">
         <v>1.8</v>
@@ -43327,7 +43333,7 @@
         <v>205</v>
       </c>
       <c r="P203" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="Q203">
         <v>2.75</v>
@@ -43533,7 +43539,7 @@
         <v>224</v>
       </c>
       <c r="P204" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="Q204">
         <v>3.55</v>
@@ -44357,7 +44363,7 @@
         <v>228</v>
       </c>
       <c r="P208" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="Q208">
         <v>2.4</v>
@@ -44563,7 +44569,7 @@
         <v>229</v>
       </c>
       <c r="P209" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="Q209">
         <v>2.5</v>
@@ -44975,7 +44981,7 @@
         <v>231</v>
       </c>
       <c r="P211" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="Q211">
         <v>3.5</v>
@@ -45056,7 +45062,7 @@
         <v>1.47</v>
       </c>
       <c r="AQ211">
-        <v>1.71</v>
+        <v>1.6</v>
       </c>
       <c r="AR211">
         <v>1.39</v>
@@ -45671,7 +45677,7 @@
         <v>1</v>
       </c>
       <c r="AP214">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AQ214">
         <v>0.57</v>
@@ -45799,7 +45805,7 @@
         <v>101</v>
       </c>
       <c r="P215" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="Q215">
         <v>4.33</v>
@@ -46005,7 +46011,7 @@
         <v>234</v>
       </c>
       <c r="P216" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="Q216">
         <v>3</v>
@@ -46211,7 +46217,7 @@
         <v>235</v>
       </c>
       <c r="P217" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="Q217">
         <v>0</v>
@@ -46623,7 +46629,7 @@
         <v>101</v>
       </c>
       <c r="P219" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="Q219">
         <v>3.2</v>
@@ -47447,7 +47453,7 @@
         <v>101</v>
       </c>
       <c r="P223" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="Q223">
         <v>3.75</v>
@@ -47653,7 +47659,7 @@
         <v>101</v>
       </c>
       <c r="P224" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="Q224">
         <v>3.4</v>
@@ -48352,7 +48358,7 @@
         <v>2.14</v>
       </c>
       <c r="AQ227">
-        <v>1.71</v>
+        <v>1.6</v>
       </c>
       <c r="AR227">
         <v>1.53</v>
@@ -48889,7 +48895,7 @@
         <v>101</v>
       </c>
       <c r="P230" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="Q230">
         <v>2.5</v>
@@ -49301,7 +49307,7 @@
         <v>240</v>
       </c>
       <c r="P232" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="Q232">
         <v>2.4</v>
@@ -49507,7 +49513,7 @@
         <v>241</v>
       </c>
       <c r="P233" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="Q233">
         <v>2.88</v>
@@ -50743,7 +50749,7 @@
         <v>245</v>
       </c>
       <c r="P239" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="Q239">
         <v>4.5</v>
@@ -50949,7 +50955,7 @@
         <v>101</v>
       </c>
       <c r="P240" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="Q240">
         <v>3.75</v>
@@ -51155,7 +51161,7 @@
         <v>101</v>
       </c>
       <c r="P241" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="Q241">
         <v>5.5</v>
@@ -51361,7 +51367,7 @@
         <v>246</v>
       </c>
       <c r="P242" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="Q242">
         <v>2.88</v>
@@ -51567,7 +51573,7 @@
         <v>101</v>
       </c>
       <c r="P243" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="Q243">
         <v>3.5</v>
@@ -51851,7 +51857,7 @@
         <v>1.44</v>
       </c>
       <c r="AP244">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AQ244">
         <v>1.38</v>
@@ -52185,7 +52191,7 @@
         <v>248</v>
       </c>
       <c r="P246" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="Q246">
         <v>2.38</v>
@@ -52391,7 +52397,7 @@
         <v>101</v>
       </c>
       <c r="P247" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="Q247">
         <v>2.6</v>
@@ -52884,7 +52890,7 @@
         <v>2.4</v>
       </c>
       <c r="AQ249">
-        <v>1.71</v>
+        <v>1.6</v>
       </c>
       <c r="AR249">
         <v>1.53</v>
@@ -53215,7 +53221,7 @@
         <v>252</v>
       </c>
       <c r="P251" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="Q251">
         <v>2.25</v>
@@ -53627,7 +53633,7 @@
         <v>254</v>
       </c>
       <c r="P253" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="Q253">
         <v>2.1</v>
@@ -53833,7 +53839,7 @@
         <v>101</v>
       </c>
       <c r="P254" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="Q254">
         <v>2.5</v>
@@ -54245,7 +54251,7 @@
         <v>114</v>
       </c>
       <c r="P256" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="Q256">
         <v>2.88</v>
@@ -54944,7 +54950,7 @@
         <v>1.43</v>
       </c>
       <c r="AQ259">
-        <v>1.71</v>
+        <v>1.6</v>
       </c>
       <c r="AR259">
         <v>1.65</v>
@@ -56305,7 +56311,7 @@
         <v>259</v>
       </c>
       <c r="P266" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="Q266">
         <v>3.6</v>
@@ -56923,7 +56929,7 @@
         <v>261</v>
       </c>
       <c r="P269" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="Q269">
         <v>2.75</v>
@@ -57129,7 +57135,7 @@
         <v>262</v>
       </c>
       <c r="P270" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="Q270">
         <v>2.4</v>
@@ -57335,7 +57341,7 @@
         <v>101</v>
       </c>
       <c r="P271" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="Q271">
         <v>4</v>
@@ -57541,7 +57547,7 @@
         <v>263</v>
       </c>
       <c r="P272" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="Q272">
         <v>3.1</v>
@@ -57953,7 +57959,7 @@
         <v>184</v>
       </c>
       <c r="P274" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="Q274">
         <v>3.25</v>
@@ -58159,7 +58165,7 @@
         <v>265</v>
       </c>
       <c r="P275" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="Q275">
         <v>3.4</v>
@@ -58365,7 +58371,7 @@
         <v>266</v>
       </c>
       <c r="P276" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="Q276">
         <v>2.88</v>
@@ -58443,7 +58449,7 @@
         <v>1.25</v>
       </c>
       <c r="AP276">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AQ276">
         <v>1.08</v>
@@ -58571,7 +58577,7 @@
         <v>267</v>
       </c>
       <c r="P277" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="Q277">
         <v>3.1</v>
@@ -58777,7 +58783,7 @@
         <v>101</v>
       </c>
       <c r="P278" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="Q278">
         <v>3.1</v>
@@ -58983,7 +58989,7 @@
         <v>128</v>
       </c>
       <c r="P279" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="Q279">
         <v>5</v>
@@ -59601,7 +59607,7 @@
         <v>101</v>
       </c>
       <c r="P282" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="Q282">
         <v>2.6</v>
@@ -60425,7 +60431,7 @@
         <v>101</v>
       </c>
       <c r="P286" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="Q286">
         <v>2.5</v>
@@ -60631,7 +60637,7 @@
         <v>270</v>
       </c>
       <c r="P287" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="Q287">
         <v>2.75</v>
@@ -61455,7 +61461,7 @@
         <v>101</v>
       </c>
       <c r="P291" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="Q291">
         <v>4</v>
@@ -61536,7 +61542,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ291">
-        <v>1.71</v>
+        <v>1.6</v>
       </c>
       <c r="AR291">
         <v>1.25</v>
@@ -62073,7 +62079,7 @@
         <v>101</v>
       </c>
       <c r="P294" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="Q294">
         <v>4</v>
@@ -62279,7 +62285,7 @@
         <v>274</v>
       </c>
       <c r="P295" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="Q295">
         <v>2</v>
@@ -62485,7 +62491,7 @@
         <v>101</v>
       </c>
       <c r="P296" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="Q296">
         <v>2.75</v>
@@ -62897,7 +62903,7 @@
         <v>276</v>
       </c>
       <c r="P298" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="Q298">
         <v>2.38</v>
@@ -63103,7 +63109,7 @@
         <v>101</v>
       </c>
       <c r="P299" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="Q299">
         <v>2.88</v>
@@ -63309,7 +63315,7 @@
         <v>101</v>
       </c>
       <c r="P300" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="Q300">
         <v>3.6</v>
@@ -64133,7 +64139,7 @@
         <v>278</v>
       </c>
       <c r="P304" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="Q304">
         <v>4</v>
@@ -65575,7 +65581,7 @@
         <v>282</v>
       </c>
       <c r="P311" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="Q311">
         <v>3.75</v>
@@ -65781,7 +65787,7 @@
         <v>195</v>
       </c>
       <c r="P312" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="Q312">
         <v>2.63</v>
@@ -66271,7 +66277,7 @@
         <v>1.71</v>
       </c>
       <c r="AP314">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AQ314">
         <v>1.67</v>
@@ -67017,7 +67023,7 @@
         <v>283</v>
       </c>
       <c r="P318" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="Q318">
         <v>3.4</v>
@@ -68331,7 +68337,7 @@
         <v>1.54</v>
       </c>
       <c r="AP324">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AQ324">
         <v>1.4</v>
@@ -68665,7 +68671,7 @@
         <v>290</v>
       </c>
       <c r="P326" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="Q326">
         <v>3.75</v>
@@ -68746,7 +68752,7 @@
         <v>1.57</v>
       </c>
       <c r="AQ326">
-        <v>1.71</v>
+        <v>1.6</v>
       </c>
       <c r="AR326">
         <v>1.38</v>
@@ -68871,7 +68877,7 @@
         <v>291</v>
       </c>
       <c r="P327" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="Q327">
         <v>3.75</v>
@@ -69489,7 +69495,7 @@
         <v>293</v>
       </c>
       <c r="P330" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="Q330">
         <v>2.63</v>
@@ -69695,7 +69701,7 @@
         <v>260</v>
       </c>
       <c r="P331" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="Q331">
         <v>3.5</v>
@@ -70107,7 +70113,7 @@
         <v>294</v>
       </c>
       <c r="P333" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="Q333">
         <v>4</v>
@@ -70725,7 +70731,7 @@
         <v>101</v>
       </c>
       <c r="P336" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="Q336">
         <v>2.63</v>
@@ -71137,7 +71143,7 @@
         <v>296</v>
       </c>
       <c r="P338" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="Q338">
         <v>3.1</v>
@@ -71343,7 +71349,7 @@
         <v>297</v>
       </c>
       <c r="P339" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="Q339">
         <v>3</v>
@@ -71706,6 +71712,212 @@
       </c>
       <c r="BP340">
         <v>1.32</v>
+      </c>
+    </row>
+    <row r="341" spans="1:68">
+      <c r="A341" s="1">
+        <v>340</v>
+      </c>
+      <c r="B341">
+        <v>7476906</v>
+      </c>
+      <c r="C341" t="s">
+        <v>68</v>
+      </c>
+      <c r="D341" t="s">
+        <v>69</v>
+      </c>
+      <c r="E341" s="2">
+        <v>45694.69791666666</v>
+      </c>
+      <c r="F341">
+        <v>31</v>
+      </c>
+      <c r="G341" t="s">
+        <v>70</v>
+      </c>
+      <c r="H341" t="s">
+        <v>74</v>
+      </c>
+      <c r="I341">
+        <v>2</v>
+      </c>
+      <c r="J341">
+        <v>1</v>
+      </c>
+      <c r="K341">
+        <v>3</v>
+      </c>
+      <c r="L341">
+        <v>5</v>
+      </c>
+      <c r="M341">
+        <v>2</v>
+      </c>
+      <c r="N341">
+        <v>7</v>
+      </c>
+      <c r="O341" t="s">
+        <v>299</v>
+      </c>
+      <c r="P341" t="s">
+        <v>431</v>
+      </c>
+      <c r="Q341">
+        <v>3</v>
+      </c>
+      <c r="R341">
+        <v>2.2</v>
+      </c>
+      <c r="S341">
+        <v>3.6</v>
+      </c>
+      <c r="T341">
+        <v>1.4</v>
+      </c>
+      <c r="U341">
+        <v>2.75</v>
+      </c>
+      <c r="V341">
+        <v>2.75</v>
+      </c>
+      <c r="W341">
+        <v>1.4</v>
+      </c>
+      <c r="X341">
+        <v>8</v>
+      </c>
+      <c r="Y341">
+        <v>1.08</v>
+      </c>
+      <c r="Z341">
+        <v>2.3</v>
+      </c>
+      <c r="AA341">
+        <v>3.33</v>
+      </c>
+      <c r="AB341">
+        <v>2.99</v>
+      </c>
+      <c r="AC341">
+        <v>1.05</v>
+      </c>
+      <c r="AD341">
+        <v>9</v>
+      </c>
+      <c r="AE341">
+        <v>1.28</v>
+      </c>
+      <c r="AF341">
+        <v>3.55</v>
+      </c>
+      <c r="AG341">
+        <v>1.89</v>
+      </c>
+      <c r="AH341">
+        <v>1.85</v>
+      </c>
+      <c r="AI341">
+        <v>1.67</v>
+      </c>
+      <c r="AJ341">
+        <v>2.1</v>
+      </c>
+      <c r="AK341">
+        <v>1.38</v>
+      </c>
+      <c r="AL341">
+        <v>1.25</v>
+      </c>
+      <c r="AM341">
+        <v>1.6</v>
+      </c>
+      <c r="AN341">
+        <v>1.57</v>
+      </c>
+      <c r="AO341">
+        <v>1.71</v>
+      </c>
+      <c r="AP341">
+        <v>1.67</v>
+      </c>
+      <c r="AQ341">
+        <v>1.6</v>
+      </c>
+      <c r="AR341">
+        <v>1.56</v>
+      </c>
+      <c r="AS341">
+        <v>1.36</v>
+      </c>
+      <c r="AT341">
+        <v>2.92</v>
+      </c>
+      <c r="AU341">
+        <v>8</v>
+      </c>
+      <c r="AV341">
+        <v>5</v>
+      </c>
+      <c r="AW341">
+        <v>2</v>
+      </c>
+      <c r="AX341">
+        <v>18</v>
+      </c>
+      <c r="AY341">
+        <v>11</v>
+      </c>
+      <c r="AZ341">
+        <v>31</v>
+      </c>
+      <c r="BA341">
+        <v>7</v>
+      </c>
+      <c r="BB341">
+        <v>7</v>
+      </c>
+      <c r="BC341">
+        <v>14</v>
+      </c>
+      <c r="BD341">
+        <v>1.9</v>
+      </c>
+      <c r="BE341">
+        <v>6.5</v>
+      </c>
+      <c r="BF341">
+        <v>2.1</v>
+      </c>
+      <c r="BG341">
+        <v>1.24</v>
+      </c>
+      <c r="BH341">
+        <v>3.55</v>
+      </c>
+      <c r="BI341">
+        <v>1.31</v>
+      </c>
+      <c r="BJ341">
+        <v>3</v>
+      </c>
+      <c r="BK341">
+        <v>1.57</v>
+      </c>
+      <c r="BL341">
+        <v>2.15</v>
+      </c>
+      <c r="BM341">
+        <v>1.98</v>
+      </c>
+      <c r="BN341">
+        <v>1.68</v>
+      </c>
+      <c r="BO341">
+        <v>2.6</v>
+      </c>
+      <c r="BP341">
+        <v>1.4</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/England EFL League Two_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/England EFL League Two_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2108" uniqueCount="432">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2120" uniqueCount="434">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -916,6 +916,9 @@
     <t>['11', '37', '54', '59', '90+4']</t>
   </si>
   <si>
+    <t>['20', '45', '63']</t>
+  </si>
+  <si>
     <t>['1', '9']</t>
   </si>
   <si>
@@ -1311,6 +1314,9 @@
   <si>
     <t>['45+4', '90+3']</t>
   </si>
+  <si>
+    <t>['31', '40', '87']</t>
+  </si>
 </sst>
 </file>
 
@@ -1671,7 +1677,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP341"/>
+  <dimension ref="A1:BP343"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -2133,7 +2139,7 @@
         <v>95</v>
       </c>
       <c r="P3" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="Q3">
         <v>2.5</v>
@@ -2545,7 +2551,7 @@
         <v>97</v>
       </c>
       <c r="P5" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="Q5">
         <v>2.4</v>
@@ -3369,7 +3375,7 @@
         <v>101</v>
       </c>
       <c r="P9" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="Q9">
         <v>2.75</v>
@@ -3575,7 +3581,7 @@
         <v>102</v>
       </c>
       <c r="P10" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="Q10">
         <v>2.63</v>
@@ -3781,7 +3787,7 @@
         <v>101</v>
       </c>
       <c r="P11" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="Q11">
         <v>2.88</v>
@@ -3862,7 +3868,7 @@
         <v>1.73</v>
       </c>
       <c r="AQ11">
-        <v>1.67</v>
+        <v>1.63</v>
       </c>
       <c r="AR11">
         <v>0</v>
@@ -4811,7 +4817,7 @@
         <v>105</v>
       </c>
       <c r="P16" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="Q16">
         <v>2.88</v>
@@ -4892,7 +4898,7 @@
         <v>1.15</v>
       </c>
       <c r="AQ16">
-        <v>0.87</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="AR16">
         <v>0</v>
@@ -5223,7 +5229,7 @@
         <v>101</v>
       </c>
       <c r="P18" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="Q18">
         <v>3.4</v>
@@ -5429,7 +5435,7 @@
         <v>107</v>
       </c>
       <c r="P19" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="Q19">
         <v>3</v>
@@ -6253,7 +6259,7 @@
         <v>101</v>
       </c>
       <c r="P23" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="Q23">
         <v>3</v>
@@ -6331,7 +6337,7 @@
         <v>0</v>
       </c>
       <c r="AP23">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="AQ23">
         <v>1.77</v>
@@ -6537,7 +6543,7 @@
         <v>0</v>
       </c>
       <c r="AP24">
-        <v>2.36</v>
+        <v>2.4</v>
       </c>
       <c r="AQ24">
         <v>1.36</v>
@@ -6665,7 +6671,7 @@
         <v>109</v>
       </c>
       <c r="P25" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="Q25">
         <v>2.63</v>
@@ -6871,7 +6877,7 @@
         <v>110</v>
       </c>
       <c r="P26" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="Q26">
         <v>2.38</v>
@@ -7695,7 +7701,7 @@
         <v>112</v>
       </c>
       <c r="P30" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="Q30">
         <v>3</v>
@@ -8803,7 +8809,7 @@
         <v>3</v>
       </c>
       <c r="AP35">
-        <v>2.36</v>
+        <v>2.4</v>
       </c>
       <c r="AQ35">
         <v>1.4</v>
@@ -9012,7 +9018,7 @@
         <v>1.57</v>
       </c>
       <c r="AQ36">
-        <v>1.67</v>
+        <v>1.63</v>
       </c>
       <c r="AR36">
         <v>1.13</v>
@@ -9137,7 +9143,7 @@
         <v>101</v>
       </c>
       <c r="P37" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="Q37">
         <v>2.6</v>
@@ -9218,7 +9224,7 @@
         <v>1.43</v>
       </c>
       <c r="AQ37">
-        <v>0.87</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="AR37">
         <v>1.61</v>
@@ -9343,7 +9349,7 @@
         <v>117</v>
       </c>
       <c r="P38" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="Q38">
         <v>2.88</v>
@@ -9755,7 +9761,7 @@
         <v>119</v>
       </c>
       <c r="P40" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="Q40">
         <v>3</v>
@@ -9833,7 +9839,7 @@
         <v>1</v>
       </c>
       <c r="AP40">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="AQ40">
         <v>1.73</v>
@@ -10167,7 +10173,7 @@
         <v>101</v>
       </c>
       <c r="P42" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="Q42">
         <v>3.75</v>
@@ -10579,7 +10585,7 @@
         <v>121</v>
       </c>
       <c r="P44" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="Q44">
         <v>2.75</v>
@@ -10785,7 +10791,7 @@
         <v>122</v>
       </c>
       <c r="P45" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="Q45">
         <v>2.63</v>
@@ -11403,7 +11409,7 @@
         <v>125</v>
       </c>
       <c r="P48" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="Q48">
         <v>3.5</v>
@@ -11815,7 +11821,7 @@
         <v>127</v>
       </c>
       <c r="P50" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="Q50">
         <v>3.6</v>
@@ -11896,7 +11902,7 @@
         <v>1.77</v>
       </c>
       <c r="AQ50">
-        <v>1.67</v>
+        <v>1.63</v>
       </c>
       <c r="AR50">
         <v>0.78</v>
@@ -12021,7 +12027,7 @@
         <v>103</v>
       </c>
       <c r="P51" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="Q51">
         <v>2.5</v>
@@ -12308,7 +12314,7 @@
         <v>1.8</v>
       </c>
       <c r="AQ52">
-        <v>0.87</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="AR52">
         <v>1.19</v>
@@ -13335,7 +13341,7 @@
         <v>0</v>
       </c>
       <c r="AP57">
-        <v>2.36</v>
+        <v>2.4</v>
       </c>
       <c r="AQ57">
         <v>0.86</v>
@@ -14365,7 +14371,7 @@
         <v>1.5</v>
       </c>
       <c r="AP62">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="AQ62">
         <v>0.67</v>
@@ -14699,7 +14705,7 @@
         <v>139</v>
       </c>
       <c r="P64" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="Q64">
         <v>3</v>
@@ -15111,7 +15117,7 @@
         <v>141</v>
       </c>
       <c r="P66" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="Q66">
         <v>3.75</v>
@@ -15729,7 +15735,7 @@
         <v>143</v>
       </c>
       <c r="P69" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="Q69">
         <v>3.2</v>
@@ -15935,7 +15941,7 @@
         <v>144</v>
       </c>
       <c r="P70" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="Q70">
         <v>3.25</v>
@@ -16141,7 +16147,7 @@
         <v>145</v>
       </c>
       <c r="P71" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="Q71">
         <v>3</v>
@@ -16347,7 +16353,7 @@
         <v>146</v>
       </c>
       <c r="P72" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="Q72">
         <v>4</v>
@@ -16428,7 +16434,7 @@
         <v>1.15</v>
       </c>
       <c r="AQ72">
-        <v>1.67</v>
+        <v>1.63</v>
       </c>
       <c r="AR72">
         <v>1.54</v>
@@ -16759,7 +16765,7 @@
         <v>101</v>
       </c>
       <c r="P74" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="Q74">
         <v>2.63</v>
@@ -16837,7 +16843,7 @@
         <v>0</v>
       </c>
       <c r="AP74">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="AQ74">
         <v>0.86</v>
@@ -16965,7 +16971,7 @@
         <v>101</v>
       </c>
       <c r="P75" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="Q75">
         <v>3.4</v>
@@ -17171,7 +17177,7 @@
         <v>101</v>
       </c>
       <c r="P76" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="Q76">
         <v>2.6</v>
@@ -17583,7 +17589,7 @@
         <v>149</v>
       </c>
       <c r="P78" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="Q78">
         <v>2.88</v>
@@ -18073,7 +18079,7 @@
         <v>1.5</v>
       </c>
       <c r="AP80">
-        <v>2.36</v>
+        <v>2.4</v>
       </c>
       <c r="AQ80">
         <v>1.38</v>
@@ -18488,7 +18494,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ82">
-        <v>0.87</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="AR82">
         <v>0.97</v>
@@ -18613,7 +18619,7 @@
         <v>153</v>
       </c>
       <c r="P83" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="Q83">
         <v>2.2</v>
@@ -19849,7 +19855,7 @@
         <v>157</v>
       </c>
       <c r="P89" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="Q89">
         <v>3.75</v>
@@ -20261,7 +20267,7 @@
         <v>101</v>
       </c>
       <c r="P91" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="Q91">
         <v>2.75</v>
@@ -20467,7 +20473,7 @@
         <v>101</v>
       </c>
       <c r="P92" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="Q92">
         <v>3.4</v>
@@ -20673,7 +20679,7 @@
         <v>159</v>
       </c>
       <c r="P93" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="Q93">
         <v>2.75</v>
@@ -21085,7 +21091,7 @@
         <v>161</v>
       </c>
       <c r="P95" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="Q95">
         <v>2.5</v>
@@ -21291,7 +21297,7 @@
         <v>162</v>
       </c>
       <c r="P96" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="Q96">
         <v>4.5</v>
@@ -22115,7 +22121,7 @@
         <v>166</v>
       </c>
       <c r="P100" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="Q100">
         <v>2.75</v>
@@ -22527,7 +22533,7 @@
         <v>167</v>
       </c>
       <c r="P102" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="Q102">
         <v>2.88</v>
@@ -22733,7 +22739,7 @@
         <v>101</v>
       </c>
       <c r="P103" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="Q103">
         <v>3</v>
@@ -22939,7 +22945,7 @@
         <v>168</v>
       </c>
       <c r="P104" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="Q104">
         <v>4</v>
@@ -23351,7 +23357,7 @@
         <v>101</v>
       </c>
       <c r="P106" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="Q106">
         <v>3.6</v>
@@ -23841,10 +23847,10 @@
         <v>1</v>
       </c>
       <c r="AP108">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="AQ108">
-        <v>0.87</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="AR108">
         <v>1.59</v>
@@ -24050,7 +24056,7 @@
         <v>1.85</v>
       </c>
       <c r="AQ109">
-        <v>1.67</v>
+        <v>1.63</v>
       </c>
       <c r="AR109">
         <v>1.69</v>
@@ -24793,7 +24799,7 @@
         <v>172</v>
       </c>
       <c r="P113" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="Q113">
         <v>2.6</v>
@@ -24999,7 +25005,7 @@
         <v>173</v>
       </c>
       <c r="P114" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="Q114">
         <v>2.4</v>
@@ -25695,7 +25701,7 @@
         <v>0.75</v>
       </c>
       <c r="AP117">
-        <v>2.36</v>
+        <v>2.4</v>
       </c>
       <c r="AQ117">
         <v>0.67</v>
@@ -25823,7 +25829,7 @@
         <v>176</v>
       </c>
       <c r="P118" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="Q118">
         <v>2.5</v>
@@ -26029,7 +26035,7 @@
         <v>101</v>
       </c>
       <c r="P119" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="Q119">
         <v>3.4</v>
@@ -26235,7 +26241,7 @@
         <v>94</v>
       </c>
       <c r="P120" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="Q120">
         <v>2.88</v>
@@ -26522,7 +26528,7 @@
         <v>1.56</v>
       </c>
       <c r="AQ121">
-        <v>1.67</v>
+        <v>1.63</v>
       </c>
       <c r="AR121">
         <v>1.34</v>
@@ -26853,7 +26859,7 @@
         <v>178</v>
       </c>
       <c r="P123" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="Q123">
         <v>2.38</v>
@@ -27265,7 +27271,7 @@
         <v>101</v>
       </c>
       <c r="P125" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="Q125">
         <v>2.1</v>
@@ -27677,7 +27683,7 @@
         <v>180</v>
       </c>
       <c r="P127" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="Q127">
         <v>3.25</v>
@@ -27883,7 +27889,7 @@
         <v>101</v>
       </c>
       <c r="P128" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="Q128">
         <v>4.75</v>
@@ -28501,7 +28507,7 @@
         <v>182</v>
       </c>
       <c r="P131" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="Q131">
         <v>2.63</v>
@@ -28707,7 +28713,7 @@
         <v>183</v>
       </c>
       <c r="P132" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="Q132">
         <v>3.5</v>
@@ -28785,7 +28791,7 @@
         <v>1.4</v>
       </c>
       <c r="AP132">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="AQ132">
         <v>1.6</v>
@@ -29119,7 +29125,7 @@
         <v>185</v>
       </c>
       <c r="P134" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="Q134">
         <v>4</v>
@@ -29325,7 +29331,7 @@
         <v>147</v>
       </c>
       <c r="P135" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="Q135">
         <v>2.6</v>
@@ -29531,7 +29537,7 @@
         <v>186</v>
       </c>
       <c r="P136" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="Q136">
         <v>3.6</v>
@@ -29737,7 +29743,7 @@
         <v>187</v>
       </c>
       <c r="P137" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="Q137">
         <v>3</v>
@@ -30021,7 +30027,7 @@
         <v>1.4</v>
       </c>
       <c r="AP138">
-        <v>2.36</v>
+        <v>2.4</v>
       </c>
       <c r="AQ138">
         <v>1</v>
@@ -30149,7 +30155,7 @@
         <v>185</v>
       </c>
       <c r="P139" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="Q139">
         <v>2.5</v>
@@ -30230,7 +30236,7 @@
         <v>0.64</v>
       </c>
       <c r="AQ139">
-        <v>0.87</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="AR139">
         <v>1.5</v>
@@ -30355,7 +30361,7 @@
         <v>189</v>
       </c>
       <c r="P140" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="Q140">
         <v>2.25</v>
@@ -31054,7 +31060,7 @@
         <v>1.13</v>
       </c>
       <c r="AQ143">
-        <v>1.67</v>
+        <v>1.63</v>
       </c>
       <c r="AR143">
         <v>1.14</v>
@@ -31179,7 +31185,7 @@
         <v>101</v>
       </c>
       <c r="P144" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="Q144">
         <v>2.25</v>
@@ -31797,7 +31803,7 @@
         <v>101</v>
       </c>
       <c r="P147" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="Q147">
         <v>3</v>
@@ -32621,7 +32627,7 @@
         <v>193</v>
       </c>
       <c r="P151" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="Q151">
         <v>2.4</v>
@@ -32827,7 +32833,7 @@
         <v>194</v>
       </c>
       <c r="P152" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="Q152">
         <v>4.5</v>
@@ -33033,7 +33039,7 @@
         <v>195</v>
       </c>
       <c r="P153" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="Q153">
         <v>2.75</v>
@@ -33317,7 +33323,7 @@
         <v>1.17</v>
       </c>
       <c r="AP154">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="AQ154">
         <v>1</v>
@@ -33445,7 +33451,7 @@
         <v>197</v>
       </c>
       <c r="P155" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="Q155">
         <v>3</v>
@@ -33857,7 +33863,7 @@
         <v>198</v>
       </c>
       <c r="P157" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="Q157">
         <v>3.4</v>
@@ -34475,7 +34481,7 @@
         <v>200</v>
       </c>
       <c r="P160" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="Q160">
         <v>3.2</v>
@@ -34553,7 +34559,7 @@
         <v>1.67</v>
       </c>
       <c r="AP160">
-        <v>2.36</v>
+        <v>2.4</v>
       </c>
       <c r="AQ160">
         <v>1.6</v>
@@ -34968,7 +34974,7 @@
         <v>1.85</v>
       </c>
       <c r="AQ162">
-        <v>0.87</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="AR162">
         <v>1.61</v>
@@ -35299,7 +35305,7 @@
         <v>203</v>
       </c>
       <c r="P164" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="Q164">
         <v>2.4</v>
@@ -35711,7 +35717,7 @@
         <v>204</v>
       </c>
       <c r="P166" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="Q166">
         <v>2.88</v>
@@ -35998,7 +36004,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ167">
-        <v>1.67</v>
+        <v>1.63</v>
       </c>
       <c r="AR167">
         <v>1.33</v>
@@ -36123,7 +36129,7 @@
         <v>206</v>
       </c>
       <c r="P168" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="Q168">
         <v>2.3</v>
@@ -36535,7 +36541,7 @@
         <v>208</v>
       </c>
       <c r="P170" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="Q170">
         <v>2.5</v>
@@ -37153,7 +37159,7 @@
         <v>101</v>
       </c>
       <c r="P173" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="Q173">
         <v>2.1</v>
@@ -37359,7 +37365,7 @@
         <v>148</v>
       </c>
       <c r="P174" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="Q174">
         <v>3.2</v>
@@ -38264,7 +38270,7 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="AQ178">
-        <v>1.67</v>
+        <v>1.63</v>
       </c>
       <c r="AR178">
         <v>1.39</v>
@@ -38389,7 +38395,7 @@
         <v>210</v>
       </c>
       <c r="P179" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="Q179">
         <v>2.3</v>
@@ -39419,7 +39425,7 @@
         <v>185</v>
       </c>
       <c r="P184" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="Q184">
         <v>3.4</v>
@@ -39625,7 +39631,7 @@
         <v>215</v>
       </c>
       <c r="P185" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="Q185">
         <v>3.2</v>
@@ -40037,7 +40043,7 @@
         <v>217</v>
       </c>
       <c r="P187" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="Q187">
         <v>2.2</v>
@@ -40655,7 +40661,7 @@
         <v>101</v>
       </c>
       <c r="P190" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="Q190">
         <v>3.25</v>
@@ -40861,7 +40867,7 @@
         <v>148</v>
       </c>
       <c r="P191" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="Q191">
         <v>2.3</v>
@@ -40942,7 +40948,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ191">
-        <v>0.87</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="AR191">
         <v>1.27</v>
@@ -41067,7 +41073,7 @@
         <v>219</v>
       </c>
       <c r="P192" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="Q192">
         <v>2.4</v>
@@ -41145,7 +41151,7 @@
         <v>0.88</v>
       </c>
       <c r="AP192">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="AQ192">
         <v>0.88</v>
@@ -42097,7 +42103,7 @@
         <v>101</v>
       </c>
       <c r="P197" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="Q197">
         <v>3.75</v>
@@ -42303,7 +42309,7 @@
         <v>221</v>
       </c>
       <c r="P198" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="Q198">
         <v>2.2</v>
@@ -42509,7 +42515,7 @@
         <v>122</v>
       </c>
       <c r="P199" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="Q199">
         <v>3.4</v>
@@ -42921,7 +42927,7 @@
         <v>222</v>
       </c>
       <c r="P201" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="Q201">
         <v>2.85</v>
@@ -43127,7 +43133,7 @@
         <v>223</v>
       </c>
       <c r="P202" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="Q202">
         <v>1.8</v>
@@ -43333,7 +43339,7 @@
         <v>205</v>
       </c>
       <c r="P203" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="Q203">
         <v>2.75</v>
@@ -43411,7 +43417,7 @@
         <v>0.88</v>
       </c>
       <c r="AP203">
-        <v>2.36</v>
+        <v>2.4</v>
       </c>
       <c r="AQ203">
         <v>0.64</v>
@@ -43539,7 +43545,7 @@
         <v>224</v>
       </c>
       <c r="P204" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="Q204">
         <v>3.55</v>
@@ -43620,7 +43626,7 @@
         <v>1.8</v>
       </c>
       <c r="AQ204">
-        <v>1.67</v>
+        <v>1.63</v>
       </c>
       <c r="AR204">
         <v>1.31</v>
@@ -44238,7 +44244,7 @@
         <v>1.73</v>
       </c>
       <c r="AQ207">
-        <v>0.87</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="AR207">
         <v>1.39</v>
@@ -44363,7 +44369,7 @@
         <v>228</v>
       </c>
       <c r="P208" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="Q208">
         <v>2.4</v>
@@ -44569,7 +44575,7 @@
         <v>229</v>
       </c>
       <c r="P209" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="Q209">
         <v>2.5</v>
@@ -44981,7 +44987,7 @@
         <v>231</v>
       </c>
       <c r="P211" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="Q211">
         <v>3.5</v>
@@ -45805,7 +45811,7 @@
         <v>101</v>
       </c>
       <c r="P215" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="Q215">
         <v>4.33</v>
@@ -46011,7 +46017,7 @@
         <v>234</v>
       </c>
       <c r="P216" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="Q216">
         <v>3</v>
@@ -46217,7 +46223,7 @@
         <v>235</v>
       </c>
       <c r="P217" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="Q217">
         <v>0</v>
@@ -46501,7 +46507,7 @@
         <v>1.57</v>
       </c>
       <c r="AP218">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="AQ218">
         <v>1.17</v>
@@ -46629,7 +46635,7 @@
         <v>101</v>
       </c>
       <c r="P219" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="Q219">
         <v>3.2</v>
@@ -47122,7 +47128,7 @@
         <v>1.29</v>
       </c>
       <c r="AQ221">
-        <v>0.87</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="AR221">
         <v>1.41</v>
@@ -47453,7 +47459,7 @@
         <v>101</v>
       </c>
       <c r="P223" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="Q223">
         <v>3.75</v>
@@ -47659,7 +47665,7 @@
         <v>101</v>
       </c>
       <c r="P224" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="Q224">
         <v>3.4</v>
@@ -48561,7 +48567,7 @@
         <v>0.8</v>
       </c>
       <c r="AP228">
-        <v>2.36</v>
+        <v>2.4</v>
       </c>
       <c r="AQ228">
         <v>1</v>
@@ -48770,7 +48776,7 @@
         <v>1.07</v>
       </c>
       <c r="AQ229">
-        <v>1.67</v>
+        <v>1.63</v>
       </c>
       <c r="AR229">
         <v>1.39</v>
@@ -48895,7 +48901,7 @@
         <v>101</v>
       </c>
       <c r="P230" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="Q230">
         <v>2.5</v>
@@ -49307,7 +49313,7 @@
         <v>240</v>
       </c>
       <c r="P232" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="Q232">
         <v>2.4</v>
@@ -49513,7 +49519,7 @@
         <v>241</v>
       </c>
       <c r="P233" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="Q233">
         <v>2.88</v>
@@ -50749,7 +50755,7 @@
         <v>245</v>
       </c>
       <c r="P239" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="Q239">
         <v>4.5</v>
@@ -50955,7 +50961,7 @@
         <v>101</v>
       </c>
       <c r="P240" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="Q240">
         <v>3.75</v>
@@ -51161,7 +51167,7 @@
         <v>101</v>
       </c>
       <c r="P241" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="Q241">
         <v>5.5</v>
@@ -51367,7 +51373,7 @@
         <v>246</v>
       </c>
       <c r="P242" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="Q242">
         <v>2.88</v>
@@ -51445,7 +51451,7 @@
         <v>1.9</v>
       </c>
       <c r="AP242">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="AQ242">
         <v>1.47</v>
@@ -51573,7 +51579,7 @@
         <v>101</v>
       </c>
       <c r="P243" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="Q243">
         <v>3.5</v>
@@ -52191,7 +52197,7 @@
         <v>248</v>
       </c>
       <c r="P246" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="Q246">
         <v>2.38</v>
@@ -52272,7 +52278,7 @@
         <v>1.43</v>
       </c>
       <c r="AQ246">
-        <v>0.87</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="AR246">
         <v>1.22</v>
@@ -52397,7 +52403,7 @@
         <v>101</v>
       </c>
       <c r="P247" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="Q247">
         <v>2.6</v>
@@ -53221,7 +53227,7 @@
         <v>252</v>
       </c>
       <c r="P251" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="Q251">
         <v>2.25</v>
@@ -53505,10 +53511,10 @@
         <v>1.91</v>
       </c>
       <c r="AP252">
-        <v>2.36</v>
+        <v>2.4</v>
       </c>
       <c r="AQ252">
-        <v>1.67</v>
+        <v>1.63</v>
       </c>
       <c r="AR252">
         <v>1.42</v>
@@ -53633,7 +53639,7 @@
         <v>254</v>
       </c>
       <c r="P253" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="Q253">
         <v>2.1</v>
@@ -53839,7 +53845,7 @@
         <v>101</v>
       </c>
       <c r="P254" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="Q254">
         <v>2.5</v>
@@ -54251,7 +54257,7 @@
         <v>114</v>
       </c>
       <c r="P256" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="Q256">
         <v>2.88</v>
@@ -55771,7 +55777,7 @@
         <v>1.45</v>
       </c>
       <c r="AP263">
-        <v>2.36</v>
+        <v>2.4</v>
       </c>
       <c r="AQ263">
         <v>1.21</v>
@@ -55980,7 +55986,7 @@
         <v>1.43</v>
       </c>
       <c r="AQ264">
-        <v>1.67</v>
+        <v>1.63</v>
       </c>
       <c r="AR264">
         <v>1.24</v>
@@ -56186,7 +56192,7 @@
         <v>1.47</v>
       </c>
       <c r="AQ265">
-        <v>0.87</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="AR265">
         <v>1.29</v>
@@ -56311,7 +56317,7 @@
         <v>259</v>
       </c>
       <c r="P266" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="Q266">
         <v>3.6</v>
@@ -56929,7 +56935,7 @@
         <v>261</v>
       </c>
       <c r="P269" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="Q269">
         <v>2.75</v>
@@ -57135,7 +57141,7 @@
         <v>262</v>
       </c>
       <c r="P270" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="Q270">
         <v>2.4</v>
@@ -57341,7 +57347,7 @@
         <v>101</v>
       </c>
       <c r="P271" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="Q271">
         <v>4</v>
@@ -57547,7 +57553,7 @@
         <v>263</v>
       </c>
       <c r="P272" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="Q272">
         <v>3.1</v>
@@ -57625,7 +57631,7 @@
         <v>1</v>
       </c>
       <c r="AP272">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="AQ272">
         <v>1.21</v>
@@ -57959,7 +57965,7 @@
         <v>184</v>
       </c>
       <c r="P274" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="Q274">
         <v>3.25</v>
@@ -58165,7 +58171,7 @@
         <v>265</v>
       </c>
       <c r="P275" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="Q275">
         <v>3.4</v>
@@ -58371,7 +58377,7 @@
         <v>266</v>
       </c>
       <c r="P276" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="Q276">
         <v>2.88</v>
@@ -58577,7 +58583,7 @@
         <v>267</v>
       </c>
       <c r="P277" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="Q277">
         <v>3.1</v>
@@ -58783,7 +58789,7 @@
         <v>101</v>
       </c>
       <c r="P278" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="Q278">
         <v>3.1</v>
@@ -58989,7 +58995,7 @@
         <v>128</v>
       </c>
       <c r="P279" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="Q279">
         <v>5</v>
@@ -59479,7 +59485,7 @@
         <v>1.58</v>
       </c>
       <c r="AP281">
-        <v>2.36</v>
+        <v>2.4</v>
       </c>
       <c r="AQ281">
         <v>1.47</v>
@@ -59607,7 +59613,7 @@
         <v>101</v>
       </c>
       <c r="P282" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="Q282">
         <v>2.6</v>
@@ -60306,7 +60312,7 @@
         <v>1.87</v>
       </c>
       <c r="AQ285">
-        <v>1.67</v>
+        <v>1.63</v>
       </c>
       <c r="AR285">
         <v>1.45</v>
@@ -60431,7 +60437,7 @@
         <v>101</v>
       </c>
       <c r="P286" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="Q286">
         <v>2.5</v>
@@ -60512,7 +60518,7 @@
         <v>1.57</v>
       </c>
       <c r="AQ286">
-        <v>0.87</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="AR286">
         <v>1.4</v>
@@ -60637,7 +60643,7 @@
         <v>270</v>
       </c>
       <c r="P287" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="Q287">
         <v>2.75</v>
@@ -61127,7 +61133,7 @@
         <v>1.42</v>
       </c>
       <c r="AP289">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="AQ289">
         <v>1.47</v>
@@ -61461,7 +61467,7 @@
         <v>101</v>
       </c>
       <c r="P291" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="Q291">
         <v>4</v>
@@ -62079,7 +62085,7 @@
         <v>101</v>
       </c>
       <c r="P294" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="Q294">
         <v>4</v>
@@ -62285,7 +62291,7 @@
         <v>274</v>
       </c>
       <c r="P295" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="Q295">
         <v>2</v>
@@ -62491,7 +62497,7 @@
         <v>101</v>
       </c>
       <c r="P296" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="Q296">
         <v>2.75</v>
@@ -62775,7 +62781,7 @@
         <v>0.75</v>
       </c>
       <c r="AP297">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="AQ297">
         <v>0.64</v>
@@ -62903,7 +62909,7 @@
         <v>276</v>
       </c>
       <c r="P298" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="Q298">
         <v>2.38</v>
@@ -63109,7 +63115,7 @@
         <v>101</v>
       </c>
       <c r="P299" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="Q299">
         <v>2.88</v>
@@ -63315,7 +63321,7 @@
         <v>101</v>
       </c>
       <c r="P300" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="Q300">
         <v>3.6</v>
@@ -64139,7 +64145,7 @@
         <v>278</v>
       </c>
       <c r="P304" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="Q304">
         <v>4</v>
@@ -64629,7 +64635,7 @@
         <v>2.09</v>
       </c>
       <c r="AP306">
-        <v>2.36</v>
+        <v>2.4</v>
       </c>
       <c r="AQ306">
         <v>1.77</v>
@@ -65581,7 +65587,7 @@
         <v>282</v>
       </c>
       <c r="P311" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="Q311">
         <v>3.75</v>
@@ -65787,7 +65793,7 @@
         <v>195</v>
       </c>
       <c r="P312" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="Q312">
         <v>2.63</v>
@@ -66074,7 +66080,7 @@
         <v>1.87</v>
       </c>
       <c r="AQ313">
-        <v>0.87</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="AR313">
         <v>1.48</v>
@@ -66280,7 +66286,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ314">
-        <v>1.67</v>
+        <v>1.63</v>
       </c>
       <c r="AR314">
         <v>1.48</v>
@@ -66895,7 +66901,7 @@
         <v>1</v>
       </c>
       <c r="AP317">
-        <v>2.36</v>
+        <v>2.4</v>
       </c>
       <c r="AQ317">
         <v>0.88</v>
@@ -67023,7 +67029,7 @@
         <v>283</v>
       </c>
       <c r="P318" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="Q318">
         <v>3.4</v>
@@ -68131,7 +68137,7 @@
         <v>0.62</v>
       </c>
       <c r="AP323">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="AQ323">
         <v>0.57</v>
@@ -68546,7 +68552,7 @@
         <v>1.56</v>
       </c>
       <c r="AQ325">
-        <v>0.87</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="AR325">
         <v>1.34</v>
@@ -68671,7 +68677,7 @@
         <v>290</v>
       </c>
       <c r="P326" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="Q326">
         <v>3.75</v>
@@ -68877,7 +68883,7 @@
         <v>291</v>
       </c>
       <c r="P327" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="Q327">
         <v>3.75</v>
@@ -69495,7 +69501,7 @@
         <v>293</v>
       </c>
       <c r="P330" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="Q330">
         <v>2.63</v>
@@ -69701,7 +69707,7 @@
         <v>260</v>
       </c>
       <c r="P331" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="Q331">
         <v>3.5</v>
@@ -70113,7 +70119,7 @@
         <v>294</v>
       </c>
       <c r="P333" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="Q333">
         <v>4</v>
@@ -70731,7 +70737,7 @@
         <v>101</v>
       </c>
       <c r="P336" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="Q336">
         <v>2.63</v>
@@ -71143,7 +71149,7 @@
         <v>296</v>
       </c>
       <c r="P338" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="Q338">
         <v>3.1</v>
@@ -71349,7 +71355,7 @@
         <v>297</v>
       </c>
       <c r="P339" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="Q339">
         <v>3</v>
@@ -71761,7 +71767,7 @@
         <v>299</v>
       </c>
       <c r="P341" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="Q341">
         <v>3</v>
@@ -71918,6 +71924,418 @@
       </c>
       <c r="BP341">
         <v>1.4</v>
+      </c>
+    </row>
+    <row r="342" spans="1:68">
+      <c r="A342" s="1">
+        <v>341</v>
+      </c>
+      <c r="B342">
+        <v>7476914</v>
+      </c>
+      <c r="C342" t="s">
+        <v>68</v>
+      </c>
+      <c r="D342" t="s">
+        <v>69</v>
+      </c>
+      <c r="E342" s="2">
+        <v>45696.39583333334</v>
+      </c>
+      <c r="F342">
+        <v>31</v>
+      </c>
+      <c r="G342" t="s">
+        <v>91</v>
+      </c>
+      <c r="H342" t="s">
+        <v>90</v>
+      </c>
+      <c r="I342">
+        <v>2</v>
+      </c>
+      <c r="J342">
+        <v>2</v>
+      </c>
+      <c r="K342">
+        <v>4</v>
+      </c>
+      <c r="L342">
+        <v>3</v>
+      </c>
+      <c r="M342">
+        <v>3</v>
+      </c>
+      <c r="N342">
+        <v>6</v>
+      </c>
+      <c r="O342" t="s">
+        <v>300</v>
+      </c>
+      <c r="P342" t="s">
+        <v>433</v>
+      </c>
+      <c r="Q342">
+        <v>3.1</v>
+      </c>
+      <c r="R342">
+        <v>2.1</v>
+      </c>
+      <c r="S342">
+        <v>3.6</v>
+      </c>
+      <c r="T342">
+        <v>1.4</v>
+      </c>
+      <c r="U342">
+        <v>2.75</v>
+      </c>
+      <c r="V342">
+        <v>3</v>
+      </c>
+      <c r="W342">
+        <v>1.36</v>
+      </c>
+      <c r="X342">
+        <v>9</v>
+      </c>
+      <c r="Y342">
+        <v>1.07</v>
+      </c>
+      <c r="Z342">
+        <v>2.45</v>
+      </c>
+      <c r="AA342">
+        <v>3.18</v>
+      </c>
+      <c r="AB342">
+        <v>2.88</v>
+      </c>
+      <c r="AC342">
+        <v>1.06</v>
+      </c>
+      <c r="AD342">
+        <v>8.5</v>
+      </c>
+      <c r="AE342">
+        <v>1.33</v>
+      </c>
+      <c r="AF342">
+        <v>3.25</v>
+      </c>
+      <c r="AG342">
+        <v>1.95</v>
+      </c>
+      <c r="AH342">
+        <v>1.79</v>
+      </c>
+      <c r="AI342">
+        <v>1.73</v>
+      </c>
+      <c r="AJ342">
+        <v>2</v>
+      </c>
+      <c r="AK342">
+        <v>1.4</v>
+      </c>
+      <c r="AL342">
+        <v>1.28</v>
+      </c>
+      <c r="AM342">
+        <v>1.55</v>
+      </c>
+      <c r="AN342">
+        <v>1.5</v>
+      </c>
+      <c r="AO342">
+        <v>1.67</v>
+      </c>
+      <c r="AP342">
+        <v>1.47</v>
+      </c>
+      <c r="AQ342">
+        <v>1.63</v>
+      </c>
+      <c r="AR342">
+        <v>1.39</v>
+      </c>
+      <c r="AS342">
+        <v>1.2</v>
+      </c>
+      <c r="AT342">
+        <v>2.59</v>
+      </c>
+      <c r="AU342">
+        <v>6</v>
+      </c>
+      <c r="AV342">
+        <v>6</v>
+      </c>
+      <c r="AW342">
+        <v>4</v>
+      </c>
+      <c r="AX342">
+        <v>9</v>
+      </c>
+      <c r="AY342">
+        <v>11</v>
+      </c>
+      <c r="AZ342">
+        <v>19</v>
+      </c>
+      <c r="BA342">
+        <v>4</v>
+      </c>
+      <c r="BB342">
+        <v>5</v>
+      </c>
+      <c r="BC342">
+        <v>9</v>
+      </c>
+      <c r="BD342">
+        <v>1.9</v>
+      </c>
+      <c r="BE342">
+        <v>6.5</v>
+      </c>
+      <c r="BF342">
+        <v>2.08</v>
+      </c>
+      <c r="BG342">
+        <v>1.25</v>
+      </c>
+      <c r="BH342">
+        <v>3.45</v>
+      </c>
+      <c r="BI342">
+        <v>1.44</v>
+      </c>
+      <c r="BJ342">
+        <v>2.55</v>
+      </c>
+      <c r="BK342">
+        <v>1.72</v>
+      </c>
+      <c r="BL342">
+        <v>1.98</v>
+      </c>
+      <c r="BM342">
+        <v>2.1</v>
+      </c>
+      <c r="BN342">
+        <v>1.63</v>
+      </c>
+      <c r="BO342">
+        <v>2.65</v>
+      </c>
+      <c r="BP342">
+        <v>1.41</v>
+      </c>
+    </row>
+    <row r="343" spans="1:68">
+      <c r="A343" s="1">
+        <v>342</v>
+      </c>
+      <c r="B343">
+        <v>7476905</v>
+      </c>
+      <c r="C343" t="s">
+        <v>68</v>
+      </c>
+      <c r="D343" t="s">
+        <v>69</v>
+      </c>
+      <c r="E343" s="2">
+        <v>45696.39583333334</v>
+      </c>
+      <c r="F343">
+        <v>31</v>
+      </c>
+      <c r="G343" t="s">
+        <v>92</v>
+      </c>
+      <c r="H343" t="s">
+        <v>77</v>
+      </c>
+      <c r="I343">
+        <v>1</v>
+      </c>
+      <c r="J343">
+        <v>0</v>
+      </c>
+      <c r="K343">
+        <v>1</v>
+      </c>
+      <c r="L343">
+        <v>1</v>
+      </c>
+      <c r="M343">
+        <v>0</v>
+      </c>
+      <c r="N343">
+        <v>1</v>
+      </c>
+      <c r="O343" t="s">
+        <v>122</v>
+      </c>
+      <c r="P343" t="s">
+        <v>101</v>
+      </c>
+      <c r="Q343">
+        <v>2.2</v>
+      </c>
+      <c r="R343">
+        <v>2.1</v>
+      </c>
+      <c r="S343">
+        <v>6</v>
+      </c>
+      <c r="T343">
+        <v>1.44</v>
+      </c>
+      <c r="U343">
+        <v>2.63</v>
+      </c>
+      <c r="V343">
+        <v>3.25</v>
+      </c>
+      <c r="W343">
+        <v>1.33</v>
+      </c>
+      <c r="X343">
+        <v>9</v>
+      </c>
+      <c r="Y343">
+        <v>1.07</v>
+      </c>
+      <c r="Z343">
+        <v>1.52</v>
+      </c>
+      <c r="AA343">
+        <v>4.1</v>
+      </c>
+      <c r="AB343">
+        <v>6</v>
+      </c>
+      <c r="AC343">
+        <v>1.05</v>
+      </c>
+      <c r="AD343">
+        <v>9</v>
+      </c>
+      <c r="AE343">
+        <v>1.35</v>
+      </c>
+      <c r="AF343">
+        <v>3.1</v>
+      </c>
+      <c r="AG343">
+        <v>1.91</v>
+      </c>
+      <c r="AH343">
+        <v>1.83</v>
+      </c>
+      <c r="AI343">
+        <v>2.1</v>
+      </c>
+      <c r="AJ343">
+        <v>1.67</v>
+      </c>
+      <c r="AK343">
+        <v>1.14</v>
+      </c>
+      <c r="AL343">
+        <v>1.2</v>
+      </c>
+      <c r="AM343">
+        <v>2.3</v>
+      </c>
+      <c r="AN343">
+        <v>2.36</v>
+      </c>
+      <c r="AO343">
+        <v>0.87</v>
+      </c>
+      <c r="AP343">
+        <v>2.4</v>
+      </c>
+      <c r="AQ343">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="AR343">
+        <v>1.45</v>
+      </c>
+      <c r="AS343">
+        <v>1.12</v>
+      </c>
+      <c r="AT343">
+        <v>2.57</v>
+      </c>
+      <c r="AU343">
+        <v>4</v>
+      </c>
+      <c r="AV343">
+        <v>2</v>
+      </c>
+      <c r="AW343">
+        <v>5</v>
+      </c>
+      <c r="AX343">
+        <v>9</v>
+      </c>
+      <c r="AY343">
+        <v>10</v>
+      </c>
+      <c r="AZ343">
+        <v>13</v>
+      </c>
+      <c r="BA343">
+        <v>2</v>
+      </c>
+      <c r="BB343">
+        <v>2</v>
+      </c>
+      <c r="BC343">
+        <v>4</v>
+      </c>
+      <c r="BD343">
+        <v>1.43</v>
+      </c>
+      <c r="BE343">
+        <v>7</v>
+      </c>
+      <c r="BF343">
+        <v>3.15</v>
+      </c>
+      <c r="BG343">
+        <v>1.3</v>
+      </c>
+      <c r="BH343">
+        <v>3.15</v>
+      </c>
+      <c r="BI343">
+        <v>1.5</v>
+      </c>
+      <c r="BJ343">
+        <v>2.33</v>
+      </c>
+      <c r="BK343">
+        <v>1.84</v>
+      </c>
+      <c r="BL343">
+        <v>1.84</v>
+      </c>
+      <c r="BM343">
+        <v>2.3</v>
+      </c>
+      <c r="BN343">
+        <v>1.53</v>
+      </c>
+      <c r="BO343">
+        <v>2.95</v>
+      </c>
+      <c r="BP343">
+        <v>1.33</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/England EFL League Two_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/England EFL League Two_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2120" uniqueCount="434">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2174" uniqueCount="440">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -919,6 +919,21 @@
     <t>['20', '45', '63']</t>
   </si>
   <si>
+    <t>['69', '74']</t>
+  </si>
+  <si>
+    <t>['60', '84', '90+5']</t>
+  </si>
+  <si>
+    <t>['66', '75']</t>
+  </si>
+  <si>
+    <t>['51', '61']</t>
+  </si>
+  <si>
+    <t>['62', '83']</t>
+  </si>
+  <si>
     <t>['1', '9']</t>
   </si>
   <si>
@@ -1317,6 +1332,9 @@
   <si>
     <t>['31', '40', '87']</t>
   </si>
+  <si>
+    <t>['33', '45+2', '82']</t>
+  </si>
 </sst>
 </file>
 
@@ -1677,7 +1695,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP343"/>
+  <dimension ref="A1:BP352"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -2139,7 +2157,7 @@
         <v>95</v>
       </c>
       <c r="P3" t="s">
-        <v>301</v>
+        <v>306</v>
       </c>
       <c r="Q3">
         <v>2.5</v>
@@ -2423,7 +2441,7 @@
         <v>0</v>
       </c>
       <c r="AP4">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AQ4">
         <v>1.47</v>
@@ -2551,7 +2569,7 @@
         <v>97</v>
       </c>
       <c r="P5" t="s">
-        <v>302</v>
+        <v>307</v>
       </c>
       <c r="Q5">
         <v>2.4</v>
@@ -2632,7 +2650,7 @@
         <v>1.8</v>
       </c>
       <c r="AQ5">
-        <v>0.67</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="AR5">
         <v>0</v>
@@ -3041,7 +3059,7 @@
         <v>0</v>
       </c>
       <c r="AP7">
-        <v>1.47</v>
+        <v>1.56</v>
       </c>
       <c r="AQ7">
         <v>1.47</v>
@@ -3250,7 +3268,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ8">
-        <v>0.86</v>
+        <v>0.8</v>
       </c>
       <c r="AR8">
         <v>0</v>
@@ -3375,7 +3393,7 @@
         <v>101</v>
       </c>
       <c r="P9" t="s">
-        <v>303</v>
+        <v>308</v>
       </c>
       <c r="Q9">
         <v>2.75</v>
@@ -3456,7 +3474,7 @@
         <v>1.13</v>
       </c>
       <c r="AQ9">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="AR9">
         <v>0</v>
@@ -3581,7 +3599,7 @@
         <v>102</v>
       </c>
       <c r="P10" t="s">
-        <v>304</v>
+        <v>309</v>
       </c>
       <c r="Q10">
         <v>2.63</v>
@@ -3659,7 +3677,7 @@
         <v>0</v>
       </c>
       <c r="AP10">
-        <v>1.56</v>
+        <v>1.47</v>
       </c>
       <c r="AQ10">
         <v>1</v>
@@ -3787,7 +3805,7 @@
         <v>101</v>
       </c>
       <c r="P11" t="s">
-        <v>305</v>
+        <v>310</v>
       </c>
       <c r="Q11">
         <v>2.88</v>
@@ -3865,7 +3883,7 @@
         <v>0</v>
       </c>
       <c r="AP11">
-        <v>1.73</v>
+        <v>1.81</v>
       </c>
       <c r="AQ11">
         <v>1.63</v>
@@ -4280,7 +4298,7 @@
         <v>2.4</v>
       </c>
       <c r="AQ13">
-        <v>0.88</v>
+        <v>0.82</v>
       </c>
       <c r="AR13">
         <v>0</v>
@@ -4692,7 +4710,7 @@
         <v>1.07</v>
       </c>
       <c r="AQ15">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="AR15">
         <v>0</v>
@@ -4817,7 +4835,7 @@
         <v>105</v>
       </c>
       <c r="P16" t="s">
-        <v>306</v>
+        <v>311</v>
       </c>
       <c r="Q16">
         <v>2.88</v>
@@ -4895,7 +4913,7 @@
         <v>0</v>
       </c>
       <c r="AP16">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AQ16">
         <v>0.8100000000000001</v>
@@ -5101,7 +5119,7 @@
         <v>0</v>
       </c>
       <c r="AP17">
-        <v>1.43</v>
+        <v>1.53</v>
       </c>
       <c r="AQ17">
         <v>1.08</v>
@@ -5229,7 +5247,7 @@
         <v>101</v>
       </c>
       <c r="P18" t="s">
-        <v>307</v>
+        <v>312</v>
       </c>
       <c r="Q18">
         <v>3.4</v>
@@ -5307,7 +5325,7 @@
         <v>0</v>
       </c>
       <c r="AP18">
-        <v>1.86</v>
+        <v>1.73</v>
       </c>
       <c r="AQ18">
         <v>1.21</v>
@@ -5435,7 +5453,7 @@
         <v>107</v>
       </c>
       <c r="P19" t="s">
-        <v>308</v>
+        <v>313</v>
       </c>
       <c r="Q19">
         <v>3</v>
@@ -5513,10 +5531,10 @@
         <v>0</v>
       </c>
       <c r="AP19">
-        <v>1.43</v>
+        <v>1.53</v>
       </c>
       <c r="AQ19">
-        <v>0.85</v>
+        <v>0.79</v>
       </c>
       <c r="AR19">
         <v>0</v>
@@ -5722,7 +5740,7 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="AQ20">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR20">
         <v>0</v>
@@ -6134,7 +6152,7 @@
         <v>1.77</v>
       </c>
       <c r="AQ22">
-        <v>0.57</v>
+        <v>0.53</v>
       </c>
       <c r="AR22">
         <v>0</v>
@@ -6259,7 +6277,7 @@
         <v>101</v>
       </c>
       <c r="P23" t="s">
-        <v>309</v>
+        <v>314</v>
       </c>
       <c r="Q23">
         <v>3</v>
@@ -6340,7 +6358,7 @@
         <v>1.47</v>
       </c>
       <c r="AQ23">
-        <v>1.77</v>
+        <v>1.64</v>
       </c>
       <c r="AR23">
         <v>0</v>
@@ -6671,7 +6689,7 @@
         <v>109</v>
       </c>
       <c r="P25" t="s">
-        <v>310</v>
+        <v>315</v>
       </c>
       <c r="Q25">
         <v>2.63</v>
@@ -6749,7 +6767,7 @@
         <v>0</v>
       </c>
       <c r="AP25">
-        <v>1.85</v>
+        <v>1.93</v>
       </c>
       <c r="AQ25">
         <v>1.17</v>
@@ -6877,7 +6895,7 @@
         <v>110</v>
       </c>
       <c r="P26" t="s">
-        <v>311</v>
+        <v>316</v>
       </c>
       <c r="Q26">
         <v>2.38</v>
@@ -6955,7 +6973,7 @@
         <v>0</v>
       </c>
       <c r="AP26">
-        <v>1.85</v>
+        <v>1.93</v>
       </c>
       <c r="AQ26">
         <v>1.47</v>
@@ -7164,7 +7182,7 @@
         <v>1.29</v>
       </c>
       <c r="AQ27">
-        <v>1.77</v>
+        <v>1.64</v>
       </c>
       <c r="AR27">
         <v>0.86</v>
@@ -7367,7 +7385,7 @@
         <v>1</v>
       </c>
       <c r="AP28">
-        <v>1.86</v>
+        <v>1.73</v>
       </c>
       <c r="AQ28">
         <v>1</v>
@@ -7576,7 +7594,7 @@
         <v>1.87</v>
       </c>
       <c r="AQ29">
-        <v>0.88</v>
+        <v>0.82</v>
       </c>
       <c r="AR29">
         <v>1.39</v>
@@ -7701,7 +7719,7 @@
         <v>112</v>
       </c>
       <c r="P30" t="s">
-        <v>312</v>
+        <v>317</v>
       </c>
       <c r="Q30">
         <v>3</v>
@@ -7985,10 +8003,10 @@
         <v>0</v>
       </c>
       <c r="AP31">
-        <v>1.56</v>
+        <v>1.47</v>
       </c>
       <c r="AQ31">
-        <v>0.86</v>
+        <v>0.8</v>
       </c>
       <c r="AR31">
         <v>1.62</v>
@@ -8191,10 +8209,10 @@
         <v>3</v>
       </c>
       <c r="AP32">
-        <v>1.47</v>
+        <v>1.56</v>
       </c>
       <c r="AQ32">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR32">
         <v>1.04</v>
@@ -8606,7 +8624,7 @@
         <v>1.8</v>
       </c>
       <c r="AQ34">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="AR34">
         <v>1.55</v>
@@ -8812,7 +8830,7 @@
         <v>2.4</v>
       </c>
       <c r="AQ35">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="AR35">
         <v>1.26</v>
@@ -9015,7 +9033,7 @@
         <v>3</v>
       </c>
       <c r="AP36">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AQ36">
         <v>1.63</v>
@@ -9143,7 +9161,7 @@
         <v>101</v>
       </c>
       <c r="P37" t="s">
-        <v>313</v>
+        <v>318</v>
       </c>
       <c r="Q37">
         <v>2.6</v>
@@ -9221,7 +9239,7 @@
         <v>1</v>
       </c>
       <c r="AP37">
-        <v>1.43</v>
+        <v>1.53</v>
       </c>
       <c r="AQ37">
         <v>0.8100000000000001</v>
@@ -9349,7 +9367,7 @@
         <v>117</v>
       </c>
       <c r="P38" t="s">
-        <v>314</v>
+        <v>319</v>
       </c>
       <c r="Q38">
         <v>2.88</v>
@@ -9761,7 +9779,7 @@
         <v>119</v>
       </c>
       <c r="P40" t="s">
-        <v>315</v>
+        <v>320</v>
       </c>
       <c r="Q40">
         <v>3</v>
@@ -10048,7 +10066,7 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="AQ41">
-        <v>0.67</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="AR41">
         <v>1.1</v>
@@ -10173,7 +10191,7 @@
         <v>101</v>
       </c>
       <c r="P42" t="s">
-        <v>316</v>
+        <v>321</v>
       </c>
       <c r="Q42">
         <v>3.75</v>
@@ -10460,7 +10478,7 @@
         <v>2.4</v>
       </c>
       <c r="AQ43">
-        <v>0.85</v>
+        <v>0.79</v>
       </c>
       <c r="AR43">
         <v>0.97</v>
@@ -10585,7 +10603,7 @@
         <v>121</v>
       </c>
       <c r="P44" t="s">
-        <v>317</v>
+        <v>322</v>
       </c>
       <c r="Q44">
         <v>2.75</v>
@@ -10666,7 +10684,7 @@
         <v>0.64</v>
       </c>
       <c r="AQ44">
-        <v>0.57</v>
+        <v>0.53</v>
       </c>
       <c r="AR44">
         <v>1.2</v>
@@ -10791,7 +10809,7 @@
         <v>122</v>
       </c>
       <c r="P45" t="s">
-        <v>318</v>
+        <v>323</v>
       </c>
       <c r="Q45">
         <v>2.63</v>
@@ -11075,7 +11093,7 @@
         <v>0</v>
       </c>
       <c r="AP46">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AQ46">
         <v>1.21</v>
@@ -11409,7 +11427,7 @@
         <v>125</v>
       </c>
       <c r="P48" t="s">
-        <v>319</v>
+        <v>324</v>
       </c>
       <c r="Q48">
         <v>3.5</v>
@@ -11487,7 +11505,7 @@
         <v>3</v>
       </c>
       <c r="AP48">
-        <v>1.43</v>
+        <v>1.53</v>
       </c>
       <c r="AQ48">
         <v>1</v>
@@ -11693,7 +11711,7 @@
         <v>0</v>
       </c>
       <c r="AP49">
-        <v>1.73</v>
+        <v>1.81</v>
       </c>
       <c r="AQ49">
         <v>1.08</v>
@@ -11821,7 +11839,7 @@
         <v>127</v>
       </c>
       <c r="P50" t="s">
-        <v>320</v>
+        <v>325</v>
       </c>
       <c r="Q50">
         <v>3.6</v>
@@ -12027,7 +12045,7 @@
         <v>103</v>
       </c>
       <c r="P51" t="s">
-        <v>321</v>
+        <v>326</v>
       </c>
       <c r="Q51">
         <v>2.5</v>
@@ -12105,7 +12123,7 @@
         <v>1</v>
       </c>
       <c r="AP51">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AQ51">
         <v>1</v>
@@ -12723,10 +12741,10 @@
         <v>1.5</v>
       </c>
       <c r="AP54">
-        <v>1.43</v>
+        <v>1.53</v>
       </c>
       <c r="AQ54">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="AR54">
         <v>2.03</v>
@@ -12929,10 +12947,10 @@
         <v>0</v>
       </c>
       <c r="AP55">
-        <v>1.86</v>
+        <v>1.73</v>
       </c>
       <c r="AQ55">
-        <v>0.88</v>
+        <v>0.82</v>
       </c>
       <c r="AR55">
         <v>1</v>
@@ -13138,7 +13156,7 @@
         <v>1.87</v>
       </c>
       <c r="AQ56">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR56">
         <v>1.21</v>
@@ -13344,7 +13362,7 @@
         <v>2.4</v>
       </c>
       <c r="AQ57">
-        <v>0.86</v>
+        <v>0.8</v>
       </c>
       <c r="AR57">
         <v>1.74</v>
@@ -13547,10 +13565,10 @@
         <v>1.5</v>
       </c>
       <c r="AP58">
-        <v>1.56</v>
+        <v>1.47</v>
       </c>
       <c r="AQ58">
-        <v>1.77</v>
+        <v>1.64</v>
       </c>
       <c r="AR58">
         <v>1.63</v>
@@ -13753,7 +13771,7 @@
         <v>0</v>
       </c>
       <c r="AP59">
-        <v>1.85</v>
+        <v>1.93</v>
       </c>
       <c r="AQ59">
         <v>1</v>
@@ -14374,7 +14392,7 @@
         <v>1.47</v>
       </c>
       <c r="AQ62">
-        <v>0.67</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="AR62">
         <v>1.82</v>
@@ -14577,10 +14595,10 @@
         <v>0</v>
       </c>
       <c r="AP63">
-        <v>1.73</v>
+        <v>1.81</v>
       </c>
       <c r="AQ63">
-        <v>0.85</v>
+        <v>0.79</v>
       </c>
       <c r="AR63">
         <v>1.34</v>
@@ -14705,7 +14723,7 @@
         <v>139</v>
       </c>
       <c r="P64" t="s">
-        <v>312</v>
+        <v>317</v>
       </c>
       <c r="Q64">
         <v>3</v>
@@ -15117,7 +15135,7 @@
         <v>141</v>
       </c>
       <c r="P66" t="s">
-        <v>322</v>
+        <v>327</v>
       </c>
       <c r="Q66">
         <v>3.75</v>
@@ -15404,7 +15422,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ67">
-        <v>0.57</v>
+        <v>0.53</v>
       </c>
       <c r="AR67">
         <v>1.34</v>
@@ -15607,7 +15625,7 @@
         <v>1.5</v>
       </c>
       <c r="AP68">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AQ68">
         <v>1.47</v>
@@ -15735,7 +15753,7 @@
         <v>143</v>
       </c>
       <c r="P69" t="s">
-        <v>323</v>
+        <v>328</v>
       </c>
       <c r="Q69">
         <v>3.2</v>
@@ -15941,7 +15959,7 @@
         <v>144</v>
       </c>
       <c r="P70" t="s">
-        <v>324</v>
+        <v>329</v>
       </c>
       <c r="Q70">
         <v>3.25</v>
@@ -16019,7 +16037,7 @@
         <v>1.5</v>
       </c>
       <c r="AP70">
-        <v>1.43</v>
+        <v>1.53</v>
       </c>
       <c r="AQ70">
         <v>0.64</v>
@@ -16147,7 +16165,7 @@
         <v>145</v>
       </c>
       <c r="P71" t="s">
-        <v>325</v>
+        <v>330</v>
       </c>
       <c r="Q71">
         <v>3</v>
@@ -16353,7 +16371,7 @@
         <v>146</v>
       </c>
       <c r="P72" t="s">
-        <v>326</v>
+        <v>331</v>
       </c>
       <c r="Q72">
         <v>4</v>
@@ -16431,7 +16449,7 @@
         <v>2</v>
       </c>
       <c r="AP72">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AQ72">
         <v>1.63</v>
@@ -16640,7 +16658,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ73">
-        <v>0.85</v>
+        <v>0.79</v>
       </c>
       <c r="AR73">
         <v>1.28</v>
@@ -16765,7 +16783,7 @@
         <v>101</v>
       </c>
       <c r="P74" t="s">
-        <v>327</v>
+        <v>332</v>
       </c>
       <c r="Q74">
         <v>2.63</v>
@@ -16846,7 +16864,7 @@
         <v>1.47</v>
       </c>
       <c r="AQ74">
-        <v>0.86</v>
+        <v>0.8</v>
       </c>
       <c r="AR74">
         <v>1.69</v>
@@ -16971,7 +16989,7 @@
         <v>101</v>
       </c>
       <c r="P75" t="s">
-        <v>328</v>
+        <v>333</v>
       </c>
       <c r="Q75">
         <v>3.4</v>
@@ -17049,10 +17067,10 @@
         <v>1</v>
       </c>
       <c r="AP75">
-        <v>1.73</v>
+        <v>1.81</v>
       </c>
       <c r="AQ75">
-        <v>1.77</v>
+        <v>1.64</v>
       </c>
       <c r="AR75">
         <v>1.26</v>
@@ -17177,7 +17195,7 @@
         <v>101</v>
       </c>
       <c r="P76" t="s">
-        <v>312</v>
+        <v>317</v>
       </c>
       <c r="Q76">
         <v>2.6</v>
@@ -17255,10 +17273,10 @@
         <v>1.33</v>
       </c>
       <c r="AP76">
-        <v>1.85</v>
+        <v>1.93</v>
       </c>
       <c r="AQ76">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR76">
         <v>1.78</v>
@@ -17461,10 +17479,10 @@
         <v>1.33</v>
       </c>
       <c r="AP77">
-        <v>1.43</v>
+        <v>1.53</v>
       </c>
       <c r="AQ77">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="AR77">
         <v>1.15</v>
@@ -17589,7 +17607,7 @@
         <v>149</v>
       </c>
       <c r="P78" t="s">
-        <v>329</v>
+        <v>334</v>
       </c>
       <c r="Q78">
         <v>2.88</v>
@@ -17667,7 +17685,7 @@
         <v>1</v>
       </c>
       <c r="AP78">
-        <v>1.56</v>
+        <v>1.47</v>
       </c>
       <c r="AQ78">
         <v>1.6</v>
@@ -17873,10 +17891,10 @@
         <v>1.33</v>
       </c>
       <c r="AP79">
-        <v>1.43</v>
+        <v>1.53</v>
       </c>
       <c r="AQ79">
-        <v>0.57</v>
+        <v>0.53</v>
       </c>
       <c r="AR79">
         <v>1.92</v>
@@ -18082,7 +18100,7 @@
         <v>2.4</v>
       </c>
       <c r="AQ80">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="AR80">
         <v>1.6</v>
@@ -18285,10 +18303,10 @@
         <v>1</v>
       </c>
       <c r="AP81">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AQ81">
-        <v>0.67</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="AR81">
         <v>1.2</v>
@@ -18491,7 +18509,7 @@
         <v>1.33</v>
       </c>
       <c r="AP82">
-        <v>1.86</v>
+        <v>1.73</v>
       </c>
       <c r="AQ82">
         <v>0.8100000000000001</v>
@@ -18619,7 +18637,7 @@
         <v>153</v>
       </c>
       <c r="P83" t="s">
-        <v>330</v>
+        <v>335</v>
       </c>
       <c r="Q83">
         <v>2.2</v>
@@ -18697,10 +18715,10 @@
         <v>0</v>
       </c>
       <c r="AP83">
-        <v>1.47</v>
+        <v>1.56</v>
       </c>
       <c r="AQ83">
-        <v>0.88</v>
+        <v>0.82</v>
       </c>
       <c r="AR83">
         <v>1.21</v>
@@ -19855,7 +19873,7 @@
         <v>157</v>
       </c>
       <c r="P89" t="s">
-        <v>331</v>
+        <v>336</v>
       </c>
       <c r="Q89">
         <v>3.75</v>
@@ -20267,7 +20285,7 @@
         <v>101</v>
       </c>
       <c r="P91" t="s">
-        <v>332</v>
+        <v>337</v>
       </c>
       <c r="Q91">
         <v>2.75</v>
@@ -20473,7 +20491,7 @@
         <v>101</v>
       </c>
       <c r="P92" t="s">
-        <v>333</v>
+        <v>338</v>
       </c>
       <c r="Q92">
         <v>3.4</v>
@@ -20679,7 +20697,7 @@
         <v>159</v>
       </c>
       <c r="P93" t="s">
-        <v>334</v>
+        <v>339</v>
       </c>
       <c r="Q93">
         <v>2.75</v>
@@ -21091,7 +21109,7 @@
         <v>161</v>
       </c>
       <c r="P95" t="s">
-        <v>335</v>
+        <v>340</v>
       </c>
       <c r="Q95">
         <v>2.5</v>
@@ -21297,7 +21315,7 @@
         <v>162</v>
       </c>
       <c r="P96" t="s">
-        <v>336</v>
+        <v>341</v>
       </c>
       <c r="Q96">
         <v>4.5</v>
@@ -22121,7 +22139,7 @@
         <v>166</v>
       </c>
       <c r="P100" t="s">
-        <v>337</v>
+        <v>342</v>
       </c>
       <c r="Q100">
         <v>2.75</v>
@@ -22533,7 +22551,7 @@
         <v>167</v>
       </c>
       <c r="P102" t="s">
-        <v>338</v>
+        <v>343</v>
       </c>
       <c r="Q102">
         <v>2.88</v>
@@ -22739,7 +22757,7 @@
         <v>101</v>
       </c>
       <c r="P103" t="s">
-        <v>339</v>
+        <v>344</v>
       </c>
       <c r="Q103">
         <v>3</v>
@@ -22945,7 +22963,7 @@
         <v>168</v>
       </c>
       <c r="P104" t="s">
-        <v>340</v>
+        <v>345</v>
       </c>
       <c r="Q104">
         <v>4</v>
@@ -23357,7 +23375,7 @@
         <v>101</v>
       </c>
       <c r="P106" t="s">
-        <v>341</v>
+        <v>346</v>
       </c>
       <c r="Q106">
         <v>3.6</v>
@@ -23435,7 +23453,7 @@
         <v>1</v>
       </c>
       <c r="AP106">
-        <v>1.43</v>
+        <v>1.53</v>
       </c>
       <c r="AQ106">
         <v>1.6</v>
@@ -23641,10 +23659,10 @@
         <v>1</v>
       </c>
       <c r="AP107">
-        <v>1.47</v>
+        <v>1.56</v>
       </c>
       <c r="AQ107">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="AR107">
         <v>1.69</v>
@@ -24053,7 +24071,7 @@
         <v>1.75</v>
       </c>
       <c r="AP109">
-        <v>1.85</v>
+        <v>1.93</v>
       </c>
       <c r="AQ109">
         <v>1.63</v>
@@ -24259,10 +24277,10 @@
         <v>1</v>
       </c>
       <c r="AP110">
-        <v>1.56</v>
+        <v>1.47</v>
       </c>
       <c r="AQ110">
-        <v>0.57</v>
+        <v>0.53</v>
       </c>
       <c r="AR110">
         <v>1.38</v>
@@ -24465,10 +24483,10 @@
         <v>1.75</v>
       </c>
       <c r="AP111">
-        <v>1.86</v>
+        <v>1.73</v>
       </c>
       <c r="AQ111">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR111">
         <v>1.19</v>
@@ -24671,10 +24689,10 @@
         <v>1.33</v>
       </c>
       <c r="AP112">
-        <v>1.73</v>
+        <v>1.81</v>
       </c>
       <c r="AQ112">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="AR112">
         <v>1.25</v>
@@ -24799,7 +24817,7 @@
         <v>172</v>
       </c>
       <c r="P113" t="s">
-        <v>342</v>
+        <v>347</v>
       </c>
       <c r="Q113">
         <v>2.6</v>
@@ -24880,7 +24898,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ113">
-        <v>1.77</v>
+        <v>1.64</v>
       </c>
       <c r="AR113">
         <v>1.34</v>
@@ -25005,7 +25023,7 @@
         <v>173</v>
       </c>
       <c r="P114" t="s">
-        <v>343</v>
+        <v>348</v>
       </c>
       <c r="Q114">
         <v>2.4</v>
@@ -25083,10 +25101,10 @@
         <v>0.25</v>
       </c>
       <c r="AP114">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AQ114">
-        <v>0.85</v>
+        <v>0.79</v>
       </c>
       <c r="AR114">
         <v>1.49</v>
@@ -25289,10 +25307,10 @@
         <v>0.25</v>
       </c>
       <c r="AP115">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AQ115">
-        <v>0.88</v>
+        <v>0.82</v>
       </c>
       <c r="AR115">
         <v>1.49</v>
@@ -25495,10 +25513,10 @@
         <v>0.75</v>
       </c>
       <c r="AP116">
-        <v>1.43</v>
+        <v>1.53</v>
       </c>
       <c r="AQ116">
-        <v>0.86</v>
+        <v>0.8</v>
       </c>
       <c r="AR116">
         <v>1.85</v>
@@ -25704,7 +25722,7 @@
         <v>2.4</v>
       </c>
       <c r="AQ117">
-        <v>0.67</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="AR117">
         <v>1.54</v>
@@ -25829,7 +25847,7 @@
         <v>176</v>
       </c>
       <c r="P118" t="s">
-        <v>344</v>
+        <v>349</v>
       </c>
       <c r="Q118">
         <v>2.5</v>
@@ -26035,7 +26053,7 @@
         <v>101</v>
       </c>
       <c r="P119" t="s">
-        <v>345</v>
+        <v>350</v>
       </c>
       <c r="Q119">
         <v>3.4</v>
@@ -26241,7 +26259,7 @@
         <v>94</v>
       </c>
       <c r="P120" t="s">
-        <v>346</v>
+        <v>351</v>
       </c>
       <c r="Q120">
         <v>2.88</v>
@@ -26319,7 +26337,7 @@
         <v>1.2</v>
       </c>
       <c r="AP120">
-        <v>1.73</v>
+        <v>1.81</v>
       </c>
       <c r="AQ120">
         <v>1.47</v>
@@ -26525,7 +26543,7 @@
         <v>2</v>
       </c>
       <c r="AP121">
-        <v>1.56</v>
+        <v>1.47</v>
       </c>
       <c r="AQ121">
         <v>1.63</v>
@@ -26734,7 +26752,7 @@
         <v>1.13</v>
       </c>
       <c r="AQ122">
-        <v>0.67</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="AR122">
         <v>1.16</v>
@@ -26859,7 +26877,7 @@
         <v>178</v>
       </c>
       <c r="P123" t="s">
-        <v>347</v>
+        <v>352</v>
       </c>
       <c r="Q123">
         <v>2.38</v>
@@ -27271,7 +27289,7 @@
         <v>101</v>
       </c>
       <c r="P125" t="s">
-        <v>329</v>
+        <v>334</v>
       </c>
       <c r="Q125">
         <v>2.1</v>
@@ -27349,10 +27367,10 @@
         <v>0.2</v>
       </c>
       <c r="AP125">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AQ125">
-        <v>0.88</v>
+        <v>0.82</v>
       </c>
       <c r="AR125">
         <v>1.43</v>
@@ -27558,7 +27576,7 @@
         <v>2.14</v>
       </c>
       <c r="AQ126">
-        <v>0.86</v>
+        <v>0.8</v>
       </c>
       <c r="AR126">
         <v>1.5</v>
@@ -27683,7 +27701,7 @@
         <v>180</v>
       </c>
       <c r="P127" t="s">
-        <v>348</v>
+        <v>353</v>
       </c>
       <c r="Q127">
         <v>3.25</v>
@@ -27889,7 +27907,7 @@
         <v>101</v>
       </c>
       <c r="P128" t="s">
-        <v>349</v>
+        <v>354</v>
       </c>
       <c r="Q128">
         <v>4.75</v>
@@ -28173,7 +28191,7 @@
         <v>1.2</v>
       </c>
       <c r="AP129">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AQ129">
         <v>0.64</v>
@@ -28379,10 +28397,10 @@
         <v>1</v>
       </c>
       <c r="AP130">
-        <v>1.85</v>
+        <v>1.93</v>
       </c>
       <c r="AQ130">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="AR130">
         <v>1.71</v>
@@ -28507,7 +28525,7 @@
         <v>182</v>
       </c>
       <c r="P131" t="s">
-        <v>350</v>
+        <v>355</v>
       </c>
       <c r="Q131">
         <v>2.63</v>
@@ -28713,7 +28731,7 @@
         <v>183</v>
       </c>
       <c r="P132" t="s">
-        <v>351</v>
+        <v>356</v>
       </c>
       <c r="Q132">
         <v>3.5</v>
@@ -28997,7 +29015,7 @@
         <v>0.75</v>
       </c>
       <c r="AP133">
-        <v>1.86</v>
+        <v>1.73</v>
       </c>
       <c r="AQ133">
         <v>1.36</v>
@@ -29125,7 +29143,7 @@
         <v>185</v>
       </c>
       <c r="P134" t="s">
-        <v>352</v>
+        <v>357</v>
       </c>
       <c r="Q134">
         <v>4</v>
@@ -29331,7 +29349,7 @@
         <v>147</v>
       </c>
       <c r="P135" t="s">
-        <v>353</v>
+        <v>358</v>
       </c>
       <c r="Q135">
         <v>2.6</v>
@@ -29409,10 +29427,10 @@
         <v>0.2</v>
       </c>
       <c r="AP135">
-        <v>1.43</v>
+        <v>1.53</v>
       </c>
       <c r="AQ135">
-        <v>0.85</v>
+        <v>0.79</v>
       </c>
       <c r="AR135">
         <v>1.78</v>
@@ -29537,7 +29555,7 @@
         <v>186</v>
       </c>
       <c r="P136" t="s">
-        <v>354</v>
+        <v>359</v>
       </c>
       <c r="Q136">
         <v>3.6</v>
@@ -29615,10 +29633,10 @@
         <v>1.4</v>
       </c>
       <c r="AP136">
-        <v>1.43</v>
+        <v>1.53</v>
       </c>
       <c r="AQ136">
-        <v>1.77</v>
+        <v>1.64</v>
       </c>
       <c r="AR136">
         <v>1.16</v>
@@ -29743,7 +29761,7 @@
         <v>187</v>
       </c>
       <c r="P137" t="s">
-        <v>355</v>
+        <v>360</v>
       </c>
       <c r="Q137">
         <v>3</v>
@@ -29824,7 +29842,7 @@
         <v>1.07</v>
       </c>
       <c r="AQ137">
-        <v>0.57</v>
+        <v>0.53</v>
       </c>
       <c r="AR137">
         <v>1.32</v>
@@ -30030,7 +30048,7 @@
         <v>2.4</v>
       </c>
       <c r="AQ138">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR138">
         <v>1.55</v>
@@ -30155,7 +30173,7 @@
         <v>185</v>
       </c>
       <c r="P139" t="s">
-        <v>338</v>
+        <v>343</v>
       </c>
       <c r="Q139">
         <v>2.5</v>
@@ -30361,7 +30379,7 @@
         <v>189</v>
       </c>
       <c r="P140" t="s">
-        <v>329</v>
+        <v>334</v>
       </c>
       <c r="Q140">
         <v>2.25</v>
@@ -30442,7 +30460,7 @@
         <v>2.4</v>
       </c>
       <c r="AQ140">
-        <v>0.86</v>
+        <v>0.8</v>
       </c>
       <c r="AR140">
         <v>1.55</v>
@@ -30645,7 +30663,7 @@
         <v>1.17</v>
       </c>
       <c r="AP141">
-        <v>1.73</v>
+        <v>1.81</v>
       </c>
       <c r="AQ141">
         <v>1</v>
@@ -30851,7 +30869,7 @@
         <v>0.6</v>
       </c>
       <c r="AP142">
-        <v>1.56</v>
+        <v>1.47</v>
       </c>
       <c r="AQ142">
         <v>1</v>
@@ -31185,7 +31203,7 @@
         <v>101</v>
       </c>
       <c r="P144" t="s">
-        <v>356</v>
+        <v>361</v>
       </c>
       <c r="Q144">
         <v>2.25</v>
@@ -31266,7 +31284,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ144">
-        <v>0.67</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="AR144">
         <v>1.19</v>
@@ -31469,7 +31487,7 @@
         <v>1.4</v>
       </c>
       <c r="AP145">
-        <v>1.47</v>
+        <v>1.56</v>
       </c>
       <c r="AQ145">
         <v>1.47</v>
@@ -31678,7 +31696,7 @@
         <v>1.87</v>
       </c>
       <c r="AQ146">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="AR146">
         <v>1.18</v>
@@ -31803,7 +31821,7 @@
         <v>101</v>
       </c>
       <c r="P147" t="s">
-        <v>357</v>
+        <v>362</v>
       </c>
       <c r="Q147">
         <v>3</v>
@@ -32293,7 +32311,7 @@
         <v>2</v>
       </c>
       <c r="AP149">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AQ149">
         <v>1.73</v>
@@ -32502,7 +32520,7 @@
         <v>2.14</v>
       </c>
       <c r="AQ150">
-        <v>0.88</v>
+        <v>0.82</v>
       </c>
       <c r="AR150">
         <v>1.49</v>
@@ -32627,7 +32645,7 @@
         <v>193</v>
       </c>
       <c r="P151" t="s">
-        <v>358</v>
+        <v>363</v>
       </c>
       <c r="Q151">
         <v>2.4</v>
@@ -32833,7 +32851,7 @@
         <v>194</v>
       </c>
       <c r="P152" t="s">
-        <v>359</v>
+        <v>364</v>
       </c>
       <c r="Q152">
         <v>4.5</v>
@@ -33039,7 +33057,7 @@
         <v>195</v>
       </c>
       <c r="P153" t="s">
-        <v>360</v>
+        <v>365</v>
       </c>
       <c r="Q153">
         <v>2.75</v>
@@ -33117,7 +33135,7 @@
         <v>0.8</v>
       </c>
       <c r="AP153">
-        <v>1.43</v>
+        <v>1.53</v>
       </c>
       <c r="AQ153">
         <v>1.36</v>
@@ -33326,7 +33344,7 @@
         <v>1.47</v>
       </c>
       <c r="AQ154">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR154">
         <v>1.33</v>
@@ -33451,7 +33469,7 @@
         <v>197</v>
       </c>
       <c r="P155" t="s">
-        <v>361</v>
+        <v>366</v>
       </c>
       <c r="Q155">
         <v>3</v>
@@ -33532,7 +33550,7 @@
         <v>1.77</v>
       </c>
       <c r="AQ155">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="AR155">
         <v>1.41</v>
@@ -33863,7 +33881,7 @@
         <v>198</v>
       </c>
       <c r="P157" t="s">
-        <v>362</v>
+        <v>367</v>
       </c>
       <c r="Q157">
         <v>3.4</v>
@@ -33941,7 +33959,7 @@
         <v>1.17</v>
       </c>
       <c r="AP157">
-        <v>1.43</v>
+        <v>1.53</v>
       </c>
       <c r="AQ157">
         <v>1.08</v>
@@ -34147,10 +34165,10 @@
         <v>1.33</v>
       </c>
       <c r="AP158">
-        <v>1.86</v>
+        <v>1.73</v>
       </c>
       <c r="AQ158">
-        <v>0.57</v>
+        <v>0.53</v>
       </c>
       <c r="AR158">
         <v>1.15</v>
@@ -34356,7 +34374,7 @@
         <v>0.64</v>
       </c>
       <c r="AQ159">
-        <v>0.85</v>
+        <v>0.79</v>
       </c>
       <c r="AR159">
         <v>1.63</v>
@@ -34481,7 +34499,7 @@
         <v>200</v>
       </c>
       <c r="P160" t="s">
-        <v>363</v>
+        <v>368</v>
       </c>
       <c r="Q160">
         <v>3.2</v>
@@ -34765,10 +34783,10 @@
         <v>1.67</v>
       </c>
       <c r="AP161">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AQ161">
-        <v>1.77</v>
+        <v>1.64</v>
       </c>
       <c r="AR161">
         <v>1.36</v>
@@ -34971,7 +34989,7 @@
         <v>1</v>
       </c>
       <c r="AP162">
-        <v>1.85</v>
+        <v>1.93</v>
       </c>
       <c r="AQ162">
         <v>0.8100000000000001</v>
@@ -35305,7 +35323,7 @@
         <v>203</v>
       </c>
       <c r="P164" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="Q164">
         <v>2.4</v>
@@ -35383,7 +35401,7 @@
         <v>1.17</v>
       </c>
       <c r="AP164">
-        <v>1.47</v>
+        <v>1.56</v>
       </c>
       <c r="AQ164">
         <v>1.36</v>
@@ -35589,10 +35607,10 @@
         <v>0.57</v>
       </c>
       <c r="AP165">
-        <v>1.73</v>
+        <v>1.81</v>
       </c>
       <c r="AQ165">
-        <v>0.86</v>
+        <v>0.8</v>
       </c>
       <c r="AR165">
         <v>1.4</v>
@@ -35717,7 +35735,7 @@
         <v>204</v>
       </c>
       <c r="P166" t="s">
-        <v>365</v>
+        <v>370</v>
       </c>
       <c r="Q166">
         <v>2.88</v>
@@ -35798,7 +35816,7 @@
         <v>1.13</v>
       </c>
       <c r="AQ166">
-        <v>0.88</v>
+        <v>0.82</v>
       </c>
       <c r="AR166">
         <v>1.16</v>
@@ -36129,7 +36147,7 @@
         <v>206</v>
       </c>
       <c r="P168" t="s">
-        <v>366</v>
+        <v>371</v>
       </c>
       <c r="Q168">
         <v>2.3</v>
@@ -36416,7 +36434,7 @@
         <v>1.29</v>
       </c>
       <c r="AQ169">
-        <v>0.67</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="AR169">
         <v>1.25</v>
@@ -36541,7 +36559,7 @@
         <v>208</v>
       </c>
       <c r="P170" t="s">
-        <v>367</v>
+        <v>372</v>
       </c>
       <c r="Q170">
         <v>2.5</v>
@@ -36619,7 +36637,7 @@
         <v>1</v>
       </c>
       <c r="AP170">
-        <v>1.56</v>
+        <v>1.47</v>
       </c>
       <c r="AQ170">
         <v>1</v>
@@ -36825,7 +36843,7 @@
         <v>1.14</v>
       </c>
       <c r="AP171">
-        <v>1.47</v>
+        <v>1.56</v>
       </c>
       <c r="AQ171">
         <v>1</v>
@@ -37159,7 +37177,7 @@
         <v>101</v>
       </c>
       <c r="P173" t="s">
-        <v>368</v>
+        <v>373</v>
       </c>
       <c r="Q173">
         <v>2.1</v>
@@ -37365,7 +37383,7 @@
         <v>148</v>
       </c>
       <c r="P174" t="s">
-        <v>329</v>
+        <v>334</v>
       </c>
       <c r="Q174">
         <v>3.2</v>
@@ -37446,7 +37464,7 @@
         <v>1.8</v>
       </c>
       <c r="AQ174">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="AR174">
         <v>1.27</v>
@@ -37649,7 +37667,7 @@
         <v>0.67</v>
       </c>
       <c r="AP175">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AQ175">
         <v>1.21</v>
@@ -38395,7 +38413,7 @@
         <v>210</v>
       </c>
       <c r="P179" t="s">
-        <v>369</v>
+        <v>374</v>
       </c>
       <c r="Q179">
         <v>2.3</v>
@@ -38473,10 +38491,10 @@
         <v>1</v>
       </c>
       <c r="AP179">
-        <v>1.56</v>
+        <v>1.47</v>
       </c>
       <c r="AQ179">
-        <v>0.85</v>
+        <v>0.79</v>
       </c>
       <c r="AR179">
         <v>1.29</v>
@@ -38885,7 +38903,7 @@
         <v>1.75</v>
       </c>
       <c r="AP181">
-        <v>1.86</v>
+        <v>1.73</v>
       </c>
       <c r="AQ181">
         <v>1.73</v>
@@ -39300,7 +39318,7 @@
         <v>1.07</v>
       </c>
       <c r="AQ183">
-        <v>0.86</v>
+        <v>0.8</v>
       </c>
       <c r="AR183">
         <v>1.45</v>
@@ -39425,7 +39443,7 @@
         <v>185</v>
       </c>
       <c r="P184" t="s">
-        <v>370</v>
+        <v>375</v>
       </c>
       <c r="Q184">
         <v>3.4</v>
@@ -39503,10 +39521,10 @@
         <v>0.67</v>
       </c>
       <c r="AP184">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AQ184">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="AR184">
         <v>1.39</v>
@@ -39631,7 +39649,7 @@
         <v>215</v>
       </c>
       <c r="P185" t="s">
-        <v>371</v>
+        <v>376</v>
       </c>
       <c r="Q185">
         <v>3.2</v>
@@ -39709,7 +39727,7 @@
         <v>0.88</v>
       </c>
       <c r="AP185">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AQ185">
         <v>1</v>
@@ -39915,7 +39933,7 @@
         <v>1</v>
       </c>
       <c r="AP186">
-        <v>1.43</v>
+        <v>1.53</v>
       </c>
       <c r="AQ186">
         <v>1</v>
@@ -40043,7 +40061,7 @@
         <v>217</v>
       </c>
       <c r="P187" t="s">
-        <v>372</v>
+        <v>377</v>
       </c>
       <c r="Q187">
         <v>2.2</v>
@@ -40330,7 +40348,7 @@
         <v>1.8</v>
       </c>
       <c r="AQ188">
-        <v>0.57</v>
+        <v>0.53</v>
       </c>
       <c r="AR188">
         <v>1.31</v>
@@ -40533,10 +40551,10 @@
         <v>0.75</v>
       </c>
       <c r="AP189">
-        <v>1.85</v>
+        <v>1.93</v>
       </c>
       <c r="AQ189">
-        <v>0.67</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="AR189">
         <v>1.71</v>
@@ -40661,7 +40679,7 @@
         <v>101</v>
       </c>
       <c r="P190" t="s">
-        <v>319</v>
+        <v>324</v>
       </c>
       <c r="Q190">
         <v>3.25</v>
@@ -40739,7 +40757,7 @@
         <v>0.71</v>
       </c>
       <c r="AP190">
-        <v>1.43</v>
+        <v>1.53</v>
       </c>
       <c r="AQ190">
         <v>1.21</v>
@@ -40867,7 +40885,7 @@
         <v>148</v>
       </c>
       <c r="P191" t="s">
-        <v>373</v>
+        <v>378</v>
       </c>
       <c r="Q191">
         <v>2.3</v>
@@ -41073,7 +41091,7 @@
         <v>219</v>
       </c>
       <c r="P192" t="s">
-        <v>374</v>
+        <v>379</v>
       </c>
       <c r="Q192">
         <v>2.4</v>
@@ -41154,7 +41172,7 @@
         <v>1.47</v>
       </c>
       <c r="AQ192">
-        <v>0.88</v>
+        <v>0.82</v>
       </c>
       <c r="AR192">
         <v>1.24</v>
@@ -41360,7 +41378,7 @@
         <v>2.14</v>
       </c>
       <c r="AQ193">
-        <v>1.77</v>
+        <v>1.64</v>
       </c>
       <c r="AR193">
         <v>1.56</v>
@@ -42103,7 +42121,7 @@
         <v>101</v>
       </c>
       <c r="P197" t="s">
-        <v>375</v>
+        <v>380</v>
       </c>
       <c r="Q197">
         <v>3.75</v>
@@ -42184,7 +42202,7 @@
         <v>1.29</v>
       </c>
       <c r="AQ197">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="AR197">
         <v>1.32</v>
@@ -42309,7 +42327,7 @@
         <v>221</v>
       </c>
       <c r="P198" t="s">
-        <v>376</v>
+        <v>381</v>
       </c>
       <c r="Q198">
         <v>2.2</v>
@@ -42390,7 +42408,7 @@
         <v>2.4</v>
       </c>
       <c r="AQ198">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="AR198">
         <v>1.48</v>
@@ -42515,7 +42533,7 @@
         <v>122</v>
       </c>
       <c r="P199" t="s">
-        <v>329</v>
+        <v>334</v>
       </c>
       <c r="Q199">
         <v>3.4</v>
@@ -42799,7 +42817,7 @@
         <v>1</v>
       </c>
       <c r="AP200">
-        <v>1.47</v>
+        <v>1.56</v>
       </c>
       <c r="AQ200">
         <v>1.21</v>
@@ -42927,7 +42945,7 @@
         <v>222</v>
       </c>
       <c r="P201" t="s">
-        <v>377</v>
+        <v>382</v>
       </c>
       <c r="Q201">
         <v>2.85</v>
@@ -43005,7 +43023,7 @@
         <v>0.88</v>
       </c>
       <c r="AP201">
-        <v>1.43</v>
+        <v>1.53</v>
       </c>
       <c r="AQ201">
         <v>1</v>
@@ -43133,7 +43151,7 @@
         <v>223</v>
       </c>
       <c r="P202" t="s">
-        <v>378</v>
+        <v>383</v>
       </c>
       <c r="Q202">
         <v>1.8</v>
@@ -43214,7 +43232,7 @@
         <v>2.14</v>
       </c>
       <c r="AQ202">
-        <v>0.67</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="AR202">
         <v>1.53</v>
@@ -43339,7 +43357,7 @@
         <v>205</v>
       </c>
       <c r="P203" t="s">
-        <v>379</v>
+        <v>384</v>
       </c>
       <c r="Q203">
         <v>2.75</v>
@@ -43545,7 +43563,7 @@
         <v>224</v>
       </c>
       <c r="P204" t="s">
-        <v>380</v>
+        <v>385</v>
       </c>
       <c r="Q204">
         <v>3.55</v>
@@ -43829,7 +43847,7 @@
         <v>0.89</v>
       </c>
       <c r="AP205">
-        <v>1.43</v>
+        <v>1.53</v>
       </c>
       <c r="AQ205">
         <v>1</v>
@@ -44035,7 +44053,7 @@
         <v>1.63</v>
       </c>
       <c r="AP206">
-        <v>1.56</v>
+        <v>1.47</v>
       </c>
       <c r="AQ206">
         <v>1.21</v>
@@ -44241,7 +44259,7 @@
         <v>1.13</v>
       </c>
       <c r="AP207">
-        <v>1.73</v>
+        <v>1.81</v>
       </c>
       <c r="AQ207">
         <v>0.8100000000000001</v>
@@ -44369,7 +44387,7 @@
         <v>228</v>
       </c>
       <c r="P208" t="s">
-        <v>381</v>
+        <v>386</v>
       </c>
       <c r="Q208">
         <v>2.4</v>
@@ -44450,7 +44468,7 @@
         <v>1.29</v>
       </c>
       <c r="AQ208">
-        <v>0.88</v>
+        <v>0.82</v>
       </c>
       <c r="AR208">
         <v>1.38</v>
@@ -44575,7 +44593,7 @@
         <v>229</v>
       </c>
       <c r="P209" t="s">
-        <v>382</v>
+        <v>387</v>
       </c>
       <c r="Q209">
         <v>2.5</v>
@@ -44862,7 +44880,7 @@
         <v>1.07</v>
       </c>
       <c r="AQ210">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR210">
         <v>1.4</v>
@@ -44987,7 +45005,7 @@
         <v>231</v>
       </c>
       <c r="P211" t="s">
-        <v>383</v>
+        <v>388</v>
       </c>
       <c r="Q211">
         <v>3.5</v>
@@ -45065,7 +45083,7 @@
         <v>1.75</v>
       </c>
       <c r="AP211">
-        <v>1.47</v>
+        <v>1.56</v>
       </c>
       <c r="AQ211">
         <v>1.6</v>
@@ -45271,7 +45289,7 @@
         <v>1</v>
       </c>
       <c r="AP212">
-        <v>1.86</v>
+        <v>1.73</v>
       </c>
       <c r="AQ212">
         <v>1</v>
@@ -45480,7 +45498,7 @@
         <v>1.77</v>
       </c>
       <c r="AQ213">
-        <v>1.77</v>
+        <v>1.64</v>
       </c>
       <c r="AR213">
         <v>1.25</v>
@@ -45686,7 +45704,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ214">
-        <v>0.57</v>
+        <v>0.53</v>
       </c>
       <c r="AR214">
         <v>1.49</v>
@@ -45811,7 +45829,7 @@
         <v>101</v>
       </c>
       <c r="P215" t="s">
-        <v>384</v>
+        <v>389</v>
       </c>
       <c r="Q215">
         <v>4.33</v>
@@ -45892,7 +45910,7 @@
         <v>1.13</v>
       </c>
       <c r="AQ215">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="AR215">
         <v>1.24</v>
@@ -46017,7 +46035,7 @@
         <v>234</v>
       </c>
       <c r="P216" t="s">
-        <v>385</v>
+        <v>390</v>
       </c>
       <c r="Q216">
         <v>3</v>
@@ -46095,10 +46113,10 @@
         <v>1.25</v>
       </c>
       <c r="AP216">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AQ216">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="AR216">
         <v>1.37</v>
@@ -46223,7 +46241,7 @@
         <v>235</v>
       </c>
       <c r="P217" t="s">
-        <v>386</v>
+        <v>391</v>
       </c>
       <c r="Q217">
         <v>0</v>
@@ -46304,7 +46322,7 @@
         <v>1.87</v>
       </c>
       <c r="AQ217">
-        <v>0.85</v>
+        <v>0.79</v>
       </c>
       <c r="AR217">
         <v>1.35</v>
@@ -46635,7 +46653,7 @@
         <v>101</v>
       </c>
       <c r="P219" t="s">
-        <v>387</v>
+        <v>392</v>
       </c>
       <c r="Q219">
         <v>3.2</v>
@@ -47331,7 +47349,7 @@
         <v>1.4</v>
       </c>
       <c r="AP222">
-        <v>1.73</v>
+        <v>1.81</v>
       </c>
       <c r="AQ222">
         <v>1.73</v>
@@ -47459,7 +47477,7 @@
         <v>101</v>
       </c>
       <c r="P223" t="s">
-        <v>388</v>
+        <v>393</v>
       </c>
       <c r="Q223">
         <v>3.75</v>
@@ -47665,7 +47683,7 @@
         <v>101</v>
       </c>
       <c r="P224" t="s">
-        <v>389</v>
+        <v>394</v>
       </c>
       <c r="Q224">
         <v>3.4</v>
@@ -47743,7 +47761,7 @@
         <v>1.44</v>
       </c>
       <c r="AP224">
-        <v>1.43</v>
+        <v>1.53</v>
       </c>
       <c r="AQ224">
         <v>1.47</v>
@@ -47949,10 +47967,10 @@
         <v>0.8</v>
       </c>
       <c r="AP225">
-        <v>1.43</v>
+        <v>1.53</v>
       </c>
       <c r="AQ225">
-        <v>0.67</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="AR225">
         <v>1.66</v>
@@ -48901,7 +48919,7 @@
         <v>101</v>
       </c>
       <c r="P230" t="s">
-        <v>357</v>
+        <v>362</v>
       </c>
       <c r="Q230">
         <v>2.5</v>
@@ -48979,10 +48997,10 @@
         <v>1</v>
       </c>
       <c r="AP230">
-        <v>1.56</v>
+        <v>1.47</v>
       </c>
       <c r="AQ230">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR230">
         <v>1.31</v>
@@ -49188,7 +49206,7 @@
         <v>1.8</v>
       </c>
       <c r="AQ231">
-        <v>0.88</v>
+        <v>0.82</v>
       </c>
       <c r="AR231">
         <v>1.3</v>
@@ -49313,7 +49331,7 @@
         <v>240</v>
       </c>
       <c r="P232" t="s">
-        <v>390</v>
+        <v>395</v>
       </c>
       <c r="Q232">
         <v>2.4</v>
@@ -49391,7 +49409,7 @@
         <v>0.78</v>
       </c>
       <c r="AP232">
-        <v>1.47</v>
+        <v>1.56</v>
       </c>
       <c r="AQ232">
         <v>1</v>
@@ -49519,7 +49537,7 @@
         <v>241</v>
       </c>
       <c r="P233" t="s">
-        <v>391</v>
+        <v>396</v>
       </c>
       <c r="Q233">
         <v>2.88</v>
@@ -49600,7 +49618,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ233">
-        <v>0.85</v>
+        <v>0.79</v>
       </c>
       <c r="AR233">
         <v>1.21</v>
@@ -49803,7 +49821,7 @@
         <v>1</v>
       </c>
       <c r="AP234">
-        <v>1.86</v>
+        <v>1.73</v>
       </c>
       <c r="AQ234">
         <v>1.21</v>
@@ -50012,7 +50030,7 @@
         <v>1.87</v>
       </c>
       <c r="AQ235">
-        <v>0.57</v>
+        <v>0.53</v>
       </c>
       <c r="AR235">
         <v>1.36</v>
@@ -50215,7 +50233,7 @@
         <v>1.38</v>
       </c>
       <c r="AP236">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AQ236">
         <v>1.17</v>
@@ -50424,7 +50442,7 @@
         <v>1.77</v>
       </c>
       <c r="AQ237">
-        <v>0.86</v>
+        <v>0.8</v>
       </c>
       <c r="AR237">
         <v>1.18</v>
@@ -50627,7 +50645,7 @@
         <v>1</v>
       </c>
       <c r="AP238">
-        <v>1.85</v>
+        <v>1.93</v>
       </c>
       <c r="AQ238">
         <v>1</v>
@@ -50755,7 +50773,7 @@
         <v>245</v>
       </c>
       <c r="P239" t="s">
-        <v>392</v>
+        <v>397</v>
       </c>
       <c r="Q239">
         <v>4.5</v>
@@ -50961,7 +50979,7 @@
         <v>101</v>
       </c>
       <c r="P240" t="s">
-        <v>393</v>
+        <v>398</v>
       </c>
       <c r="Q240">
         <v>3.75</v>
@@ -51042,7 +51060,7 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="AQ240">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="AR240">
         <v>1.34</v>
@@ -51167,7 +51185,7 @@
         <v>101</v>
       </c>
       <c r="P241" t="s">
-        <v>394</v>
+        <v>399</v>
       </c>
       <c r="Q241">
         <v>5.5</v>
@@ -51248,7 +51266,7 @@
         <v>1.13</v>
       </c>
       <c r="AQ241">
-        <v>1.77</v>
+        <v>1.64</v>
       </c>
       <c r="AR241">
         <v>1.17</v>
@@ -51373,7 +51391,7 @@
         <v>246</v>
       </c>
       <c r="P242" t="s">
-        <v>395</v>
+        <v>400</v>
       </c>
       <c r="Q242">
         <v>2.88</v>
@@ -51579,7 +51597,7 @@
         <v>101</v>
       </c>
       <c r="P243" t="s">
-        <v>396</v>
+        <v>401</v>
       </c>
       <c r="Q243">
         <v>3.5</v>
@@ -51657,7 +51675,7 @@
         <v>1</v>
       </c>
       <c r="AP243">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AQ243">
         <v>1.36</v>
@@ -51866,7 +51884,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ244">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="AR244">
         <v>1.52</v>
@@ -52197,7 +52215,7 @@
         <v>248</v>
       </c>
       <c r="P246" t="s">
-        <v>329</v>
+        <v>334</v>
       </c>
       <c r="Q246">
         <v>2.38</v>
@@ -52275,7 +52293,7 @@
         <v>0.9</v>
       </c>
       <c r="AP246">
-        <v>1.43</v>
+        <v>1.53</v>
       </c>
       <c r="AQ246">
         <v>0.8100000000000001</v>
@@ -52403,7 +52421,7 @@
         <v>101</v>
       </c>
       <c r="P247" t="s">
-        <v>397</v>
+        <v>402</v>
       </c>
       <c r="Q247">
         <v>2.6</v>
@@ -52481,7 +52499,7 @@
         <v>1.27</v>
       </c>
       <c r="AP247">
-        <v>1.56</v>
+        <v>1.47</v>
       </c>
       <c r="AQ247">
         <v>1.73</v>
@@ -52687,7 +52705,7 @@
         <v>0.8</v>
       </c>
       <c r="AP248">
-        <v>1.73</v>
+        <v>1.81</v>
       </c>
       <c r="AQ248">
         <v>0.64</v>
@@ -53099,7 +53117,7 @@
         <v>1.6</v>
       </c>
       <c r="AP250">
-        <v>1.47</v>
+        <v>1.56</v>
       </c>
       <c r="AQ250">
         <v>1.21</v>
@@ -53227,7 +53245,7 @@
         <v>252</v>
       </c>
       <c r="P251" t="s">
-        <v>398</v>
+        <v>403</v>
       </c>
       <c r="Q251">
         <v>2.25</v>
@@ -53639,7 +53657,7 @@
         <v>254</v>
       </c>
       <c r="P253" t="s">
-        <v>399</v>
+        <v>404</v>
       </c>
       <c r="Q253">
         <v>2.1</v>
@@ -53720,7 +53738,7 @@
         <v>1.07</v>
       </c>
       <c r="AQ253">
-        <v>0.67</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="AR253">
         <v>1.47</v>
@@ -53845,7 +53863,7 @@
         <v>101</v>
       </c>
       <c r="P254" t="s">
-        <v>400</v>
+        <v>405</v>
       </c>
       <c r="Q254">
         <v>2.5</v>
@@ -53926,7 +53944,7 @@
         <v>0.64</v>
       </c>
       <c r="AQ254">
-        <v>0.88</v>
+        <v>0.82</v>
       </c>
       <c r="AR254">
         <v>1.38</v>
@@ -54129,10 +54147,10 @@
         <v>1.22</v>
       </c>
       <c r="AP255">
-        <v>1.43</v>
+        <v>1.53</v>
       </c>
       <c r="AQ255">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR255">
         <v>1.66</v>
@@ -54257,7 +54275,7 @@
         <v>114</v>
       </c>
       <c r="P256" t="s">
-        <v>395</v>
+        <v>400</v>
       </c>
       <c r="Q256">
         <v>2.88</v>
@@ -54953,7 +54971,7 @@
         <v>1.55</v>
       </c>
       <c r="AP259">
-        <v>1.43</v>
+        <v>1.53</v>
       </c>
       <c r="AQ259">
         <v>1.6</v>
@@ -55159,10 +55177,10 @@
         <v>1.17</v>
       </c>
       <c r="AP260">
-        <v>1.73</v>
+        <v>1.81</v>
       </c>
       <c r="AQ260">
-        <v>0.88</v>
+        <v>0.82</v>
       </c>
       <c r="AR260">
         <v>1.42</v>
@@ -55368,7 +55386,7 @@
         <v>2.4</v>
       </c>
       <c r="AQ261">
-        <v>0.67</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="AR261">
         <v>1.51</v>
@@ -55571,7 +55589,7 @@
         <v>1.45</v>
       </c>
       <c r="AP262">
-        <v>1.56</v>
+        <v>1.47</v>
       </c>
       <c r="AQ262">
         <v>1.47</v>
@@ -55983,7 +56001,7 @@
         <v>1.75</v>
       </c>
       <c r="AP264">
-        <v>1.43</v>
+        <v>1.53</v>
       </c>
       <c r="AQ264">
         <v>1.63</v>
@@ -56189,7 +56207,7 @@
         <v>0.82</v>
       </c>
       <c r="AP265">
-        <v>1.47</v>
+        <v>1.56</v>
       </c>
       <c r="AQ265">
         <v>0.8100000000000001</v>
@@ -56317,7 +56335,7 @@
         <v>259</v>
       </c>
       <c r="P266" t="s">
-        <v>401</v>
+        <v>406</v>
       </c>
       <c r="Q266">
         <v>3.6</v>
@@ -56604,7 +56622,7 @@
         <v>2.14</v>
       </c>
       <c r="AQ267">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR267">
         <v>1.44</v>
@@ -56810,7 +56828,7 @@
         <v>1.77</v>
       </c>
       <c r="AQ268">
-        <v>0.85</v>
+        <v>0.79</v>
       </c>
       <c r="AR268">
         <v>1.16</v>
@@ -56935,7 +56953,7 @@
         <v>261</v>
       </c>
       <c r="P269" t="s">
-        <v>402</v>
+        <v>407</v>
       </c>
       <c r="Q269">
         <v>2.75</v>
@@ -57013,10 +57031,10 @@
         <v>0.9</v>
       </c>
       <c r="AP269">
-        <v>1.86</v>
+        <v>1.73</v>
       </c>
       <c r="AQ269">
-        <v>0.86</v>
+        <v>0.8</v>
       </c>
       <c r="AR269">
         <v>1.12</v>
@@ -57141,7 +57159,7 @@
         <v>262</v>
       </c>
       <c r="P270" t="s">
-        <v>403</v>
+        <v>408</v>
       </c>
       <c r="Q270">
         <v>2.4</v>
@@ -57347,7 +57365,7 @@
         <v>101</v>
       </c>
       <c r="P271" t="s">
-        <v>404</v>
+        <v>409</v>
       </c>
       <c r="Q271">
         <v>4</v>
@@ -57553,7 +57571,7 @@
         <v>263</v>
       </c>
       <c r="P272" t="s">
-        <v>405</v>
+        <v>410</v>
       </c>
       <c r="Q272">
         <v>3.1</v>
@@ -57840,7 +57858,7 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="AQ273">
-        <v>0.57</v>
+        <v>0.53</v>
       </c>
       <c r="AR273">
         <v>1.29</v>
@@ -57965,7 +57983,7 @@
         <v>184</v>
       </c>
       <c r="P274" t="s">
-        <v>406</v>
+        <v>411</v>
       </c>
       <c r="Q274">
         <v>3.25</v>
@@ -58043,10 +58061,10 @@
         <v>2</v>
       </c>
       <c r="AP274">
-        <v>1.85</v>
+        <v>1.93</v>
       </c>
       <c r="AQ274">
-        <v>1.77</v>
+        <v>1.64</v>
       </c>
       <c r="AR274">
         <v>1.79</v>
@@ -58171,7 +58189,7 @@
         <v>265</v>
       </c>
       <c r="P275" t="s">
-        <v>407</v>
+        <v>412</v>
       </c>
       <c r="Q275">
         <v>3.4</v>
@@ -58249,7 +58267,7 @@
         <v>0.91</v>
       </c>
       <c r="AP275">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AQ275">
         <v>1</v>
@@ -58377,7 +58395,7 @@
         <v>266</v>
       </c>
       <c r="P276" t="s">
-        <v>408</v>
+        <v>413</v>
       </c>
       <c r="Q276">
         <v>2.88</v>
@@ -58583,7 +58601,7 @@
         <v>267</v>
       </c>
       <c r="P277" t="s">
-        <v>409</v>
+        <v>414</v>
       </c>
       <c r="Q277">
         <v>3.1</v>
@@ -58661,7 +58679,7 @@
         <v>1.73</v>
       </c>
       <c r="AP277">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AQ277">
         <v>1.47</v>
@@ -58789,7 +58807,7 @@
         <v>101</v>
       </c>
       <c r="P278" t="s">
-        <v>410</v>
+        <v>415</v>
       </c>
       <c r="Q278">
         <v>3.1</v>
@@ -58870,7 +58888,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ278">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="AR278">
         <v>1.25</v>
@@ -58995,7 +59013,7 @@
         <v>128</v>
       </c>
       <c r="P279" t="s">
-        <v>411</v>
+        <v>416</v>
       </c>
       <c r="Q279">
         <v>5</v>
@@ -59076,7 +59094,7 @@
         <v>1.77</v>
       </c>
       <c r="AQ279">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="AR279">
         <v>1.24</v>
@@ -59279,7 +59297,7 @@
         <v>0.77</v>
       </c>
       <c r="AP280">
-        <v>1.85</v>
+        <v>1.93</v>
       </c>
       <c r="AQ280">
         <v>1</v>
@@ -59613,7 +59631,7 @@
         <v>101</v>
       </c>
       <c r="P282" t="s">
-        <v>412</v>
+        <v>417</v>
       </c>
       <c r="Q282">
         <v>2.6</v>
@@ -59691,7 +59709,7 @@
         <v>0.73</v>
       </c>
       <c r="AP282">
-        <v>1.43</v>
+        <v>1.53</v>
       </c>
       <c r="AQ282">
         <v>1</v>
@@ -59900,7 +59918,7 @@
         <v>1.29</v>
       </c>
       <c r="AQ283">
-        <v>0.86</v>
+        <v>0.8</v>
       </c>
       <c r="AR283">
         <v>1.46</v>
@@ -60103,7 +60121,7 @@
         <v>1.36</v>
       </c>
       <c r="AP284">
-        <v>1.56</v>
+        <v>1.47</v>
       </c>
       <c r="AQ284">
         <v>1.36</v>
@@ -60437,7 +60455,7 @@
         <v>101</v>
       </c>
       <c r="P286" t="s">
-        <v>413</v>
+        <v>418</v>
       </c>
       <c r="Q286">
         <v>2.5</v>
@@ -60515,7 +60533,7 @@
         <v>0.83</v>
       </c>
       <c r="AP286">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AQ286">
         <v>0.8100000000000001</v>
@@ -60643,7 +60661,7 @@
         <v>270</v>
       </c>
       <c r="P287" t="s">
-        <v>350</v>
+        <v>355</v>
       </c>
       <c r="Q287">
         <v>2.75</v>
@@ -60721,10 +60739,10 @@
         <v>1.73</v>
       </c>
       <c r="AP287">
-        <v>1.86</v>
+        <v>1.73</v>
       </c>
       <c r="AQ287">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="AR287">
         <v>1.18</v>
@@ -60930,7 +60948,7 @@
         <v>2.4</v>
       </c>
       <c r="AQ288">
-        <v>0.57</v>
+        <v>0.53</v>
       </c>
       <c r="AR288">
         <v>1.53</v>
@@ -61342,7 +61360,7 @@
         <v>1.13</v>
       </c>
       <c r="AQ290">
-        <v>0.85</v>
+        <v>0.79</v>
       </c>
       <c r="AR290">
         <v>1.09</v>
@@ -61467,7 +61485,7 @@
         <v>101</v>
       </c>
       <c r="P291" t="s">
-        <v>414</v>
+        <v>419</v>
       </c>
       <c r="Q291">
         <v>4</v>
@@ -61960,7 +61978,7 @@
         <v>2.14</v>
       </c>
       <c r="AQ293">
-        <v>0.57</v>
+        <v>0.53</v>
       </c>
       <c r="AR293">
         <v>1.4</v>
@@ -62085,7 +62103,7 @@
         <v>101</v>
       </c>
       <c r="P294" t="s">
-        <v>313</v>
+        <v>318</v>
       </c>
       <c r="Q294">
         <v>4</v>
@@ -62291,7 +62309,7 @@
         <v>274</v>
       </c>
       <c r="P295" t="s">
-        <v>415</v>
+        <v>420</v>
       </c>
       <c r="Q295">
         <v>2</v>
@@ -62372,7 +62390,7 @@
         <v>1.77</v>
       </c>
       <c r="AQ295">
-        <v>0.67</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="AR295">
         <v>1.19</v>
@@ -62497,7 +62515,7 @@
         <v>101</v>
       </c>
       <c r="P296" t="s">
-        <v>416</v>
+        <v>421</v>
       </c>
       <c r="Q296">
         <v>2.75</v>
@@ -62575,7 +62593,7 @@
         <v>1.1</v>
       </c>
       <c r="AP296">
-        <v>1.73</v>
+        <v>1.81</v>
       </c>
       <c r="AQ296">
         <v>1.17</v>
@@ -62909,7 +62927,7 @@
         <v>276</v>
       </c>
       <c r="P298" t="s">
-        <v>417</v>
+        <v>422</v>
       </c>
       <c r="Q298">
         <v>2.38</v>
@@ -63115,7 +63133,7 @@
         <v>101</v>
       </c>
       <c r="P299" t="s">
-        <v>418</v>
+        <v>423</v>
       </c>
       <c r="Q299">
         <v>2.88</v>
@@ -63321,7 +63339,7 @@
         <v>101</v>
       </c>
       <c r="P300" t="s">
-        <v>419</v>
+        <v>424</v>
       </c>
       <c r="Q300">
         <v>3.6</v>
@@ -63399,7 +63417,7 @@
         <v>1.54</v>
       </c>
       <c r="AP300">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AQ300">
         <v>1.73</v>
@@ -63605,7 +63623,7 @@
         <v>1.33</v>
       </c>
       <c r="AP301">
-        <v>1.43</v>
+        <v>1.53</v>
       </c>
       <c r="AQ301">
         <v>1.21</v>
@@ -64017,7 +64035,7 @@
         <v>1.3</v>
       </c>
       <c r="AP303">
-        <v>1.47</v>
+        <v>1.56</v>
       </c>
       <c r="AQ303">
         <v>1.08</v>
@@ -64145,7 +64163,7 @@
         <v>278</v>
       </c>
       <c r="P304" t="s">
-        <v>420</v>
+        <v>425</v>
       </c>
       <c r="Q304">
         <v>4</v>
@@ -64429,10 +64447,10 @@
         <v>1.45</v>
       </c>
       <c r="AP305">
-        <v>1.56</v>
+        <v>1.47</v>
       </c>
       <c r="AQ305">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="AR305">
         <v>1.33</v>
@@ -64638,7 +64656,7 @@
         <v>2.4</v>
       </c>
       <c r="AQ306">
-        <v>1.77</v>
+        <v>1.64</v>
       </c>
       <c r="AR306">
         <v>1.4</v>
@@ -64841,7 +64859,7 @@
         <v>0.92</v>
       </c>
       <c r="AP307">
-        <v>1.86</v>
+        <v>1.73</v>
       </c>
       <c r="AQ307">
         <v>1</v>
@@ -65047,7 +65065,7 @@
         <v>1.46</v>
       </c>
       <c r="AP308">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AQ308">
         <v>1.47</v>
@@ -65253,10 +65271,10 @@
         <v>1.08</v>
       </c>
       <c r="AP309">
-        <v>1.43</v>
+        <v>1.53</v>
       </c>
       <c r="AQ309">
-        <v>0.88</v>
+        <v>0.82</v>
       </c>
       <c r="AR309">
         <v>1.52</v>
@@ -65462,7 +65480,7 @@
         <v>1.29</v>
       </c>
       <c r="AQ310">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR310">
         <v>1.47</v>
@@ -65587,7 +65605,7 @@
         <v>282</v>
       </c>
       <c r="P311" t="s">
-        <v>421</v>
+        <v>426</v>
       </c>
       <c r="Q311">
         <v>3.75</v>
@@ -65793,7 +65811,7 @@
         <v>195</v>
       </c>
       <c r="P312" t="s">
-        <v>422</v>
+        <v>427</v>
       </c>
       <c r="Q312">
         <v>2.63</v>
@@ -65871,10 +65889,10 @@
         <v>0.75</v>
       </c>
       <c r="AP312">
-        <v>1.47</v>
+        <v>1.56</v>
       </c>
       <c r="AQ312">
-        <v>0.86</v>
+        <v>0.8</v>
       </c>
       <c r="AR312">
         <v>1.34</v>
@@ -66489,10 +66507,10 @@
         <v>1.58</v>
       </c>
       <c r="AP315">
-        <v>1.85</v>
+        <v>1.93</v>
       </c>
       <c r="AQ315">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="AR315">
         <v>1.73</v>
@@ -66695,10 +66713,10 @@
         <v>0.83</v>
       </c>
       <c r="AP316">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AQ316">
-        <v>0.85</v>
+        <v>0.79</v>
       </c>
       <c r="AR316">
         <v>1.27</v>
@@ -66904,7 +66922,7 @@
         <v>2.4</v>
       </c>
       <c r="AQ317">
-        <v>0.88</v>
+        <v>0.82</v>
       </c>
       <c r="AR317">
         <v>1.41</v>
@@ -67029,7 +67047,7 @@
         <v>283</v>
       </c>
       <c r="P318" t="s">
-        <v>423</v>
+        <v>428</v>
       </c>
       <c r="Q318">
         <v>3.4</v>
@@ -67107,10 +67125,10 @@
         <v>1.42</v>
       </c>
       <c r="AP318">
-        <v>1.86</v>
+        <v>1.73</v>
       </c>
       <c r="AQ318">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="AR318">
         <v>1.24</v>
@@ -67313,10 +67331,10 @@
         <v>1.92</v>
       </c>
       <c r="AP319">
-        <v>1.47</v>
+        <v>1.56</v>
       </c>
       <c r="AQ319">
-        <v>1.77</v>
+        <v>1.64</v>
       </c>
       <c r="AR319">
         <v>1.37</v>
@@ -67519,10 +67537,10 @@
         <v>1</v>
       </c>
       <c r="AP320">
-        <v>1.43</v>
+        <v>1.53</v>
       </c>
       <c r="AQ320">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR320">
         <v>1.28</v>
@@ -67725,10 +67743,10 @@
         <v>0.92</v>
       </c>
       <c r="AP321">
-        <v>1.85</v>
+        <v>1.93</v>
       </c>
       <c r="AQ321">
-        <v>0.86</v>
+        <v>0.8</v>
       </c>
       <c r="AR321">
         <v>1.74</v>
@@ -67931,10 +67949,10 @@
         <v>0.64</v>
       </c>
       <c r="AP322">
-        <v>1.73</v>
+        <v>1.81</v>
       </c>
       <c r="AQ322">
-        <v>0.67</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="AR322">
         <v>1.46</v>
@@ -68140,7 +68158,7 @@
         <v>1.47</v>
       </c>
       <c r="AQ323">
-        <v>0.57</v>
+        <v>0.53</v>
       </c>
       <c r="AR323">
         <v>1.34</v>
@@ -68346,7 +68364,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ324">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="AR324">
         <v>1.53</v>
@@ -68549,7 +68567,7 @@
         <v>0.93</v>
       </c>
       <c r="AP325">
-        <v>1.56</v>
+        <v>1.47</v>
       </c>
       <c r="AQ325">
         <v>0.8100000000000001</v>
@@ -68677,7 +68695,7 @@
         <v>290</v>
       </c>
       <c r="P326" t="s">
-        <v>424</v>
+        <v>429</v>
       </c>
       <c r="Q326">
         <v>3.75</v>
@@ -68755,7 +68773,7 @@
         <v>1.62</v>
       </c>
       <c r="AP326">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AQ326">
         <v>1.6</v>
@@ -68883,7 +68901,7 @@
         <v>291</v>
       </c>
       <c r="P327" t="s">
-        <v>425</v>
+        <v>430</v>
       </c>
       <c r="Q327">
         <v>3.75</v>
@@ -69501,7 +69519,7 @@
         <v>293</v>
       </c>
       <c r="P330" t="s">
-        <v>426</v>
+        <v>431</v>
       </c>
       <c r="Q330">
         <v>2.63</v>
@@ -69707,7 +69725,7 @@
         <v>260</v>
       </c>
       <c r="P331" t="s">
-        <v>427</v>
+        <v>432</v>
       </c>
       <c r="Q331">
         <v>3.5</v>
@@ -70119,7 +70137,7 @@
         <v>294</v>
       </c>
       <c r="P333" t="s">
-        <v>428</v>
+        <v>433</v>
       </c>
       <c r="Q333">
         <v>4</v>
@@ -70737,7 +70755,7 @@
         <v>101</v>
       </c>
       <c r="P336" t="s">
-        <v>429</v>
+        <v>434</v>
       </c>
       <c r="Q336">
         <v>2.63</v>
@@ -71149,7 +71167,7 @@
         <v>296</v>
       </c>
       <c r="P338" t="s">
-        <v>430</v>
+        <v>435</v>
       </c>
       <c r="Q338">
         <v>3.1</v>
@@ -71355,7 +71373,7 @@
         <v>297</v>
       </c>
       <c r="P339" t="s">
-        <v>431</v>
+        <v>436</v>
       </c>
       <c r="Q339">
         <v>3</v>
@@ -71433,10 +71451,10 @@
         <v>1.43</v>
       </c>
       <c r="AP339">
-        <v>1.73</v>
+        <v>1.81</v>
       </c>
       <c r="AQ339">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="AR339">
         <v>1.51</v>
@@ -71642,7 +71660,7 @@
         <v>1.77</v>
       </c>
       <c r="AQ340">
-        <v>0.88</v>
+        <v>0.82</v>
       </c>
       <c r="AR340">
         <v>1.23</v>
@@ -71767,7 +71785,7 @@
         <v>299</v>
       </c>
       <c r="P341" t="s">
-        <v>432</v>
+        <v>437</v>
       </c>
       <c r="Q341">
         <v>3</v>
@@ -71973,7 +71991,7 @@
         <v>300</v>
       </c>
       <c r="P342" t="s">
-        <v>433</v>
+        <v>438</v>
       </c>
       <c r="Q342">
         <v>3.1</v>
@@ -72336,6 +72354,1860 @@
       </c>
       <c r="BP343">
         <v>1.33</v>
+      </c>
+    </row>
+    <row r="344" spans="1:68">
+      <c r="A344" s="1">
+        <v>343</v>
+      </c>
+      <c r="B344">
+        <v>7476907</v>
+      </c>
+      <c r="C344" t="s">
+        <v>68</v>
+      </c>
+      <c r="D344" t="s">
+        <v>69</v>
+      </c>
+      <c r="E344" s="2">
+        <v>45696.5</v>
+      </c>
+      <c r="F344">
+        <v>31</v>
+      </c>
+      <c r="G344" t="s">
+        <v>85</v>
+      </c>
+      <c r="H344" t="s">
+        <v>81</v>
+      </c>
+      <c r="I344">
+        <v>0</v>
+      </c>
+      <c r="J344">
+        <v>0</v>
+      </c>
+      <c r="K344">
+        <v>0</v>
+      </c>
+      <c r="L344">
+        <v>2</v>
+      </c>
+      <c r="M344">
+        <v>1</v>
+      </c>
+      <c r="N344">
+        <v>3</v>
+      </c>
+      <c r="O344" t="s">
+        <v>301</v>
+      </c>
+      <c r="P344" t="s">
+        <v>281</v>
+      </c>
+      <c r="Q344">
+        <v>3.75</v>
+      </c>
+      <c r="R344">
+        <v>2</v>
+      </c>
+      <c r="S344">
+        <v>3.2</v>
+      </c>
+      <c r="T344">
+        <v>1.5</v>
+      </c>
+      <c r="U344">
+        <v>2.5</v>
+      </c>
+      <c r="V344">
+        <v>3.5</v>
+      </c>
+      <c r="W344">
+        <v>1.29</v>
+      </c>
+      <c r="X344">
+        <v>10</v>
+      </c>
+      <c r="Y344">
+        <v>1.06</v>
+      </c>
+      <c r="Z344">
+        <v>3.03</v>
+      </c>
+      <c r="AA344">
+        <v>3</v>
+      </c>
+      <c r="AB344">
+        <v>2.46</v>
+      </c>
+      <c r="AC344">
+        <v>1.08</v>
+      </c>
+      <c r="AD344">
+        <v>7.5</v>
+      </c>
+      <c r="AE344">
+        <v>1.42</v>
+      </c>
+      <c r="AF344">
+        <v>2.8</v>
+      </c>
+      <c r="AG344">
+        <v>2.2</v>
+      </c>
+      <c r="AH344">
+        <v>1.61</v>
+      </c>
+      <c r="AI344">
+        <v>1.91</v>
+      </c>
+      <c r="AJ344">
+        <v>1.8</v>
+      </c>
+      <c r="AK344">
+        <v>1.53</v>
+      </c>
+      <c r="AL344">
+        <v>1.3</v>
+      </c>
+      <c r="AM344">
+        <v>1.38</v>
+      </c>
+      <c r="AN344">
+        <v>1.43</v>
+      </c>
+      <c r="AO344">
+        <v>1.77</v>
+      </c>
+      <c r="AP344">
+        <v>1.53</v>
+      </c>
+      <c r="AQ344">
+        <v>1.64</v>
+      </c>
+      <c r="AR344">
+        <v>1.55</v>
+      </c>
+      <c r="AS344">
+        <v>1.34</v>
+      </c>
+      <c r="AT344">
+        <v>2.89</v>
+      </c>
+      <c r="AU344">
+        <v>4</v>
+      </c>
+      <c r="AV344">
+        <v>5</v>
+      </c>
+      <c r="AW344">
+        <v>7</v>
+      </c>
+      <c r="AX344">
+        <v>3</v>
+      </c>
+      <c r="AY344">
+        <v>14</v>
+      </c>
+      <c r="AZ344">
+        <v>10</v>
+      </c>
+      <c r="BA344">
+        <v>7</v>
+      </c>
+      <c r="BB344">
+        <v>2</v>
+      </c>
+      <c r="BC344">
+        <v>9</v>
+      </c>
+      <c r="BD344">
+        <v>2.15</v>
+      </c>
+      <c r="BE344">
+        <v>6.75</v>
+      </c>
+      <c r="BF344">
+        <v>1.84</v>
+      </c>
+      <c r="BG344">
+        <v>1.21</v>
+      </c>
+      <c r="BH344">
+        <v>3.8</v>
+      </c>
+      <c r="BI344">
+        <v>1.37</v>
+      </c>
+      <c r="BJ344">
+        <v>2.8</v>
+      </c>
+      <c r="BK344">
+        <v>1.61</v>
+      </c>
+      <c r="BL344">
+        <v>2.14</v>
+      </c>
+      <c r="BM344">
+        <v>1.96</v>
+      </c>
+      <c r="BN344">
+        <v>1.73</v>
+      </c>
+      <c r="BO344">
+        <v>2.45</v>
+      </c>
+      <c r="BP344">
+        <v>1.48</v>
+      </c>
+    </row>
+    <row r="345" spans="1:68">
+      <c r="A345" s="1">
+        <v>344</v>
+      </c>
+      <c r="B345">
+        <v>7476908</v>
+      </c>
+      <c r="C345" t="s">
+        <v>68</v>
+      </c>
+      <c r="D345" t="s">
+        <v>69</v>
+      </c>
+      <c r="E345" s="2">
+        <v>45696.5</v>
+      </c>
+      <c r="F345">
+        <v>31</v>
+      </c>
+      <c r="G345" t="s">
+        <v>86</v>
+      </c>
+      <c r="H345" t="s">
+        <v>89</v>
+      </c>
+      <c r="I345">
+        <v>0</v>
+      </c>
+      <c r="J345">
+        <v>2</v>
+      </c>
+      <c r="K345">
+        <v>2</v>
+      </c>
+      <c r="L345">
+        <v>0</v>
+      </c>
+      <c r="M345">
+        <v>3</v>
+      </c>
+      <c r="N345">
+        <v>3</v>
+      </c>
+      <c r="O345" t="s">
+        <v>101</v>
+      </c>
+      <c r="P345" t="s">
+        <v>439</v>
+      </c>
+      <c r="Q345">
+        <v>1.91</v>
+      </c>
+      <c r="R345">
+        <v>2.38</v>
+      </c>
+      <c r="S345">
+        <v>7.5</v>
+      </c>
+      <c r="T345">
+        <v>1.36</v>
+      </c>
+      <c r="U345">
+        <v>3</v>
+      </c>
+      <c r="V345">
+        <v>2.63</v>
+      </c>
+      <c r="W345">
+        <v>1.44</v>
+      </c>
+      <c r="X345">
+        <v>7</v>
+      </c>
+      <c r="Y345">
+        <v>1.1</v>
+      </c>
+      <c r="Z345">
+        <v>1.44</v>
+      </c>
+      <c r="AA345">
+        <v>4.5</v>
+      </c>
+      <c r="AB345">
+        <v>6.5</v>
+      </c>
+      <c r="AC345">
+        <v>1.04</v>
+      </c>
+      <c r="AD345">
+        <v>10</v>
+      </c>
+      <c r="AE345">
+        <v>1.25</v>
+      </c>
+      <c r="AF345">
+        <v>3.9</v>
+      </c>
+      <c r="AG345">
+        <v>1.77</v>
+      </c>
+      <c r="AH345">
+        <v>1.98</v>
+      </c>
+      <c r="AI345">
+        <v>2</v>
+      </c>
+      <c r="AJ345">
+        <v>1.73</v>
+      </c>
+      <c r="AK345">
+        <v>1.1</v>
+      </c>
+      <c r="AL345">
+        <v>1.15</v>
+      </c>
+      <c r="AM345">
+        <v>2.75</v>
+      </c>
+      <c r="AN345">
+        <v>1.86</v>
+      </c>
+      <c r="AO345">
+        <v>0.67</v>
+      </c>
+      <c r="AP345">
+        <v>1.73</v>
+      </c>
+      <c r="AQ345">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="AR345">
+        <v>1.21</v>
+      </c>
+      <c r="AS345">
+        <v>0.86</v>
+      </c>
+      <c r="AT345">
+        <v>2.07</v>
+      </c>
+      <c r="AU345">
+        <v>5</v>
+      </c>
+      <c r="AV345">
+        <v>4</v>
+      </c>
+      <c r="AW345">
+        <v>14</v>
+      </c>
+      <c r="AX345">
+        <v>4</v>
+      </c>
+      <c r="AY345">
+        <v>25</v>
+      </c>
+      <c r="AZ345">
+        <v>8</v>
+      </c>
+      <c r="BA345">
+        <v>14</v>
+      </c>
+      <c r="BB345">
+        <v>4</v>
+      </c>
+      <c r="BC345">
+        <v>18</v>
+      </c>
+      <c r="BD345">
+        <v>1.4</v>
+      </c>
+      <c r="BE345">
+        <v>7</v>
+      </c>
+      <c r="BF345">
+        <v>3.3</v>
+      </c>
+      <c r="BG345">
+        <v>1.37</v>
+      </c>
+      <c r="BH345">
+        <v>2.8</v>
+      </c>
+      <c r="BI345">
+        <v>1.63</v>
+      </c>
+      <c r="BJ345">
+        <v>2.12</v>
+      </c>
+      <c r="BK345">
+        <v>1.8</v>
+      </c>
+      <c r="BL345">
+        <v>2</v>
+      </c>
+      <c r="BM345">
+        <v>2.55</v>
+      </c>
+      <c r="BN345">
+        <v>1.43</v>
+      </c>
+      <c r="BO345">
+        <v>3.3</v>
+      </c>
+      <c r="BP345">
+        <v>1.27</v>
+      </c>
+    </row>
+    <row r="346" spans="1:68">
+      <c r="A346" s="1">
+        <v>345</v>
+      </c>
+      <c r="B346">
+        <v>7476909</v>
+      </c>
+      <c r="C346" t="s">
+        <v>68</v>
+      </c>
+      <c r="D346" t="s">
+        <v>69</v>
+      </c>
+      <c r="E346" s="2">
+        <v>45696.5</v>
+      </c>
+      <c r="F346">
+        <v>31</v>
+      </c>
+      <c r="G346" t="s">
+        <v>75</v>
+      </c>
+      <c r="H346" t="s">
+        <v>73</v>
+      </c>
+      <c r="I346">
+        <v>1</v>
+      </c>
+      <c r="J346">
+        <v>0</v>
+      </c>
+      <c r="K346">
+        <v>1</v>
+      </c>
+      <c r="L346">
+        <v>2</v>
+      </c>
+      <c r="M346">
+        <v>0</v>
+      </c>
+      <c r="N346">
+        <v>2</v>
+      </c>
+      <c r="O346" t="s">
+        <v>262</v>
+      </c>
+      <c r="P346" t="s">
+        <v>101</v>
+      </c>
+      <c r="Q346">
+        <v>2.75</v>
+      </c>
+      <c r="R346">
+        <v>2.1</v>
+      </c>
+      <c r="S346">
+        <v>4.33</v>
+      </c>
+      <c r="T346">
+        <v>1.44</v>
+      </c>
+      <c r="U346">
+        <v>2.63</v>
+      </c>
+      <c r="V346">
+        <v>3.25</v>
+      </c>
+      <c r="W346">
+        <v>1.33</v>
+      </c>
+      <c r="X346">
+        <v>9</v>
+      </c>
+      <c r="Y346">
+        <v>1.07</v>
+      </c>
+      <c r="Z346">
+        <v>1.96</v>
+      </c>
+      <c r="AA346">
+        <v>3.5</v>
+      </c>
+      <c r="AB346">
+        <v>3.66</v>
+      </c>
+      <c r="AC346">
+        <v>1.06</v>
+      </c>
+      <c r="AD346">
+        <v>8.5</v>
+      </c>
+      <c r="AE346">
+        <v>1.35</v>
+      </c>
+      <c r="AF346">
+        <v>3.1</v>
+      </c>
+      <c r="AG346">
+        <v>1.98</v>
+      </c>
+      <c r="AH346">
+        <v>1.77</v>
+      </c>
+      <c r="AI346">
+        <v>1.83</v>
+      </c>
+      <c r="AJ346">
+        <v>1.83</v>
+      </c>
+      <c r="AK346">
+        <v>1.25</v>
+      </c>
+      <c r="AL346">
+        <v>1.25</v>
+      </c>
+      <c r="AM346">
+        <v>1.8</v>
+      </c>
+      <c r="AN346">
+        <v>1.47</v>
+      </c>
+      <c r="AO346">
+        <v>0.85</v>
+      </c>
+      <c r="AP346">
+        <v>1.56</v>
+      </c>
+      <c r="AQ346">
+        <v>0.79</v>
+      </c>
+      <c r="AR346">
+        <v>1.34</v>
+      </c>
+      <c r="AS346">
+        <v>1.12</v>
+      </c>
+      <c r="AT346">
+        <v>2.46</v>
+      </c>
+      <c r="AU346">
+        <v>8</v>
+      </c>
+      <c r="AV346">
+        <v>0</v>
+      </c>
+      <c r="AW346">
+        <v>7</v>
+      </c>
+      <c r="AX346">
+        <v>9</v>
+      </c>
+      <c r="AY346">
+        <v>16</v>
+      </c>
+      <c r="AZ346">
+        <v>10</v>
+      </c>
+      <c r="BA346">
+        <v>5</v>
+      </c>
+      <c r="BB346">
+        <v>4</v>
+      </c>
+      <c r="BC346">
+        <v>9</v>
+      </c>
+      <c r="BD346">
+        <v>1.67</v>
+      </c>
+      <c r="BE346">
+        <v>6.75</v>
+      </c>
+      <c r="BF346">
+        <v>2.43</v>
+      </c>
+      <c r="BG346">
+        <v>1.27</v>
+      </c>
+      <c r="BH346">
+        <v>3.3</v>
+      </c>
+      <c r="BI346">
+        <v>1.47</v>
+      </c>
+      <c r="BJ346">
+        <v>2.43</v>
+      </c>
+      <c r="BK346">
+        <v>1.77</v>
+      </c>
+      <c r="BL346">
+        <v>1.91</v>
+      </c>
+      <c r="BM346">
+        <v>2.2</v>
+      </c>
+      <c r="BN346">
+        <v>1.58</v>
+      </c>
+      <c r="BO346">
+        <v>2.8</v>
+      </c>
+      <c r="BP346">
+        <v>1.36</v>
+      </c>
+    </row>
+    <row r="347" spans="1:68">
+      <c r="A347" s="1">
+        <v>346</v>
+      </c>
+      <c r="B347">
+        <v>7476904</v>
+      </c>
+      <c r="C347" t="s">
+        <v>68</v>
+      </c>
+      <c r="D347" t="s">
+        <v>69</v>
+      </c>
+      <c r="E347" s="2">
+        <v>45696.5</v>
+      </c>
+      <c r="F347">
+        <v>31</v>
+      </c>
+      <c r="G347" t="s">
+        <v>72</v>
+      </c>
+      <c r="H347" t="s">
+        <v>76</v>
+      </c>
+      <c r="I347">
+        <v>0</v>
+      </c>
+      <c r="J347">
+        <v>0</v>
+      </c>
+      <c r="K347">
+        <v>0</v>
+      </c>
+      <c r="L347">
+        <v>3</v>
+      </c>
+      <c r="M347">
+        <v>0</v>
+      </c>
+      <c r="N347">
+        <v>3</v>
+      </c>
+      <c r="O347" t="s">
+        <v>302</v>
+      </c>
+      <c r="P347" t="s">
+        <v>101</v>
+      </c>
+      <c r="Q347">
+        <v>3</v>
+      </c>
+      <c r="R347">
+        <v>1.95</v>
+      </c>
+      <c r="S347">
+        <v>4.33</v>
+      </c>
+      <c r="T347">
+        <v>1.53</v>
+      </c>
+      <c r="U347">
+        <v>2.38</v>
+      </c>
+      <c r="V347">
+        <v>3.75</v>
+      </c>
+      <c r="W347">
+        <v>1.25</v>
+      </c>
+      <c r="X347">
+        <v>11</v>
+      </c>
+      <c r="Y347">
+        <v>1.05</v>
+      </c>
+      <c r="Z347">
+        <v>2.16</v>
+      </c>
+      <c r="AA347">
+        <v>3.06</v>
+      </c>
+      <c r="AB347">
+        <v>3.56</v>
+      </c>
+      <c r="AC347">
+        <v>1.1</v>
+      </c>
+      <c r="AD347">
+        <v>6.5</v>
+      </c>
+      <c r="AE347">
+        <v>1.48</v>
+      </c>
+      <c r="AF347">
+        <v>2.6</v>
+      </c>
+      <c r="AG347">
+        <v>2.3</v>
+      </c>
+      <c r="AH347">
+        <v>1.57</v>
+      </c>
+      <c r="AI347">
+        <v>2.1</v>
+      </c>
+      <c r="AJ347">
+        <v>1.67</v>
+      </c>
+      <c r="AK347">
+        <v>1.28</v>
+      </c>
+      <c r="AL347">
+        <v>1.3</v>
+      </c>
+      <c r="AM347">
+        <v>1.67</v>
+      </c>
+      <c r="AN347">
+        <v>1.57</v>
+      </c>
+      <c r="AO347">
+        <v>1</v>
+      </c>
+      <c r="AP347">
+        <v>1.67</v>
+      </c>
+      <c r="AQ347">
+        <v>0.93</v>
+      </c>
+      <c r="AR347">
+        <v>1.37</v>
+      </c>
+      <c r="AS347">
+        <v>1.02</v>
+      </c>
+      <c r="AT347">
+        <v>2.39</v>
+      </c>
+      <c r="AU347">
+        <v>7</v>
+      </c>
+      <c r="AV347">
+        <v>2</v>
+      </c>
+      <c r="AW347">
+        <v>9</v>
+      </c>
+      <c r="AX347">
+        <v>8</v>
+      </c>
+      <c r="AY347">
+        <v>19</v>
+      </c>
+      <c r="AZ347">
+        <v>14</v>
+      </c>
+      <c r="BA347">
+        <v>5</v>
+      </c>
+      <c r="BB347">
+        <v>1</v>
+      </c>
+      <c r="BC347">
+        <v>6</v>
+      </c>
+      <c r="BD347">
+        <v>1.68</v>
+      </c>
+      <c r="BE347">
+        <v>6.4</v>
+      </c>
+      <c r="BF347">
+        <v>2.48</v>
+      </c>
+      <c r="BG347">
+        <v>1.41</v>
+      </c>
+      <c r="BH347">
+        <v>2.65</v>
+      </c>
+      <c r="BI347">
+        <v>1.71</v>
+      </c>
+      <c r="BJ347">
+        <v>2</v>
+      </c>
+      <c r="BK347">
+        <v>1.98</v>
+      </c>
+      <c r="BL347">
+        <v>1.82</v>
+      </c>
+      <c r="BM347">
+        <v>2.7</v>
+      </c>
+      <c r="BN347">
+        <v>1.4</v>
+      </c>
+      <c r="BO347">
+        <v>3.55</v>
+      </c>
+      <c r="BP347">
+        <v>1.24</v>
+      </c>
+    </row>
+    <row r="348" spans="1:68">
+      <c r="A348" s="1">
+        <v>347</v>
+      </c>
+      <c r="B348">
+        <v>7476903</v>
+      </c>
+      <c r="C348" t="s">
+        <v>68</v>
+      </c>
+      <c r="D348" t="s">
+        <v>69</v>
+      </c>
+      <c r="E348" s="2">
+        <v>45696.5</v>
+      </c>
+      <c r="F348">
+        <v>31</v>
+      </c>
+      <c r="G348" t="s">
+        <v>84</v>
+      </c>
+      <c r="H348" t="s">
+        <v>71</v>
+      </c>
+      <c r="I348">
+        <v>0</v>
+      </c>
+      <c r="J348">
+        <v>0</v>
+      </c>
+      <c r="K348">
+        <v>0</v>
+      </c>
+      <c r="L348">
+        <v>0</v>
+      </c>
+      <c r="M348">
+        <v>0</v>
+      </c>
+      <c r="N348">
+        <v>0</v>
+      </c>
+      <c r="O348" t="s">
+        <v>101</v>
+      </c>
+      <c r="P348" t="s">
+        <v>101</v>
+      </c>
+      <c r="Q348">
+        <v>4.33</v>
+      </c>
+      <c r="R348">
+        <v>2.05</v>
+      </c>
+      <c r="S348">
+        <v>2.88</v>
+      </c>
+      <c r="T348">
+        <v>1.5</v>
+      </c>
+      <c r="U348">
+        <v>2.5</v>
+      </c>
+      <c r="V348">
+        <v>3.4</v>
+      </c>
+      <c r="W348">
+        <v>1.3</v>
+      </c>
+      <c r="X348">
+        <v>10</v>
+      </c>
+      <c r="Y348">
+        <v>1.06</v>
+      </c>
+      <c r="Z348">
+        <v>3.56</v>
+      </c>
+      <c r="AA348">
+        <v>3.16</v>
+      </c>
+      <c r="AB348">
+        <v>2.12</v>
+      </c>
+      <c r="AC348">
+        <v>1.07</v>
+      </c>
+      <c r="AD348">
+        <v>8</v>
+      </c>
+      <c r="AE348">
+        <v>1.4</v>
+      </c>
+      <c r="AF348">
+        <v>2.9</v>
+      </c>
+      <c r="AG348">
+        <v>2.1</v>
+      </c>
+      <c r="AH348">
+        <v>1.67</v>
+      </c>
+      <c r="AI348">
+        <v>1.91</v>
+      </c>
+      <c r="AJ348">
+        <v>1.8</v>
+      </c>
+      <c r="AK348">
+        <v>1.67</v>
+      </c>
+      <c r="AL348">
+        <v>1.28</v>
+      </c>
+      <c r="AM348">
+        <v>1.3</v>
+      </c>
+      <c r="AN348">
+        <v>1.15</v>
+      </c>
+      <c r="AO348">
+        <v>1.38</v>
+      </c>
+      <c r="AP348">
+        <v>1.14</v>
+      </c>
+      <c r="AQ348">
+        <v>1.36</v>
+      </c>
+      <c r="AR348">
+        <v>1.22</v>
+      </c>
+      <c r="AS348">
+        <v>1.26</v>
+      </c>
+      <c r="AT348">
+        <v>2.48</v>
+      </c>
+      <c r="AU348">
+        <v>0</v>
+      </c>
+      <c r="AV348">
+        <v>2</v>
+      </c>
+      <c r="AW348">
+        <v>10</v>
+      </c>
+      <c r="AX348">
+        <v>8</v>
+      </c>
+      <c r="AY348">
+        <v>12</v>
+      </c>
+      <c r="AZ348">
+        <v>11</v>
+      </c>
+      <c r="BA348">
+        <v>9</v>
+      </c>
+      <c r="BB348">
+        <v>2</v>
+      </c>
+      <c r="BC348">
+        <v>11</v>
+      </c>
+      <c r="BD348">
+        <v>2.33</v>
+      </c>
+      <c r="BE348">
+        <v>6.5</v>
+      </c>
+      <c r="BF348">
+        <v>1.74</v>
+      </c>
+      <c r="BG348">
+        <v>1.29</v>
+      </c>
+      <c r="BH348">
+        <v>3.15</v>
+      </c>
+      <c r="BI348">
+        <v>1.5</v>
+      </c>
+      <c r="BJ348">
+        <v>2.38</v>
+      </c>
+      <c r="BK348">
+        <v>1.81</v>
+      </c>
+      <c r="BL348">
+        <v>1.88</v>
+      </c>
+      <c r="BM348">
+        <v>2.25</v>
+      </c>
+      <c r="BN348">
+        <v>1.55</v>
+      </c>
+      <c r="BO348">
+        <v>2.9</v>
+      </c>
+      <c r="BP348">
+        <v>1.35</v>
+      </c>
+    </row>
+    <row r="349" spans="1:68">
+      <c r="A349" s="1">
+        <v>348</v>
+      </c>
+      <c r="B349">
+        <v>7476911</v>
+      </c>
+      <c r="C349" t="s">
+        <v>68</v>
+      </c>
+      <c r="D349" t="s">
+        <v>69</v>
+      </c>
+      <c r="E349" s="2">
+        <v>45696.5</v>
+      </c>
+      <c r="F349">
+        <v>31</v>
+      </c>
+      <c r="G349" t="s">
+        <v>78</v>
+      </c>
+      <c r="H349" t="s">
+        <v>83</v>
+      </c>
+      <c r="I349">
+        <v>0</v>
+      </c>
+      <c r="J349">
+        <v>0</v>
+      </c>
+      <c r="K349">
+        <v>0</v>
+      </c>
+      <c r="L349">
+        <v>0</v>
+      </c>
+      <c r="M349">
+        <v>1</v>
+      </c>
+      <c r="N349">
+        <v>1</v>
+      </c>
+      <c r="O349" t="s">
+        <v>101</v>
+      </c>
+      <c r="P349" t="s">
+        <v>130</v>
+      </c>
+      <c r="Q349">
+        <v>2.88</v>
+      </c>
+      <c r="R349">
+        <v>2.2</v>
+      </c>
+      <c r="S349">
+        <v>3.75</v>
+      </c>
+      <c r="T349">
+        <v>1.36</v>
+      </c>
+      <c r="U349">
+        <v>3</v>
+      </c>
+      <c r="V349">
+        <v>2.75</v>
+      </c>
+      <c r="W349">
+        <v>1.4</v>
+      </c>
+      <c r="X349">
+        <v>7</v>
+      </c>
+      <c r="Y349">
+        <v>1.1</v>
+      </c>
+      <c r="Z349">
+        <v>2.18</v>
+      </c>
+      <c r="AA349">
+        <v>3.37</v>
+      </c>
+      <c r="AB349">
+        <v>3.17</v>
+      </c>
+      <c r="AC349">
+        <v>1.05</v>
+      </c>
+      <c r="AD349">
+        <v>9</v>
+      </c>
+      <c r="AE349">
+        <v>1.28</v>
+      </c>
+      <c r="AF349">
+        <v>3.55</v>
+      </c>
+      <c r="AG349">
+        <v>1.82</v>
+      </c>
+      <c r="AH349">
+        <v>1.92</v>
+      </c>
+      <c r="AI349">
+        <v>1.67</v>
+      </c>
+      <c r="AJ349">
+        <v>2.1</v>
+      </c>
+      <c r="AK349">
+        <v>1.35</v>
+      </c>
+      <c r="AL349">
+        <v>1.25</v>
+      </c>
+      <c r="AM349">
+        <v>1.65</v>
+      </c>
+      <c r="AN349">
+        <v>1.56</v>
+      </c>
+      <c r="AO349">
+        <v>1.4</v>
+      </c>
+      <c r="AP349">
+        <v>1.47</v>
+      </c>
+      <c r="AQ349">
+        <v>1.5</v>
+      </c>
+      <c r="AR349">
+        <v>1.33</v>
+      </c>
+      <c r="AS349">
+        <v>1.24</v>
+      </c>
+      <c r="AT349">
+        <v>2.57</v>
+      </c>
+      <c r="AU349">
+        <v>5</v>
+      </c>
+      <c r="AV349">
+        <v>5</v>
+      </c>
+      <c r="AW349">
+        <v>11</v>
+      </c>
+      <c r="AX349">
+        <v>6</v>
+      </c>
+      <c r="AY349">
+        <v>23</v>
+      </c>
+      <c r="AZ349">
+        <v>15</v>
+      </c>
+      <c r="BA349">
+        <v>11</v>
+      </c>
+      <c r="BB349">
+        <v>5</v>
+      </c>
+      <c r="BC349">
+        <v>16</v>
+      </c>
+      <c r="BD349">
+        <v>1.77</v>
+      </c>
+      <c r="BE349">
+        <v>6.4</v>
+      </c>
+      <c r="BF349">
+        <v>2.28</v>
+      </c>
+      <c r="BG349">
+        <v>1.29</v>
+      </c>
+      <c r="BH349">
+        <v>3.2</v>
+      </c>
+      <c r="BI349">
+        <v>1.5</v>
+      </c>
+      <c r="BJ349">
+        <v>2.4</v>
+      </c>
+      <c r="BK349">
+        <v>1.82</v>
+      </c>
+      <c r="BL349">
+        <v>1.98</v>
+      </c>
+      <c r="BM349">
+        <v>2.28</v>
+      </c>
+      <c r="BN349">
+        <v>1.54</v>
+      </c>
+      <c r="BO349">
+        <v>2.9</v>
+      </c>
+      <c r="BP349">
+        <v>1.34</v>
+      </c>
+    </row>
+    <row r="350" spans="1:68">
+      <c r="A350" s="1">
+        <v>349</v>
+      </c>
+      <c r="B350">
+        <v>7476912</v>
+      </c>
+      <c r="C350" t="s">
+        <v>68</v>
+      </c>
+      <c r="D350" t="s">
+        <v>69</v>
+      </c>
+      <c r="E350" s="2">
+        <v>45696.5</v>
+      </c>
+      <c r="F350">
+        <v>31</v>
+      </c>
+      <c r="G350" t="s">
+        <v>93</v>
+      </c>
+      <c r="H350" t="s">
+        <v>88</v>
+      </c>
+      <c r="I350">
+        <v>0</v>
+      </c>
+      <c r="J350">
+        <v>0</v>
+      </c>
+      <c r="K350">
+        <v>0</v>
+      </c>
+      <c r="L350">
+        <v>2</v>
+      </c>
+      <c r="M350">
+        <v>0</v>
+      </c>
+      <c r="N350">
+        <v>2</v>
+      </c>
+      <c r="O350" t="s">
+        <v>303</v>
+      </c>
+      <c r="P350" t="s">
+        <v>101</v>
+      </c>
+      <c r="Q350">
+        <v>1.83</v>
+      </c>
+      <c r="R350">
+        <v>2.6</v>
+      </c>
+      <c r="S350">
+        <v>7</v>
+      </c>
+      <c r="T350">
+        <v>1.29</v>
+      </c>
+      <c r="U350">
+        <v>3.5</v>
+      </c>
+      <c r="V350">
+        <v>2.38</v>
+      </c>
+      <c r="W350">
+        <v>1.53</v>
+      </c>
+      <c r="X350">
+        <v>5.5</v>
+      </c>
+      <c r="Y350">
+        <v>1.14</v>
+      </c>
+      <c r="Z350">
+        <v>1.4</v>
+      </c>
+      <c r="AA350">
+        <v>4.75</v>
+      </c>
+      <c r="AB350">
+        <v>6.9</v>
+      </c>
+      <c r="AC350">
+        <v>1.03</v>
+      </c>
+      <c r="AD350">
+        <v>11</v>
+      </c>
+      <c r="AE350">
+        <v>1.18</v>
+      </c>
+      <c r="AF350">
+        <v>4.75</v>
+      </c>
+      <c r="AG350">
+        <v>1.57</v>
+      </c>
+      <c r="AH350">
+        <v>2.3</v>
+      </c>
+      <c r="AI350">
+        <v>1.83</v>
+      </c>
+      <c r="AJ350">
+        <v>1.83</v>
+      </c>
+      <c r="AK350">
+        <v>1.09</v>
+      </c>
+      <c r="AL350">
+        <v>1.13</v>
+      </c>
+      <c r="AM350">
+        <v>2.85</v>
+      </c>
+      <c r="AN350">
+        <v>1.85</v>
+      </c>
+      <c r="AO350">
+        <v>0.88</v>
+      </c>
+      <c r="AP350">
+        <v>1.93</v>
+      </c>
+      <c r="AQ350">
+        <v>0.82</v>
+      </c>
+      <c r="AR350">
+        <v>1.71</v>
+      </c>
+      <c r="AS350">
+        <v>1.1</v>
+      </c>
+      <c r="AT350">
+        <v>2.81</v>
+      </c>
+      <c r="AU350">
+        <v>9</v>
+      </c>
+      <c r="AV350">
+        <v>5</v>
+      </c>
+      <c r="AW350">
+        <v>8</v>
+      </c>
+      <c r="AX350">
+        <v>9</v>
+      </c>
+      <c r="AY350">
+        <v>18</v>
+      </c>
+      <c r="AZ350">
+        <v>15</v>
+      </c>
+      <c r="BA350">
+        <v>4</v>
+      </c>
+      <c r="BB350">
+        <v>5</v>
+      </c>
+      <c r="BC350">
+        <v>9</v>
+      </c>
+      <c r="BD350">
+        <v>1.35</v>
+      </c>
+      <c r="BE350">
+        <v>7.5</v>
+      </c>
+      <c r="BF350">
+        <v>3.45</v>
+      </c>
+      <c r="BG350">
+        <v>1.2</v>
+      </c>
+      <c r="BH350">
+        <v>3.95</v>
+      </c>
+      <c r="BI350">
+        <v>1.34</v>
+      </c>
+      <c r="BJ350">
+        <v>2.9</v>
+      </c>
+      <c r="BK350">
+        <v>1.56</v>
+      </c>
+      <c r="BL350">
+        <v>2.23</v>
+      </c>
+      <c r="BM350">
+        <v>1.89</v>
+      </c>
+      <c r="BN350">
+        <v>1.8</v>
+      </c>
+      <c r="BO350">
+        <v>2.33</v>
+      </c>
+      <c r="BP350">
+        <v>1.52</v>
+      </c>
+    </row>
+    <row r="351" spans="1:68">
+      <c r="A351" s="1">
+        <v>350</v>
+      </c>
+      <c r="B351">
+        <v>7476913</v>
+      </c>
+      <c r="C351" t="s">
+        <v>68</v>
+      </c>
+      <c r="D351" t="s">
+        <v>69</v>
+      </c>
+      <c r="E351" s="2">
+        <v>45696.5</v>
+      </c>
+      <c r="F351">
+        <v>31</v>
+      </c>
+      <c r="G351" t="s">
+        <v>79</v>
+      </c>
+      <c r="H351" t="s">
+        <v>80</v>
+      </c>
+      <c r="I351">
+        <v>0</v>
+      </c>
+      <c r="J351">
+        <v>0</v>
+      </c>
+      <c r="K351">
+        <v>0</v>
+      </c>
+      <c r="L351">
+        <v>2</v>
+      </c>
+      <c r="M351">
+        <v>0</v>
+      </c>
+      <c r="N351">
+        <v>2</v>
+      </c>
+      <c r="O351" t="s">
+        <v>304</v>
+      </c>
+      <c r="P351" t="s">
+        <v>101</v>
+      </c>
+      <c r="Q351">
+        <v>2.4</v>
+      </c>
+      <c r="R351">
+        <v>2.05</v>
+      </c>
+      <c r="S351">
+        <v>5.5</v>
+      </c>
+      <c r="T351">
+        <v>1.5</v>
+      </c>
+      <c r="U351">
+        <v>2.5</v>
+      </c>
+      <c r="V351">
+        <v>3.4</v>
+      </c>
+      <c r="W351">
+        <v>1.3</v>
+      </c>
+      <c r="X351">
+        <v>10</v>
+      </c>
+      <c r="Y351">
+        <v>1.06</v>
+      </c>
+      <c r="Z351">
+        <v>1.75</v>
+      </c>
+      <c r="AA351">
+        <v>3.5</v>
+      </c>
+      <c r="AB351">
+        <v>4.75</v>
+      </c>
+      <c r="AC351">
+        <v>1.07</v>
+      </c>
+      <c r="AD351">
+        <v>8</v>
+      </c>
+      <c r="AE351">
+        <v>1.4</v>
+      </c>
+      <c r="AF351">
+        <v>2.9</v>
+      </c>
+      <c r="AG351">
+        <v>2.2</v>
+      </c>
+      <c r="AH351">
+        <v>1.61</v>
+      </c>
+      <c r="AI351">
+        <v>2.1</v>
+      </c>
+      <c r="AJ351">
+        <v>1.67</v>
+      </c>
+      <c r="AK351">
+        <v>1.18</v>
+      </c>
+      <c r="AL351">
+        <v>1.25</v>
+      </c>
+      <c r="AM351">
+        <v>2</v>
+      </c>
+      <c r="AN351">
+        <v>1.73</v>
+      </c>
+      <c r="AO351">
+        <v>0.57</v>
+      </c>
+      <c r="AP351">
+        <v>1.81</v>
+      </c>
+      <c r="AQ351">
+        <v>0.53</v>
+      </c>
+      <c r="AR351">
+        <v>1.55</v>
+      </c>
+      <c r="AS351">
+        <v>1.18</v>
+      </c>
+      <c r="AT351">
+        <v>2.73</v>
+      </c>
+      <c r="AU351">
+        <v>6</v>
+      </c>
+      <c r="AV351">
+        <v>5</v>
+      </c>
+      <c r="AW351">
+        <v>8</v>
+      </c>
+      <c r="AX351">
+        <v>5</v>
+      </c>
+      <c r="AY351">
+        <v>18</v>
+      </c>
+      <c r="AZ351">
+        <v>13</v>
+      </c>
+      <c r="BA351">
+        <v>1</v>
+      </c>
+      <c r="BB351">
+        <v>6</v>
+      </c>
+      <c r="BC351">
+        <v>7</v>
+      </c>
+      <c r="BD351">
+        <v>1.5</v>
+      </c>
+      <c r="BE351">
+        <v>6.75</v>
+      </c>
+      <c r="BF351">
+        <v>2.9</v>
+      </c>
+      <c r="BG351">
+        <v>1.3</v>
+      </c>
+      <c r="BH351">
+        <v>3.1</v>
+      </c>
+      <c r="BI351">
+        <v>1.52</v>
+      </c>
+      <c r="BJ351">
+        <v>2.33</v>
+      </c>
+      <c r="BK351">
+        <v>1.84</v>
+      </c>
+      <c r="BL351">
+        <v>1.84</v>
+      </c>
+      <c r="BM351">
+        <v>2.3</v>
+      </c>
+      <c r="BN351">
+        <v>1.54</v>
+      </c>
+      <c r="BO351">
+        <v>2.9</v>
+      </c>
+      <c r="BP351">
+        <v>1.34</v>
+      </c>
+    </row>
+    <row r="352" spans="1:68">
+      <c r="A352" s="1">
+        <v>351</v>
+      </c>
+      <c r="B352">
+        <v>7476910</v>
+      </c>
+      <c r="C352" t="s">
+        <v>68</v>
+      </c>
+      <c r="D352" t="s">
+        <v>69</v>
+      </c>
+      <c r="E352" s="2">
+        <v>45696.5</v>
+      </c>
+      <c r="F352">
+        <v>31</v>
+      </c>
+      <c r="G352" t="s">
+        <v>87</v>
+      </c>
+      <c r="H352" t="s">
+        <v>82</v>
+      </c>
+      <c r="I352">
+        <v>0</v>
+      </c>
+      <c r="J352">
+        <v>1</v>
+      </c>
+      <c r="K352">
+        <v>1</v>
+      </c>
+      <c r="L352">
+        <v>2</v>
+      </c>
+      <c r="M352">
+        <v>1</v>
+      </c>
+      <c r="N352">
+        <v>3</v>
+      </c>
+      <c r="O352" t="s">
+        <v>305</v>
+      </c>
+      <c r="P352" t="s">
+        <v>165</v>
+      </c>
+      <c r="Q352">
+        <v>2.75</v>
+      </c>
+      <c r="R352">
+        <v>2.1</v>
+      </c>
+      <c r="S352">
+        <v>4</v>
+      </c>
+      <c r="T352">
+        <v>1.4</v>
+      </c>
+      <c r="U352">
+        <v>2.75</v>
+      </c>
+      <c r="V352">
+        <v>3</v>
+      </c>
+      <c r="W352">
+        <v>1.36</v>
+      </c>
+      <c r="X352">
+        <v>8</v>
+      </c>
+      <c r="Y352">
+        <v>1.08</v>
+      </c>
+      <c r="Z352">
+        <v>2.15</v>
+      </c>
+      <c r="AA352">
+        <v>3.47</v>
+      </c>
+      <c r="AB352">
+        <v>3.17</v>
+      </c>
+      <c r="AC352">
+        <v>1.06</v>
+      </c>
+      <c r="AD352">
+        <v>8.5</v>
+      </c>
+      <c r="AE352">
+        <v>1.3</v>
+      </c>
+      <c r="AF352">
+        <v>3.35</v>
+      </c>
+      <c r="AG352">
+        <v>1.92</v>
+      </c>
+      <c r="AH352">
+        <v>1.82</v>
+      </c>
+      <c r="AI352">
+        <v>1.8</v>
+      </c>
+      <c r="AJ352">
+        <v>1.91</v>
+      </c>
+      <c r="AK352">
+        <v>1.3</v>
+      </c>
+      <c r="AL352">
+        <v>1.25</v>
+      </c>
+      <c r="AM352">
+        <v>1.7</v>
+      </c>
+      <c r="AN352">
+        <v>1.43</v>
+      </c>
+      <c r="AO352">
+        <v>0.86</v>
+      </c>
+      <c r="AP352">
+        <v>1.53</v>
+      </c>
+      <c r="AQ352">
+        <v>0.8</v>
+      </c>
+      <c r="AR352">
+        <v>1.3</v>
+      </c>
+      <c r="AS352">
+        <v>1.17</v>
+      </c>
+      <c r="AT352">
+        <v>2.47</v>
+      </c>
+      <c r="AU352">
+        <v>13</v>
+      </c>
+      <c r="AV352">
+        <v>4</v>
+      </c>
+      <c r="AW352">
+        <v>13</v>
+      </c>
+      <c r="AX352">
+        <v>3</v>
+      </c>
+      <c r="AY352">
+        <v>35</v>
+      </c>
+      <c r="AZ352">
+        <v>9</v>
+      </c>
+      <c r="BA352">
+        <v>12</v>
+      </c>
+      <c r="BB352">
+        <v>4</v>
+      </c>
+      <c r="BC352">
+        <v>16</v>
+      </c>
+      <c r="BD352">
+        <v>1.83</v>
+      </c>
+      <c r="BE352">
+        <v>6.25</v>
+      </c>
+      <c r="BF352">
+        <v>2.18</v>
+      </c>
+      <c r="BG352">
+        <v>1.41</v>
+      </c>
+      <c r="BH352">
+        <v>2.65</v>
+      </c>
+      <c r="BI352">
+        <v>1.67</v>
+      </c>
+      <c r="BJ352">
+        <v>2.05</v>
+      </c>
+      <c r="BK352">
+        <v>2.08</v>
+      </c>
+      <c r="BL352">
+        <v>1.65</v>
+      </c>
+      <c r="BM352">
+        <v>2.65</v>
+      </c>
+      <c r="BN352">
+        <v>1.41</v>
+      </c>
+      <c r="BO352">
+        <v>3.55</v>
+      </c>
+      <c r="BP352">
+        <v>1.24</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/England EFL League Two_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/England EFL League Two_20242025.xlsx
@@ -72514,13 +72514,13 @@
         <v>10</v>
       </c>
       <c r="BA344">
+        <v>5</v>
+      </c>
+      <c r="BB344">
+        <v>2</v>
+      </c>
+      <c r="BC344">
         <v>7</v>
-      </c>
-      <c r="BB344">
-        <v>2</v>
-      </c>
-      <c r="BC344">
-        <v>9</v>
       </c>
       <c r="BD344">
         <v>2.15</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/England EFL League Two_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/England EFL League Two_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2174" uniqueCount="440">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2210" uniqueCount="441">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -934,6 +934,9 @@
     <t>['62', '83']</t>
   </si>
   <si>
+    <t>['41', '45+2', '56']</t>
+  </si>
+  <si>
     <t>['1', '9']</t>
   </si>
   <si>
@@ -1695,7 +1698,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP352"/>
+  <dimension ref="A1:BP358"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -2157,7 +2160,7 @@
         <v>95</v>
       </c>
       <c r="P3" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="Q3">
         <v>2.5</v>
@@ -2235,7 +2238,7 @@
         <v>0</v>
       </c>
       <c r="AP3">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="AQ3">
         <v>1.21</v>
@@ -2441,10 +2444,10 @@
         <v>0</v>
       </c>
       <c r="AP4">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="AQ4">
-        <v>1.47</v>
+        <v>1.38</v>
       </c>
       <c r="AR4">
         <v>0</v>
@@ -2569,7 +2572,7 @@
         <v>97</v>
       </c>
       <c r="P5" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="Q5">
         <v>2.4</v>
@@ -2856,7 +2859,7 @@
         <v>1.87</v>
       </c>
       <c r="AQ6">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR6">
         <v>0</v>
@@ -3268,7 +3271,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ8">
-        <v>0.8</v>
+        <v>0.75</v>
       </c>
       <c r="AR8">
         <v>0</v>
@@ -3393,7 +3396,7 @@
         <v>101</v>
       </c>
       <c r="P9" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="Q9">
         <v>2.75</v>
@@ -3599,7 +3602,7 @@
         <v>102</v>
       </c>
       <c r="P10" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="Q10">
         <v>2.63</v>
@@ -3805,7 +3808,7 @@
         <v>101</v>
       </c>
       <c r="P11" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="Q11">
         <v>2.88</v>
@@ -4089,7 +4092,7 @@
         <v>0</v>
       </c>
       <c r="AP12">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="AQ12">
         <v>1.73</v>
@@ -4295,7 +4298,7 @@
         <v>0</v>
       </c>
       <c r="AP13">
-        <v>2.4</v>
+        <v>2.31</v>
       </c>
       <c r="AQ13">
         <v>0.82</v>
@@ -4835,7 +4838,7 @@
         <v>105</v>
       </c>
       <c r="P16" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="Q16">
         <v>2.88</v>
@@ -5122,7 +5125,7 @@
         <v>1.53</v>
       </c>
       <c r="AQ17">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR17">
         <v>0</v>
@@ -5247,7 +5250,7 @@
         <v>101</v>
       </c>
       <c r="P18" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="Q18">
         <v>3.4</v>
@@ -5453,7 +5456,7 @@
         <v>107</v>
       </c>
       <c r="P19" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="Q19">
         <v>3</v>
@@ -5943,7 +5946,7 @@
         <v>0</v>
       </c>
       <c r="AP21">
-        <v>1.77</v>
+        <v>1.86</v>
       </c>
       <c r="AQ21">
         <v>1.6</v>
@@ -6277,7 +6280,7 @@
         <v>101</v>
       </c>
       <c r="P23" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="Q23">
         <v>3</v>
@@ -6561,7 +6564,7 @@
         <v>0</v>
       </c>
       <c r="AP24">
-        <v>2.4</v>
+        <v>2.44</v>
       </c>
       <c r="AQ24">
         <v>1.36</v>
@@ -6689,7 +6692,7 @@
         <v>109</v>
       </c>
       <c r="P25" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="Q25">
         <v>2.63</v>
@@ -6770,7 +6773,7 @@
         <v>1.93</v>
       </c>
       <c r="AQ25">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AR25">
         <v>0</v>
@@ -6895,7 +6898,7 @@
         <v>110</v>
       </c>
       <c r="P26" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="Q26">
         <v>2.38</v>
@@ -7179,7 +7182,7 @@
         <v>3</v>
       </c>
       <c r="AP27">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="AQ27">
         <v>1.64</v>
@@ -7719,7 +7722,7 @@
         <v>112</v>
       </c>
       <c r="P30" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="Q30">
         <v>3</v>
@@ -7797,10 +7800,10 @@
         <v>0</v>
       </c>
       <c r="AP30">
-        <v>1.77</v>
+        <v>1.86</v>
       </c>
       <c r="AQ30">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR30">
         <v>0</v>
@@ -8006,7 +8009,7 @@
         <v>1.47</v>
       </c>
       <c r="AQ31">
-        <v>0.8</v>
+        <v>0.75</v>
       </c>
       <c r="AR31">
         <v>1.62</v>
@@ -8827,7 +8830,7 @@
         <v>3</v>
       </c>
       <c r="AP35">
-        <v>2.4</v>
+        <v>2.44</v>
       </c>
       <c r="AQ35">
         <v>1.5</v>
@@ -9033,7 +9036,7 @@
         <v>3</v>
       </c>
       <c r="AP36">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="AQ36">
         <v>1.63</v>
@@ -9161,7 +9164,7 @@
         <v>101</v>
       </c>
       <c r="P37" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="Q37">
         <v>2.6</v>
@@ -9367,7 +9370,7 @@
         <v>117</v>
       </c>
       <c r="P38" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="Q38">
         <v>2.88</v>
@@ -9779,7 +9782,7 @@
         <v>119</v>
       </c>
       <c r="P40" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="Q40">
         <v>3</v>
@@ -10191,7 +10194,7 @@
         <v>101</v>
       </c>
       <c r="P42" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="Q42">
         <v>3.75</v>
@@ -10475,7 +10478,7 @@
         <v>0</v>
       </c>
       <c r="AP43">
-        <v>2.4</v>
+        <v>2.31</v>
       </c>
       <c r="AQ43">
         <v>0.79</v>
@@ -10603,7 +10606,7 @@
         <v>121</v>
       </c>
       <c r="P44" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="Q44">
         <v>2.75</v>
@@ -10809,7 +10812,7 @@
         <v>122</v>
       </c>
       <c r="P45" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="Q45">
         <v>2.63</v>
@@ -10890,7 +10893,7 @@
         <v>1.07</v>
       </c>
       <c r="AQ45">
-        <v>1.47</v>
+        <v>1.38</v>
       </c>
       <c r="AR45">
         <v>1.02</v>
@@ -11299,10 +11302,10 @@
         <v>1</v>
       </c>
       <c r="AP47">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="AQ47">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AR47">
         <v>1.5</v>
@@ -11427,7 +11430,7 @@
         <v>125</v>
       </c>
       <c r="P48" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="Q48">
         <v>3.5</v>
@@ -11714,7 +11717,7 @@
         <v>1.81</v>
       </c>
       <c r="AQ49">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR49">
         <v>1.1</v>
@@ -11839,7 +11842,7 @@
         <v>127</v>
       </c>
       <c r="P50" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="Q50">
         <v>3.6</v>
@@ -11917,7 +11920,7 @@
         <v>1.5</v>
       </c>
       <c r="AP50">
-        <v>1.77</v>
+        <v>1.86</v>
       </c>
       <c r="AQ50">
         <v>1.63</v>
@@ -12045,7 +12048,7 @@
         <v>103</v>
       </c>
       <c r="P51" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="Q51">
         <v>2.5</v>
@@ -12123,7 +12126,7 @@
         <v>1</v>
       </c>
       <c r="AP51">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="AQ51">
         <v>1</v>
@@ -13359,10 +13362,10 @@
         <v>0</v>
       </c>
       <c r="AP57">
-        <v>2.4</v>
+        <v>2.44</v>
       </c>
       <c r="AQ57">
-        <v>0.8</v>
+        <v>0.75</v>
       </c>
       <c r="AR57">
         <v>1.74</v>
@@ -13774,7 +13777,7 @@
         <v>1.93</v>
       </c>
       <c r="AQ59">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR59">
         <v>1.79</v>
@@ -14183,10 +14186,10 @@
         <v>0</v>
       </c>
       <c r="AP61">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="AQ61">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR61">
         <v>1.47</v>
@@ -14723,7 +14726,7 @@
         <v>139</v>
       </c>
       <c r="P64" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="Q64">
         <v>3</v>
@@ -14801,7 +14804,7 @@
         <v>1.5</v>
       </c>
       <c r="AP64">
-        <v>2.4</v>
+        <v>2.31</v>
       </c>
       <c r="AQ64">
         <v>1</v>
@@ -15135,7 +15138,7 @@
         <v>141</v>
       </c>
       <c r="P66" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="Q66">
         <v>3.75</v>
@@ -15628,7 +15631,7 @@
         <v>1.14</v>
       </c>
       <c r="AQ68">
-        <v>1.47</v>
+        <v>1.38</v>
       </c>
       <c r="AR68">
         <v>1.88</v>
@@ -15753,7 +15756,7 @@
         <v>143</v>
       </c>
       <c r="P69" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="Q69">
         <v>3.2</v>
@@ -15959,7 +15962,7 @@
         <v>144</v>
       </c>
       <c r="P70" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="Q70">
         <v>3.25</v>
@@ -16165,7 +16168,7 @@
         <v>145</v>
       </c>
       <c r="P71" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="Q71">
         <v>3</v>
@@ -16246,7 +16249,7 @@
         <v>0.64</v>
       </c>
       <c r="AQ71">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AR71">
         <v>1.35</v>
@@ -16371,7 +16374,7 @@
         <v>146</v>
       </c>
       <c r="P72" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="Q72">
         <v>4</v>
@@ -16783,7 +16786,7 @@
         <v>101</v>
       </c>
       <c r="P74" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="Q74">
         <v>2.63</v>
@@ -16864,7 +16867,7 @@
         <v>1.47</v>
       </c>
       <c r="AQ74">
-        <v>0.8</v>
+        <v>0.75</v>
       </c>
       <c r="AR74">
         <v>1.69</v>
@@ -16989,7 +16992,7 @@
         <v>101</v>
       </c>
       <c r="P75" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="Q75">
         <v>3.4</v>
@@ -17195,7 +17198,7 @@
         <v>101</v>
       </c>
       <c r="P76" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="Q76">
         <v>2.6</v>
@@ -17607,7 +17610,7 @@
         <v>149</v>
       </c>
       <c r="P78" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="Q78">
         <v>2.88</v>
@@ -18097,7 +18100,7 @@
         <v>1.5</v>
       </c>
       <c r="AP80">
-        <v>2.4</v>
+        <v>2.44</v>
       </c>
       <c r="AQ80">
         <v>1.36</v>
@@ -18303,7 +18306,7 @@
         <v>1</v>
       </c>
       <c r="AP81">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="AQ81">
         <v>0.8100000000000001</v>
@@ -18637,7 +18640,7 @@
         <v>153</v>
       </c>
       <c r="P83" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="Q83">
         <v>2.2</v>
@@ -18921,7 +18924,7 @@
         <v>1</v>
       </c>
       <c r="AP84">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="AQ84">
         <v>1.36</v>
@@ -19127,7 +19130,7 @@
         <v>0.67</v>
       </c>
       <c r="AP85">
-        <v>2.4</v>
+        <v>2.31</v>
       </c>
       <c r="AQ85">
         <v>1.21</v>
@@ -19873,7 +19876,7 @@
         <v>157</v>
       </c>
       <c r="P89" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="Q89">
         <v>3.75</v>
@@ -19951,10 +19954,10 @@
         <v>2</v>
       </c>
       <c r="AP89">
-        <v>1.77</v>
+        <v>1.86</v>
       </c>
       <c r="AQ89">
-        <v>1.47</v>
+        <v>1.38</v>
       </c>
       <c r="AR89">
         <v>0.82</v>
@@ -20160,7 +20163,7 @@
         <v>1.07</v>
       </c>
       <c r="AQ90">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR90">
         <v>1.27</v>
@@ -20285,7 +20288,7 @@
         <v>101</v>
       </c>
       <c r="P91" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="Q91">
         <v>2.75</v>
@@ -20491,7 +20494,7 @@
         <v>101</v>
       </c>
       <c r="P92" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="Q92">
         <v>3.4</v>
@@ -20572,7 +20575,7 @@
         <v>1.8</v>
       </c>
       <c r="AQ92">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AR92">
         <v>1.26</v>
@@ -20697,7 +20700,7 @@
         <v>159</v>
       </c>
       <c r="P93" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="Q93">
         <v>2.75</v>
@@ -21109,7 +21112,7 @@
         <v>161</v>
       </c>
       <c r="P95" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="Q95">
         <v>2.5</v>
@@ -21315,7 +21318,7 @@
         <v>162</v>
       </c>
       <c r="P96" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="Q96">
         <v>4.5</v>
@@ -21396,7 +21399,7 @@
         <v>1.13</v>
       </c>
       <c r="AQ96">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR96">
         <v>1.14</v>
@@ -21599,7 +21602,7 @@
         <v>0.75</v>
       </c>
       <c r="AP97">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="AQ97">
         <v>1</v>
@@ -21805,7 +21808,7 @@
         <v>1</v>
       </c>
       <c r="AP98">
-        <v>1.77</v>
+        <v>1.86</v>
       </c>
       <c r="AQ98">
         <v>1.36</v>
@@ -22139,7 +22142,7 @@
         <v>166</v>
       </c>
       <c r="P100" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="Q100">
         <v>2.75</v>
@@ -22217,10 +22220,10 @@
         <v>1.75</v>
       </c>
       <c r="AP100">
-        <v>2.4</v>
+        <v>2.31</v>
       </c>
       <c r="AQ100">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AR100">
         <v>1.61</v>
@@ -22551,7 +22554,7 @@
         <v>167</v>
       </c>
       <c r="P102" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="Q102">
         <v>2.88</v>
@@ -22632,7 +22635,7 @@
         <v>1.8</v>
       </c>
       <c r="AQ102">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR102">
         <v>1.14</v>
@@ -22757,7 +22760,7 @@
         <v>101</v>
       </c>
       <c r="P103" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="Q103">
         <v>3</v>
@@ -22963,7 +22966,7 @@
         <v>168</v>
       </c>
       <c r="P104" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="Q104">
         <v>4</v>
@@ -23375,7 +23378,7 @@
         <v>101</v>
       </c>
       <c r="P106" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="Q106">
         <v>3.6</v>
@@ -24817,7 +24820,7 @@
         <v>172</v>
       </c>
       <c r="P113" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="Q113">
         <v>2.6</v>
@@ -25023,7 +25026,7 @@
         <v>173</v>
       </c>
       <c r="P114" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="Q114">
         <v>2.4</v>
@@ -25101,7 +25104,7 @@
         <v>0.25</v>
       </c>
       <c r="AP114">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="AQ114">
         <v>0.79</v>
@@ -25516,7 +25519,7 @@
         <v>1.53</v>
       </c>
       <c r="AQ116">
-        <v>0.8</v>
+        <v>0.75</v>
       </c>
       <c r="AR116">
         <v>1.85</v>
@@ -25719,7 +25722,7 @@
         <v>0.75</v>
       </c>
       <c r="AP117">
-        <v>2.4</v>
+        <v>2.44</v>
       </c>
       <c r="AQ117">
         <v>0.8100000000000001</v>
@@ -25847,7 +25850,7 @@
         <v>176</v>
       </c>
       <c r="P118" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="Q118">
         <v>2.5</v>
@@ -26053,7 +26056,7 @@
         <v>101</v>
       </c>
       <c r="P119" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="Q119">
         <v>3.4</v>
@@ -26131,7 +26134,7 @@
         <v>0.8</v>
       </c>
       <c r="AP119">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="AQ119">
         <v>1</v>
@@ -26259,7 +26262,7 @@
         <v>94</v>
       </c>
       <c r="P120" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="Q120">
         <v>2.88</v>
@@ -26877,7 +26880,7 @@
         <v>178</v>
       </c>
       <c r="P123" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="Q123">
         <v>2.38</v>
@@ -26958,7 +26961,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ123">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR123">
         <v>1.25</v>
@@ -27164,7 +27167,7 @@
         <v>1.87</v>
       </c>
       <c r="AQ124">
-        <v>1.47</v>
+        <v>1.38</v>
       </c>
       <c r="AR124">
         <v>1.08</v>
@@ -27289,7 +27292,7 @@
         <v>101</v>
       </c>
       <c r="P125" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="Q125">
         <v>2.1</v>
@@ -27367,7 +27370,7 @@
         <v>0.2</v>
       </c>
       <c r="AP125">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="AQ125">
         <v>0.82</v>
@@ -27573,10 +27576,10 @@
         <v>0.8</v>
       </c>
       <c r="AP126">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="AQ126">
-        <v>0.8</v>
+        <v>0.75</v>
       </c>
       <c r="AR126">
         <v>1.5</v>
@@ -27701,7 +27704,7 @@
         <v>180</v>
       </c>
       <c r="P127" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="Q127">
         <v>3.25</v>
@@ -27907,7 +27910,7 @@
         <v>101</v>
       </c>
       <c r="P128" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="Q128">
         <v>4.75</v>
@@ -27985,7 +27988,7 @@
         <v>1.4</v>
       </c>
       <c r="AP128">
-        <v>1.77</v>
+        <v>1.86</v>
       </c>
       <c r="AQ128">
         <v>1.21</v>
@@ -28525,7 +28528,7 @@
         <v>182</v>
       </c>
       <c r="P131" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="Q131">
         <v>2.63</v>
@@ -28606,7 +28609,7 @@
         <v>1.77</v>
       </c>
       <c r="AQ131">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AR131">
         <v>1.51</v>
@@ -28731,7 +28734,7 @@
         <v>183</v>
       </c>
       <c r="P132" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="Q132">
         <v>3.5</v>
@@ -29143,7 +29146,7 @@
         <v>185</v>
       </c>
       <c r="P134" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="Q134">
         <v>4</v>
@@ -29224,7 +29227,7 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="AQ134">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR134">
         <v>1.35</v>
@@ -29349,7 +29352,7 @@
         <v>147</v>
       </c>
       <c r="P135" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="Q135">
         <v>2.6</v>
@@ -29555,7 +29558,7 @@
         <v>186</v>
       </c>
       <c r="P136" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="Q136">
         <v>3.6</v>
@@ -29761,7 +29764,7 @@
         <v>187</v>
       </c>
       <c r="P137" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="Q137">
         <v>3</v>
@@ -30045,7 +30048,7 @@
         <v>1.4</v>
       </c>
       <c r="AP138">
-        <v>2.4</v>
+        <v>2.44</v>
       </c>
       <c r="AQ138">
         <v>0.93</v>
@@ -30173,7 +30176,7 @@
         <v>185</v>
       </c>
       <c r="P139" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="Q139">
         <v>2.5</v>
@@ -30379,7 +30382,7 @@
         <v>189</v>
       </c>
       <c r="P140" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="Q140">
         <v>2.25</v>
@@ -30457,10 +30460,10 @@
         <v>0.67</v>
       </c>
       <c r="AP140">
-        <v>2.4</v>
+        <v>2.31</v>
       </c>
       <c r="AQ140">
-        <v>0.8</v>
+        <v>0.75</v>
       </c>
       <c r="AR140">
         <v>1.55</v>
@@ -30872,7 +30875,7 @@
         <v>1.47</v>
       </c>
       <c r="AQ142">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR142">
         <v>1.27</v>
@@ -31203,7 +31206,7 @@
         <v>101</v>
       </c>
       <c r="P144" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="Q144">
         <v>2.25</v>
@@ -31490,7 +31493,7 @@
         <v>1.56</v>
       </c>
       <c r="AQ145">
-        <v>1.47</v>
+        <v>1.38</v>
       </c>
       <c r="AR145">
         <v>1.61</v>
@@ -31821,7 +31824,7 @@
         <v>101</v>
       </c>
       <c r="P147" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="Q147">
         <v>3</v>
@@ -31899,7 +31902,7 @@
         <v>1.5</v>
       </c>
       <c r="AP147">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="AQ147">
         <v>1.47</v>
@@ -32311,7 +32314,7 @@
         <v>2</v>
       </c>
       <c r="AP149">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="AQ149">
         <v>1.73</v>
@@ -32517,7 +32520,7 @@
         <v>0.67</v>
       </c>
       <c r="AP150">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="AQ150">
         <v>0.82</v>
@@ -32645,7 +32648,7 @@
         <v>193</v>
       </c>
       <c r="P151" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="Q151">
         <v>2.4</v>
@@ -32851,7 +32854,7 @@
         <v>194</v>
       </c>
       <c r="P152" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="Q152">
         <v>4.5</v>
@@ -33057,7 +33060,7 @@
         <v>195</v>
       </c>
       <c r="P153" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="Q153">
         <v>2.75</v>
@@ -33469,7 +33472,7 @@
         <v>197</v>
       </c>
       <c r="P155" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="Q155">
         <v>3</v>
@@ -33753,10 +33756,10 @@
         <v>1.67</v>
       </c>
       <c r="AP156">
-        <v>1.77</v>
+        <v>1.86</v>
       </c>
       <c r="AQ156">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AR156">
         <v>1.14</v>
@@ -33881,7 +33884,7 @@
         <v>198</v>
       </c>
       <c r="P157" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="Q157">
         <v>3.4</v>
@@ -33962,7 +33965,7 @@
         <v>1.53</v>
       </c>
       <c r="AQ157">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR157">
         <v>1.15</v>
@@ -34499,7 +34502,7 @@
         <v>200</v>
       </c>
       <c r="P160" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="Q160">
         <v>3.2</v>
@@ -34577,7 +34580,7 @@
         <v>1.67</v>
       </c>
       <c r="AP160">
-        <v>2.4</v>
+        <v>2.44</v>
       </c>
       <c r="AQ160">
         <v>1.6</v>
@@ -35323,7 +35326,7 @@
         <v>203</v>
       </c>
       <c r="P164" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="Q164">
         <v>2.4</v>
@@ -35610,7 +35613,7 @@
         <v>1.81</v>
       </c>
       <c r="AQ165">
-        <v>0.8</v>
+        <v>0.75</v>
       </c>
       <c r="AR165">
         <v>1.4</v>
@@ -35735,7 +35738,7 @@
         <v>204</v>
       </c>
       <c r="P166" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="Q166">
         <v>2.88</v>
@@ -36147,7 +36150,7 @@
         <v>206</v>
       </c>
       <c r="P168" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="Q168">
         <v>2.3</v>
@@ -36225,10 +36228,10 @@
         <v>1.67</v>
       </c>
       <c r="AP168">
-        <v>2.4</v>
+        <v>2.31</v>
       </c>
       <c r="AQ168">
-        <v>1.47</v>
+        <v>1.38</v>
       </c>
       <c r="AR168">
         <v>1.52</v>
@@ -36431,7 +36434,7 @@
         <v>0.86</v>
       </c>
       <c r="AP169">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="AQ169">
         <v>0.8100000000000001</v>
@@ -36559,7 +36562,7 @@
         <v>208</v>
       </c>
       <c r="P170" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="Q170">
         <v>2.5</v>
@@ -37049,7 +37052,7 @@
         <v>1.71</v>
       </c>
       <c r="AP172">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="AQ172">
         <v>1.47</v>
@@ -37177,7 +37180,7 @@
         <v>101</v>
       </c>
       <c r="P173" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="Q173">
         <v>2.1</v>
@@ -37258,7 +37261,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ173">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR173">
         <v>1.48</v>
@@ -37383,7 +37386,7 @@
         <v>148</v>
       </c>
       <c r="P174" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="Q174">
         <v>3.2</v>
@@ -37667,7 +37670,7 @@
         <v>0.67</v>
       </c>
       <c r="AP175">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="AQ175">
         <v>1.21</v>
@@ -38079,7 +38082,7 @@
         <v>1.88</v>
       </c>
       <c r="AP177">
-        <v>1.77</v>
+        <v>1.86</v>
       </c>
       <c r="AQ177">
         <v>1.47</v>
@@ -38413,7 +38416,7 @@
         <v>210</v>
       </c>
       <c r="P179" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="Q179">
         <v>2.3</v>
@@ -39318,7 +39321,7 @@
         <v>1.07</v>
       </c>
       <c r="AQ183">
-        <v>0.8</v>
+        <v>0.75</v>
       </c>
       <c r="AR183">
         <v>1.45</v>
@@ -39443,7 +39446,7 @@
         <v>185</v>
       </c>
       <c r="P184" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="Q184">
         <v>3.4</v>
@@ -39521,7 +39524,7 @@
         <v>0.67</v>
       </c>
       <c r="AP184">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="AQ184">
         <v>1.36</v>
@@ -39649,7 +39652,7 @@
         <v>215</v>
       </c>
       <c r="P185" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="Q185">
         <v>3.2</v>
@@ -40061,7 +40064,7 @@
         <v>217</v>
       </c>
       <c r="P187" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="Q187">
         <v>2.2</v>
@@ -40139,10 +40142,10 @@
         <v>0.86</v>
       </c>
       <c r="AP187">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="AQ187">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR187">
         <v>1.62</v>
@@ -40679,7 +40682,7 @@
         <v>101</v>
       </c>
       <c r="P190" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="Q190">
         <v>3.25</v>
@@ -40885,7 +40888,7 @@
         <v>148</v>
       </c>
       <c r="P191" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="Q191">
         <v>2.3</v>
@@ -41091,7 +41094,7 @@
         <v>219</v>
       </c>
       <c r="P192" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="Q192">
         <v>2.4</v>
@@ -41375,7 +41378,7 @@
         <v>1.57</v>
       </c>
       <c r="AP193">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="AQ193">
         <v>1.64</v>
@@ -41996,7 +41999,7 @@
         <v>1.77</v>
       </c>
       <c r="AQ196">
-        <v>1.47</v>
+        <v>1.38</v>
       </c>
       <c r="AR196">
         <v>1.37</v>
@@ -42121,7 +42124,7 @@
         <v>101</v>
       </c>
       <c r="P197" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="Q197">
         <v>3.75</v>
@@ -42199,7 +42202,7 @@
         <v>1</v>
       </c>
       <c r="AP197">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="AQ197">
         <v>1.36</v>
@@ -42327,7 +42330,7 @@
         <v>221</v>
       </c>
       <c r="P198" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="Q198">
         <v>2.2</v>
@@ -42405,7 +42408,7 @@
         <v>1.29</v>
       </c>
       <c r="AP198">
-        <v>2.4</v>
+        <v>2.31</v>
       </c>
       <c r="AQ198">
         <v>1.5</v>
@@ -42533,7 +42536,7 @@
         <v>122</v>
       </c>
       <c r="P199" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="Q199">
         <v>3.4</v>
@@ -42614,7 +42617,7 @@
         <v>0.64</v>
       </c>
       <c r="AQ199">
-        <v>1.47</v>
+        <v>1.38</v>
       </c>
       <c r="AR199">
         <v>1.51</v>
@@ -42945,7 +42948,7 @@
         <v>222</v>
       </c>
       <c r="P201" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="Q201">
         <v>2.85</v>
@@ -43026,7 +43029,7 @@
         <v>1.53</v>
       </c>
       <c r="AQ201">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR201">
         <v>1.24</v>
@@ -43151,7 +43154,7 @@
         <v>223</v>
       </c>
       <c r="P202" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="Q202">
         <v>1.8</v>
@@ -43229,7 +43232,7 @@
         <v>0.78</v>
       </c>
       <c r="AP202">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="AQ202">
         <v>0.8100000000000001</v>
@@ -43357,7 +43360,7 @@
         <v>205</v>
       </c>
       <c r="P203" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="Q203">
         <v>2.75</v>
@@ -43435,7 +43438,7 @@
         <v>0.88</v>
       </c>
       <c r="AP203">
-        <v>2.4</v>
+        <v>2.44</v>
       </c>
       <c r="AQ203">
         <v>0.64</v>
@@ -43563,7 +43566,7 @@
         <v>224</v>
       </c>
       <c r="P204" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="Q204">
         <v>3.55</v>
@@ -44387,7 +44390,7 @@
         <v>228</v>
       </c>
       <c r="P208" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="Q208">
         <v>2.4</v>
@@ -44465,7 +44468,7 @@
         <v>1.11</v>
       </c>
       <c r="AP208">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="AQ208">
         <v>0.82</v>
@@ -44593,7 +44596,7 @@
         <v>229</v>
       </c>
       <c r="P209" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="Q209">
         <v>2.5</v>
@@ -44671,7 +44674,7 @@
         <v>1.56</v>
       </c>
       <c r="AP209">
-        <v>2.4</v>
+        <v>2.31</v>
       </c>
       <c r="AQ209">
         <v>1.73</v>
@@ -45005,7 +45008,7 @@
         <v>231</v>
       </c>
       <c r="P211" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="Q211">
         <v>3.5</v>
@@ -45829,7 +45832,7 @@
         <v>101</v>
       </c>
       <c r="P215" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="Q215">
         <v>4.33</v>
@@ -46035,7 +46038,7 @@
         <v>234</v>
       </c>
       <c r="P216" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="Q216">
         <v>3</v>
@@ -46241,7 +46244,7 @@
         <v>235</v>
       </c>
       <c r="P217" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="Q217">
         <v>0</v>
@@ -46528,7 +46531,7 @@
         <v>1.47</v>
       </c>
       <c r="AQ218">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AR218">
         <v>1.22</v>
@@ -46653,7 +46656,7 @@
         <v>101</v>
       </c>
       <c r="P219" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="Q219">
         <v>3.2</v>
@@ -47143,7 +47146,7 @@
         <v>1</v>
       </c>
       <c r="AP221">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="AQ221">
         <v>0.8100000000000001</v>
@@ -47477,7 +47480,7 @@
         <v>101</v>
       </c>
       <c r="P223" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="Q223">
         <v>3.75</v>
@@ -47683,7 +47686,7 @@
         <v>101</v>
       </c>
       <c r="P224" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="Q224">
         <v>3.4</v>
@@ -47764,7 +47767,7 @@
         <v>1.53</v>
       </c>
       <c r="AQ224">
-        <v>1.47</v>
+        <v>1.38</v>
       </c>
       <c r="AR224">
         <v>1.28</v>
@@ -48173,7 +48176,7 @@
         <v>0.89</v>
       </c>
       <c r="AP226">
-        <v>2.4</v>
+        <v>2.31</v>
       </c>
       <c r="AQ226">
         <v>0.64</v>
@@ -48379,7 +48382,7 @@
         <v>1.89</v>
       </c>
       <c r="AP227">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="AQ227">
         <v>1.6</v>
@@ -48585,7 +48588,7 @@
         <v>0.8</v>
       </c>
       <c r="AP228">
-        <v>2.4</v>
+        <v>2.44</v>
       </c>
       <c r="AQ228">
         <v>1</v>
@@ -48919,7 +48922,7 @@
         <v>101</v>
       </c>
       <c r="P230" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="Q230">
         <v>2.5</v>
@@ -49331,7 +49334,7 @@
         <v>240</v>
       </c>
       <c r="P232" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="Q232">
         <v>2.4</v>
@@ -49412,7 +49415,7 @@
         <v>1.56</v>
       </c>
       <c r="AQ232">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR232">
         <v>1.34</v>
@@ -49537,7 +49540,7 @@
         <v>241</v>
       </c>
       <c r="P233" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="Q233">
         <v>2.88</v>
@@ -50233,10 +50236,10 @@
         <v>1.38</v>
       </c>
       <c r="AP236">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="AQ236">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AR236">
         <v>1.41</v>
@@ -50442,7 +50445,7 @@
         <v>1.77</v>
       </c>
       <c r="AQ237">
-        <v>0.8</v>
+        <v>0.75</v>
       </c>
       <c r="AR237">
         <v>1.18</v>
@@ -50773,7 +50776,7 @@
         <v>245</v>
       </c>
       <c r="P239" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="Q239">
         <v>4.5</v>
@@ -50851,10 +50854,10 @@
         <v>1.43</v>
       </c>
       <c r="AP239">
-        <v>1.77</v>
+        <v>1.86</v>
       </c>
       <c r="AQ239">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR239">
         <v>1.15</v>
@@ -50979,7 +50982,7 @@
         <v>101</v>
       </c>
       <c r="P240" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="Q240">
         <v>3.75</v>
@@ -51185,7 +51188,7 @@
         <v>101</v>
       </c>
       <c r="P241" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="Q241">
         <v>5.5</v>
@@ -51391,7 +51394,7 @@
         <v>246</v>
       </c>
       <c r="P242" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="Q242">
         <v>2.88</v>
@@ -51597,7 +51600,7 @@
         <v>101</v>
       </c>
       <c r="P243" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="Q243">
         <v>3.5</v>
@@ -52090,7 +52093,7 @@
         <v>1.8</v>
       </c>
       <c r="AQ245">
-        <v>1.47</v>
+        <v>1.38</v>
       </c>
       <c r="AR245">
         <v>1.29</v>
@@ -52215,7 +52218,7 @@
         <v>248</v>
       </c>
       <c r="P246" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="Q246">
         <v>2.38</v>
@@ -52421,7 +52424,7 @@
         <v>101</v>
       </c>
       <c r="P247" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="Q247">
         <v>2.6</v>
@@ -52911,7 +52914,7 @@
         <v>1.7</v>
       </c>
       <c r="AP249">
-        <v>2.4</v>
+        <v>2.31</v>
       </c>
       <c r="AQ249">
         <v>1.6</v>
@@ -53245,7 +53248,7 @@
         <v>252</v>
       </c>
       <c r="P251" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="Q251">
         <v>2.25</v>
@@ -53323,7 +53326,7 @@
         <v>0.73</v>
       </c>
       <c r="AP251">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="AQ251">
         <v>1</v>
@@ -53529,7 +53532,7 @@
         <v>1.91</v>
       </c>
       <c r="AP252">
-        <v>2.4</v>
+        <v>2.44</v>
       </c>
       <c r="AQ252">
         <v>1.63</v>
@@ -53657,7 +53660,7 @@
         <v>254</v>
       </c>
       <c r="P253" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="Q253">
         <v>2.1</v>
@@ -53863,7 +53866,7 @@
         <v>101</v>
       </c>
       <c r="P254" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="Q254">
         <v>2.5</v>
@@ -54275,7 +54278,7 @@
         <v>114</v>
       </c>
       <c r="P256" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="Q256">
         <v>2.88</v>
@@ -54562,7 +54565,7 @@
         <v>0.64</v>
       </c>
       <c r="AQ257">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR257">
         <v>1.34</v>
@@ -54765,7 +54768,7 @@
         <v>0.73</v>
       </c>
       <c r="AP258">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="AQ258">
         <v>0.64</v>
@@ -55383,7 +55386,7 @@
         <v>0.75</v>
       </c>
       <c r="AP261">
-        <v>2.4</v>
+        <v>2.31</v>
       </c>
       <c r="AQ261">
         <v>0.8100000000000001</v>
@@ -55592,7 +55595,7 @@
         <v>1.47</v>
       </c>
       <c r="AQ262">
-        <v>1.47</v>
+        <v>1.38</v>
       </c>
       <c r="AR262">
         <v>1.35</v>
@@ -55795,7 +55798,7 @@
         <v>1.45</v>
       </c>
       <c r="AP263">
-        <v>2.4</v>
+        <v>2.44</v>
       </c>
       <c r="AQ263">
         <v>1.21</v>
@@ -56335,7 +56338,7 @@
         <v>259</v>
       </c>
       <c r="P266" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="Q266">
         <v>3.6</v>
@@ -56619,7 +56622,7 @@
         <v>1.1</v>
       </c>
       <c r="AP267">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="AQ267">
         <v>0.93</v>
@@ -56953,7 +56956,7 @@
         <v>261</v>
       </c>
       <c r="P269" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="Q269">
         <v>2.75</v>
@@ -57034,7 +57037,7 @@
         <v>1.73</v>
       </c>
       <c r="AQ269">
-        <v>0.8</v>
+        <v>0.75</v>
       </c>
       <c r="AR269">
         <v>1.12</v>
@@ -57159,7 +57162,7 @@
         <v>262</v>
       </c>
       <c r="P270" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="Q270">
         <v>2.4</v>
@@ -57240,7 +57243,7 @@
         <v>1.87</v>
       </c>
       <c r="AQ270">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AR270">
         <v>1.45</v>
@@ -57365,7 +57368,7 @@
         <v>101</v>
       </c>
       <c r="P271" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="Q271">
         <v>4</v>
@@ -57571,7 +57574,7 @@
         <v>263</v>
       </c>
       <c r="P272" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="Q272">
         <v>3.1</v>
@@ -57983,7 +57986,7 @@
         <v>184</v>
       </c>
       <c r="P274" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="Q274">
         <v>3.25</v>
@@ -58189,7 +58192,7 @@
         <v>265</v>
       </c>
       <c r="P275" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="Q275">
         <v>3.4</v>
@@ -58267,7 +58270,7 @@
         <v>0.91</v>
       </c>
       <c r="AP275">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="AQ275">
         <v>1</v>
@@ -58395,7 +58398,7 @@
         <v>266</v>
       </c>
       <c r="P276" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="Q276">
         <v>2.88</v>
@@ -58476,7 +58479,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ276">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR276">
         <v>1.46</v>
@@ -58601,7 +58604,7 @@
         <v>267</v>
       </c>
       <c r="P277" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="Q277">
         <v>3.1</v>
@@ -58807,7 +58810,7 @@
         <v>101</v>
       </c>
       <c r="P278" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="Q278">
         <v>3.1</v>
@@ -59013,7 +59016,7 @@
         <v>128</v>
       </c>
       <c r="P279" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="Q279">
         <v>5</v>
@@ -59091,7 +59094,7 @@
         <v>1.3</v>
       </c>
       <c r="AP279">
-        <v>1.77</v>
+        <v>1.86</v>
       </c>
       <c r="AQ279">
         <v>1.36</v>
@@ -59503,7 +59506,7 @@
         <v>1.58</v>
       </c>
       <c r="AP281">
-        <v>2.4</v>
+        <v>2.44</v>
       </c>
       <c r="AQ281">
         <v>1.47</v>
@@ -59631,7 +59634,7 @@
         <v>101</v>
       </c>
       <c r="P282" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="Q282">
         <v>2.6</v>
@@ -59712,7 +59715,7 @@
         <v>1.53</v>
       </c>
       <c r="AQ282">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR282">
         <v>1.6</v>
@@ -59915,10 +59918,10 @@
         <v>0.82</v>
       </c>
       <c r="AP283">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="AQ283">
-        <v>0.8</v>
+        <v>0.75</v>
       </c>
       <c r="AR283">
         <v>1.46</v>
@@ -60455,7 +60458,7 @@
         <v>101</v>
       </c>
       <c r="P286" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="Q286">
         <v>2.5</v>
@@ -60533,7 +60536,7 @@
         <v>0.83</v>
       </c>
       <c r="AP286">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="AQ286">
         <v>0.8100000000000001</v>
@@ -60661,7 +60664,7 @@
         <v>270</v>
       </c>
       <c r="P287" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="Q287">
         <v>2.75</v>
@@ -60945,7 +60948,7 @@
         <v>0.73</v>
       </c>
       <c r="AP288">
-        <v>2.4</v>
+        <v>2.31</v>
       </c>
       <c r="AQ288">
         <v>0.53</v>
@@ -61154,7 +61157,7 @@
         <v>1.47</v>
       </c>
       <c r="AQ289">
-        <v>1.47</v>
+        <v>1.38</v>
       </c>
       <c r="AR289">
         <v>1.31</v>
@@ -61485,7 +61488,7 @@
         <v>101</v>
       </c>
       <c r="P291" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="Q291">
         <v>4</v>
@@ -61975,7 +61978,7 @@
         <v>0.67</v>
       </c>
       <c r="AP293">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="AQ293">
         <v>0.53</v>
@@ -62103,7 +62106,7 @@
         <v>101</v>
       </c>
       <c r="P294" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="Q294">
         <v>4</v>
@@ -62184,7 +62187,7 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="AQ294">
-        <v>1.47</v>
+        <v>1.38</v>
       </c>
       <c r="AR294">
         <v>1.31</v>
@@ -62309,7 +62312,7 @@
         <v>274</v>
       </c>
       <c r="P295" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="Q295">
         <v>2</v>
@@ -62515,7 +62518,7 @@
         <v>101</v>
       </c>
       <c r="P296" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="Q296">
         <v>2.75</v>
@@ -62596,7 +62599,7 @@
         <v>1.81</v>
       </c>
       <c r="AQ296">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AR296">
         <v>1.45</v>
@@ -62927,7 +62930,7 @@
         <v>276</v>
       </c>
       <c r="P298" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="Q298">
         <v>2.38</v>
@@ -63005,10 +63008,10 @@
         <v>1.44</v>
       </c>
       <c r="AP298">
-        <v>2.4</v>
+        <v>2.31</v>
       </c>
       <c r="AQ298">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR298">
         <v>1.58</v>
@@ -63133,7 +63136,7 @@
         <v>101</v>
       </c>
       <c r="P299" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="Q299">
         <v>2.88</v>
@@ -63339,7 +63342,7 @@
         <v>101</v>
       </c>
       <c r="P300" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="Q300">
         <v>3.6</v>
@@ -64038,7 +64041,7 @@
         <v>1.56</v>
       </c>
       <c r="AQ303">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR303">
         <v>1.31</v>
@@ -64163,7 +64166,7 @@
         <v>278</v>
       </c>
       <c r="P304" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="Q304">
         <v>4</v>
@@ -64241,7 +64244,7 @@
         <v>0.71</v>
       </c>
       <c r="AP304">
-        <v>1.77</v>
+        <v>1.86</v>
       </c>
       <c r="AQ304">
         <v>1</v>
@@ -64653,7 +64656,7 @@
         <v>2.09</v>
       </c>
       <c r="AP306">
-        <v>2.4</v>
+        <v>2.44</v>
       </c>
       <c r="AQ306">
         <v>1.64</v>
@@ -64862,7 +64865,7 @@
         <v>1.73</v>
       </c>
       <c r="AQ307">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR307">
         <v>1.21</v>
@@ -65065,7 +65068,7 @@
         <v>1.46</v>
       </c>
       <c r="AP308">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="AQ308">
         <v>1.47</v>
@@ -65477,7 +65480,7 @@
         <v>1</v>
       </c>
       <c r="AP310">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="AQ310">
         <v>0.93</v>
@@ -65605,7 +65608,7 @@
         <v>282</v>
       </c>
       <c r="P311" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="Q311">
         <v>3.75</v>
@@ -65811,7 +65814,7 @@
         <v>195</v>
       </c>
       <c r="P312" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="Q312">
         <v>2.63</v>
@@ -65892,7 +65895,7 @@
         <v>1.56</v>
       </c>
       <c r="AQ312">
-        <v>0.8</v>
+        <v>0.75</v>
       </c>
       <c r="AR312">
         <v>1.34</v>
@@ -66919,7 +66922,7 @@
         <v>1</v>
       </c>
       <c r="AP317">
-        <v>2.4</v>
+        <v>2.44</v>
       </c>
       <c r="AQ317">
         <v>0.82</v>
@@ -67047,7 +67050,7 @@
         <v>283</v>
       </c>
       <c r="P318" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="Q318">
         <v>3.4</v>
@@ -67746,7 +67749,7 @@
         <v>1.93</v>
       </c>
       <c r="AQ321">
-        <v>0.8</v>
+        <v>0.75</v>
       </c>
       <c r="AR321">
         <v>1.74</v>
@@ -68695,7 +68698,7 @@
         <v>290</v>
       </c>
       <c r="P326" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="Q326">
         <v>3.75</v>
@@ -68773,7 +68776,7 @@
         <v>1.62</v>
       </c>
       <c r="AP326">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="AQ326">
         <v>1.6</v>
@@ -68901,7 +68904,7 @@
         <v>291</v>
       </c>
       <c r="P327" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="Q327">
         <v>3.75</v>
@@ -69394,7 +69397,7 @@
         <v>1.77</v>
       </c>
       <c r="AQ329">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR329">
         <v>1.33</v>
@@ -69519,7 +69522,7 @@
         <v>293</v>
       </c>
       <c r="P330" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="Q330">
         <v>2.63</v>
@@ -69597,7 +69600,7 @@
         <v>1.38</v>
       </c>
       <c r="AP330">
-        <v>2.4</v>
+        <v>2.31</v>
       </c>
       <c r="AQ330">
         <v>1.36</v>
@@ -69725,7 +69728,7 @@
         <v>260</v>
       </c>
       <c r="P331" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="Q331">
         <v>3.5</v>
@@ -69803,7 +69806,7 @@
         <v>1.08</v>
       </c>
       <c r="AP331">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="AQ331">
         <v>1.21</v>
@@ -70009,7 +70012,7 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="AP332">
-        <v>1.77</v>
+        <v>1.86</v>
       </c>
       <c r="AQ332">
         <v>0.64</v>
@@ -70137,7 +70140,7 @@
         <v>294</v>
       </c>
       <c r="P333" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="Q333">
         <v>4</v>
@@ -70218,7 +70221,7 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="AQ333">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AR333">
         <v>1.34</v>
@@ -70424,7 +70427,7 @@
         <v>1.13</v>
       </c>
       <c r="AQ334">
-        <v>1.47</v>
+        <v>1.38</v>
       </c>
       <c r="AR334">
         <v>1.08</v>
@@ -70630,7 +70633,7 @@
         <v>1.87</v>
       </c>
       <c r="AQ335">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR335">
         <v>1.49</v>
@@ -70755,7 +70758,7 @@
         <v>101</v>
       </c>
       <c r="P336" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="Q336">
         <v>2.63</v>
@@ -71039,7 +71042,7 @@
         <v>1.08</v>
       </c>
       <c r="AP337">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="AQ337">
         <v>1</v>
@@ -71167,7 +71170,7 @@
         <v>296</v>
       </c>
       <c r="P338" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="Q338">
         <v>3.1</v>
@@ -71373,7 +71376,7 @@
         <v>297</v>
       </c>
       <c r="P339" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="Q339">
         <v>3</v>
@@ -71657,7 +71660,7 @@
         <v>0.93</v>
       </c>
       <c r="AP340">
-        <v>1.77</v>
+        <v>1.86</v>
       </c>
       <c r="AQ340">
         <v>0.82</v>
@@ -71785,7 +71788,7 @@
         <v>299</v>
       </c>
       <c r="P341" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="Q341">
         <v>3</v>
@@ -71991,7 +71994,7 @@
         <v>300</v>
       </c>
       <c r="P342" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="Q342">
         <v>3.1</v>
@@ -72275,7 +72278,7 @@
         <v>0.87</v>
       </c>
       <c r="AP343">
-        <v>2.4</v>
+        <v>2.44</v>
       </c>
       <c r="AQ343">
         <v>0.8100000000000001</v>
@@ -72609,7 +72612,7 @@
         <v>101</v>
       </c>
       <c r="P345" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="Q345">
         <v>1.91</v>
@@ -73099,7 +73102,7 @@
         <v>1</v>
       </c>
       <c r="AP347">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="AQ347">
         <v>0.93</v>
@@ -74132,7 +74135,7 @@
         <v>1.53</v>
       </c>
       <c r="AQ352">
-        <v>0.8</v>
+        <v>0.75</v>
       </c>
       <c r="AR352">
         <v>1.3</v>
@@ -74208,6 +74211,1242 @@
       </c>
       <c r="BP352">
         <v>1.24</v>
+      </c>
+    </row>
+    <row r="353" spans="1:68">
+      <c r="A353" s="1">
+        <v>352</v>
+      </c>
+      <c r="B353">
+        <v>7476641</v>
+      </c>
+      <c r="C353" t="s">
+        <v>68</v>
+      </c>
+      <c r="D353" t="s">
+        <v>69</v>
+      </c>
+      <c r="E353" s="2">
+        <v>45699.69791666666</v>
+      </c>
+      <c r="F353">
+        <v>9</v>
+      </c>
+      <c r="G353" t="s">
+        <v>71</v>
+      </c>
+      <c r="H353" t="s">
+        <v>86</v>
+      </c>
+      <c r="I353">
+        <v>2</v>
+      </c>
+      <c r="J353">
+        <v>0</v>
+      </c>
+      <c r="K353">
+        <v>2</v>
+      </c>
+      <c r="L353">
+        <v>3</v>
+      </c>
+      <c r="M353">
+        <v>0</v>
+      </c>
+      <c r="N353">
+        <v>3</v>
+      </c>
+      <c r="O353" t="s">
+        <v>306</v>
+      </c>
+      <c r="P353" t="s">
+        <v>101</v>
+      </c>
+      <c r="Q353">
+        <v>2.63</v>
+      </c>
+      <c r="R353">
+        <v>2</v>
+      </c>
+      <c r="S353">
+        <v>5</v>
+      </c>
+      <c r="T353">
+        <v>1.53</v>
+      </c>
+      <c r="U353">
+        <v>2.38</v>
+      </c>
+      <c r="V353">
+        <v>3.75</v>
+      </c>
+      <c r="W353">
+        <v>1.25</v>
+      </c>
+      <c r="X353">
+        <v>11</v>
+      </c>
+      <c r="Y353">
+        <v>1.05</v>
+      </c>
+      <c r="Z353">
+        <v>2.14</v>
+      </c>
+      <c r="AA353">
+        <v>3.18</v>
+      </c>
+      <c r="AB353">
+        <v>3.47</v>
+      </c>
+      <c r="AC353">
+        <v>1.09</v>
+      </c>
+      <c r="AD353">
+        <v>7</v>
+      </c>
+      <c r="AE353">
+        <v>1.48</v>
+      </c>
+      <c r="AF353">
+        <v>2.65</v>
+      </c>
+      <c r="AG353">
+        <v>2.37</v>
+      </c>
+      <c r="AH353">
+        <v>1.53</v>
+      </c>
+      <c r="AI353">
+        <v>2.2</v>
+      </c>
+      <c r="AJ353">
+        <v>1.62</v>
+      </c>
+      <c r="AK353">
+        <v>1.22</v>
+      </c>
+      <c r="AL353">
+        <v>1.28</v>
+      </c>
+      <c r="AM353">
+        <v>1.8</v>
+      </c>
+      <c r="AN353">
+        <v>2.14</v>
+      </c>
+      <c r="AO353">
+        <v>1.47</v>
+      </c>
+      <c r="AP353">
+        <v>2.2</v>
+      </c>
+      <c r="AQ353">
+        <v>1.38</v>
+      </c>
+      <c r="AR353">
+        <v>1.41</v>
+      </c>
+      <c r="AS353">
+        <v>1.12</v>
+      </c>
+      <c r="AT353">
+        <v>2.53</v>
+      </c>
+      <c r="AU353">
+        <v>8</v>
+      </c>
+      <c r="AV353">
+        <v>0</v>
+      </c>
+      <c r="AW353">
+        <v>6</v>
+      </c>
+      <c r="AX353">
+        <v>5</v>
+      </c>
+      <c r="AY353">
+        <v>15</v>
+      </c>
+      <c r="AZ353">
+        <v>8</v>
+      </c>
+      <c r="BA353">
+        <v>1</v>
+      </c>
+      <c r="BB353">
+        <v>3</v>
+      </c>
+      <c r="BC353">
+        <v>4</v>
+      </c>
+      <c r="BD353">
+        <v>1.52</v>
+      </c>
+      <c r="BE353">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="BF353">
+        <v>3</v>
+      </c>
+      <c r="BG353">
+        <v>1.22</v>
+      </c>
+      <c r="BH353">
+        <v>3.48</v>
+      </c>
+      <c r="BI353">
+        <v>1.45</v>
+      </c>
+      <c r="BJ353">
+        <v>2.48</v>
+      </c>
+      <c r="BK353">
+        <v>1.8</v>
+      </c>
+      <c r="BL353">
+        <v>1.91</v>
+      </c>
+      <c r="BM353">
+        <v>2.3</v>
+      </c>
+      <c r="BN353">
+        <v>1.52</v>
+      </c>
+      <c r="BO353">
+        <v>3.04</v>
+      </c>
+      <c r="BP353">
+        <v>1.29</v>
+      </c>
+    </row>
+    <row r="354" spans="1:68">
+      <c r="A354" s="1">
+        <v>353</v>
+      </c>
+      <c r="B354">
+        <v>7476734</v>
+      </c>
+      <c r="C354" t="s">
+        <v>68</v>
+      </c>
+      <c r="D354" t="s">
+        <v>69</v>
+      </c>
+      <c r="E354" s="2">
+        <v>45699.69791666666</v>
+      </c>
+      <c r="F354">
+        <v>16</v>
+      </c>
+      <c r="G354" t="s">
+        <v>80</v>
+      </c>
+      <c r="H354" t="s">
+        <v>75</v>
+      </c>
+      <c r="I354">
+        <v>0</v>
+      </c>
+      <c r="J354">
+        <v>0</v>
+      </c>
+      <c r="K354">
+        <v>0</v>
+      </c>
+      <c r="L354">
+        <v>0</v>
+      </c>
+      <c r="M354">
+        <v>0</v>
+      </c>
+      <c r="N354">
+        <v>0</v>
+      </c>
+      <c r="O354" t="s">
+        <v>101</v>
+      </c>
+      <c r="P354" t="s">
+        <v>101</v>
+      </c>
+      <c r="Q354">
+        <v>2.95</v>
+      </c>
+      <c r="R354">
+        <v>2.05</v>
+      </c>
+      <c r="S354">
+        <v>3.4</v>
+      </c>
+      <c r="T354">
+        <v>1.4</v>
+      </c>
+      <c r="U354">
+        <v>2.7</v>
+      </c>
+      <c r="V354">
+        <v>2.8</v>
+      </c>
+      <c r="W354">
+        <v>1.38</v>
+      </c>
+      <c r="X354">
+        <v>6.65</v>
+      </c>
+      <c r="Y354">
+        <v>1.09</v>
+      </c>
+      <c r="Z354">
+        <v>2.77</v>
+      </c>
+      <c r="AA354">
+        <v>3.27</v>
+      </c>
+      <c r="AB354">
+        <v>2.48</v>
+      </c>
+      <c r="AC354">
+        <v>1.06</v>
+      </c>
+      <c r="AD354">
+        <v>8.5</v>
+      </c>
+      <c r="AE354">
+        <v>1.3</v>
+      </c>
+      <c r="AF354">
+        <v>3.45</v>
+      </c>
+      <c r="AG354">
+        <v>2.05</v>
+      </c>
+      <c r="AH354">
+        <v>1.73</v>
+      </c>
+      <c r="AI354">
+        <v>1.7</v>
+      </c>
+      <c r="AJ354">
+        <v>2</v>
+      </c>
+      <c r="AK354">
+        <v>1.38</v>
+      </c>
+      <c r="AL354">
+        <v>1.25</v>
+      </c>
+      <c r="AM354">
+        <v>1.57</v>
+      </c>
+      <c r="AN354">
+        <v>1.29</v>
+      </c>
+      <c r="AO354">
+        <v>1.17</v>
+      </c>
+      <c r="AP354">
+        <v>1.27</v>
+      </c>
+      <c r="AQ354">
+        <v>1.15</v>
+      </c>
+      <c r="AR354">
+        <v>1.52</v>
+      </c>
+      <c r="AS354">
+        <v>1.19</v>
+      </c>
+      <c r="AT354">
+        <v>2.71</v>
+      </c>
+      <c r="AU354">
+        <v>3</v>
+      </c>
+      <c r="AV354">
+        <v>0</v>
+      </c>
+      <c r="AW354">
+        <v>12</v>
+      </c>
+      <c r="AX354">
+        <v>7</v>
+      </c>
+      <c r="AY354">
+        <v>15</v>
+      </c>
+      <c r="AZ354">
+        <v>8</v>
+      </c>
+      <c r="BA354">
+        <v>3</v>
+      </c>
+      <c r="BB354">
+        <v>0</v>
+      </c>
+      <c r="BC354">
+        <v>3</v>
+      </c>
+      <c r="BD354">
+        <v>1.82</v>
+      </c>
+      <c r="BE354">
+        <v>6.55</v>
+      </c>
+      <c r="BF354">
+        <v>2.48</v>
+      </c>
+      <c r="BG354">
+        <v>1.25</v>
+      </c>
+      <c r="BH354">
+        <v>3.6</v>
+      </c>
+      <c r="BI354">
+        <v>1.35</v>
+      </c>
+      <c r="BJ354">
+        <v>2.74</v>
+      </c>
+      <c r="BK354">
+        <v>1.64</v>
+      </c>
+      <c r="BL354">
+        <v>2.07</v>
+      </c>
+      <c r="BM354">
+        <v>1.95</v>
+      </c>
+      <c r="BN354">
+        <v>1.77</v>
+      </c>
+      <c r="BO354">
+        <v>2.71</v>
+      </c>
+      <c r="BP354">
+        <v>1.38</v>
+      </c>
+    </row>
+    <row r="355" spans="1:68">
+      <c r="A355" s="1">
+        <v>354</v>
+      </c>
+      <c r="B355">
+        <v>7476768</v>
+      </c>
+      <c r="C355" t="s">
+        <v>68</v>
+      </c>
+      <c r="D355" t="s">
+        <v>69</v>
+      </c>
+      <c r="E355" s="2">
+        <v>45699.69791666666</v>
+      </c>
+      <c r="F355">
+        <v>19</v>
+      </c>
+      <c r="G355" t="s">
+        <v>89</v>
+      </c>
+      <c r="H355" t="s">
+        <v>82</v>
+      </c>
+      <c r="I355">
+        <v>0</v>
+      </c>
+      <c r="J355">
+        <v>0</v>
+      </c>
+      <c r="K355">
+        <v>0</v>
+      </c>
+      <c r="L355">
+        <v>1</v>
+      </c>
+      <c r="M355">
+        <v>0</v>
+      </c>
+      <c r="N355">
+        <v>1</v>
+      </c>
+      <c r="O355" t="s">
+        <v>266</v>
+      </c>
+      <c r="P355" t="s">
+        <v>101</v>
+      </c>
+      <c r="Q355">
+        <v>3.75</v>
+      </c>
+      <c r="R355">
+        <v>2.1</v>
+      </c>
+      <c r="S355">
+        <v>2.88</v>
+      </c>
+      <c r="T355">
+        <v>1.4</v>
+      </c>
+      <c r="U355">
+        <v>2.75</v>
+      </c>
+      <c r="V355">
+        <v>3</v>
+      </c>
+      <c r="W355">
+        <v>1.36</v>
+      </c>
+      <c r="X355">
+        <v>8</v>
+      </c>
+      <c r="Y355">
+        <v>1.08</v>
+      </c>
+      <c r="Z355">
+        <v>2.98</v>
+      </c>
+      <c r="AA355">
+        <v>3.37</v>
+      </c>
+      <c r="AB355">
+        <v>2.29</v>
+      </c>
+      <c r="AC355">
+        <v>1.05</v>
+      </c>
+      <c r="AD355">
+        <v>11</v>
+      </c>
+      <c r="AE355">
+        <v>1.3</v>
+      </c>
+      <c r="AF355">
+        <v>3.4</v>
+      </c>
+      <c r="AG355">
+        <v>1.98</v>
+      </c>
+      <c r="AH355">
+        <v>1.77</v>
+      </c>
+      <c r="AI355">
+        <v>1.73</v>
+      </c>
+      <c r="AJ355">
+        <v>2</v>
+      </c>
+      <c r="AK355">
+        <v>1.65</v>
+      </c>
+      <c r="AL355">
+        <v>1.25</v>
+      </c>
+      <c r="AM355">
+        <v>1.38</v>
+      </c>
+      <c r="AN355">
+        <v>1.77</v>
+      </c>
+      <c r="AO355">
+        <v>0.8</v>
+      </c>
+      <c r="AP355">
+        <v>1.86</v>
+      </c>
+      <c r="AQ355">
+        <v>0.75</v>
+      </c>
+      <c r="AR355">
+        <v>1.24</v>
+      </c>
+      <c r="AS355">
+        <v>1.16</v>
+      </c>
+      <c r="AT355">
+        <v>2.4</v>
+      </c>
+      <c r="AU355">
+        <v>2</v>
+      </c>
+      <c r="AV355">
+        <v>5</v>
+      </c>
+      <c r="AW355">
+        <v>8</v>
+      </c>
+      <c r="AX355">
+        <v>14</v>
+      </c>
+      <c r="AY355">
+        <v>11</v>
+      </c>
+      <c r="AZ355">
+        <v>25</v>
+      </c>
+      <c r="BA355">
+        <v>3</v>
+      </c>
+      <c r="BB355">
+        <v>10</v>
+      </c>
+      <c r="BC355">
+        <v>13</v>
+      </c>
+      <c r="BD355">
+        <v>2.62</v>
+      </c>
+      <c r="BE355">
+        <v>8</v>
+      </c>
+      <c r="BF355">
+        <v>1.69</v>
+      </c>
+      <c r="BG355">
+        <v>1.27</v>
+      </c>
+      <c r="BH355">
+        <v>3.5</v>
+      </c>
+      <c r="BI355">
+        <v>1.5</v>
+      </c>
+      <c r="BJ355">
+        <v>2.5</v>
+      </c>
+      <c r="BK355">
+        <v>1.77</v>
+      </c>
+      <c r="BL355">
+        <v>1.95</v>
+      </c>
+      <c r="BM355">
+        <v>2.3</v>
+      </c>
+      <c r="BN355">
+        <v>1.57</v>
+      </c>
+      <c r="BO355">
+        <v>3</v>
+      </c>
+      <c r="BP355">
+        <v>1.36</v>
+      </c>
+    </row>
+    <row r="356" spans="1:68">
+      <c r="A356" s="1">
+        <v>355</v>
+      </c>
+      <c r="B356">
+        <v>7476761</v>
+      </c>
+      <c r="C356" t="s">
+        <v>68</v>
+      </c>
+      <c r="D356" t="s">
+        <v>69</v>
+      </c>
+      <c r="E356" s="2">
+        <v>45699.69791666666</v>
+      </c>
+      <c r="F356">
+        <v>19</v>
+      </c>
+      <c r="G356" t="s">
+        <v>72</v>
+      </c>
+      <c r="H356" t="s">
+        <v>78</v>
+      </c>
+      <c r="I356">
+        <v>1</v>
+      </c>
+      <c r="J356">
+        <v>1</v>
+      </c>
+      <c r="K356">
+        <v>2</v>
+      </c>
+      <c r="L356">
+        <v>2</v>
+      </c>
+      <c r="M356">
+        <v>1</v>
+      </c>
+      <c r="N356">
+        <v>3</v>
+      </c>
+      <c r="O356" t="s">
+        <v>194</v>
+      </c>
+      <c r="P356" t="s">
+        <v>118</v>
+      </c>
+      <c r="Q356">
+        <v>3.4</v>
+      </c>
+      <c r="R356">
+        <v>2.05</v>
+      </c>
+      <c r="S356">
+        <v>3.4</v>
+      </c>
+      <c r="T356">
+        <v>1.44</v>
+      </c>
+      <c r="U356">
+        <v>2.63</v>
+      </c>
+      <c r="V356">
+        <v>3.4</v>
+      </c>
+      <c r="W356">
+        <v>1.3</v>
+      </c>
+      <c r="X356">
+        <v>10</v>
+      </c>
+      <c r="Y356">
+        <v>1.06</v>
+      </c>
+      <c r="Z356">
+        <v>2.4</v>
+      </c>
+      <c r="AA356">
+        <v>3.25</v>
+      </c>
+      <c r="AB356">
+        <v>2.9</v>
+      </c>
+      <c r="AC356">
+        <v>1.07</v>
+      </c>
+      <c r="AD356">
+        <v>8</v>
+      </c>
+      <c r="AE356">
+        <v>1.38</v>
+      </c>
+      <c r="AF356">
+        <v>3</v>
+      </c>
+      <c r="AG356">
+        <v>2</v>
+      </c>
+      <c r="AH356">
+        <v>1.73</v>
+      </c>
+      <c r="AI356">
+        <v>1.83</v>
+      </c>
+      <c r="AJ356">
+        <v>1.83</v>
+      </c>
+      <c r="AK356">
+        <v>1.45</v>
+      </c>
+      <c r="AL356">
+        <v>1.28</v>
+      </c>
+      <c r="AM356">
+        <v>1.48</v>
+      </c>
+      <c r="AN356">
+        <v>1.67</v>
+      </c>
+      <c r="AO356">
+        <v>1.08</v>
+      </c>
+      <c r="AP356">
+        <v>1.75</v>
+      </c>
+      <c r="AQ356">
+        <v>1</v>
+      </c>
+      <c r="AR356">
+        <v>1.41</v>
+      </c>
+      <c r="AS356">
+        <v>1.38</v>
+      </c>
+      <c r="AT356">
+        <v>2.79</v>
+      </c>
+      <c r="AU356">
+        <v>5</v>
+      </c>
+      <c r="AV356">
+        <v>3</v>
+      </c>
+      <c r="AW356">
+        <v>9</v>
+      </c>
+      <c r="AX356">
+        <v>7</v>
+      </c>
+      <c r="AY356">
+        <v>18</v>
+      </c>
+      <c r="AZ356">
+        <v>13</v>
+      </c>
+      <c r="BA356">
+        <v>4</v>
+      </c>
+      <c r="BB356">
+        <v>3</v>
+      </c>
+      <c r="BC356">
+        <v>7</v>
+      </c>
+      <c r="BD356">
+        <v>1.65</v>
+      </c>
+      <c r="BE356">
+        <v>6</v>
+      </c>
+      <c r="BF356">
+        <v>2.8</v>
+      </c>
+      <c r="BG356">
+        <v>1.25</v>
+      </c>
+      <c r="BH356">
+        <v>3.14</v>
+      </c>
+      <c r="BI356">
+        <v>1.49</v>
+      </c>
+      <c r="BJ356">
+        <v>2.3</v>
+      </c>
+      <c r="BK356">
+        <v>1.89</v>
+      </c>
+      <c r="BL356">
+        <v>1.81</v>
+      </c>
+      <c r="BM356">
+        <v>2.41</v>
+      </c>
+      <c r="BN356">
+        <v>1.45</v>
+      </c>
+      <c r="BO356">
+        <v>3.22</v>
+      </c>
+      <c r="BP356">
+        <v>1.24</v>
+      </c>
+    </row>
+    <row r="357" spans="1:68">
+      <c r="A357" s="1">
+        <v>356</v>
+      </c>
+      <c r="B357">
+        <v>7476737</v>
+      </c>
+      <c r="C357" t="s">
+        <v>68</v>
+      </c>
+      <c r="D357" t="s">
+        <v>69</v>
+      </c>
+      <c r="E357" s="2">
+        <v>45699.69791666666</v>
+      </c>
+      <c r="F357">
+        <v>17</v>
+      </c>
+      <c r="G357" t="s">
+        <v>92</v>
+      </c>
+      <c r="H357" t="s">
+        <v>84</v>
+      </c>
+      <c r="I357">
+        <v>1</v>
+      </c>
+      <c r="J357">
+        <v>0</v>
+      </c>
+      <c r="K357">
+        <v>1</v>
+      </c>
+      <c r="L357">
+        <v>1</v>
+      </c>
+      <c r="M357">
+        <v>0</v>
+      </c>
+      <c r="N357">
+        <v>1</v>
+      </c>
+      <c r="O357" t="s">
+        <v>102</v>
+      </c>
+      <c r="P357" t="s">
+        <v>101</v>
+      </c>
+      <c r="Q357">
+        <v>2.38</v>
+      </c>
+      <c r="R357">
+        <v>2.25</v>
+      </c>
+      <c r="S357">
+        <v>4.75</v>
+      </c>
+      <c r="T357">
+        <v>1.36</v>
+      </c>
+      <c r="U357">
+        <v>3</v>
+      </c>
+      <c r="V357">
+        <v>2.75</v>
+      </c>
+      <c r="W357">
+        <v>1.4</v>
+      </c>
+      <c r="X357">
+        <v>7</v>
+      </c>
+      <c r="Y357">
+        <v>1.1</v>
+      </c>
+      <c r="Z357">
+        <v>1.72</v>
+      </c>
+      <c r="AA357">
+        <v>3.59</v>
+      </c>
+      <c r="AB357">
+        <v>4.75</v>
+      </c>
+      <c r="AC357">
+        <v>1.05</v>
+      </c>
+      <c r="AD357">
+        <v>9.5</v>
+      </c>
+      <c r="AE357">
+        <v>1.28</v>
+      </c>
+      <c r="AF357">
+        <v>3.65</v>
+      </c>
+      <c r="AG357">
+        <v>1.82</v>
+      </c>
+      <c r="AH357">
+        <v>1.92</v>
+      </c>
+      <c r="AI357">
+        <v>1.8</v>
+      </c>
+      <c r="AJ357">
+        <v>1.91</v>
+      </c>
+      <c r="AK357">
+        <v>1.18</v>
+      </c>
+      <c r="AL357">
+        <v>1.22</v>
+      </c>
+      <c r="AM357">
+        <v>2.05</v>
+      </c>
+      <c r="AN357">
+        <v>2.4</v>
+      </c>
+      <c r="AO357">
+        <v>1</v>
+      </c>
+      <c r="AP357">
+        <v>2.44</v>
+      </c>
+      <c r="AQ357">
+        <v>0.93</v>
+      </c>
+      <c r="AR357">
+        <v>1.44</v>
+      </c>
+      <c r="AS357">
+        <v>1.35</v>
+      </c>
+      <c r="AT357">
+        <v>2.79</v>
+      </c>
+      <c r="AU357">
+        <v>4</v>
+      </c>
+      <c r="AV357">
+        <v>2</v>
+      </c>
+      <c r="AW357">
+        <v>4</v>
+      </c>
+      <c r="AX357">
+        <v>6</v>
+      </c>
+      <c r="AY357">
+        <v>8</v>
+      </c>
+      <c r="AZ357">
+        <v>9</v>
+      </c>
+      <c r="BA357">
+        <v>8</v>
+      </c>
+      <c r="BB357">
+        <v>3</v>
+      </c>
+      <c r="BC357">
+        <v>11</v>
+      </c>
+      <c r="BD357">
+        <v>1.37</v>
+      </c>
+      <c r="BE357">
+        <v>8.5</v>
+      </c>
+      <c r="BF357">
+        <v>3.86</v>
+      </c>
+      <c r="BG357">
+        <v>1.25</v>
+      </c>
+      <c r="BH357">
+        <v>3.58</v>
+      </c>
+      <c r="BI357">
+        <v>1.45</v>
+      </c>
+      <c r="BJ357">
+        <v>2.55</v>
+      </c>
+      <c r="BK357">
+        <v>1.75</v>
+      </c>
+      <c r="BL357">
+        <v>1.96</v>
+      </c>
+      <c r="BM357">
+        <v>2.21</v>
+      </c>
+      <c r="BN357">
+        <v>1.59</v>
+      </c>
+      <c r="BO357">
+        <v>2.9</v>
+      </c>
+      <c r="BP357">
+        <v>1.36</v>
+      </c>
+    </row>
+    <row r="358" spans="1:68">
+      <c r="A358" s="1">
+        <v>357</v>
+      </c>
+      <c r="B358">
+        <v>7476735</v>
+      </c>
+      <c r="C358" t="s">
+        <v>68</v>
+      </c>
+      <c r="D358" t="s">
+        <v>69</v>
+      </c>
+      <c r="E358" s="2">
+        <v>45699.69791666666</v>
+      </c>
+      <c r="F358">
+        <v>16</v>
+      </c>
+      <c r="G358" t="s">
+        <v>81</v>
+      </c>
+      <c r="H358" t="s">
+        <v>76</v>
+      </c>
+      <c r="I358">
+        <v>0</v>
+      </c>
+      <c r="J358">
+        <v>0</v>
+      </c>
+      <c r="K358">
+        <v>0</v>
+      </c>
+      <c r="L358">
+        <v>1</v>
+      </c>
+      <c r="M358">
+        <v>1</v>
+      </c>
+      <c r="N358">
+        <v>2</v>
+      </c>
+      <c r="O358" t="s">
+        <v>178</v>
+      </c>
+      <c r="P358" t="s">
+        <v>319</v>
+      </c>
+      <c r="Q358">
+        <v>2.45</v>
+      </c>
+      <c r="R358">
+        <v>2.05</v>
+      </c>
+      <c r="S358">
+        <v>4.5</v>
+      </c>
+      <c r="T358">
+        <v>1.42</v>
+      </c>
+      <c r="U358">
+        <v>2.62</v>
+      </c>
+      <c r="V358">
+        <v>2.95</v>
+      </c>
+      <c r="W358">
+        <v>1.35</v>
+      </c>
+      <c r="X358">
+        <v>6.85</v>
+      </c>
+      <c r="Y358">
+        <v>1.07</v>
+      </c>
+      <c r="Z358">
+        <v>1.72</v>
+      </c>
+      <c r="AA358">
+        <v>3.59</v>
+      </c>
+      <c r="AB358">
+        <v>4.75</v>
+      </c>
+      <c r="AC358">
+        <v>1.07</v>
+      </c>
+      <c r="AD358">
+        <v>8</v>
+      </c>
+      <c r="AE358">
+        <v>1.36</v>
+      </c>
+      <c r="AF358">
+        <v>3.1</v>
+      </c>
+      <c r="AG358">
+        <v>1.77</v>
+      </c>
+      <c r="AH358">
+        <v>1.98</v>
+      </c>
+      <c r="AI358">
+        <v>1.85</v>
+      </c>
+      <c r="AJ358">
+        <v>1.8</v>
+      </c>
+      <c r="AK358">
+        <v>1.2</v>
+      </c>
+      <c r="AL358">
+        <v>1.25</v>
+      </c>
+      <c r="AM358">
+        <v>1.95</v>
+      </c>
+      <c r="AN358">
+        <v>2.4</v>
+      </c>
+      <c r="AO358">
+        <v>0.93</v>
+      </c>
+      <c r="AP358">
+        <v>2.31</v>
+      </c>
+      <c r="AQ358">
+        <v>0.93</v>
+      </c>
+      <c r="AR358">
+        <v>1.68</v>
+      </c>
+      <c r="AS358">
+        <v>1.03</v>
+      </c>
+      <c r="AT358">
+        <v>2.71</v>
+      </c>
+      <c r="AU358">
+        <v>3</v>
+      </c>
+      <c r="AV358">
+        <v>4</v>
+      </c>
+      <c r="AW358">
+        <v>8</v>
+      </c>
+      <c r="AX358">
+        <v>8</v>
+      </c>
+      <c r="AY358">
+        <v>11</v>
+      </c>
+      <c r="AZ358">
+        <v>12</v>
+      </c>
+      <c r="BA358">
+        <v>8</v>
+      </c>
+      <c r="BB358">
+        <v>1</v>
+      </c>
+      <c r="BC358">
+        <v>9</v>
+      </c>
+      <c r="BD358">
+        <v>1.31</v>
+      </c>
+      <c r="BE358">
+        <v>9.6</v>
+      </c>
+      <c r="BF358">
+        <v>4.2</v>
+      </c>
+      <c r="BG358">
+        <v>1.26</v>
+      </c>
+      <c r="BH358">
+        <v>3.22</v>
+      </c>
+      <c r="BI358">
+        <v>1.5</v>
+      </c>
+      <c r="BJ358">
+        <v>2.35</v>
+      </c>
+      <c r="BK358">
+        <v>1.88</v>
+      </c>
+      <c r="BL358">
+        <v>1.82</v>
+      </c>
+      <c r="BM358">
+        <v>2.42</v>
+      </c>
+      <c r="BN358">
+        <v>1.47</v>
+      </c>
+      <c r="BO358">
+        <v>3.2</v>
+      </c>
+      <c r="BP358">
+        <v>1.26</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/England EFL League Two_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/England EFL League Two_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2210" uniqueCount="441">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2216" uniqueCount="441">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -1698,7 +1698,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP358"/>
+  <dimension ref="A1:BP359"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -4095,7 +4095,7 @@
         <v>1.27</v>
       </c>
       <c r="AQ12">
-        <v>1.73</v>
+        <v>1.63</v>
       </c>
       <c r="AR12">
         <v>0</v>
@@ -6152,7 +6152,7 @@
         <v>0</v>
       </c>
       <c r="AP22">
-        <v>1.77</v>
+        <v>1.86</v>
       </c>
       <c r="AQ22">
         <v>0.53</v>
@@ -9448,7 +9448,7 @@
         <v>0</v>
       </c>
       <c r="AP38">
-        <v>1.77</v>
+        <v>1.86</v>
       </c>
       <c r="AQ38">
         <v>1.6</v>
@@ -9863,7 +9863,7 @@
         <v>1.47</v>
       </c>
       <c r="AQ40">
-        <v>1.73</v>
+        <v>1.63</v>
       </c>
       <c r="AR40">
         <v>0</v>
@@ -15010,7 +15010,7 @@
         <v>1.5</v>
       </c>
       <c r="AP65">
-        <v>1.77</v>
+        <v>1.86</v>
       </c>
       <c r="AQ65">
         <v>1.21</v>
@@ -15837,7 +15837,7 @@
         <v>1.07</v>
       </c>
       <c r="AQ69">
-        <v>1.73</v>
+        <v>1.63</v>
       </c>
       <c r="AR69">
         <v>1.03</v>
@@ -19545,7 +19545,7 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="AQ87">
-        <v>1.73</v>
+        <v>1.63</v>
       </c>
       <c r="AR87">
         <v>1.28</v>
@@ -19748,7 +19748,7 @@
         <v>1</v>
       </c>
       <c r="AP88">
-        <v>1.77</v>
+        <v>1.86</v>
       </c>
       <c r="AQ88">
         <v>1</v>
@@ -21190,7 +21190,7 @@
         <v>0.5</v>
       </c>
       <c r="AP95">
-        <v>1.77</v>
+        <v>1.86</v>
       </c>
       <c r="AQ95">
         <v>1.21</v>
@@ -22841,7 +22841,7 @@
         <v>0.64</v>
       </c>
       <c r="AQ103">
-        <v>1.73</v>
+        <v>1.63</v>
       </c>
       <c r="AR103">
         <v>1.32</v>
@@ -25931,7 +25931,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ118">
-        <v>1.73</v>
+        <v>1.63</v>
       </c>
       <c r="AR118">
         <v>1.26</v>
@@ -28606,7 +28606,7 @@
         <v>2</v>
       </c>
       <c r="AP131">
-        <v>1.77</v>
+        <v>1.86</v>
       </c>
       <c r="AQ131">
         <v>1.15</v>
@@ -32317,7 +32317,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ149">
-        <v>1.73</v>
+        <v>1.63</v>
       </c>
       <c r="AR149">
         <v>1.45</v>
@@ -33550,7 +33550,7 @@
         <v>0.8</v>
       </c>
       <c r="AP155">
-        <v>1.77</v>
+        <v>1.86</v>
       </c>
       <c r="AQ155">
         <v>1.36</v>
@@ -37879,7 +37879,7 @@
         <v>1.87</v>
       </c>
       <c r="AQ176">
-        <v>1.73</v>
+        <v>1.63</v>
       </c>
       <c r="AR176">
         <v>1.32</v>
@@ -38909,7 +38909,7 @@
         <v>1.73</v>
       </c>
       <c r="AQ181">
-        <v>1.73</v>
+        <v>1.63</v>
       </c>
       <c r="AR181">
         <v>1.19</v>
@@ -41996,7 +41996,7 @@
         <v>1.57</v>
       </c>
       <c r="AP196">
-        <v>1.77</v>
+        <v>1.86</v>
       </c>
       <c r="AQ196">
         <v>1.38</v>
@@ -44677,7 +44677,7 @@
         <v>2.31</v>
       </c>
       <c r="AQ209">
-        <v>1.73</v>
+        <v>1.63</v>
       </c>
       <c r="AR209">
         <v>1.49</v>
@@ -45498,7 +45498,7 @@
         <v>1.75</v>
       </c>
       <c r="AP213">
-        <v>1.77</v>
+        <v>1.86</v>
       </c>
       <c r="AQ213">
         <v>1.64</v>
@@ -47355,7 +47355,7 @@
         <v>1.81</v>
       </c>
       <c r="AQ222">
-        <v>1.73</v>
+        <v>1.63</v>
       </c>
       <c r="AR222">
         <v>1.41</v>
@@ -50442,7 +50442,7 @@
         <v>0.89</v>
       </c>
       <c r="AP237">
-        <v>1.77</v>
+        <v>1.86</v>
       </c>
       <c r="AQ237">
         <v>0.75</v>
@@ -52505,7 +52505,7 @@
         <v>1.47</v>
       </c>
       <c r="AQ247">
-        <v>1.73</v>
+        <v>1.63</v>
       </c>
       <c r="AR247">
         <v>1.35</v>
@@ -56419,7 +56419,7 @@
         <v>1.8</v>
       </c>
       <c r="AQ266">
-        <v>1.73</v>
+        <v>1.63</v>
       </c>
       <c r="AR266">
         <v>1.31</v>
@@ -56828,7 +56828,7 @@
         <v>0.9</v>
       </c>
       <c r="AP268">
-        <v>1.77</v>
+        <v>1.86</v>
       </c>
       <c r="AQ268">
         <v>0.79</v>
@@ -62390,7 +62390,7 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="AP295">
-        <v>1.77</v>
+        <v>1.86</v>
       </c>
       <c r="AQ295">
         <v>0.8100000000000001</v>
@@ -63423,7 +63423,7 @@
         <v>1.14</v>
       </c>
       <c r="AQ300">
-        <v>1.73</v>
+        <v>1.63</v>
       </c>
       <c r="AR300">
         <v>1.29</v>
@@ -68985,7 +68985,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ327">
-        <v>1.73</v>
+        <v>1.63</v>
       </c>
       <c r="AR327">
         <v>1.28</v>
@@ -69394,7 +69394,7 @@
         <v>1.08</v>
       </c>
       <c r="AP329">
-        <v>1.77</v>
+        <v>1.86</v>
       </c>
       <c r="AQ329">
         <v>0.93</v>
@@ -75447,6 +75447,212 @@
       </c>
       <c r="BP358">
         <v>1.26</v>
+      </c>
+    </row>
+    <row r="359" spans="1:68">
+      <c r="A359" s="1">
+        <v>358</v>
+      </c>
+      <c r="B359">
+        <v>7476924</v>
+      </c>
+      <c r="C359" t="s">
+        <v>68</v>
+      </c>
+      <c r="D359" t="s">
+        <v>69</v>
+      </c>
+      <c r="E359" s="2">
+        <v>45701.70833333334</v>
+      </c>
+      <c r="F359">
+        <v>32</v>
+      </c>
+      <c r="G359" t="s">
+        <v>90</v>
+      </c>
+      <c r="H359" t="s">
+        <v>93</v>
+      </c>
+      <c r="I359">
+        <v>0</v>
+      </c>
+      <c r="J359">
+        <v>0</v>
+      </c>
+      <c r="K359">
+        <v>0</v>
+      </c>
+      <c r="L359">
+        <v>1</v>
+      </c>
+      <c r="M359">
+        <v>0</v>
+      </c>
+      <c r="N359">
+        <v>1</v>
+      </c>
+      <c r="O359" t="s">
+        <v>206</v>
+      </c>
+      <c r="P359" t="s">
+        <v>101</v>
+      </c>
+      <c r="Q359">
+        <v>3.4</v>
+      </c>
+      <c r="R359">
+        <v>2.1</v>
+      </c>
+      <c r="S359">
+        <v>3.2</v>
+      </c>
+      <c r="T359">
+        <v>1.4</v>
+      </c>
+      <c r="U359">
+        <v>2.75</v>
+      </c>
+      <c r="V359">
+        <v>3</v>
+      </c>
+      <c r="W359">
+        <v>1.36</v>
+      </c>
+      <c r="X359">
+        <v>8</v>
+      </c>
+      <c r="Y359">
+        <v>1.08</v>
+      </c>
+      <c r="Z359">
+        <v>2.49</v>
+      </c>
+      <c r="AA359">
+        <v>3.23</v>
+      </c>
+      <c r="AB359">
+        <v>2.79</v>
+      </c>
+      <c r="AC359">
+        <v>1.06</v>
+      </c>
+      <c r="AD359">
+        <v>8.5</v>
+      </c>
+      <c r="AE359">
+        <v>1.3</v>
+      </c>
+      <c r="AF359">
+        <v>3.35</v>
+      </c>
+      <c r="AG359">
+        <v>1.92</v>
+      </c>
+      <c r="AH359">
+        <v>1.82</v>
+      </c>
+      <c r="AI359">
+        <v>1.73</v>
+      </c>
+      <c r="AJ359">
+        <v>2</v>
+      </c>
+      <c r="AK359">
+        <v>1.48</v>
+      </c>
+      <c r="AL359">
+        <v>1.28</v>
+      </c>
+      <c r="AM359">
+        <v>1.45</v>
+      </c>
+      <c r="AN359">
+        <v>1.77</v>
+      </c>
+      <c r="AO359">
+        <v>1.73</v>
+      </c>
+      <c r="AP359">
+        <v>1.86</v>
+      </c>
+      <c r="AQ359">
+        <v>1.63</v>
+      </c>
+      <c r="AR359">
+        <v>1.32</v>
+      </c>
+      <c r="AS359">
+        <v>1.3</v>
+      </c>
+      <c r="AT359">
+        <v>2.62</v>
+      </c>
+      <c r="AU359">
+        <v>2</v>
+      </c>
+      <c r="AV359">
+        <v>4</v>
+      </c>
+      <c r="AW359">
+        <v>6</v>
+      </c>
+      <c r="AX359">
+        <v>8</v>
+      </c>
+      <c r="AY359">
+        <v>8</v>
+      </c>
+      <c r="AZ359">
+        <v>14</v>
+      </c>
+      <c r="BA359">
+        <v>4</v>
+      </c>
+      <c r="BB359">
+        <v>3</v>
+      </c>
+      <c r="BC359">
+        <v>7</v>
+      </c>
+      <c r="BD359">
+        <v>2.22</v>
+      </c>
+      <c r="BE359">
+        <v>6.45</v>
+      </c>
+      <c r="BF359">
+        <v>2</v>
+      </c>
+      <c r="BG359">
+        <v>1.19</v>
+      </c>
+      <c r="BH359">
+        <v>3.78</v>
+      </c>
+      <c r="BI359">
+        <v>1.39</v>
+      </c>
+      <c r="BJ359">
+        <v>2.67</v>
+      </c>
+      <c r="BK359">
+        <v>1.71</v>
+      </c>
+      <c r="BL359">
+        <v>2.02</v>
+      </c>
+      <c r="BM359">
+        <v>2.14</v>
+      </c>
+      <c r="BN359">
+        <v>1.6</v>
+      </c>
+      <c r="BO359">
+        <v>2.83</v>
+      </c>
+      <c r="BP359">
+        <v>1.33</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/England EFL League Two_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/England EFL League Two_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2282" uniqueCount="447">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2300" uniqueCount="447">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -1716,7 +1716,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP370"/>
+  <dimension ref="A1:BP373"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -2259,7 +2259,7 @@
         <v>2.25</v>
       </c>
       <c r="AQ3">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="AR3">
         <v>0</v>
@@ -3080,7 +3080,7 @@
         <v>0</v>
       </c>
       <c r="AP7">
-        <v>1.56</v>
+        <v>1.53</v>
       </c>
       <c r="AQ7">
         <v>1.56</v>
@@ -4731,7 +4731,7 @@
         <v>1.2</v>
       </c>
       <c r="AQ15">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AR15">
         <v>0</v>
@@ -5758,7 +5758,7 @@
         <v>0</v>
       </c>
       <c r="AP20">
-        <v>0.86</v>
+        <v>0.8</v>
       </c>
       <c r="AQ20">
         <v>0.93</v>
@@ -5967,7 +5967,7 @@
         <v>1.8</v>
       </c>
       <c r="AQ21">
-        <v>1.6</v>
+        <v>1.69</v>
       </c>
       <c r="AR21">
         <v>0</v>
@@ -6788,7 +6788,7 @@
         <v>0</v>
       </c>
       <c r="AP25">
-        <v>1.93</v>
+        <v>1.87</v>
       </c>
       <c r="AQ25">
         <v>1.07</v>
@@ -6994,7 +6994,7 @@
         <v>0</v>
       </c>
       <c r="AP26">
-        <v>1.93</v>
+        <v>1.87</v>
       </c>
       <c r="AQ26">
         <v>1.56</v>
@@ -8230,7 +8230,7 @@
         <v>3</v>
       </c>
       <c r="AP32">
-        <v>1.56</v>
+        <v>1.53</v>
       </c>
       <c r="AQ32">
         <v>0.93</v>
@@ -8645,7 +8645,7 @@
         <v>1.88</v>
       </c>
       <c r="AQ34">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AR34">
         <v>1.55</v>
@@ -9469,7 +9469,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ38">
-        <v>1.6</v>
+        <v>1.69</v>
       </c>
       <c r="AR38">
         <v>0</v>
@@ -10084,7 +10084,7 @@
         <v>0</v>
       </c>
       <c r="AP41">
-        <v>0.86</v>
+        <v>0.8</v>
       </c>
       <c r="AQ41">
         <v>0.8100000000000001</v>
@@ -11117,7 +11117,7 @@
         <v>1.14</v>
       </c>
       <c r="AQ46">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="AR46">
         <v>2.58</v>
@@ -13792,7 +13792,7 @@
         <v>0</v>
       </c>
       <c r="AP59">
-        <v>1.93</v>
+        <v>1.87</v>
       </c>
       <c r="AQ59">
         <v>0.88</v>
@@ -14001,7 +14001,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ60">
-        <v>1.6</v>
+        <v>1.69</v>
       </c>
       <c r="AR60">
         <v>1.11</v>
@@ -15234,10 +15234,10 @@
         <v>0.5</v>
       </c>
       <c r="AP66">
-        <v>0.86</v>
+        <v>0.8</v>
       </c>
       <c r="AQ66">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="AR66">
         <v>1.41</v>
@@ -17294,7 +17294,7 @@
         <v>1.33</v>
       </c>
       <c r="AP76">
-        <v>1.93</v>
+        <v>1.87</v>
       </c>
       <c r="AQ76">
         <v>0.93</v>
@@ -17709,7 +17709,7 @@
         <v>1.47</v>
       </c>
       <c r="AQ78">
-        <v>1.6</v>
+        <v>1.69</v>
       </c>
       <c r="AR78">
         <v>1.48</v>
@@ -18121,7 +18121,7 @@
         <v>2.44</v>
       </c>
       <c r="AQ80">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AR80">
         <v>1.6</v>
@@ -18736,7 +18736,7 @@
         <v>0</v>
       </c>
       <c r="AP83">
-        <v>1.56</v>
+        <v>1.53</v>
       </c>
       <c r="AQ83">
         <v>0.82</v>
@@ -19151,7 +19151,7 @@
         <v>2.35</v>
       </c>
       <c r="AQ85">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="AR85">
         <v>1.6</v>
@@ -19560,7 +19560,7 @@
         <v>2.33</v>
       </c>
       <c r="AP87">
-        <v>0.86</v>
+        <v>0.8</v>
       </c>
       <c r="AQ87">
         <v>1.63</v>
@@ -21211,7 +21211,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ95">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="AR95">
         <v>1.55</v>
@@ -22032,7 +22032,7 @@
         <v>0.75</v>
       </c>
       <c r="AP99">
-        <v>0.86</v>
+        <v>0.8</v>
       </c>
       <c r="AQ99">
         <v>1</v>
@@ -23477,7 +23477,7 @@
         <v>1.53</v>
       </c>
       <c r="AQ106">
-        <v>1.6</v>
+        <v>1.69</v>
       </c>
       <c r="AR106">
         <v>1.16</v>
@@ -23680,7 +23680,7 @@
         <v>1</v>
       </c>
       <c r="AP107">
-        <v>1.56</v>
+        <v>1.53</v>
       </c>
       <c r="AQ107">
         <v>1.5</v>
@@ -24092,7 +24092,7 @@
         <v>1.75</v>
       </c>
       <c r="AP109">
-        <v>1.93</v>
+        <v>1.87</v>
       </c>
       <c r="AQ109">
         <v>1.63</v>
@@ -24713,7 +24713,7 @@
         <v>1.81</v>
       </c>
       <c r="AQ112">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AR112">
         <v>1.25</v>
@@ -28418,10 +28418,10 @@
         <v>1</v>
       </c>
       <c r="AP130">
-        <v>1.93</v>
+        <v>1.87</v>
       </c>
       <c r="AQ130">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AR130">
         <v>1.71</v>
@@ -28833,7 +28833,7 @@
         <v>1.47</v>
       </c>
       <c r="AQ132">
-        <v>1.6</v>
+        <v>1.69</v>
       </c>
       <c r="AR132">
         <v>1.44</v>
@@ -29242,7 +29242,7 @@
         <v>0.8</v>
       </c>
       <c r="AP134">
-        <v>0.86</v>
+        <v>0.8</v>
       </c>
       <c r="AQ134">
         <v>1</v>
@@ -31508,7 +31508,7 @@
         <v>1.4</v>
       </c>
       <c r="AP145">
-        <v>1.56</v>
+        <v>1.53</v>
       </c>
       <c r="AQ145">
         <v>1.35</v>
@@ -32747,7 +32747,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ151">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="AR151">
         <v>1.31</v>
@@ -32950,7 +32950,7 @@
         <v>1.67</v>
       </c>
       <c r="AP152">
-        <v>0.86</v>
+        <v>0.8</v>
       </c>
       <c r="AQ152">
         <v>1.13</v>
@@ -33571,7 +33571,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ155">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AR155">
         <v>1.41</v>
@@ -34601,7 +34601,7 @@
         <v>2.44</v>
       </c>
       <c r="AQ160">
-        <v>1.6</v>
+        <v>1.69</v>
       </c>
       <c r="AR160">
         <v>1.54</v>
@@ -35010,7 +35010,7 @@
         <v>1</v>
       </c>
       <c r="AP162">
-        <v>1.93</v>
+        <v>1.87</v>
       </c>
       <c r="AQ162">
         <v>0.8100000000000001</v>
@@ -35422,7 +35422,7 @@
         <v>1.17</v>
       </c>
       <c r="AP164">
-        <v>1.56</v>
+        <v>1.53</v>
       </c>
       <c r="AQ164">
         <v>1.27</v>
@@ -36864,7 +36864,7 @@
         <v>1.14</v>
       </c>
       <c r="AP171">
-        <v>1.56</v>
+        <v>1.53</v>
       </c>
       <c r="AQ171">
         <v>1</v>
@@ -37691,7 +37691,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ175">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="AR175">
         <v>1.45</v>
@@ -38306,7 +38306,7 @@
         <v>2</v>
       </c>
       <c r="AP178">
-        <v>0.86</v>
+        <v>0.8</v>
       </c>
       <c r="AQ178">
         <v>1.63</v>
@@ -39545,7 +39545,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ184">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AR184">
         <v>1.39</v>
@@ -40572,7 +40572,7 @@
         <v>0.75</v>
       </c>
       <c r="AP189">
-        <v>1.93</v>
+        <v>1.87</v>
       </c>
       <c r="AQ189">
         <v>0.8100000000000001</v>
@@ -40781,7 +40781,7 @@
         <v>1.53</v>
       </c>
       <c r="AQ190">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="AR190">
         <v>1.22</v>
@@ -41605,7 +41605,7 @@
         <v>0.67</v>
       </c>
       <c r="AQ194">
-        <v>1.6</v>
+        <v>1.69</v>
       </c>
       <c r="AR194">
         <v>1.51</v>
@@ -42223,7 +42223,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ197">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AR197">
         <v>1.32</v>
@@ -42838,10 +42838,10 @@
         <v>1</v>
       </c>
       <c r="AP200">
-        <v>1.56</v>
+        <v>1.53</v>
       </c>
       <c r="AQ200">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="AR200">
         <v>1.45</v>
@@ -45104,10 +45104,10 @@
         <v>1.75</v>
       </c>
       <c r="AP211">
-        <v>1.56</v>
+        <v>1.53</v>
       </c>
       <c r="AQ211">
-        <v>1.6</v>
+        <v>1.69</v>
       </c>
       <c r="AR211">
         <v>1.39</v>
@@ -45931,7 +45931,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ215">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AR215">
         <v>1.24</v>
@@ -46752,7 +46752,7 @@
         <v>1.78</v>
       </c>
       <c r="AP219">
-        <v>0.86</v>
+        <v>0.8</v>
       </c>
       <c r="AQ219">
         <v>1.56</v>
@@ -48403,7 +48403,7 @@
         <v>2.25</v>
       </c>
       <c r="AQ227">
-        <v>1.6</v>
+        <v>1.69</v>
       </c>
       <c r="AR227">
         <v>1.53</v>
@@ -49430,7 +49430,7 @@
         <v>0.78</v>
       </c>
       <c r="AP232">
-        <v>1.56</v>
+        <v>1.53</v>
       </c>
       <c r="AQ232">
         <v>0.88</v>
@@ -49845,7 +49845,7 @@
         <v>1.73</v>
       </c>
       <c r="AQ234">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="AR234">
         <v>1.16</v>
@@ -50666,7 +50666,7 @@
         <v>1</v>
       </c>
       <c r="AP238">
-        <v>1.93</v>
+        <v>1.87</v>
       </c>
       <c r="AQ238">
         <v>1</v>
@@ -51078,7 +51078,7 @@
         <v>1.44</v>
       </c>
       <c r="AP240">
-        <v>0.86</v>
+        <v>0.8</v>
       </c>
       <c r="AQ240">
         <v>1.5</v>
@@ -51905,7 +51905,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ244">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AR244">
         <v>1.52</v>
@@ -52935,7 +52935,7 @@
         <v>2.35</v>
       </c>
       <c r="AQ249">
-        <v>1.6</v>
+        <v>1.69</v>
       </c>
       <c r="AR249">
         <v>1.53</v>
@@ -53138,7 +53138,7 @@
         <v>1.6</v>
       </c>
       <c r="AP250">
-        <v>1.56</v>
+        <v>1.53</v>
       </c>
       <c r="AQ250">
         <v>1.13</v>
@@ -54995,7 +54995,7 @@
         <v>1.53</v>
       </c>
       <c r="AQ259">
-        <v>1.6</v>
+        <v>1.69</v>
       </c>
       <c r="AR259">
         <v>1.65</v>
@@ -56228,7 +56228,7 @@
         <v>0.82</v>
       </c>
       <c r="AP265">
-        <v>1.56</v>
+        <v>1.53</v>
       </c>
       <c r="AQ265">
         <v>0.8100000000000001</v>
@@ -57673,7 +57673,7 @@
         <v>1.47</v>
       </c>
       <c r="AQ272">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="AR272">
         <v>1.26</v>
@@ -57876,7 +57876,7 @@
         <v>0.8</v>
       </c>
       <c r="AP273">
-        <v>0.86</v>
+        <v>0.8</v>
       </c>
       <c r="AQ273">
         <v>0.53</v>
@@ -58082,7 +58082,7 @@
         <v>2</v>
       </c>
       <c r="AP274">
-        <v>1.93</v>
+        <v>1.87</v>
       </c>
       <c r="AQ274">
         <v>1.64</v>
@@ -59115,7 +59115,7 @@
         <v>1.8</v>
       </c>
       <c r="AQ279">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AR279">
         <v>1.24</v>
@@ -59318,7 +59318,7 @@
         <v>0.77</v>
       </c>
       <c r="AP280">
-        <v>1.93</v>
+        <v>1.87</v>
       </c>
       <c r="AQ280">
         <v>0.9399999999999999</v>
@@ -61587,7 +61587,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ291">
-        <v>1.6</v>
+        <v>1.69</v>
       </c>
       <c r="AR291">
         <v>1.25</v>
@@ -62202,7 +62202,7 @@
         <v>1.38</v>
       </c>
       <c r="AP294">
-        <v>0.86</v>
+        <v>0.8</v>
       </c>
       <c r="AQ294">
         <v>1.35</v>
@@ -63235,7 +63235,7 @@
         <v>1.2</v>
       </c>
       <c r="AQ299">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="AR299">
         <v>1.46</v>
@@ -63853,7 +63853,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ302">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="AR302">
         <v>1.08</v>
@@ -64056,7 +64056,7 @@
         <v>1.3</v>
       </c>
       <c r="AP303">
-        <v>1.56</v>
+        <v>1.53</v>
       </c>
       <c r="AQ303">
         <v>1</v>
@@ -64471,7 +64471,7 @@
         <v>1.47</v>
       </c>
       <c r="AQ305">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AR305">
         <v>1.33</v>
@@ -65910,7 +65910,7 @@
         <v>0.75</v>
       </c>
       <c r="AP312">
-        <v>1.56</v>
+        <v>1.53</v>
       </c>
       <c r="AQ312">
         <v>0.75</v>
@@ -66528,7 +66528,7 @@
         <v>1.58</v>
       </c>
       <c r="AP315">
-        <v>1.93</v>
+        <v>1.87</v>
       </c>
       <c r="AQ315">
         <v>1.5</v>
@@ -67149,7 +67149,7 @@
         <v>1.73</v>
       </c>
       <c r="AQ318">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AR318">
         <v>1.24</v>
@@ -67352,7 +67352,7 @@
         <v>1.92</v>
       </c>
       <c r="AP319">
-        <v>1.56</v>
+        <v>1.53</v>
       </c>
       <c r="AQ319">
         <v>1.64</v>
@@ -67764,7 +67764,7 @@
         <v>0.92</v>
       </c>
       <c r="AP321">
-        <v>1.93</v>
+        <v>1.87</v>
       </c>
       <c r="AQ321">
         <v>0.75</v>
@@ -68797,7 +68797,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ326">
-        <v>1.6</v>
+        <v>1.69</v>
       </c>
       <c r="AR326">
         <v>1.38</v>
@@ -69827,7 +69827,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ331">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="AR331">
         <v>1.52</v>
@@ -70236,7 +70236,7 @@
         <v>1.27</v>
       </c>
       <c r="AP333">
-        <v>0.86</v>
+        <v>0.8</v>
       </c>
       <c r="AQ333">
         <v>1.07</v>
@@ -71887,7 +71887,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ341">
-        <v>1.6</v>
+        <v>1.69</v>
       </c>
       <c r="AR341">
         <v>1.56</v>
@@ -72914,7 +72914,7 @@
         <v>0.85</v>
       </c>
       <c r="AP346">
-        <v>1.56</v>
+        <v>1.53</v>
       </c>
       <c r="AQ346">
         <v>0.79</v>
@@ -73329,7 +73329,7 @@
         <v>1.14</v>
       </c>
       <c r="AQ348">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AR348">
         <v>1.22</v>
@@ -73738,7 +73738,7 @@
         <v>0.88</v>
       </c>
       <c r="AP350">
-        <v>1.93</v>
+        <v>1.87</v>
       </c>
       <c r="AQ350">
         <v>0.82</v>
@@ -76828,7 +76828,7 @@
         <v>0.93</v>
       </c>
       <c r="AP365">
-        <v>0.86</v>
+        <v>0.8</v>
       </c>
       <c r="AQ365">
         <v>0.88</v>
@@ -77449,7 +77449,7 @@
         <v>0.67</v>
       </c>
       <c r="AQ368">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="AR368">
         <v>1.35</v>
@@ -77937,6 +77937,624 @@
       </c>
       <c r="BP370">
         <v>1.41</v>
+      </c>
+    </row>
+    <row r="371" spans="1:68">
+      <c r="A371" s="1">
+        <v>370</v>
+      </c>
+      <c r="B371">
+        <v>7476850</v>
+      </c>
+      <c r="C371" t="s">
+        <v>68</v>
+      </c>
+      <c r="D371" t="s">
+        <v>69</v>
+      </c>
+      <c r="E371" s="2">
+        <v>45706.69791666666</v>
+      </c>
+      <c r="F371">
+        <v>26</v>
+      </c>
+      <c r="G371" t="s">
+        <v>88</v>
+      </c>
+      <c r="H371" t="s">
+        <v>74</v>
+      </c>
+      <c r="I371">
+        <v>0</v>
+      </c>
+      <c r="J371">
+        <v>1</v>
+      </c>
+      <c r="K371">
+        <v>1</v>
+      </c>
+      <c r="L371">
+        <v>0</v>
+      </c>
+      <c r="M371">
+        <v>1</v>
+      </c>
+      <c r="N371">
+        <v>1</v>
+      </c>
+      <c r="O371" t="s">
+        <v>101</v>
+      </c>
+      <c r="P371" t="s">
+        <v>220</v>
+      </c>
+      <c r="Q371">
+        <v>4.33</v>
+      </c>
+      <c r="R371">
+        <v>2.2</v>
+      </c>
+      <c r="S371">
+        <v>2.6</v>
+      </c>
+      <c r="T371">
+        <v>1.4</v>
+      </c>
+      <c r="U371">
+        <v>2.75</v>
+      </c>
+      <c r="V371">
+        <v>2.75</v>
+      </c>
+      <c r="W371">
+        <v>1.4</v>
+      </c>
+      <c r="X371">
+        <v>8</v>
+      </c>
+      <c r="Y371">
+        <v>1.08</v>
+      </c>
+      <c r="Z371">
+        <v>3.6</v>
+      </c>
+      <c r="AA371">
+        <v>3.6</v>
+      </c>
+      <c r="AB371">
+        <v>1.87</v>
+      </c>
+      <c r="AC371">
+        <v>1</v>
+      </c>
+      <c r="AD371">
+        <v>9.1</v>
+      </c>
+      <c r="AE371">
+        <v>1.24</v>
+      </c>
+      <c r="AF371">
+        <v>3.36</v>
+      </c>
+      <c r="AG371">
+        <v>1.7</v>
+      </c>
+      <c r="AH371">
+        <v>2.05</v>
+      </c>
+      <c r="AI371">
+        <v>1.8</v>
+      </c>
+      <c r="AJ371">
+        <v>1.91</v>
+      </c>
+      <c r="AK371">
+        <v>1.86</v>
+      </c>
+      <c r="AL371">
+        <v>1.27</v>
+      </c>
+      <c r="AM371">
+        <v>1.25</v>
+      </c>
+      <c r="AN371">
+        <v>0.86</v>
+      </c>
+      <c r="AO371">
+        <v>1.6</v>
+      </c>
+      <c r="AP371">
+        <v>0.8</v>
+      </c>
+      <c r="AQ371">
+        <v>1.69</v>
+      </c>
+      <c r="AR371">
+        <v>1.39</v>
+      </c>
+      <c r="AS371">
+        <v>1.43</v>
+      </c>
+      <c r="AT371">
+        <v>2.82</v>
+      </c>
+      <c r="AU371">
+        <v>2</v>
+      </c>
+      <c r="AV371">
+        <v>4</v>
+      </c>
+      <c r="AW371">
+        <v>17</v>
+      </c>
+      <c r="AX371">
+        <v>9</v>
+      </c>
+      <c r="AY371">
+        <v>26</v>
+      </c>
+      <c r="AZ371">
+        <v>17</v>
+      </c>
+      <c r="BA371">
+        <v>4</v>
+      </c>
+      <c r="BB371">
+        <v>9</v>
+      </c>
+      <c r="BC371">
+        <v>13</v>
+      </c>
+      <c r="BD371">
+        <v>2.66</v>
+      </c>
+      <c r="BE371">
+        <v>7.4</v>
+      </c>
+      <c r="BF371">
+        <v>1.71</v>
+      </c>
+      <c r="BG371">
+        <v>1.2</v>
+      </c>
+      <c r="BH371">
+        <v>3.8</v>
+      </c>
+      <c r="BI371">
+        <v>1.35</v>
+      </c>
+      <c r="BJ371">
+        <v>2.74</v>
+      </c>
+      <c r="BK371">
+        <v>1.64</v>
+      </c>
+      <c r="BL371">
+        <v>2.07</v>
+      </c>
+      <c r="BM371">
+        <v>2.08</v>
+      </c>
+      <c r="BN371">
+        <v>1.67</v>
+      </c>
+      <c r="BO371">
+        <v>2.71</v>
+      </c>
+      <c r="BP371">
+        <v>1.38</v>
+      </c>
+    </row>
+    <row r="372" spans="1:68">
+      <c r="A372" s="1">
+        <v>371</v>
+      </c>
+      <c r="B372">
+        <v>7476769</v>
+      </c>
+      <c r="C372" t="s">
+        <v>68</v>
+      </c>
+      <c r="D372" t="s">
+        <v>69</v>
+      </c>
+      <c r="E372" s="2">
+        <v>45706.69791666666</v>
+      </c>
+      <c r="F372">
+        <v>19</v>
+      </c>
+      <c r="G372" t="s">
+        <v>93</v>
+      </c>
+      <c r="H372" t="s">
+        <v>85</v>
+      </c>
+      <c r="I372">
+        <v>1</v>
+      </c>
+      <c r="J372">
+        <v>0</v>
+      </c>
+      <c r="K372">
+        <v>1</v>
+      </c>
+      <c r="L372">
+        <v>1</v>
+      </c>
+      <c r="M372">
+        <v>1</v>
+      </c>
+      <c r="N372">
+        <v>2</v>
+      </c>
+      <c r="O372" t="s">
+        <v>220</v>
+      </c>
+      <c r="P372" t="s">
+        <v>237</v>
+      </c>
+      <c r="Q372">
+        <v>2.75</v>
+      </c>
+      <c r="R372">
+        <v>2.1</v>
+      </c>
+      <c r="S372">
+        <v>4.33</v>
+      </c>
+      <c r="T372">
+        <v>1.44</v>
+      </c>
+      <c r="U372">
+        <v>2.63</v>
+      </c>
+      <c r="V372">
+        <v>3.25</v>
+      </c>
+      <c r="W372">
+        <v>1.33</v>
+      </c>
+      <c r="X372">
+        <v>9</v>
+      </c>
+      <c r="Y372">
+        <v>1.07</v>
+      </c>
+      <c r="Z372">
+        <v>1.92</v>
+      </c>
+      <c r="AA372">
+        <v>3.64</v>
+      </c>
+      <c r="AB372">
+        <v>3.64</v>
+      </c>
+      <c r="AC372">
+        <v>1.04</v>
+      </c>
+      <c r="AD372">
+        <v>13</v>
+      </c>
+      <c r="AE372">
+        <v>1.25</v>
+      </c>
+      <c r="AF372">
+        <v>3.75</v>
+      </c>
+      <c r="AG372">
+        <v>1.85</v>
+      </c>
+      <c r="AH372">
+        <v>1.85</v>
+      </c>
+      <c r="AI372">
+        <v>1.83</v>
+      </c>
+      <c r="AJ372">
+        <v>1.83</v>
+      </c>
+      <c r="AK372">
+        <v>1.3</v>
+      </c>
+      <c r="AL372">
+        <v>1.25</v>
+      </c>
+      <c r="AM372">
+        <v>1.78</v>
+      </c>
+      <c r="AN372">
+        <v>1.93</v>
+      </c>
+      <c r="AO372">
+        <v>1.2</v>
+      </c>
+      <c r="AP372">
+        <v>1.87</v>
+      </c>
+      <c r="AQ372">
+        <v>1.19</v>
+      </c>
+      <c r="AR372">
+        <v>1.74</v>
+      </c>
+      <c r="AS372">
+        <v>1.15</v>
+      </c>
+      <c r="AT372">
+        <v>2.89</v>
+      </c>
+      <c r="AU372">
+        <v>3</v>
+      </c>
+      <c r="AV372">
+        <v>8</v>
+      </c>
+      <c r="AW372">
+        <v>12</v>
+      </c>
+      <c r="AX372">
+        <v>6</v>
+      </c>
+      <c r="AY372">
+        <v>17</v>
+      </c>
+      <c r="AZ372">
+        <v>14</v>
+      </c>
+      <c r="BA372">
+        <v>8</v>
+      </c>
+      <c r="BB372">
+        <v>3</v>
+      </c>
+      <c r="BC372">
+        <v>11</v>
+      </c>
+      <c r="BD372">
+        <v>1.78</v>
+      </c>
+      <c r="BE372">
+        <v>6.1</v>
+      </c>
+      <c r="BF372">
+        <v>2.5</v>
+      </c>
+      <c r="BG372">
+        <v>1.2</v>
+      </c>
+      <c r="BH372">
+        <v>4</v>
+      </c>
+      <c r="BI372">
+        <v>1.28</v>
+      </c>
+      <c r="BJ372">
+        <v>3.3</v>
+      </c>
+      <c r="BK372">
+        <v>1.52</v>
+      </c>
+      <c r="BL372">
+        <v>2.32</v>
+      </c>
+      <c r="BM372">
+        <v>1.92</v>
+      </c>
+      <c r="BN372">
+        <v>1.78</v>
+      </c>
+      <c r="BO372">
+        <v>2.55</v>
+      </c>
+      <c r="BP372">
+        <v>1.45</v>
+      </c>
+    </row>
+    <row r="373" spans="1:68">
+      <c r="A373" s="1">
+        <v>372</v>
+      </c>
+      <c r="B373">
+        <v>7476838</v>
+      </c>
+      <c r="C373" t="s">
+        <v>68</v>
+      </c>
+      <c r="D373" t="s">
+        <v>69</v>
+      </c>
+      <c r="E373" s="2">
+        <v>45706.69791666666</v>
+      </c>
+      <c r="F373">
+        <v>25</v>
+      </c>
+      <c r="G373" t="s">
+        <v>75</v>
+      </c>
+      <c r="H373" t="s">
+        <v>71</v>
+      </c>
+      <c r="I373">
+        <v>0</v>
+      </c>
+      <c r="J373">
+        <v>0</v>
+      </c>
+      <c r="K373">
+        <v>0</v>
+      </c>
+      <c r="L373">
+        <v>0</v>
+      </c>
+      <c r="M373">
+        <v>0</v>
+      </c>
+      <c r="N373">
+        <v>0</v>
+      </c>
+      <c r="O373" t="s">
+        <v>101</v>
+      </c>
+      <c r="P373" t="s">
+        <v>101</v>
+      </c>
+      <c r="Q373">
+        <v>3.2</v>
+      </c>
+      <c r="R373">
+        <v>2.1</v>
+      </c>
+      <c r="S373">
+        <v>3.5</v>
+      </c>
+      <c r="T373">
+        <v>1.4</v>
+      </c>
+      <c r="U373">
+        <v>2.75</v>
+      </c>
+      <c r="V373">
+        <v>3</v>
+      </c>
+      <c r="W373">
+        <v>1.36</v>
+      </c>
+      <c r="X373">
+        <v>9</v>
+      </c>
+      <c r="Y373">
+        <v>1.07</v>
+      </c>
+      <c r="Z373">
+        <v>2.91</v>
+      </c>
+      <c r="AA373">
+        <v>2.93</v>
+      </c>
+      <c r="AB373">
+        <v>2.59</v>
+      </c>
+      <c r="AC373">
+        <v>1.05</v>
+      </c>
+      <c r="AD373">
+        <v>10</v>
+      </c>
+      <c r="AE373">
+        <v>1.33</v>
+      </c>
+      <c r="AF373">
+        <v>3.25</v>
+      </c>
+      <c r="AG373">
+        <v>1.67</v>
+      </c>
+      <c r="AH373">
+        <v>2.1</v>
+      </c>
+      <c r="AI373">
+        <v>1.73</v>
+      </c>
+      <c r="AJ373">
+        <v>2</v>
+      </c>
+      <c r="AK373">
+        <v>1.44</v>
+      </c>
+      <c r="AL373">
+        <v>1.3</v>
+      </c>
+      <c r="AM373">
+        <v>1.5</v>
+      </c>
+      <c r="AN373">
+        <v>1.56</v>
+      </c>
+      <c r="AO373">
+        <v>1.36</v>
+      </c>
+      <c r="AP373">
+        <v>1.53</v>
+      </c>
+      <c r="AQ373">
+        <v>1.33</v>
+      </c>
+      <c r="AR373">
+        <v>1.37</v>
+      </c>
+      <c r="AS373">
+        <v>1.26</v>
+      </c>
+      <c r="AT373">
+        <v>2.63</v>
+      </c>
+      <c r="AU373">
+        <v>6</v>
+      </c>
+      <c r="AV373">
+        <v>2</v>
+      </c>
+      <c r="AW373">
+        <v>16</v>
+      </c>
+      <c r="AX373">
+        <v>4</v>
+      </c>
+      <c r="AY373">
+        <v>23</v>
+      </c>
+      <c r="AZ373">
+        <v>6</v>
+      </c>
+      <c r="BA373">
+        <v>16</v>
+      </c>
+      <c r="BB373">
+        <v>2</v>
+      </c>
+      <c r="BC373">
+        <v>18</v>
+      </c>
+      <c r="BD373">
+        <v>2.08</v>
+      </c>
+      <c r="BE373">
+        <v>6.45</v>
+      </c>
+      <c r="BF373">
+        <v>2.13</v>
+      </c>
+      <c r="BG373">
+        <v>1.18</v>
+      </c>
+      <c r="BH373">
+        <v>3.84</v>
+      </c>
+      <c r="BI373">
+        <v>1.39</v>
+      </c>
+      <c r="BJ373">
+        <v>2.67</v>
+      </c>
+      <c r="BK373">
+        <v>1.7</v>
+      </c>
+      <c r="BL373">
+        <v>2.05</v>
+      </c>
+      <c r="BM373">
+        <v>2.12</v>
+      </c>
+      <c r="BN373">
+        <v>1.61</v>
+      </c>
+      <c r="BO373">
+        <v>2.78</v>
+      </c>
+      <c r="BP373">
+        <v>1.34</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/England EFL League Two_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/England EFL League Two_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2300" uniqueCount="447">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2372" uniqueCount="456">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -949,6 +949,30 @@
     <t>['52', '55', '90+11']</t>
   </si>
   <si>
+    <t>['37', '50', '85']</t>
+  </si>
+  <si>
+    <t>['61']</t>
+  </si>
+  <si>
+    <t>['30', '45']</t>
+  </si>
+  <si>
+    <t>['43', '52']</t>
+  </si>
+  <si>
+    <t>['80', '83']</t>
+  </si>
+  <si>
+    <t>['57']</t>
+  </si>
+  <si>
+    <t>['11', '60']</t>
+  </si>
+  <si>
+    <t>['23', '64']</t>
+  </si>
+  <si>
     <t>['1', '9']</t>
   </si>
   <si>
@@ -1183,9 +1207,6 @@
     <t>['26', '90+7']</t>
   </si>
   <si>
-    <t>['57']</t>
-  </si>
-  <si>
     <t>['90+4']</t>
   </si>
   <si>
@@ -1244,9 +1265,6 @@
   </si>
   <si>
     <t>['72', '79']</t>
-  </si>
-  <si>
-    <t>['61']</t>
   </si>
   <si>
     <t>['26', '39', '58', '62', '90+3']</t>
@@ -1355,6 +1373,15 @@
   </si>
   <si>
     <t>['32', '46']</t>
+  </si>
+  <si>
+    <t>['53', '87']</t>
+  </si>
+  <si>
+    <t>['30', '53', '82']</t>
+  </si>
+  <si>
+    <t>['2', '61']</t>
   </si>
 </sst>
 </file>
@@ -1716,7 +1743,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP373"/>
+  <dimension ref="A1:BP385"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -2178,7 +2205,7 @@
         <v>95</v>
       </c>
       <c r="P3" t="s">
-        <v>311</v>
+        <v>319</v>
       </c>
       <c r="Q3">
         <v>2.5</v>
@@ -2590,7 +2617,7 @@
         <v>97</v>
       </c>
       <c r="P5" t="s">
-        <v>312</v>
+        <v>320</v>
       </c>
       <c r="Q5">
         <v>2.4</v>
@@ -3414,7 +3441,7 @@
         <v>101</v>
       </c>
       <c r="P9" t="s">
-        <v>313</v>
+        <v>321</v>
       </c>
       <c r="Q9">
         <v>2.75</v>
@@ -3620,7 +3647,7 @@
         <v>102</v>
       </c>
       <c r="P10" t="s">
-        <v>314</v>
+        <v>322</v>
       </c>
       <c r="Q10">
         <v>2.63</v>
@@ -3826,7 +3853,7 @@
         <v>101</v>
       </c>
       <c r="P11" t="s">
-        <v>315</v>
+        <v>323</v>
       </c>
       <c r="Q11">
         <v>2.88</v>
@@ -4522,10 +4549,10 @@
         <v>0</v>
       </c>
       <c r="AP14">
-        <v>0.67</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AQ14">
-        <v>0.6</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AR14">
         <v>0</v>
@@ -4728,10 +4755,10 @@
         <v>0</v>
       </c>
       <c r="AP15">
-        <v>1.2</v>
+        <v>1.31</v>
       </c>
       <c r="AQ15">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AR15">
         <v>0</v>
@@ -4856,7 +4883,7 @@
         <v>105</v>
       </c>
       <c r="P16" t="s">
-        <v>316</v>
+        <v>324</v>
       </c>
       <c r="Q16">
         <v>2.88</v>
@@ -4934,10 +4961,10 @@
         <v>0</v>
       </c>
       <c r="AP16">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="AQ16">
-        <v>0.8100000000000001</v>
+        <v>0.76</v>
       </c>
       <c r="AR16">
         <v>0</v>
@@ -5140,10 +5167,10 @@
         <v>0</v>
       </c>
       <c r="AP17">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AQ17">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR17">
         <v>0</v>
@@ -5268,7 +5295,7 @@
         <v>101</v>
       </c>
       <c r="P18" t="s">
-        <v>317</v>
+        <v>325</v>
       </c>
       <c r="Q18">
         <v>3.4</v>
@@ -5346,10 +5373,10 @@
         <v>0</v>
       </c>
       <c r="AP18">
-        <v>1.73</v>
+        <v>1.81</v>
       </c>
       <c r="AQ18">
-        <v>1.13</v>
+        <v>1.06</v>
       </c>
       <c r="AR18">
         <v>0</v>
@@ -5474,7 +5501,7 @@
         <v>107</v>
       </c>
       <c r="P19" t="s">
-        <v>318</v>
+        <v>326</v>
       </c>
       <c r="Q19">
         <v>3</v>
@@ -5552,10 +5579,10 @@
         <v>0</v>
       </c>
       <c r="AP19">
-        <v>1.53</v>
+        <v>1.63</v>
       </c>
       <c r="AQ19">
-        <v>0.79</v>
+        <v>0.93</v>
       </c>
       <c r="AR19">
         <v>0</v>
@@ -5758,10 +5785,10 @@
         <v>0</v>
       </c>
       <c r="AP20">
-        <v>0.8</v>
+        <v>0.75</v>
       </c>
       <c r="AQ20">
-        <v>0.93</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AR20">
         <v>0</v>
@@ -5964,10 +5991,10 @@
         <v>0</v>
       </c>
       <c r="AP21">
-        <v>1.8</v>
+        <v>1.69</v>
       </c>
       <c r="AQ21">
-        <v>1.69</v>
+        <v>1.76</v>
       </c>
       <c r="AR21">
         <v>0</v>
@@ -6170,10 +6197,10 @@
         <v>0</v>
       </c>
       <c r="AP22">
-        <v>1.86</v>
+        <v>1.93</v>
       </c>
       <c r="AQ22">
-        <v>0.53</v>
+        <v>0.5</v>
       </c>
       <c r="AR22">
         <v>0</v>
@@ -6298,7 +6325,7 @@
         <v>101</v>
       </c>
       <c r="P23" t="s">
-        <v>319</v>
+        <v>327</v>
       </c>
       <c r="Q23">
         <v>3</v>
@@ -6376,10 +6403,10 @@
         <v>0</v>
       </c>
       <c r="AP23">
-        <v>1.47</v>
+        <v>1.56</v>
       </c>
       <c r="AQ23">
-        <v>1.64</v>
+        <v>1.73</v>
       </c>
       <c r="AR23">
         <v>0</v>
@@ -6582,10 +6609,10 @@
         <v>0</v>
       </c>
       <c r="AP24">
-        <v>2.44</v>
+        <v>2.47</v>
       </c>
       <c r="AQ24">
-        <v>1.27</v>
+        <v>1.19</v>
       </c>
       <c r="AR24">
         <v>0</v>
@@ -6710,7 +6737,7 @@
         <v>109</v>
       </c>
       <c r="P25" t="s">
-        <v>320</v>
+        <v>328</v>
       </c>
       <c r="Q25">
         <v>2.63</v>
@@ -6788,10 +6815,10 @@
         <v>0</v>
       </c>
       <c r="AP25">
-        <v>1.87</v>
+        <v>1.94</v>
       </c>
       <c r="AQ25">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="AR25">
         <v>0</v>
@@ -6916,7 +6943,7 @@
         <v>110</v>
       </c>
       <c r="P26" t="s">
-        <v>321</v>
+        <v>329</v>
       </c>
       <c r="Q26">
         <v>2.38</v>
@@ -6994,7 +7021,7 @@
         <v>0</v>
       </c>
       <c r="AP26">
-        <v>1.87</v>
+        <v>1.94</v>
       </c>
       <c r="AQ26">
         <v>1.56</v>
@@ -7203,7 +7230,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ27">
-        <v>1.64</v>
+        <v>1.73</v>
       </c>
       <c r="AR27">
         <v>0.86</v>
@@ -7406,7 +7433,7 @@
         <v>1</v>
       </c>
       <c r="AP28">
-        <v>1.73</v>
+        <v>1.81</v>
       </c>
       <c r="AQ28">
         <v>0.9399999999999999</v>
@@ -7740,7 +7767,7 @@
         <v>112</v>
       </c>
       <c r="P30" t="s">
-        <v>322</v>
+        <v>330</v>
       </c>
       <c r="Q30">
         <v>3</v>
@@ -7818,7 +7845,7 @@
         <v>0</v>
       </c>
       <c r="AP30">
-        <v>1.8</v>
+        <v>1.69</v>
       </c>
       <c r="AQ30">
         <v>0.88</v>
@@ -8233,7 +8260,7 @@
         <v>1.53</v>
       </c>
       <c r="AQ32">
-        <v>0.93</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AR32">
         <v>1.04</v>
@@ -8439,7 +8466,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ33">
-        <v>1.27</v>
+        <v>1.19</v>
       </c>
       <c r="AR33">
         <v>1.27</v>
@@ -8645,7 +8672,7 @@
         <v>1.88</v>
       </c>
       <c r="AQ34">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AR34">
         <v>1.55</v>
@@ -8848,7 +8875,7 @@
         <v>3</v>
       </c>
       <c r="AP35">
-        <v>2.44</v>
+        <v>2.47</v>
       </c>
       <c r="AQ35">
         <v>1.5</v>
@@ -9182,7 +9209,7 @@
         <v>101</v>
       </c>
       <c r="P37" t="s">
-        <v>323</v>
+        <v>331</v>
       </c>
       <c r="Q37">
         <v>2.6</v>
@@ -9260,10 +9287,10 @@
         <v>1</v>
       </c>
       <c r="AP37">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AQ37">
-        <v>0.8100000000000001</v>
+        <v>0.76</v>
       </c>
       <c r="AR37">
         <v>1.61</v>
@@ -9388,7 +9415,7 @@
         <v>117</v>
       </c>
       <c r="P38" t="s">
-        <v>324</v>
+        <v>332</v>
       </c>
       <c r="Q38">
         <v>2.88</v>
@@ -9466,10 +9493,10 @@
         <v>0</v>
       </c>
       <c r="AP38">
-        <v>1.86</v>
+        <v>1.93</v>
       </c>
       <c r="AQ38">
-        <v>1.69</v>
+        <v>1.76</v>
       </c>
       <c r="AR38">
         <v>0</v>
@@ -9675,7 +9702,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ39">
-        <v>1.13</v>
+        <v>1.06</v>
       </c>
       <c r="AR39">
         <v>1.62</v>
@@ -9800,7 +9827,7 @@
         <v>119</v>
       </c>
       <c r="P40" t="s">
-        <v>325</v>
+        <v>333</v>
       </c>
       <c r="Q40">
         <v>3</v>
@@ -9878,7 +9905,7 @@
         <v>1</v>
       </c>
       <c r="AP40">
-        <v>1.47</v>
+        <v>1.56</v>
       </c>
       <c r="AQ40">
         <v>1.63</v>
@@ -10084,7 +10111,7 @@
         <v>0</v>
       </c>
       <c r="AP41">
-        <v>0.8</v>
+        <v>0.75</v>
       </c>
       <c r="AQ41">
         <v>0.8100000000000001</v>
@@ -10212,7 +10239,7 @@
         <v>101</v>
       </c>
       <c r="P42" t="s">
-        <v>326</v>
+        <v>334</v>
       </c>
       <c r="Q42">
         <v>3.75</v>
@@ -10293,7 +10320,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ42">
-        <v>0.6</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AR42">
         <v>1.15</v>
@@ -10499,7 +10526,7 @@
         <v>2.35</v>
       </c>
       <c r="AQ43">
-        <v>0.79</v>
+        <v>0.93</v>
       </c>
       <c r="AR43">
         <v>0.97</v>
@@ -10624,7 +10651,7 @@
         <v>121</v>
       </c>
       <c r="P44" t="s">
-        <v>327</v>
+        <v>335</v>
       </c>
       <c r="Q44">
         <v>2.75</v>
@@ -10702,10 +10729,10 @@
         <v>1</v>
       </c>
       <c r="AP44">
-        <v>0.67</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AQ44">
-        <v>0.53</v>
+        <v>0.5</v>
       </c>
       <c r="AR44">
         <v>1.2</v>
@@ -10830,7 +10857,7 @@
         <v>122</v>
       </c>
       <c r="P45" t="s">
-        <v>328</v>
+        <v>336</v>
       </c>
       <c r="Q45">
         <v>2.63</v>
@@ -10908,7 +10935,7 @@
         <v>0</v>
       </c>
       <c r="AP45">
-        <v>1.2</v>
+        <v>1.31</v>
       </c>
       <c r="AQ45">
         <v>1.35</v>
@@ -11114,7 +11141,7 @@
         <v>0</v>
       </c>
       <c r="AP46">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="AQ46">
         <v>1.19</v>
@@ -11323,7 +11350,7 @@
         <v>2.25</v>
       </c>
       <c r="AQ47">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="AR47">
         <v>1.5</v>
@@ -11448,7 +11475,7 @@
         <v>125</v>
       </c>
       <c r="P48" t="s">
-        <v>329</v>
+        <v>337</v>
       </c>
       <c r="Q48">
         <v>3.5</v>
@@ -11526,7 +11553,7 @@
         <v>3</v>
       </c>
       <c r="AP48">
-        <v>1.53</v>
+        <v>1.63</v>
       </c>
       <c r="AQ48">
         <v>1</v>
@@ -11735,7 +11762,7 @@
         <v>1.81</v>
       </c>
       <c r="AQ49">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR49">
         <v>1.1</v>
@@ -11860,7 +11887,7 @@
         <v>127</v>
       </c>
       <c r="P50" t="s">
-        <v>330</v>
+        <v>338</v>
       </c>
       <c r="Q50">
         <v>3.6</v>
@@ -11938,7 +11965,7 @@
         <v>1.5</v>
       </c>
       <c r="AP50">
-        <v>1.8</v>
+        <v>1.69</v>
       </c>
       <c r="AQ50">
         <v>1.63</v>
@@ -12066,7 +12093,7 @@
         <v>103</v>
       </c>
       <c r="P51" t="s">
-        <v>331</v>
+        <v>339</v>
       </c>
       <c r="Q51">
         <v>2.5</v>
@@ -12353,7 +12380,7 @@
         <v>1.88</v>
       </c>
       <c r="AQ52">
-        <v>0.8100000000000001</v>
+        <v>0.76</v>
       </c>
       <c r="AR52">
         <v>1.19</v>
@@ -12762,7 +12789,7 @@
         <v>1.5</v>
       </c>
       <c r="AP54">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AQ54">
         <v>1.5</v>
@@ -12968,7 +12995,7 @@
         <v>0</v>
       </c>
       <c r="AP55">
-        <v>1.73</v>
+        <v>1.81</v>
       </c>
       <c r="AQ55">
         <v>0.82</v>
@@ -13177,7 +13204,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ56">
-        <v>0.93</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AR56">
         <v>1.21</v>
@@ -13380,7 +13407,7 @@
         <v>0</v>
       </c>
       <c r="AP57">
-        <v>2.44</v>
+        <v>2.47</v>
       </c>
       <c r="AQ57">
         <v>0.75</v>
@@ -13589,7 +13616,7 @@
         <v>1.47</v>
       </c>
       <c r="AQ58">
-        <v>1.64</v>
+        <v>1.73</v>
       </c>
       <c r="AR58">
         <v>1.63</v>
@@ -13792,7 +13819,7 @@
         <v>0</v>
       </c>
       <c r="AP59">
-        <v>1.87</v>
+        <v>1.94</v>
       </c>
       <c r="AQ59">
         <v>0.88</v>
@@ -14001,7 +14028,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ60">
-        <v>1.69</v>
+        <v>1.76</v>
       </c>
       <c r="AR60">
         <v>1.11</v>
@@ -14207,7 +14234,7 @@
         <v>2.25</v>
       </c>
       <c r="AQ61">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR61">
         <v>1.47</v>
@@ -14410,7 +14437,7 @@
         <v>1.5</v>
       </c>
       <c r="AP62">
-        <v>1.47</v>
+        <v>1.56</v>
       </c>
       <c r="AQ62">
         <v>0.8100000000000001</v>
@@ -14619,7 +14646,7 @@
         <v>1.81</v>
       </c>
       <c r="AQ63">
-        <v>0.79</v>
+        <v>0.93</v>
       </c>
       <c r="AR63">
         <v>1.34</v>
@@ -14744,7 +14771,7 @@
         <v>139</v>
       </c>
       <c r="P64" t="s">
-        <v>322</v>
+        <v>330</v>
       </c>
       <c r="Q64">
         <v>3</v>
@@ -15028,10 +15055,10 @@
         <v>1.5</v>
       </c>
       <c r="AP65">
-        <v>1.86</v>
+        <v>1.93</v>
       </c>
       <c r="AQ65">
-        <v>1.13</v>
+        <v>1.06</v>
       </c>
       <c r="AR65">
         <v>1.4</v>
@@ -15156,7 +15183,7 @@
         <v>141</v>
       </c>
       <c r="P66" t="s">
-        <v>332</v>
+        <v>340</v>
       </c>
       <c r="Q66">
         <v>3.75</v>
@@ -15234,7 +15261,7 @@
         <v>0.5</v>
       </c>
       <c r="AP66">
-        <v>0.8</v>
+        <v>0.75</v>
       </c>
       <c r="AQ66">
         <v>1.19</v>
@@ -15443,7 +15470,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ67">
-        <v>0.53</v>
+        <v>0.5</v>
       </c>
       <c r="AR67">
         <v>1.34</v>
@@ -15646,7 +15673,7 @@
         <v>1.5</v>
       </c>
       <c r="AP68">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="AQ68">
         <v>1.35</v>
@@ -15774,7 +15801,7 @@
         <v>143</v>
       </c>
       <c r="P69" t="s">
-        <v>333</v>
+        <v>341</v>
       </c>
       <c r="Q69">
         <v>3.2</v>
@@ -15852,7 +15879,7 @@
         <v>2</v>
       </c>
       <c r="AP69">
-        <v>1.2</v>
+        <v>1.31</v>
       </c>
       <c r="AQ69">
         <v>1.63</v>
@@ -15980,7 +16007,7 @@
         <v>144</v>
       </c>
       <c r="P70" t="s">
-        <v>334</v>
+        <v>342</v>
       </c>
       <c r="Q70">
         <v>3.25</v>
@@ -16058,10 +16085,10 @@
         <v>1.5</v>
       </c>
       <c r="AP70">
-        <v>1.53</v>
+        <v>1.63</v>
       </c>
       <c r="AQ70">
-        <v>0.6</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AR70">
         <v>1.23</v>
@@ -16186,7 +16213,7 @@
         <v>145</v>
       </c>
       <c r="P71" t="s">
-        <v>335</v>
+        <v>343</v>
       </c>
       <c r="Q71">
         <v>3</v>
@@ -16264,10 +16291,10 @@
         <v>0.5</v>
       </c>
       <c r="AP71">
-        <v>0.67</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AQ71">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="AR71">
         <v>1.35</v>
@@ -16392,7 +16419,7 @@
         <v>146</v>
       </c>
       <c r="P72" t="s">
-        <v>336</v>
+        <v>344</v>
       </c>
       <c r="Q72">
         <v>4</v>
@@ -16470,7 +16497,7 @@
         <v>2</v>
       </c>
       <c r="AP72">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="AQ72">
         <v>1.63</v>
@@ -16679,7 +16706,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ73">
-        <v>0.79</v>
+        <v>0.93</v>
       </c>
       <c r="AR73">
         <v>1.28</v>
@@ -16804,7 +16831,7 @@
         <v>101</v>
       </c>
       <c r="P74" t="s">
-        <v>337</v>
+        <v>345</v>
       </c>
       <c r="Q74">
         <v>2.63</v>
@@ -16882,7 +16909,7 @@
         <v>0</v>
       </c>
       <c r="AP74">
-        <v>1.47</v>
+        <v>1.56</v>
       </c>
       <c r="AQ74">
         <v>0.75</v>
@@ -17010,7 +17037,7 @@
         <v>101</v>
       </c>
       <c r="P75" t="s">
-        <v>338</v>
+        <v>346</v>
       </c>
       <c r="Q75">
         <v>3.4</v>
@@ -17091,7 +17118,7 @@
         <v>1.81</v>
       </c>
       <c r="AQ75">
-        <v>1.64</v>
+        <v>1.73</v>
       </c>
       <c r="AR75">
         <v>1.26</v>
@@ -17216,7 +17243,7 @@
         <v>101</v>
       </c>
       <c r="P76" t="s">
-        <v>322</v>
+        <v>330</v>
       </c>
       <c r="Q76">
         <v>2.6</v>
@@ -17294,10 +17321,10 @@
         <v>1.33</v>
       </c>
       <c r="AP76">
-        <v>1.87</v>
+        <v>1.94</v>
       </c>
       <c r="AQ76">
-        <v>0.93</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AR76">
         <v>1.78</v>
@@ -17500,7 +17527,7 @@
         <v>1.33</v>
       </c>
       <c r="AP77">
-        <v>1.53</v>
+        <v>1.63</v>
       </c>
       <c r="AQ77">
         <v>1.5</v>
@@ -17628,7 +17655,7 @@
         <v>149</v>
       </c>
       <c r="P78" t="s">
-        <v>339</v>
+        <v>347</v>
       </c>
       <c r="Q78">
         <v>2.88</v>
@@ -17709,7 +17736,7 @@
         <v>1.47</v>
       </c>
       <c r="AQ78">
-        <v>1.69</v>
+        <v>1.76</v>
       </c>
       <c r="AR78">
         <v>1.48</v>
@@ -17912,10 +17939,10 @@
         <v>1.33</v>
       </c>
       <c r="AP79">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AQ79">
-        <v>0.53</v>
+        <v>0.5</v>
       </c>
       <c r="AR79">
         <v>1.92</v>
@@ -18118,10 +18145,10 @@
         <v>1.5</v>
       </c>
       <c r="AP80">
-        <v>2.44</v>
+        <v>2.47</v>
       </c>
       <c r="AQ80">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AR80">
         <v>1.6</v>
@@ -18530,10 +18557,10 @@
         <v>1.33</v>
       </c>
       <c r="AP82">
-        <v>1.73</v>
+        <v>1.81</v>
       </c>
       <c r="AQ82">
-        <v>0.8100000000000001</v>
+        <v>0.76</v>
       </c>
       <c r="AR82">
         <v>0.97</v>
@@ -18658,7 +18685,7 @@
         <v>153</v>
       </c>
       <c r="P83" t="s">
-        <v>340</v>
+        <v>348</v>
       </c>
       <c r="Q83">
         <v>2.2</v>
@@ -18945,7 +18972,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ84">
-        <v>1.27</v>
+        <v>1.19</v>
       </c>
       <c r="AR84">
         <v>0.73</v>
@@ -19560,7 +19587,7 @@
         <v>2.33</v>
       </c>
       <c r="AP87">
-        <v>0.8</v>
+        <v>0.75</v>
       </c>
       <c r="AQ87">
         <v>1.63</v>
@@ -19766,7 +19793,7 @@
         <v>1</v>
       </c>
       <c r="AP88">
-        <v>1.86</v>
+        <v>1.93</v>
       </c>
       <c r="AQ88">
         <v>0.9399999999999999</v>
@@ -19894,7 +19921,7 @@
         <v>157</v>
       </c>
       <c r="P89" t="s">
-        <v>341</v>
+        <v>349</v>
       </c>
       <c r="Q89">
         <v>3.75</v>
@@ -19972,7 +19999,7 @@
         <v>2</v>
       </c>
       <c r="AP89">
-        <v>1.8</v>
+        <v>1.69</v>
       </c>
       <c r="AQ89">
         <v>1.35</v>
@@ -20178,10 +20205,10 @@
         <v>0</v>
       </c>
       <c r="AP90">
-        <v>1.2</v>
+        <v>1.31</v>
       </c>
       <c r="AQ90">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR90">
         <v>1.27</v>
@@ -20306,7 +20333,7 @@
         <v>101</v>
       </c>
       <c r="P91" t="s">
-        <v>342</v>
+        <v>350</v>
       </c>
       <c r="Q91">
         <v>2.75</v>
@@ -20387,7 +20414,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ91">
-        <v>1.13</v>
+        <v>1.06</v>
       </c>
       <c r="AR91">
         <v>1.18</v>
@@ -20512,7 +20539,7 @@
         <v>101</v>
       </c>
       <c r="P92" t="s">
-        <v>343</v>
+        <v>351</v>
       </c>
       <c r="Q92">
         <v>3.4</v>
@@ -20593,7 +20620,7 @@
         <v>1.88</v>
       </c>
       <c r="AQ92">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="AR92">
         <v>1.26</v>
@@ -20718,7 +20745,7 @@
         <v>159</v>
       </c>
       <c r="P93" t="s">
-        <v>344</v>
+        <v>352</v>
       </c>
       <c r="Q93">
         <v>2.75</v>
@@ -20796,7 +20823,7 @@
         <v>0</v>
       </c>
       <c r="AP93">
-        <v>0.67</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AQ93">
         <v>1.56</v>
@@ -21005,7 +21032,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ94">
-        <v>0.6</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AR94">
         <v>1.4</v>
@@ -21130,7 +21157,7 @@
         <v>161</v>
       </c>
       <c r="P95" t="s">
-        <v>345</v>
+        <v>353</v>
       </c>
       <c r="Q95">
         <v>2.5</v>
@@ -21208,7 +21235,7 @@
         <v>0.5</v>
       </c>
       <c r="AP95">
-        <v>1.86</v>
+        <v>1.93</v>
       </c>
       <c r="AQ95">
         <v>1.19</v>
@@ -21336,7 +21363,7 @@
         <v>162</v>
       </c>
       <c r="P96" t="s">
-        <v>346</v>
+        <v>354</v>
       </c>
       <c r="Q96">
         <v>4.5</v>
@@ -21417,7 +21444,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ96">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR96">
         <v>1.14</v>
@@ -21826,10 +21853,10 @@
         <v>1</v>
       </c>
       <c r="AP98">
-        <v>1.8</v>
+        <v>1.69</v>
       </c>
       <c r="AQ98">
-        <v>1.27</v>
+        <v>1.19</v>
       </c>
       <c r="AR98">
         <v>0.92</v>
@@ -22032,7 +22059,7 @@
         <v>0.75</v>
       </c>
       <c r="AP99">
-        <v>0.8</v>
+        <v>0.75</v>
       </c>
       <c r="AQ99">
         <v>1</v>
@@ -22160,7 +22187,7 @@
         <v>166</v>
       </c>
       <c r="P100" t="s">
-        <v>347</v>
+        <v>355</v>
       </c>
       <c r="Q100">
         <v>2.75</v>
@@ -22241,7 +22268,7 @@
         <v>2.35</v>
       </c>
       <c r="AQ100">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="AR100">
         <v>1.61</v>
@@ -22572,7 +22599,7 @@
         <v>167</v>
       </c>
       <c r="P102" t="s">
-        <v>348</v>
+        <v>356</v>
       </c>
       <c r="Q102">
         <v>2.88</v>
@@ -22778,7 +22805,7 @@
         <v>101</v>
       </c>
       <c r="P103" t="s">
-        <v>349</v>
+        <v>357</v>
       </c>
       <c r="Q103">
         <v>3</v>
@@ -22856,7 +22883,7 @@
         <v>2</v>
       </c>
       <c r="AP103">
-        <v>0.67</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AQ103">
         <v>1.63</v>
@@ -22984,7 +23011,7 @@
         <v>168</v>
       </c>
       <c r="P104" t="s">
-        <v>350</v>
+        <v>358</v>
       </c>
       <c r="Q104">
         <v>4</v>
@@ -23062,10 +23089,10 @@
         <v>1.5</v>
       </c>
       <c r="AP104">
-        <v>1.2</v>
+        <v>1.31</v>
       </c>
       <c r="AQ104">
-        <v>1.13</v>
+        <v>1.06</v>
       </c>
       <c r="AR104">
         <v>1.27</v>
@@ -23271,7 +23298,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ105">
-        <v>0.6</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AR105">
         <v>1</v>
@@ -23396,7 +23423,7 @@
         <v>101</v>
       </c>
       <c r="P106" t="s">
-        <v>351</v>
+        <v>359</v>
       </c>
       <c r="Q106">
         <v>3.6</v>
@@ -23474,10 +23501,10 @@
         <v>1</v>
       </c>
       <c r="AP106">
-        <v>1.53</v>
+        <v>1.63</v>
       </c>
       <c r="AQ106">
-        <v>1.69</v>
+        <v>1.76</v>
       </c>
       <c r="AR106">
         <v>1.16</v>
@@ -23886,10 +23913,10 @@
         <v>1</v>
       </c>
       <c r="AP108">
-        <v>1.47</v>
+        <v>1.56</v>
       </c>
       <c r="AQ108">
-        <v>0.8100000000000001</v>
+        <v>0.76</v>
       </c>
       <c r="AR108">
         <v>1.59</v>
@@ -24092,7 +24119,7 @@
         <v>1.75</v>
       </c>
       <c r="AP109">
-        <v>1.87</v>
+        <v>1.94</v>
       </c>
       <c r="AQ109">
         <v>1.63</v>
@@ -24301,7 +24328,7 @@
         <v>1.47</v>
       </c>
       <c r="AQ110">
-        <v>0.53</v>
+        <v>0.5</v>
       </c>
       <c r="AR110">
         <v>1.38</v>
@@ -24504,10 +24531,10 @@
         <v>1.75</v>
       </c>
       <c r="AP111">
-        <v>1.73</v>
+        <v>1.81</v>
       </c>
       <c r="AQ111">
-        <v>0.93</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AR111">
         <v>1.19</v>
@@ -24713,7 +24740,7 @@
         <v>1.81</v>
       </c>
       <c r="AQ112">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AR112">
         <v>1.25</v>
@@ -24838,7 +24865,7 @@
         <v>172</v>
       </c>
       <c r="P113" t="s">
-        <v>352</v>
+        <v>360</v>
       </c>
       <c r="Q113">
         <v>2.6</v>
@@ -24919,7 +24946,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ113">
-        <v>1.64</v>
+        <v>1.73</v>
       </c>
       <c r="AR113">
         <v>1.34</v>
@@ -25044,7 +25071,7 @@
         <v>173</v>
       </c>
       <c r="P114" t="s">
-        <v>353</v>
+        <v>361</v>
       </c>
       <c r="Q114">
         <v>2.4</v>
@@ -25125,7 +25152,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ114">
-        <v>0.79</v>
+        <v>0.93</v>
       </c>
       <c r="AR114">
         <v>1.49</v>
@@ -25328,7 +25355,7 @@
         <v>0.25</v>
       </c>
       <c r="AP115">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="AQ115">
         <v>0.82</v>
@@ -25534,7 +25561,7 @@
         <v>0.75</v>
       </c>
       <c r="AP116">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AQ116">
         <v>0.75</v>
@@ -25740,7 +25767,7 @@
         <v>0.75</v>
       </c>
       <c r="AP117">
-        <v>2.44</v>
+        <v>2.47</v>
       </c>
       <c r="AQ117">
         <v>0.8100000000000001</v>
@@ -25868,7 +25895,7 @@
         <v>176</v>
       </c>
       <c r="P118" t="s">
-        <v>354</v>
+        <v>362</v>
       </c>
       <c r="Q118">
         <v>2.5</v>
@@ -26074,7 +26101,7 @@
         <v>101</v>
       </c>
       <c r="P119" t="s">
-        <v>355</v>
+        <v>363</v>
       </c>
       <c r="Q119">
         <v>3.4</v>
@@ -26280,7 +26307,7 @@
         <v>94</v>
       </c>
       <c r="P120" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="Q120">
         <v>2.88</v>
@@ -26898,7 +26925,7 @@
         <v>178</v>
       </c>
       <c r="P123" t="s">
-        <v>357</v>
+        <v>365</v>
       </c>
       <c r="Q123">
         <v>2.38</v>
@@ -27310,7 +27337,7 @@
         <v>101</v>
       </c>
       <c r="P125" t="s">
-        <v>339</v>
+        <v>347</v>
       </c>
       <c r="Q125">
         <v>2.1</v>
@@ -27722,7 +27749,7 @@
         <v>180</v>
       </c>
       <c r="P127" t="s">
-        <v>358</v>
+        <v>366</v>
       </c>
       <c r="Q127">
         <v>3.25</v>
@@ -27928,7 +27955,7 @@
         <v>101</v>
       </c>
       <c r="P128" t="s">
-        <v>359</v>
+        <v>367</v>
       </c>
       <c r="Q128">
         <v>4.75</v>
@@ -28006,10 +28033,10 @@
         <v>1.4</v>
       </c>
       <c r="AP128">
-        <v>1.8</v>
+        <v>1.69</v>
       </c>
       <c r="AQ128">
-        <v>1.13</v>
+        <v>1.06</v>
       </c>
       <c r="AR128">
         <v>1.07</v>
@@ -28212,10 +28239,10 @@
         <v>1.2</v>
       </c>
       <c r="AP129">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="AQ129">
-        <v>0.6</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AR129">
         <v>1.45</v>
@@ -28418,10 +28445,10 @@
         <v>1</v>
       </c>
       <c r="AP130">
-        <v>1.87</v>
+        <v>1.94</v>
       </c>
       <c r="AQ130">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AR130">
         <v>1.71</v>
@@ -28546,7 +28573,7 @@
         <v>182</v>
       </c>
       <c r="P131" t="s">
-        <v>360</v>
+        <v>368</v>
       </c>
       <c r="Q131">
         <v>2.63</v>
@@ -28624,10 +28651,10 @@
         <v>2</v>
       </c>
       <c r="AP131">
-        <v>1.86</v>
+        <v>1.93</v>
       </c>
       <c r="AQ131">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="AR131">
         <v>1.51</v>
@@ -28752,7 +28779,7 @@
         <v>183</v>
       </c>
       <c r="P132" t="s">
-        <v>361</v>
+        <v>369</v>
       </c>
       <c r="Q132">
         <v>3.5</v>
@@ -28830,10 +28857,10 @@
         <v>1.4</v>
       </c>
       <c r="AP132">
-        <v>1.47</v>
+        <v>1.56</v>
       </c>
       <c r="AQ132">
-        <v>1.69</v>
+        <v>1.76</v>
       </c>
       <c r="AR132">
         <v>1.44</v>
@@ -29036,10 +29063,10 @@
         <v>0.75</v>
       </c>
       <c r="AP133">
-        <v>1.73</v>
+        <v>1.81</v>
       </c>
       <c r="AQ133">
-        <v>1.27</v>
+        <v>1.19</v>
       </c>
       <c r="AR133">
         <v>1.2</v>
@@ -29164,7 +29191,7 @@
         <v>185</v>
       </c>
       <c r="P134" t="s">
-        <v>362</v>
+        <v>370</v>
       </c>
       <c r="Q134">
         <v>4</v>
@@ -29242,10 +29269,10 @@
         <v>0.8</v>
       </c>
       <c r="AP134">
-        <v>0.8</v>
+        <v>0.75</v>
       </c>
       <c r="AQ134">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR134">
         <v>1.35</v>
@@ -29370,7 +29397,7 @@
         <v>147</v>
       </c>
       <c r="P135" t="s">
-        <v>363</v>
+        <v>371</v>
       </c>
       <c r="Q135">
         <v>2.6</v>
@@ -29448,10 +29475,10 @@
         <v>0.2</v>
       </c>
       <c r="AP135">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AQ135">
-        <v>0.79</v>
+        <v>0.93</v>
       </c>
       <c r="AR135">
         <v>1.78</v>
@@ -29576,7 +29603,7 @@
         <v>186</v>
       </c>
       <c r="P136" t="s">
-        <v>364</v>
+        <v>372</v>
       </c>
       <c r="Q136">
         <v>3.6</v>
@@ -29654,10 +29681,10 @@
         <v>1.4</v>
       </c>
       <c r="AP136">
-        <v>1.53</v>
+        <v>1.63</v>
       </c>
       <c r="AQ136">
-        <v>1.64</v>
+        <v>1.73</v>
       </c>
       <c r="AR136">
         <v>1.16</v>
@@ -29782,7 +29809,7 @@
         <v>187</v>
       </c>
       <c r="P137" t="s">
-        <v>365</v>
+        <v>373</v>
       </c>
       <c r="Q137">
         <v>3</v>
@@ -29860,10 +29887,10 @@
         <v>1</v>
       </c>
       <c r="AP137">
-        <v>1.2</v>
+        <v>1.31</v>
       </c>
       <c r="AQ137">
-        <v>0.53</v>
+        <v>0.5</v>
       </c>
       <c r="AR137">
         <v>1.32</v>
@@ -30066,10 +30093,10 @@
         <v>1.4</v>
       </c>
       <c r="AP138">
-        <v>2.44</v>
+        <v>2.47</v>
       </c>
       <c r="AQ138">
-        <v>0.93</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AR138">
         <v>1.55</v>
@@ -30194,7 +30221,7 @@
         <v>185</v>
       </c>
       <c r="P139" t="s">
-        <v>348</v>
+        <v>356</v>
       </c>
       <c r="Q139">
         <v>2.5</v>
@@ -30272,10 +30299,10 @@
         <v>1</v>
       </c>
       <c r="AP139">
-        <v>0.67</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AQ139">
-        <v>0.8100000000000001</v>
+        <v>0.76</v>
       </c>
       <c r="AR139">
         <v>1.5</v>
@@ -30400,7 +30427,7 @@
         <v>189</v>
       </c>
       <c r="P140" t="s">
-        <v>339</v>
+        <v>347</v>
       </c>
       <c r="Q140">
         <v>2.25</v>
@@ -31224,7 +31251,7 @@
         <v>101</v>
       </c>
       <c r="P144" t="s">
-        <v>366</v>
+        <v>374</v>
       </c>
       <c r="Q144">
         <v>2.25</v>
@@ -31842,7 +31869,7 @@
         <v>101</v>
       </c>
       <c r="P147" t="s">
-        <v>367</v>
+        <v>375</v>
       </c>
       <c r="Q147">
         <v>3</v>
@@ -32666,7 +32693,7 @@
         <v>193</v>
       </c>
       <c r="P151" t="s">
-        <v>368</v>
+        <v>376</v>
       </c>
       <c r="Q151">
         <v>2.4</v>
@@ -32872,7 +32899,7 @@
         <v>194</v>
       </c>
       <c r="P152" t="s">
-        <v>369</v>
+        <v>377</v>
       </c>
       <c r="Q152">
         <v>4.5</v>
@@ -32950,10 +32977,10 @@
         <v>1.67</v>
       </c>
       <c r="AP152">
-        <v>0.8</v>
+        <v>0.75</v>
       </c>
       <c r="AQ152">
-        <v>1.13</v>
+        <v>1.06</v>
       </c>
       <c r="AR152">
         <v>1.38</v>
@@ -33078,7 +33105,7 @@
         <v>195</v>
       </c>
       <c r="P153" t="s">
-        <v>370</v>
+        <v>378</v>
       </c>
       <c r="Q153">
         <v>2.75</v>
@@ -33156,10 +33183,10 @@
         <v>0.8</v>
       </c>
       <c r="AP153">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AQ153">
-        <v>1.27</v>
+        <v>1.19</v>
       </c>
       <c r="AR153">
         <v>1.74</v>
@@ -33362,10 +33389,10 @@
         <v>1.17</v>
       </c>
       <c r="AP154">
-        <v>1.47</v>
+        <v>1.56</v>
       </c>
       <c r="AQ154">
-        <v>0.93</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AR154">
         <v>1.33</v>
@@ -33490,7 +33517,7 @@
         <v>197</v>
       </c>
       <c r="P155" t="s">
-        <v>371</v>
+        <v>379</v>
       </c>
       <c r="Q155">
         <v>3</v>
@@ -33568,10 +33595,10 @@
         <v>0.8</v>
       </c>
       <c r="AP155">
-        <v>1.86</v>
+        <v>1.93</v>
       </c>
       <c r="AQ155">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AR155">
         <v>1.41</v>
@@ -33774,10 +33801,10 @@
         <v>1.67</v>
       </c>
       <c r="AP156">
-        <v>1.8</v>
+        <v>1.69</v>
       </c>
       <c r="AQ156">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="AR156">
         <v>1.14</v>
@@ -33902,7 +33929,7 @@
         <v>198</v>
       </c>
       <c r="P157" t="s">
-        <v>372</v>
+        <v>380</v>
       </c>
       <c r="Q157">
         <v>3.4</v>
@@ -33980,10 +34007,10 @@
         <v>1.17</v>
       </c>
       <c r="AP157">
-        <v>1.53</v>
+        <v>1.63</v>
       </c>
       <c r="AQ157">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR157">
         <v>1.15</v>
@@ -34186,10 +34213,10 @@
         <v>1.33</v>
       </c>
       <c r="AP158">
-        <v>1.73</v>
+        <v>1.81</v>
       </c>
       <c r="AQ158">
-        <v>0.53</v>
+        <v>0.5</v>
       </c>
       <c r="AR158">
         <v>1.15</v>
@@ -34392,10 +34419,10 @@
         <v>0.67</v>
       </c>
       <c r="AP159">
-        <v>0.67</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AQ159">
-        <v>0.79</v>
+        <v>0.93</v>
       </c>
       <c r="AR159">
         <v>1.63</v>
@@ -34520,7 +34547,7 @@
         <v>200</v>
       </c>
       <c r="P160" t="s">
-        <v>373</v>
+        <v>381</v>
       </c>
       <c r="Q160">
         <v>3.2</v>
@@ -34598,10 +34625,10 @@
         <v>1.67</v>
       </c>
       <c r="AP160">
-        <v>2.44</v>
+        <v>2.47</v>
       </c>
       <c r="AQ160">
-        <v>1.69</v>
+        <v>1.76</v>
       </c>
       <c r="AR160">
         <v>1.54</v>
@@ -34804,10 +34831,10 @@
         <v>1.67</v>
       </c>
       <c r="AP161">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="AQ161">
-        <v>1.64</v>
+        <v>1.73</v>
       </c>
       <c r="AR161">
         <v>1.36</v>
@@ -35010,10 +35037,10 @@
         <v>1</v>
       </c>
       <c r="AP162">
-        <v>1.87</v>
+        <v>1.94</v>
       </c>
       <c r="AQ162">
-        <v>0.8100000000000001</v>
+        <v>0.76</v>
       </c>
       <c r="AR162">
         <v>1.61</v>
@@ -35216,10 +35243,10 @@
         <v>1</v>
       </c>
       <c r="AP163">
-        <v>1.2</v>
+        <v>1.31</v>
       </c>
       <c r="AQ163">
-        <v>0.6</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AR163">
         <v>1.49</v>
@@ -35344,7 +35371,7 @@
         <v>203</v>
       </c>
       <c r="P164" t="s">
-        <v>374</v>
+        <v>382</v>
       </c>
       <c r="Q164">
         <v>2.4</v>
@@ -35425,7 +35452,7 @@
         <v>1.53</v>
       </c>
       <c r="AQ164">
-        <v>1.27</v>
+        <v>1.19</v>
       </c>
       <c r="AR164">
         <v>1.63</v>
@@ -35756,7 +35783,7 @@
         <v>204</v>
       </c>
       <c r="P166" t="s">
-        <v>375</v>
+        <v>383</v>
       </c>
       <c r="Q166">
         <v>2.88</v>
@@ -36168,7 +36195,7 @@
         <v>206</v>
       </c>
       <c r="P168" t="s">
-        <v>376</v>
+        <v>384</v>
       </c>
       <c r="Q168">
         <v>2.3</v>
@@ -36580,7 +36607,7 @@
         <v>208</v>
       </c>
       <c r="P170" t="s">
-        <v>377</v>
+        <v>385</v>
       </c>
       <c r="Q170">
         <v>2.5</v>
@@ -37198,7 +37225,7 @@
         <v>101</v>
       </c>
       <c r="P173" t="s">
-        <v>378</v>
+        <v>386</v>
       </c>
       <c r="Q173">
         <v>2.1</v>
@@ -37404,7 +37431,7 @@
         <v>148</v>
       </c>
       <c r="P174" t="s">
-        <v>339</v>
+        <v>347</v>
       </c>
       <c r="Q174">
         <v>3.2</v>
@@ -38100,7 +38127,7 @@
         <v>1.88</v>
       </c>
       <c r="AP177">
-        <v>1.8</v>
+        <v>1.69</v>
       </c>
       <c r="AQ177">
         <v>1.56</v>
@@ -38306,7 +38333,7 @@
         <v>2</v>
       </c>
       <c r="AP178">
-        <v>0.8</v>
+        <v>0.75</v>
       </c>
       <c r="AQ178">
         <v>1.63</v>
@@ -38434,7 +38461,7 @@
         <v>210</v>
       </c>
       <c r="P179" t="s">
-        <v>379</v>
+        <v>387</v>
       </c>
       <c r="Q179">
         <v>2.3</v>
@@ -38515,7 +38542,7 @@
         <v>1.47</v>
       </c>
       <c r="AQ179">
-        <v>0.79</v>
+        <v>0.93</v>
       </c>
       <c r="AR179">
         <v>1.29</v>
@@ -38721,7 +38748,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ180">
-        <v>1.27</v>
+        <v>1.19</v>
       </c>
       <c r="AR180">
         <v>1.38</v>
@@ -38924,7 +38951,7 @@
         <v>1.75</v>
       </c>
       <c r="AP181">
-        <v>1.73</v>
+        <v>1.81</v>
       </c>
       <c r="AQ181">
         <v>1.63</v>
@@ -39133,7 +39160,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ182">
-        <v>1.13</v>
+        <v>1.06</v>
       </c>
       <c r="AR182">
         <v>1.26</v>
@@ -39336,7 +39363,7 @@
         <v>0.88</v>
       </c>
       <c r="AP183">
-        <v>1.2</v>
+        <v>1.31</v>
       </c>
       <c r="AQ183">
         <v>0.75</v>
@@ -39464,7 +39491,7 @@
         <v>185</v>
       </c>
       <c r="P184" t="s">
-        <v>380</v>
+        <v>388</v>
       </c>
       <c r="Q184">
         <v>3.4</v>
@@ -39545,7 +39572,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ184">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AR184">
         <v>1.39</v>
@@ -39670,7 +39697,7 @@
         <v>215</v>
       </c>
       <c r="P185" t="s">
-        <v>381</v>
+        <v>389</v>
       </c>
       <c r="Q185">
         <v>3.2</v>
@@ -39748,7 +39775,7 @@
         <v>0.88</v>
       </c>
       <c r="AP185">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="AQ185">
         <v>0.9399999999999999</v>
@@ -39954,7 +39981,7 @@
         <v>1</v>
       </c>
       <c r="AP186">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AQ186">
         <v>1</v>
@@ -40082,7 +40109,7 @@
         <v>217</v>
       </c>
       <c r="P187" t="s">
-        <v>382</v>
+        <v>390</v>
       </c>
       <c r="Q187">
         <v>2.2</v>
@@ -40369,7 +40396,7 @@
         <v>1.88</v>
       </c>
       <c r="AQ188">
-        <v>0.53</v>
+        <v>0.5</v>
       </c>
       <c r="AR188">
         <v>1.31</v>
@@ -40572,7 +40599,7 @@
         <v>0.75</v>
       </c>
       <c r="AP189">
-        <v>1.87</v>
+        <v>1.94</v>
       </c>
       <c r="AQ189">
         <v>0.8100000000000001</v>
@@ -40700,7 +40727,7 @@
         <v>101</v>
       </c>
       <c r="P190" t="s">
-        <v>329</v>
+        <v>337</v>
       </c>
       <c r="Q190">
         <v>3.25</v>
@@ -40778,7 +40805,7 @@
         <v>0.71</v>
       </c>
       <c r="AP190">
-        <v>1.53</v>
+        <v>1.63</v>
       </c>
       <c r="AQ190">
         <v>1.19</v>
@@ -40906,7 +40933,7 @@
         <v>148</v>
       </c>
       <c r="P191" t="s">
-        <v>383</v>
+        <v>391</v>
       </c>
       <c r="Q191">
         <v>2.3</v>
@@ -40987,7 +41014,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ191">
-        <v>0.8100000000000001</v>
+        <v>0.76</v>
       </c>
       <c r="AR191">
         <v>1.27</v>
@@ -41112,7 +41139,7 @@
         <v>219</v>
       </c>
       <c r="P192" t="s">
-        <v>384</v>
+        <v>392</v>
       </c>
       <c r="Q192">
         <v>2.4</v>
@@ -41190,7 +41217,7 @@
         <v>0.88</v>
       </c>
       <c r="AP192">
-        <v>1.47</v>
+        <v>1.56</v>
       </c>
       <c r="AQ192">
         <v>0.82</v>
@@ -41399,7 +41426,7 @@
         <v>2.25</v>
       </c>
       <c r="AQ193">
-        <v>1.64</v>
+        <v>1.73</v>
       </c>
       <c r="AR193">
         <v>1.56</v>
@@ -41602,10 +41629,10 @@
         <v>1.86</v>
       </c>
       <c r="AP194">
-        <v>0.67</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AQ194">
-        <v>1.69</v>
+        <v>1.76</v>
       </c>
       <c r="AR194">
         <v>1.51</v>
@@ -41811,7 +41838,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ195">
-        <v>0.6</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AR195">
         <v>1.49</v>
@@ -42014,7 +42041,7 @@
         <v>1.57</v>
       </c>
       <c r="AP196">
-        <v>1.86</v>
+        <v>1.93</v>
       </c>
       <c r="AQ196">
         <v>1.35</v>
@@ -42142,7 +42169,7 @@
         <v>101</v>
       </c>
       <c r="P197" t="s">
-        <v>385</v>
+        <v>393</v>
       </c>
       <c r="Q197">
         <v>3.75</v>
@@ -42223,7 +42250,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ197">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AR197">
         <v>1.32</v>
@@ -42348,7 +42375,7 @@
         <v>221</v>
       </c>
       <c r="P198" t="s">
-        <v>386</v>
+        <v>394</v>
       </c>
       <c r="Q198">
         <v>2.2</v>
@@ -42554,7 +42581,7 @@
         <v>122</v>
       </c>
       <c r="P199" t="s">
-        <v>339</v>
+        <v>347</v>
       </c>
       <c r="Q199">
         <v>3.4</v>
@@ -42632,7 +42659,7 @@
         <v>1.5</v>
       </c>
       <c r="AP199">
-        <v>0.67</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AQ199">
         <v>1.35</v>
@@ -42966,7 +42993,7 @@
         <v>222</v>
       </c>
       <c r="P201" t="s">
-        <v>387</v>
+        <v>395</v>
       </c>
       <c r="Q201">
         <v>2.85</v>
@@ -43044,7 +43071,7 @@
         <v>0.88</v>
       </c>
       <c r="AP201">
-        <v>1.53</v>
+        <v>1.63</v>
       </c>
       <c r="AQ201">
         <v>0.88</v>
@@ -43172,7 +43199,7 @@
         <v>223</v>
       </c>
       <c r="P202" t="s">
-        <v>388</v>
+        <v>396</v>
       </c>
       <c r="Q202">
         <v>1.8</v>
@@ -43378,7 +43405,7 @@
         <v>205</v>
       </c>
       <c r="P203" t="s">
-        <v>389</v>
+        <v>316</v>
       </c>
       <c r="Q203">
         <v>2.75</v>
@@ -43456,10 +43483,10 @@
         <v>0.88</v>
       </c>
       <c r="AP203">
-        <v>2.44</v>
+        <v>2.47</v>
       </c>
       <c r="AQ203">
-        <v>0.6</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AR203">
         <v>1.53</v>
@@ -43584,7 +43611,7 @@
         <v>224</v>
       </c>
       <c r="P204" t="s">
-        <v>390</v>
+        <v>397</v>
       </c>
       <c r="Q204">
         <v>3.55</v>
@@ -43868,7 +43895,7 @@
         <v>0.89</v>
       </c>
       <c r="AP205">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AQ205">
         <v>0.9399999999999999</v>
@@ -44077,7 +44104,7 @@
         <v>1.47</v>
       </c>
       <c r="AQ206">
-        <v>1.13</v>
+        <v>1.06</v>
       </c>
       <c r="AR206">
         <v>1.27</v>
@@ -44283,7 +44310,7 @@
         <v>1.81</v>
       </c>
       <c r="AQ207">
-        <v>0.8100000000000001</v>
+        <v>0.76</v>
       </c>
       <c r="AR207">
         <v>1.39</v>
@@ -44408,7 +44435,7 @@
         <v>228</v>
       </c>
       <c r="P208" t="s">
-        <v>391</v>
+        <v>398</v>
       </c>
       <c r="Q208">
         <v>2.4</v>
@@ -44614,7 +44641,7 @@
         <v>229</v>
       </c>
       <c r="P209" t="s">
-        <v>392</v>
+        <v>399</v>
       </c>
       <c r="Q209">
         <v>2.5</v>
@@ -44898,10 +44925,10 @@
         <v>1.14</v>
       </c>
       <c r="AP210">
-        <v>1.2</v>
+        <v>1.31</v>
       </c>
       <c r="AQ210">
-        <v>0.93</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AR210">
         <v>1.4</v>
@@ -45026,7 +45053,7 @@
         <v>231</v>
       </c>
       <c r="P211" t="s">
-        <v>393</v>
+        <v>400</v>
       </c>
       <c r="Q211">
         <v>3.5</v>
@@ -45107,7 +45134,7 @@
         <v>1.53</v>
       </c>
       <c r="AQ211">
-        <v>1.69</v>
+        <v>1.76</v>
       </c>
       <c r="AR211">
         <v>1.39</v>
@@ -45310,7 +45337,7 @@
         <v>1</v>
       </c>
       <c r="AP212">
-        <v>1.73</v>
+        <v>1.81</v>
       </c>
       <c r="AQ212">
         <v>1</v>
@@ -45516,10 +45543,10 @@
         <v>1.75</v>
       </c>
       <c r="AP213">
-        <v>1.86</v>
+        <v>1.93</v>
       </c>
       <c r="AQ213">
-        <v>1.64</v>
+        <v>1.73</v>
       </c>
       <c r="AR213">
         <v>1.25</v>
@@ -45725,7 +45752,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ214">
-        <v>0.53</v>
+        <v>0.5</v>
       </c>
       <c r="AR214">
         <v>1.49</v>
@@ -45850,7 +45877,7 @@
         <v>101</v>
       </c>
       <c r="P215" t="s">
-        <v>394</v>
+        <v>401</v>
       </c>
       <c r="Q215">
         <v>4.33</v>
@@ -45931,7 +45958,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ215">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AR215">
         <v>1.24</v>
@@ -46056,7 +46083,7 @@
         <v>234</v>
       </c>
       <c r="P216" t="s">
-        <v>395</v>
+        <v>402</v>
       </c>
       <c r="Q216">
         <v>3</v>
@@ -46134,7 +46161,7 @@
         <v>1.25</v>
       </c>
       <c r="AP216">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="AQ216">
         <v>1.5</v>
@@ -46262,7 +46289,7 @@
         <v>235</v>
       </c>
       <c r="P217" t="s">
-        <v>396</v>
+        <v>403</v>
       </c>
       <c r="Q217">
         <v>0</v>
@@ -46343,7 +46370,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ217">
-        <v>0.79</v>
+        <v>0.93</v>
       </c>
       <c r="AR217">
         <v>1.35</v>
@@ -46546,10 +46573,10 @@
         <v>1.57</v>
       </c>
       <c r="AP218">
-        <v>1.47</v>
+        <v>1.56</v>
       </c>
       <c r="AQ218">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="AR218">
         <v>1.22</v>
@@ -46674,7 +46701,7 @@
         <v>101</v>
       </c>
       <c r="P219" t="s">
-        <v>397</v>
+        <v>404</v>
       </c>
       <c r="Q219">
         <v>3.2</v>
@@ -46752,7 +46779,7 @@
         <v>1.78</v>
       </c>
       <c r="AP219">
-        <v>0.8</v>
+        <v>0.75</v>
       </c>
       <c r="AQ219">
         <v>1.56</v>
@@ -46961,7 +46988,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ220">
-        <v>1.27</v>
+        <v>1.19</v>
       </c>
       <c r="AR220">
         <v>1.25</v>
@@ -47167,7 +47194,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ221">
-        <v>0.8100000000000001</v>
+        <v>0.76</v>
       </c>
       <c r="AR221">
         <v>1.41</v>
@@ -47498,7 +47525,7 @@
         <v>101</v>
       </c>
       <c r="P223" t="s">
-        <v>398</v>
+        <v>405</v>
       </c>
       <c r="Q223">
         <v>3.75</v>
@@ -47576,10 +47603,10 @@
         <v>1.44</v>
       </c>
       <c r="AP223">
-        <v>0.67</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AQ223">
-        <v>1.13</v>
+        <v>1.06</v>
       </c>
       <c r="AR223">
         <v>1.42</v>
@@ -47704,7 +47731,7 @@
         <v>101</v>
       </c>
       <c r="P224" t="s">
-        <v>399</v>
+        <v>406</v>
       </c>
       <c r="Q224">
         <v>3.4</v>
@@ -47782,7 +47809,7 @@
         <v>1.44</v>
       </c>
       <c r="AP224">
-        <v>1.53</v>
+        <v>1.63</v>
       </c>
       <c r="AQ224">
         <v>1.35</v>
@@ -47988,7 +48015,7 @@
         <v>0.8</v>
       </c>
       <c r="AP225">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AQ225">
         <v>0.8100000000000001</v>
@@ -48197,7 +48224,7 @@
         <v>2.35</v>
       </c>
       <c r="AQ226">
-        <v>0.6</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AR226">
         <v>1.56</v>
@@ -48403,7 +48430,7 @@
         <v>2.25</v>
       </c>
       <c r="AQ227">
-        <v>1.69</v>
+        <v>1.76</v>
       </c>
       <c r="AR227">
         <v>1.53</v>
@@ -48606,7 +48633,7 @@
         <v>0.8</v>
       </c>
       <c r="AP228">
-        <v>2.44</v>
+        <v>2.47</v>
       </c>
       <c r="AQ228">
         <v>0.9399999999999999</v>
@@ -48812,7 +48839,7 @@
         <v>2</v>
       </c>
       <c r="AP229">
-        <v>1.2</v>
+        <v>1.31</v>
       </c>
       <c r="AQ229">
         <v>1.63</v>
@@ -48940,7 +48967,7 @@
         <v>101</v>
       </c>
       <c r="P230" t="s">
-        <v>367</v>
+        <v>375</v>
       </c>
       <c r="Q230">
         <v>2.5</v>
@@ -49021,7 +49048,7 @@
         <v>1.47</v>
       </c>
       <c r="AQ230">
-        <v>0.93</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AR230">
         <v>1.31</v>
@@ -49352,7 +49379,7 @@
         <v>240</v>
       </c>
       <c r="P232" t="s">
-        <v>400</v>
+        <v>407</v>
       </c>
       <c r="Q232">
         <v>2.4</v>
@@ -49558,7 +49585,7 @@
         <v>241</v>
       </c>
       <c r="P233" t="s">
-        <v>401</v>
+        <v>408</v>
       </c>
       <c r="Q233">
         <v>2.88</v>
@@ -49639,7 +49666,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ233">
-        <v>0.79</v>
+        <v>0.93</v>
       </c>
       <c r="AR233">
         <v>1.21</v>
@@ -49842,7 +49869,7 @@
         <v>1</v>
       </c>
       <c r="AP234">
-        <v>1.73</v>
+        <v>1.81</v>
       </c>
       <c r="AQ234">
         <v>1.19</v>
@@ -50051,7 +50078,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ235">
-        <v>0.53</v>
+        <v>0.5</v>
       </c>
       <c r="AR235">
         <v>1.36</v>
@@ -50257,7 +50284,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ236">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="AR236">
         <v>1.41</v>
@@ -50460,7 +50487,7 @@
         <v>0.89</v>
       </c>
       <c r="AP237">
-        <v>1.86</v>
+        <v>1.93</v>
       </c>
       <c r="AQ237">
         <v>0.75</v>
@@ -50666,7 +50693,7 @@
         <v>1</v>
       </c>
       <c r="AP238">
-        <v>1.87</v>
+        <v>1.94</v>
       </c>
       <c r="AQ238">
         <v>1</v>
@@ -50794,7 +50821,7 @@
         <v>245</v>
       </c>
       <c r="P239" t="s">
-        <v>402</v>
+        <v>409</v>
       </c>
       <c r="Q239">
         <v>4.5</v>
@@ -50872,10 +50899,10 @@
         <v>1.43</v>
       </c>
       <c r="AP239">
-        <v>1.8</v>
+        <v>1.69</v>
       </c>
       <c r="AQ239">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR239">
         <v>1.15</v>
@@ -51000,7 +51027,7 @@
         <v>101</v>
       </c>
       <c r="P240" t="s">
-        <v>403</v>
+        <v>410</v>
       </c>
       <c r="Q240">
         <v>3.75</v>
@@ -51078,7 +51105,7 @@
         <v>1.44</v>
       </c>
       <c r="AP240">
-        <v>0.8</v>
+        <v>0.75</v>
       </c>
       <c r="AQ240">
         <v>1.5</v>
@@ -51206,7 +51233,7 @@
         <v>101</v>
       </c>
       <c r="P241" t="s">
-        <v>404</v>
+        <v>411</v>
       </c>
       <c r="Q241">
         <v>5.5</v>
@@ -51287,7 +51314,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ241">
-        <v>1.64</v>
+        <v>1.73</v>
       </c>
       <c r="AR241">
         <v>1.17</v>
@@ -51412,7 +51439,7 @@
         <v>246</v>
       </c>
       <c r="P242" t="s">
-        <v>405</v>
+        <v>412</v>
       </c>
       <c r="Q242">
         <v>2.88</v>
@@ -51490,7 +51517,7 @@
         <v>1.9</v>
       </c>
       <c r="AP242">
-        <v>1.47</v>
+        <v>1.56</v>
       </c>
       <c r="AQ242">
         <v>1.56</v>
@@ -51618,7 +51645,7 @@
         <v>101</v>
       </c>
       <c r="P243" t="s">
-        <v>406</v>
+        <v>413</v>
       </c>
       <c r="Q243">
         <v>3.5</v>
@@ -51696,10 +51723,10 @@
         <v>1</v>
       </c>
       <c r="AP243">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="AQ243">
-        <v>1.27</v>
+        <v>1.19</v>
       </c>
       <c r="AR243">
         <v>1.3</v>
@@ -51905,7 +51932,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ244">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AR244">
         <v>1.52</v>
@@ -52236,7 +52263,7 @@
         <v>248</v>
       </c>
       <c r="P246" t="s">
-        <v>339</v>
+        <v>347</v>
       </c>
       <c r="Q246">
         <v>2.38</v>
@@ -52314,10 +52341,10 @@
         <v>0.9</v>
       </c>
       <c r="AP246">
-        <v>1.53</v>
+        <v>1.63</v>
       </c>
       <c r="AQ246">
-        <v>0.8100000000000001</v>
+        <v>0.76</v>
       </c>
       <c r="AR246">
         <v>1.22</v>
@@ -52442,7 +52469,7 @@
         <v>101</v>
       </c>
       <c r="P247" t="s">
-        <v>407</v>
+        <v>414</v>
       </c>
       <c r="Q247">
         <v>2.6</v>
@@ -52729,7 +52756,7 @@
         <v>1.81</v>
       </c>
       <c r="AQ248">
-        <v>0.6</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AR248">
         <v>1.42</v>
@@ -52935,7 +52962,7 @@
         <v>2.35</v>
       </c>
       <c r="AQ249">
-        <v>1.69</v>
+        <v>1.76</v>
       </c>
       <c r="AR249">
         <v>1.53</v>
@@ -53141,7 +53168,7 @@
         <v>1.53</v>
       </c>
       <c r="AQ250">
-        <v>1.13</v>
+        <v>1.06</v>
       </c>
       <c r="AR250">
         <v>1.32</v>
@@ -53266,7 +53293,7 @@
         <v>252</v>
       </c>
       <c r="P251" t="s">
-        <v>408</v>
+        <v>415</v>
       </c>
       <c r="Q251">
         <v>2.25</v>
@@ -53550,7 +53577,7 @@
         <v>1.91</v>
       </c>
       <c r="AP252">
-        <v>2.44</v>
+        <v>2.47</v>
       </c>
       <c r="AQ252">
         <v>1.63</v>
@@ -53678,7 +53705,7 @@
         <v>254</v>
       </c>
       <c r="P253" t="s">
-        <v>409</v>
+        <v>416</v>
       </c>
       <c r="Q253">
         <v>2.1</v>
@@ -53756,7 +53783,7 @@
         <v>0.82</v>
       </c>
       <c r="AP253">
-        <v>1.2</v>
+        <v>1.31</v>
       </c>
       <c r="AQ253">
         <v>0.8100000000000001</v>
@@ -53884,7 +53911,7 @@
         <v>101</v>
       </c>
       <c r="P254" t="s">
-        <v>410</v>
+        <v>312</v>
       </c>
       <c r="Q254">
         <v>2.5</v>
@@ -53962,7 +53989,7 @@
         <v>1</v>
       </c>
       <c r="AP254">
-        <v>0.67</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AQ254">
         <v>0.82</v>
@@ -54168,10 +54195,10 @@
         <v>1.22</v>
       </c>
       <c r="AP255">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AQ255">
-        <v>0.93</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AR255">
         <v>1.66</v>
@@ -54296,7 +54323,7 @@
         <v>114</v>
       </c>
       <c r="P256" t="s">
-        <v>405</v>
+        <v>412</v>
       </c>
       <c r="Q256">
         <v>2.88</v>
@@ -54374,7 +54401,7 @@
         <v>0.75</v>
       </c>
       <c r="AP256">
-        <v>1.2</v>
+        <v>1.31</v>
       </c>
       <c r="AQ256">
         <v>0.9399999999999999</v>
@@ -54580,7 +54607,7 @@
         <v>0.8</v>
       </c>
       <c r="AP257">
-        <v>0.67</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AQ257">
         <v>0.88</v>
@@ -54789,7 +54816,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ258">
-        <v>0.6</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AR258">
         <v>1.44</v>
@@ -54992,10 +55019,10 @@
         <v>1.55</v>
       </c>
       <c r="AP259">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AQ259">
-        <v>1.69</v>
+        <v>1.76</v>
       </c>
       <c r="AR259">
         <v>1.65</v>
@@ -55816,10 +55843,10 @@
         <v>1.45</v>
       </c>
       <c r="AP263">
-        <v>2.44</v>
+        <v>2.47</v>
       </c>
       <c r="AQ263">
-        <v>1.13</v>
+        <v>1.06</v>
       </c>
       <c r="AR263">
         <v>1.41</v>
@@ -56022,7 +56049,7 @@
         <v>1.75</v>
       </c>
       <c r="AP264">
-        <v>1.53</v>
+        <v>1.63</v>
       </c>
       <c r="AQ264">
         <v>1.63</v>
@@ -56231,7 +56258,7 @@
         <v>1.53</v>
       </c>
       <c r="AQ265">
-        <v>0.8100000000000001</v>
+        <v>0.76</v>
       </c>
       <c r="AR265">
         <v>1.29</v>
@@ -56356,7 +56383,7 @@
         <v>259</v>
       </c>
       <c r="P266" t="s">
-        <v>411</v>
+        <v>417</v>
       </c>
       <c r="Q266">
         <v>3.6</v>
@@ -56643,7 +56670,7 @@
         <v>2.25</v>
       </c>
       <c r="AQ267">
-        <v>0.93</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AR267">
         <v>1.44</v>
@@ -56846,10 +56873,10 @@
         <v>0.9</v>
       </c>
       <c r="AP268">
-        <v>1.86</v>
+        <v>1.93</v>
       </c>
       <c r="AQ268">
-        <v>0.79</v>
+        <v>0.93</v>
       </c>
       <c r="AR268">
         <v>1.16</v>
@@ -56974,7 +57001,7 @@
         <v>261</v>
       </c>
       <c r="P269" t="s">
-        <v>412</v>
+        <v>418</v>
       </c>
       <c r="Q269">
         <v>2.75</v>
@@ -57052,7 +57079,7 @@
         <v>0.9</v>
       </c>
       <c r="AP269">
-        <v>1.73</v>
+        <v>1.81</v>
       </c>
       <c r="AQ269">
         <v>0.75</v>
@@ -57180,7 +57207,7 @@
         <v>262</v>
       </c>
       <c r="P270" t="s">
-        <v>413</v>
+        <v>419</v>
       </c>
       <c r="Q270">
         <v>2.4</v>
@@ -57261,7 +57288,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ270">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="AR270">
         <v>1.45</v>
@@ -57386,7 +57413,7 @@
         <v>101</v>
       </c>
       <c r="P271" t="s">
-        <v>414</v>
+        <v>420</v>
       </c>
       <c r="Q271">
         <v>4</v>
@@ -57467,7 +57494,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ271">
-        <v>1.27</v>
+        <v>1.19</v>
       </c>
       <c r="AR271">
         <v>1.11</v>
@@ -57592,7 +57619,7 @@
         <v>263</v>
       </c>
       <c r="P272" t="s">
-        <v>415</v>
+        <v>421</v>
       </c>
       <c r="Q272">
         <v>3.1</v>
@@ -57670,7 +57697,7 @@
         <v>1</v>
       </c>
       <c r="AP272">
-        <v>1.47</v>
+        <v>1.56</v>
       </c>
       <c r="AQ272">
         <v>1.19</v>
@@ -57876,10 +57903,10 @@
         <v>0.8</v>
       </c>
       <c r="AP273">
-        <v>0.8</v>
+        <v>0.75</v>
       </c>
       <c r="AQ273">
-        <v>0.53</v>
+        <v>0.5</v>
       </c>
       <c r="AR273">
         <v>1.29</v>
@@ -58004,7 +58031,7 @@
         <v>184</v>
       </c>
       <c r="P274" t="s">
-        <v>416</v>
+        <v>422</v>
       </c>
       <c r="Q274">
         <v>3.25</v>
@@ -58082,10 +58109,10 @@
         <v>2</v>
       </c>
       <c r="AP274">
-        <v>1.87</v>
+        <v>1.94</v>
       </c>
       <c r="AQ274">
-        <v>1.64</v>
+        <v>1.73</v>
       </c>
       <c r="AR274">
         <v>1.79</v>
@@ -58210,7 +58237,7 @@
         <v>265</v>
       </c>
       <c r="P275" t="s">
-        <v>417</v>
+        <v>423</v>
       </c>
       <c r="Q275">
         <v>3.4</v>
@@ -58416,7 +58443,7 @@
         <v>266</v>
       </c>
       <c r="P276" t="s">
-        <v>418</v>
+        <v>424</v>
       </c>
       <c r="Q276">
         <v>2.88</v>
@@ -58497,7 +58524,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ276">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR276">
         <v>1.46</v>
@@ -58622,7 +58649,7 @@
         <v>267</v>
       </c>
       <c r="P277" t="s">
-        <v>419</v>
+        <v>425</v>
       </c>
       <c r="Q277">
         <v>3.1</v>
@@ -58700,7 +58727,7 @@
         <v>1.73</v>
       </c>
       <c r="AP277">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="AQ277">
         <v>1.56</v>
@@ -58828,7 +58855,7 @@
         <v>101</v>
       </c>
       <c r="P278" t="s">
-        <v>420</v>
+        <v>426</v>
       </c>
       <c r="Q278">
         <v>3.1</v>
@@ -59034,7 +59061,7 @@
         <v>128</v>
       </c>
       <c r="P279" t="s">
-        <v>421</v>
+        <v>427</v>
       </c>
       <c r="Q279">
         <v>5</v>
@@ -59112,10 +59139,10 @@
         <v>1.3</v>
       </c>
       <c r="AP279">
-        <v>1.8</v>
+        <v>1.69</v>
       </c>
       <c r="AQ279">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AR279">
         <v>1.24</v>
@@ -59318,7 +59345,7 @@
         <v>0.77</v>
       </c>
       <c r="AP280">
-        <v>1.87</v>
+        <v>1.94</v>
       </c>
       <c r="AQ280">
         <v>0.9399999999999999</v>
@@ -59524,7 +59551,7 @@
         <v>1.58</v>
       </c>
       <c r="AP281">
-        <v>2.44</v>
+        <v>2.47</v>
       </c>
       <c r="AQ281">
         <v>1.56</v>
@@ -59652,7 +59679,7 @@
         <v>101</v>
       </c>
       <c r="P282" t="s">
-        <v>422</v>
+        <v>428</v>
       </c>
       <c r="Q282">
         <v>2.6</v>
@@ -59730,7 +59757,7 @@
         <v>0.73</v>
       </c>
       <c r="AP282">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AQ282">
         <v>0.88</v>
@@ -60145,7 +60172,7 @@
         <v>1.47</v>
       </c>
       <c r="AQ284">
-        <v>1.27</v>
+        <v>1.19</v>
       </c>
       <c r="AR284">
         <v>1.32</v>
@@ -60476,7 +60503,7 @@
         <v>101</v>
       </c>
       <c r="P286" t="s">
-        <v>423</v>
+        <v>429</v>
       </c>
       <c r="Q286">
         <v>2.5</v>
@@ -60557,7 +60584,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ286">
-        <v>0.8100000000000001</v>
+        <v>0.76</v>
       </c>
       <c r="AR286">
         <v>1.4</v>
@@ -60682,7 +60709,7 @@
         <v>270</v>
       </c>
       <c r="P287" t="s">
-        <v>360</v>
+        <v>368</v>
       </c>
       <c r="Q287">
         <v>2.75</v>
@@ -60760,7 +60787,7 @@
         <v>1.73</v>
       </c>
       <c r="AP287">
-        <v>1.73</v>
+        <v>1.81</v>
       </c>
       <c r="AQ287">
         <v>1.5</v>
@@ -60969,7 +60996,7 @@
         <v>2.35</v>
       </c>
       <c r="AQ288">
-        <v>0.53</v>
+        <v>0.5</v>
       </c>
       <c r="AR288">
         <v>1.53</v>
@@ -61172,7 +61199,7 @@
         <v>1.42</v>
       </c>
       <c r="AP289">
-        <v>1.47</v>
+        <v>1.56</v>
       </c>
       <c r="AQ289">
         <v>1.35</v>
@@ -61381,7 +61408,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ290">
-        <v>0.79</v>
+        <v>0.93</v>
       </c>
       <c r="AR290">
         <v>1.09</v>
@@ -61506,7 +61533,7 @@
         <v>101</v>
       </c>
       <c r="P291" t="s">
-        <v>424</v>
+        <v>430</v>
       </c>
       <c r="Q291">
         <v>4</v>
@@ -61587,7 +61614,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ291">
-        <v>1.69</v>
+        <v>1.76</v>
       </c>
       <c r="AR291">
         <v>1.25</v>
@@ -61790,7 +61817,7 @@
         <v>0.92</v>
       </c>
       <c r="AP292">
-        <v>0.67</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AQ292">
         <v>1</v>
@@ -61999,7 +62026,7 @@
         <v>2.25</v>
       </c>
       <c r="AQ293">
-        <v>0.53</v>
+        <v>0.5</v>
       </c>
       <c r="AR293">
         <v>1.4</v>
@@ -62124,7 +62151,7 @@
         <v>101</v>
       </c>
       <c r="P294" t="s">
-        <v>323</v>
+        <v>331</v>
       </c>
       <c r="Q294">
         <v>4</v>
@@ -62202,7 +62229,7 @@
         <v>1.38</v>
       </c>
       <c r="AP294">
-        <v>0.8</v>
+        <v>0.75</v>
       </c>
       <c r="AQ294">
         <v>1.35</v>
@@ -62330,7 +62357,7 @@
         <v>274</v>
       </c>
       <c r="P295" t="s">
-        <v>425</v>
+        <v>431</v>
       </c>
       <c r="Q295">
         <v>2</v>
@@ -62408,7 +62435,7 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="AP295">
-        <v>1.86</v>
+        <v>1.93</v>
       </c>
       <c r="AQ295">
         <v>0.8100000000000001</v>
@@ -62536,7 +62563,7 @@
         <v>101</v>
       </c>
       <c r="P296" t="s">
-        <v>426</v>
+        <v>432</v>
       </c>
       <c r="Q296">
         <v>2.75</v>
@@ -62617,7 +62644,7 @@
         <v>1.81</v>
       </c>
       <c r="AQ296">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="AR296">
         <v>1.45</v>
@@ -62820,10 +62847,10 @@
         <v>0.75</v>
       </c>
       <c r="AP297">
-        <v>1.47</v>
+        <v>1.56</v>
       </c>
       <c r="AQ297">
-        <v>0.6</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AR297">
         <v>1.32</v>
@@ -62948,7 +62975,7 @@
         <v>276</v>
       </c>
       <c r="P298" t="s">
-        <v>427</v>
+        <v>433</v>
       </c>
       <c r="Q298">
         <v>2.38</v>
@@ -63029,7 +63056,7 @@
         <v>2.35</v>
       </c>
       <c r="AQ298">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR298">
         <v>1.58</v>
@@ -63154,7 +63181,7 @@
         <v>101</v>
       </c>
       <c r="P299" t="s">
-        <v>428</v>
+        <v>434</v>
       </c>
       <c r="Q299">
         <v>2.88</v>
@@ -63232,7 +63259,7 @@
         <v>0.91</v>
       </c>
       <c r="AP299">
-        <v>1.2</v>
+        <v>1.31</v>
       </c>
       <c r="AQ299">
         <v>1.19</v>
@@ -63360,7 +63387,7 @@
         <v>101</v>
       </c>
       <c r="P300" t="s">
-        <v>429</v>
+        <v>435</v>
       </c>
       <c r="Q300">
         <v>3.6</v>
@@ -63438,7 +63465,7 @@
         <v>1.54</v>
       </c>
       <c r="AP300">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="AQ300">
         <v>1.63</v>
@@ -63644,10 +63671,10 @@
         <v>1.33</v>
       </c>
       <c r="AP301">
-        <v>1.53</v>
+        <v>1.63</v>
       </c>
       <c r="AQ301">
-        <v>1.13</v>
+        <v>1.06</v>
       </c>
       <c r="AR301">
         <v>1.29</v>
@@ -64059,7 +64086,7 @@
         <v>1.53</v>
       </c>
       <c r="AQ303">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR303">
         <v>1.31</v>
@@ -64184,7 +64211,7 @@
         <v>278</v>
       </c>
       <c r="P304" t="s">
-        <v>430</v>
+        <v>436</v>
       </c>
       <c r="Q304">
         <v>4</v>
@@ -64262,7 +64289,7 @@
         <v>0.71</v>
       </c>
       <c r="AP304">
-        <v>1.8</v>
+        <v>1.69</v>
       </c>
       <c r="AQ304">
         <v>0.9399999999999999</v>
@@ -64471,7 +64498,7 @@
         <v>1.47</v>
       </c>
       <c r="AQ305">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AR305">
         <v>1.33</v>
@@ -64674,10 +64701,10 @@
         <v>2.09</v>
       </c>
       <c r="AP306">
-        <v>2.44</v>
+        <v>2.47</v>
       </c>
       <c r="AQ306">
-        <v>1.64</v>
+        <v>1.73</v>
       </c>
       <c r="AR306">
         <v>1.4</v>
@@ -64880,7 +64907,7 @@
         <v>0.92</v>
       </c>
       <c r="AP307">
-        <v>1.73</v>
+        <v>1.81</v>
       </c>
       <c r="AQ307">
         <v>0.88</v>
@@ -65292,7 +65319,7 @@
         <v>1.08</v>
       </c>
       <c r="AP309">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AQ309">
         <v>0.82</v>
@@ -65501,7 +65528,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ310">
-        <v>0.93</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AR310">
         <v>1.47</v>
@@ -65626,7 +65653,7 @@
         <v>282</v>
       </c>
       <c r="P311" t="s">
-        <v>431</v>
+        <v>437</v>
       </c>
       <c r="Q311">
         <v>3.75</v>
@@ -65707,7 +65734,7 @@
         <v>1.88</v>
       </c>
       <c r="AQ311">
-        <v>1.27</v>
+        <v>1.19</v>
       </c>
       <c r="AR311">
         <v>1.34</v>
@@ -65832,7 +65859,7 @@
         <v>195</v>
       </c>
       <c r="P312" t="s">
-        <v>432</v>
+        <v>438</v>
       </c>
       <c r="Q312">
         <v>2.63</v>
@@ -66119,7 +66146,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ313">
-        <v>0.8100000000000001</v>
+        <v>0.76</v>
       </c>
       <c r="AR313">
         <v>1.48</v>
@@ -66528,7 +66555,7 @@
         <v>1.58</v>
       </c>
       <c r="AP315">
-        <v>1.87</v>
+        <v>1.94</v>
       </c>
       <c r="AQ315">
         <v>1.5</v>
@@ -66734,10 +66761,10 @@
         <v>0.83</v>
       </c>
       <c r="AP316">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="AQ316">
-        <v>0.79</v>
+        <v>0.93</v>
       </c>
       <c r="AR316">
         <v>1.27</v>
@@ -66940,7 +66967,7 @@
         <v>1</v>
       </c>
       <c r="AP317">
-        <v>2.44</v>
+        <v>2.47</v>
       </c>
       <c r="AQ317">
         <v>0.82</v>
@@ -67068,7 +67095,7 @@
         <v>283</v>
       </c>
       <c r="P318" t="s">
-        <v>433</v>
+        <v>439</v>
       </c>
       <c r="Q318">
         <v>3.4</v>
@@ -67146,10 +67173,10 @@
         <v>1.42</v>
       </c>
       <c r="AP318">
-        <v>1.73</v>
+        <v>1.81</v>
       </c>
       <c r="AQ318">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AR318">
         <v>1.24</v>
@@ -67355,7 +67382,7 @@
         <v>1.53</v>
       </c>
       <c r="AQ319">
-        <v>1.64</v>
+        <v>1.73</v>
       </c>
       <c r="AR319">
         <v>1.37</v>
@@ -67558,10 +67585,10 @@
         <v>1</v>
       </c>
       <c r="AP320">
-        <v>1.53</v>
+        <v>1.63</v>
       </c>
       <c r="AQ320">
-        <v>0.93</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AR320">
         <v>1.28</v>
@@ -67764,7 +67791,7 @@
         <v>0.92</v>
       </c>
       <c r="AP321">
-        <v>1.87</v>
+        <v>1.94</v>
       </c>
       <c r="AQ321">
         <v>0.75</v>
@@ -68176,10 +68203,10 @@
         <v>0.62</v>
       </c>
       <c r="AP323">
-        <v>1.47</v>
+        <v>1.56</v>
       </c>
       <c r="AQ323">
-        <v>0.53</v>
+        <v>0.5</v>
       </c>
       <c r="AR323">
         <v>1.34</v>
@@ -68591,7 +68618,7 @@
         <v>1.47</v>
       </c>
       <c r="AQ325">
-        <v>0.8100000000000001</v>
+        <v>0.76</v>
       </c>
       <c r="AR325">
         <v>1.34</v>
@@ -68716,7 +68743,7 @@
         <v>290</v>
       </c>
       <c r="P326" t="s">
-        <v>434</v>
+        <v>440</v>
       </c>
       <c r="Q326">
         <v>3.75</v>
@@ -68797,7 +68824,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ326">
-        <v>1.69</v>
+        <v>1.76</v>
       </c>
       <c r="AR326">
         <v>1.38</v>
@@ -68922,7 +68949,7 @@
         <v>291</v>
       </c>
       <c r="P327" t="s">
-        <v>435</v>
+        <v>441</v>
       </c>
       <c r="Q327">
         <v>3.75</v>
@@ -69209,7 +69236,7 @@
         <v>1.88</v>
       </c>
       <c r="AQ328">
-        <v>1.13</v>
+        <v>1.06</v>
       </c>
       <c r="AR328">
         <v>1.38</v>
@@ -69412,7 +69439,7 @@
         <v>1.08</v>
       </c>
       <c r="AP329">
-        <v>1.86</v>
+        <v>1.93</v>
       </c>
       <c r="AQ329">
         <v>0.88</v>
@@ -69540,7 +69567,7 @@
         <v>293</v>
       </c>
       <c r="P330" t="s">
-        <v>436</v>
+        <v>442</v>
       </c>
       <c r="Q330">
         <v>2.63</v>
@@ -69621,7 +69648,7 @@
         <v>2.35</v>
       </c>
       <c r="AQ330">
-        <v>1.27</v>
+        <v>1.19</v>
       </c>
       <c r="AR330">
         <v>1.67</v>
@@ -69746,7 +69773,7 @@
         <v>260</v>
       </c>
       <c r="P331" t="s">
-        <v>437</v>
+        <v>443</v>
       </c>
       <c r="Q331">
         <v>3.5</v>
@@ -70030,10 +70057,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="AP332">
-        <v>1.8</v>
+        <v>1.69</v>
       </c>
       <c r="AQ332">
-        <v>0.6</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AR332">
         <v>1.27</v>
@@ -70158,7 +70185,7 @@
         <v>294</v>
       </c>
       <c r="P333" t="s">
-        <v>438</v>
+        <v>444</v>
       </c>
       <c r="Q333">
         <v>4</v>
@@ -70236,10 +70263,10 @@
         <v>1.27</v>
       </c>
       <c r="AP333">
-        <v>0.8</v>
+        <v>0.75</v>
       </c>
       <c r="AQ333">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="AR333">
         <v>1.34</v>
@@ -70651,7 +70678,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ335">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR335">
         <v>1.49</v>
@@ -70776,7 +70803,7 @@
         <v>101</v>
       </c>
       <c r="P336" t="s">
-        <v>439</v>
+        <v>445</v>
       </c>
       <c r="Q336">
         <v>2.63</v>
@@ -70854,7 +70881,7 @@
         <v>1.36</v>
       </c>
       <c r="AP336">
-        <v>1.2</v>
+        <v>1.31</v>
       </c>
       <c r="AQ336">
         <v>1.56</v>
@@ -71188,7 +71215,7 @@
         <v>296</v>
       </c>
       <c r="P338" t="s">
-        <v>440</v>
+        <v>446</v>
       </c>
       <c r="Q338">
         <v>3.1</v>
@@ -71266,7 +71293,7 @@
         <v>0.87</v>
       </c>
       <c r="AP338">
-        <v>0.67</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AQ338">
         <v>0.9399999999999999</v>
@@ -71394,7 +71421,7 @@
         <v>297</v>
       </c>
       <c r="P339" t="s">
-        <v>441</v>
+        <v>447</v>
       </c>
       <c r="Q339">
         <v>3</v>
@@ -71678,7 +71705,7 @@
         <v>0.93</v>
       </c>
       <c r="AP340">
-        <v>1.8</v>
+        <v>1.69</v>
       </c>
       <c r="AQ340">
         <v>0.82</v>
@@ -71806,7 +71833,7 @@
         <v>299</v>
       </c>
       <c r="P341" t="s">
-        <v>442</v>
+        <v>448</v>
       </c>
       <c r="Q341">
         <v>3</v>
@@ -71887,7 +71914,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ341">
-        <v>1.69</v>
+        <v>1.76</v>
       </c>
       <c r="AR341">
         <v>1.56</v>
@@ -72012,7 +72039,7 @@
         <v>300</v>
       </c>
       <c r="P342" t="s">
-        <v>443</v>
+        <v>449</v>
       </c>
       <c r="Q342">
         <v>3.1</v>
@@ -72090,7 +72117,7 @@
         <v>1.67</v>
       </c>
       <c r="AP342">
-        <v>1.47</v>
+        <v>1.56</v>
       </c>
       <c r="AQ342">
         <v>1.63</v>
@@ -72296,10 +72323,10 @@
         <v>0.87</v>
       </c>
       <c r="AP343">
-        <v>2.44</v>
+        <v>2.47</v>
       </c>
       <c r="AQ343">
-        <v>0.8100000000000001</v>
+        <v>0.76</v>
       </c>
       <c r="AR343">
         <v>1.45</v>
@@ -72502,10 +72529,10 @@
         <v>1.77</v>
       </c>
       <c r="AP344">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AQ344">
-        <v>1.64</v>
+        <v>1.73</v>
       </c>
       <c r="AR344">
         <v>1.55</v>
@@ -72630,7 +72657,7 @@
         <v>101</v>
       </c>
       <c r="P345" t="s">
-        <v>444</v>
+        <v>450</v>
       </c>
       <c r="Q345">
         <v>1.91</v>
@@ -72708,7 +72735,7 @@
         <v>0.67</v>
       </c>
       <c r="AP345">
-        <v>1.73</v>
+        <v>1.81</v>
       </c>
       <c r="AQ345">
         <v>0.8100000000000001</v>
@@ -72917,7 +72944,7 @@
         <v>1.53</v>
       </c>
       <c r="AQ346">
-        <v>0.79</v>
+        <v>0.93</v>
       </c>
       <c r="AR346">
         <v>1.34</v>
@@ -73123,7 +73150,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ347">
-        <v>0.93</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AR347">
         <v>1.37</v>
@@ -73326,10 +73353,10 @@
         <v>1.38</v>
       </c>
       <c r="AP348">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="AQ348">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AR348">
         <v>1.22</v>
@@ -73738,7 +73765,7 @@
         <v>0.88</v>
       </c>
       <c r="AP350">
-        <v>1.87</v>
+        <v>1.94</v>
       </c>
       <c r="AQ350">
         <v>0.82</v>
@@ -73947,7 +73974,7 @@
         <v>1.81</v>
       </c>
       <c r="AQ351">
-        <v>0.53</v>
+        <v>0.5</v>
       </c>
       <c r="AR351">
         <v>1.55</v>
@@ -74150,7 +74177,7 @@
         <v>0.86</v>
       </c>
       <c r="AP352">
-        <v>1.53</v>
+        <v>1.63</v>
       </c>
       <c r="AQ352">
         <v>0.75</v>
@@ -74565,7 +74592,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ354">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="AR354">
         <v>1.52</v>
@@ -74768,7 +74795,7 @@
         <v>0.8</v>
       </c>
       <c r="AP355">
-        <v>1.8</v>
+        <v>1.69</v>
       </c>
       <c r="AQ355">
         <v>0.75</v>
@@ -74977,7 +75004,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ356">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR356">
         <v>1.41</v>
@@ -75180,7 +75207,7 @@
         <v>1</v>
       </c>
       <c r="AP357">
-        <v>2.44</v>
+        <v>2.47</v>
       </c>
       <c r="AQ357">
         <v>0.88</v>
@@ -75308,7 +75335,7 @@
         <v>178</v>
       </c>
       <c r="P358" t="s">
-        <v>323</v>
+        <v>331</v>
       </c>
       <c r="Q358">
         <v>2.45</v>
@@ -75389,7 +75416,7 @@
         <v>2.35</v>
       </c>
       <c r="AQ358">
-        <v>0.93</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AR358">
         <v>1.68</v>
@@ -75592,7 +75619,7 @@
         <v>1.73</v>
       </c>
       <c r="AP359">
-        <v>1.86</v>
+        <v>1.93</v>
       </c>
       <c r="AQ359">
         <v>1.63</v>
@@ -75720,7 +75747,7 @@
         <v>206</v>
       </c>
       <c r="P360" t="s">
-        <v>445</v>
+        <v>451</v>
       </c>
       <c r="Q360">
         <v>2.3</v>
@@ -76007,7 +76034,7 @@
         <v>2.25</v>
       </c>
       <c r="AQ361">
-        <v>1.27</v>
+        <v>1.19</v>
       </c>
       <c r="AR361">
         <v>1.43</v>
@@ -76132,7 +76159,7 @@
         <v>205</v>
       </c>
       <c r="P362" t="s">
-        <v>400</v>
+        <v>407</v>
       </c>
       <c r="Q362">
         <v>3.5</v>
@@ -76213,7 +76240,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ362">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR362">
         <v>1.51</v>
@@ -76416,10 +76443,10 @@
         <v>1.15</v>
       </c>
       <c r="AP363">
-        <v>1.2</v>
+        <v>1.31</v>
       </c>
       <c r="AQ363">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="AR363">
         <v>1.51</v>
@@ -76622,7 +76649,7 @@
         <v>1</v>
       </c>
       <c r="AP364">
-        <v>1.8</v>
+        <v>1.69</v>
       </c>
       <c r="AQ364">
         <v>1</v>
@@ -76828,7 +76855,7 @@
         <v>0.93</v>
       </c>
       <c r="AP365">
-        <v>0.8</v>
+        <v>0.75</v>
       </c>
       <c r="AQ365">
         <v>0.88</v>
@@ -77446,7 +77473,7 @@
         <v>1.21</v>
       </c>
       <c r="AP368">
-        <v>0.67</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AQ368">
         <v>1.19</v>
@@ -77574,7 +77601,7 @@
         <v>309</v>
       </c>
       <c r="P369" t="s">
-        <v>446</v>
+        <v>452</v>
       </c>
       <c r="Q369">
         <v>3.25</v>
@@ -77655,7 +77682,7 @@
         <v>1.88</v>
       </c>
       <c r="AQ369">
-        <v>0.6</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AR369">
         <v>1.36</v>
@@ -77861,7 +77888,7 @@
         <v>2.35</v>
       </c>
       <c r="AQ370">
-        <v>1.13</v>
+        <v>1.06</v>
       </c>
       <c r="AR370">
         <v>1.65</v>
@@ -78064,10 +78091,10 @@
         <v>1.6</v>
       </c>
       <c r="AP371">
-        <v>0.8</v>
+        <v>0.75</v>
       </c>
       <c r="AQ371">
-        <v>1.69</v>
+        <v>1.76</v>
       </c>
       <c r="AR371">
         <v>1.39</v>
@@ -78270,7 +78297,7 @@
         <v>1.2</v>
       </c>
       <c r="AP372">
-        <v>1.87</v>
+        <v>1.94</v>
       </c>
       <c r="AQ372">
         <v>1.19</v>
@@ -78479,7 +78506,7 @@
         <v>1.53</v>
       </c>
       <c r="AQ373">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AR373">
         <v>1.37</v>
@@ -78555,6 +78582,2478 @@
       </c>
       <c r="BP373">
         <v>1.34</v>
+      </c>
+    </row>
+    <row r="374" spans="1:68">
+      <c r="A374" s="1">
+        <v>373</v>
+      </c>
+      <c r="B374">
+        <v>7476932</v>
+      </c>
+      <c r="C374" t="s">
+        <v>68</v>
+      </c>
+      <c r="D374" t="s">
+        <v>69</v>
+      </c>
+      <c r="E374" s="2">
+        <v>45710.39583333334</v>
+      </c>
+      <c r="F374">
+        <v>33</v>
+      </c>
+      <c r="G374" t="s">
+        <v>86</v>
+      </c>
+      <c r="H374" t="s">
+        <v>72</v>
+      </c>
+      <c r="I374">
+        <v>1</v>
+      </c>
+      <c r="J374">
+        <v>0</v>
+      </c>
+      <c r="K374">
+        <v>1</v>
+      </c>
+      <c r="L374">
+        <v>3</v>
+      </c>
+      <c r="M374">
+        <v>0</v>
+      </c>
+      <c r="N374">
+        <v>3</v>
+      </c>
+      <c r="O374" t="s">
+        <v>311</v>
+      </c>
+      <c r="P374" t="s">
+        <v>101</v>
+      </c>
+      <c r="Q374">
+        <v>3.1</v>
+      </c>
+      <c r="R374">
+        <v>1.91</v>
+      </c>
+      <c r="S374">
+        <v>4.33</v>
+      </c>
+      <c r="T374">
+        <v>1.57</v>
+      </c>
+      <c r="U374">
+        <v>2.25</v>
+      </c>
+      <c r="V374">
+        <v>3.75</v>
+      </c>
+      <c r="W374">
+        <v>1.25</v>
+      </c>
+      <c r="X374">
+        <v>13</v>
+      </c>
+      <c r="Y374">
+        <v>1.04</v>
+      </c>
+      <c r="Z374">
+        <v>2.49</v>
+      </c>
+      <c r="AA374">
+        <v>3.02</v>
+      </c>
+      <c r="AB374">
+        <v>2.97</v>
+      </c>
+      <c r="AC374">
+        <v>1.06</v>
+      </c>
+      <c r="AD374">
+        <v>6.2</v>
+      </c>
+      <c r="AE374">
+        <v>1.5</v>
+      </c>
+      <c r="AF374">
+        <v>2.4</v>
+      </c>
+      <c r="AG374">
+        <v>2.41</v>
+      </c>
+      <c r="AH374">
+        <v>1.5</v>
+      </c>
+      <c r="AI374">
+        <v>2.2</v>
+      </c>
+      <c r="AJ374">
+        <v>1.62</v>
+      </c>
+      <c r="AK374">
+        <v>1.37</v>
+      </c>
+      <c r="AL374">
+        <v>1.36</v>
+      </c>
+      <c r="AM374">
+        <v>1.5</v>
+      </c>
+      <c r="AN374">
+        <v>1.73</v>
+      </c>
+      <c r="AO374">
+        <v>0.6</v>
+      </c>
+      <c r="AP374">
+        <v>1.81</v>
+      </c>
+      <c r="AQ374">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="AR374">
+        <v>1.26</v>
+      </c>
+      <c r="AS374">
+        <v>1.16</v>
+      </c>
+      <c r="AT374">
+        <v>2.42</v>
+      </c>
+      <c r="AU374">
+        <v>9</v>
+      </c>
+      <c r="AV374">
+        <v>0</v>
+      </c>
+      <c r="AW374">
+        <v>3</v>
+      </c>
+      <c r="AX374">
+        <v>10</v>
+      </c>
+      <c r="AY374">
+        <v>12</v>
+      </c>
+      <c r="AZ374">
+        <v>11</v>
+      </c>
+      <c r="BA374">
+        <v>5</v>
+      </c>
+      <c r="BB374">
+        <v>5</v>
+      </c>
+      <c r="BC374">
+        <v>10</v>
+      </c>
+      <c r="BD374">
+        <v>1.84</v>
+      </c>
+      <c r="BE374">
+        <v>6.5</v>
+      </c>
+      <c r="BF374">
+        <v>2.15</v>
+      </c>
+      <c r="BG374">
+        <v>1.28</v>
+      </c>
+      <c r="BH374">
+        <v>3.3</v>
+      </c>
+      <c r="BI374">
+        <v>1.47</v>
+      </c>
+      <c r="BJ374">
+        <v>2.43</v>
+      </c>
+      <c r="BK374">
+        <v>1.79</v>
+      </c>
+      <c r="BL374">
+        <v>1.9</v>
+      </c>
+      <c r="BM374">
+        <v>2.23</v>
+      </c>
+      <c r="BN374">
+        <v>1.57</v>
+      </c>
+      <c r="BO374">
+        <v>2.88</v>
+      </c>
+      <c r="BP374">
+        <v>1.35</v>
+      </c>
+    </row>
+    <row r="375" spans="1:68">
+      <c r="A375" s="1">
+        <v>374</v>
+      </c>
+      <c r="B375">
+        <v>7476934</v>
+      </c>
+      <c r="C375" t="s">
+        <v>68</v>
+      </c>
+      <c r="D375" t="s">
+        <v>69</v>
+      </c>
+      <c r="E375" s="2">
+        <v>45710.39583333334</v>
+      </c>
+      <c r="F375">
+        <v>33</v>
+      </c>
+      <c r="G375" t="s">
+        <v>88</v>
+      </c>
+      <c r="H375" t="s">
+        <v>81</v>
+      </c>
+      <c r="I375">
+        <v>0</v>
+      </c>
+      <c r="J375">
+        <v>0</v>
+      </c>
+      <c r="K375">
+        <v>0</v>
+      </c>
+      <c r="L375">
+        <v>0</v>
+      </c>
+      <c r="M375">
+        <v>2</v>
+      </c>
+      <c r="N375">
+        <v>2</v>
+      </c>
+      <c r="O375" t="s">
+        <v>101</v>
+      </c>
+      <c r="P375" t="s">
+        <v>453</v>
+      </c>
+      <c r="Q375">
+        <v>5.5</v>
+      </c>
+      <c r="R375">
+        <v>2.25</v>
+      </c>
+      <c r="S375">
+        <v>2.2</v>
+      </c>
+      <c r="T375">
+        <v>1.4</v>
+      </c>
+      <c r="U375">
+        <v>2.75</v>
+      </c>
+      <c r="V375">
+        <v>2.75</v>
+      </c>
+      <c r="W375">
+        <v>1.4</v>
+      </c>
+      <c r="X375">
+        <v>8</v>
+      </c>
+      <c r="Y375">
+        <v>1.08</v>
+      </c>
+      <c r="Z375">
+        <v>4.5</v>
+      </c>
+      <c r="AA375">
+        <v>4.33</v>
+      </c>
+      <c r="AB375">
+        <v>1.62</v>
+      </c>
+      <c r="AC375">
+        <v>1.03</v>
+      </c>
+      <c r="AD375">
+        <v>13</v>
+      </c>
+      <c r="AE375">
+        <v>1.28</v>
+      </c>
+      <c r="AF375">
+        <v>3.6</v>
+      </c>
+      <c r="AG375">
+        <v>1.89</v>
+      </c>
+      <c r="AH375">
+        <v>1.85</v>
+      </c>
+      <c r="AI375">
+        <v>1.91</v>
+      </c>
+      <c r="AJ375">
+        <v>1.8</v>
+      </c>
+      <c r="AK375">
+        <v>2.35</v>
+      </c>
+      <c r="AL375">
+        <v>1.18</v>
+      </c>
+      <c r="AM375">
+        <v>1.17</v>
+      </c>
+      <c r="AN375">
+        <v>0.8</v>
+      </c>
+      <c r="AO375">
+        <v>1.64</v>
+      </c>
+      <c r="AP375">
+        <v>0.75</v>
+      </c>
+      <c r="AQ375">
+        <v>1.73</v>
+      </c>
+      <c r="AR375">
+        <v>1.41</v>
+      </c>
+      <c r="AS375">
+        <v>1.33</v>
+      </c>
+      <c r="AT375">
+        <v>2.74</v>
+      </c>
+      <c r="AU375">
+        <v>4</v>
+      </c>
+      <c r="AV375">
+        <v>7</v>
+      </c>
+      <c r="AW375">
+        <v>15</v>
+      </c>
+      <c r="AX375">
+        <v>9</v>
+      </c>
+      <c r="AY375">
+        <v>21</v>
+      </c>
+      <c r="AZ375">
+        <v>18</v>
+      </c>
+      <c r="BA375">
+        <v>3</v>
+      </c>
+      <c r="BB375">
+        <v>7</v>
+      </c>
+      <c r="BC375">
+        <v>10</v>
+      </c>
+      <c r="BD375">
+        <v>3.05</v>
+      </c>
+      <c r="BE375">
+        <v>7</v>
+      </c>
+      <c r="BF375">
+        <v>1.44</v>
+      </c>
+      <c r="BG375">
+        <v>1.19</v>
+      </c>
+      <c r="BH375">
+        <v>4.1</v>
+      </c>
+      <c r="BI375">
+        <v>1.34</v>
+      </c>
+      <c r="BJ375">
+        <v>2.9</v>
+      </c>
+      <c r="BK375">
+        <v>1.56</v>
+      </c>
+      <c r="BL375">
+        <v>2.23</v>
+      </c>
+      <c r="BM375">
+        <v>1.95</v>
+      </c>
+      <c r="BN375">
+        <v>1.85</v>
+      </c>
+      <c r="BO375">
+        <v>2.33</v>
+      </c>
+      <c r="BP375">
+        <v>1.52</v>
+      </c>
+    </row>
+    <row r="376" spans="1:68">
+      <c r="A376" s="1">
+        <v>375</v>
+      </c>
+      <c r="B376">
+        <v>7476931</v>
+      </c>
+      <c r="C376" t="s">
+        <v>68</v>
+      </c>
+      <c r="D376" t="s">
+        <v>69</v>
+      </c>
+      <c r="E376" s="2">
+        <v>45710.5</v>
+      </c>
+      <c r="F376">
+        <v>33</v>
+      </c>
+      <c r="G376" t="s">
+        <v>85</v>
+      </c>
+      <c r="H376" t="s">
+        <v>71</v>
+      </c>
+      <c r="I376">
+        <v>0</v>
+      </c>
+      <c r="J376">
+        <v>1</v>
+      </c>
+      <c r="K376">
+        <v>1</v>
+      </c>
+      <c r="L376">
+        <v>1</v>
+      </c>
+      <c r="M376">
+        <v>1</v>
+      </c>
+      <c r="N376">
+        <v>2</v>
+      </c>
+      <c r="O376" t="s">
+        <v>218</v>
+      </c>
+      <c r="P376" t="s">
+        <v>356</v>
+      </c>
+      <c r="Q376">
+        <v>3.5</v>
+      </c>
+      <c r="R376">
+        <v>1.95</v>
+      </c>
+      <c r="S376">
+        <v>3.5</v>
+      </c>
+      <c r="T376">
+        <v>1.53</v>
+      </c>
+      <c r="U376">
+        <v>2.38</v>
+      </c>
+      <c r="V376">
+        <v>3.5</v>
+      </c>
+      <c r="W376">
+        <v>1.29</v>
+      </c>
+      <c r="X376">
+        <v>11</v>
+      </c>
+      <c r="Y376">
+        <v>1.05</v>
+      </c>
+      <c r="Z376">
+        <v>2.62</v>
+      </c>
+      <c r="AA376">
+        <v>3.27</v>
+      </c>
+      <c r="AB376">
+        <v>2.62</v>
+      </c>
+      <c r="AC376">
+        <v>1.08</v>
+      </c>
+      <c r="AD376">
+        <v>8.5</v>
+      </c>
+      <c r="AE376">
+        <v>1.57</v>
+      </c>
+      <c r="AF376">
+        <v>2.25</v>
+      </c>
+      <c r="AG376">
+        <v>2.45</v>
+      </c>
+      <c r="AH376">
+        <v>1.5</v>
+      </c>
+      <c r="AI376">
+        <v>2</v>
+      </c>
+      <c r="AJ376">
+        <v>1.73</v>
+      </c>
+      <c r="AK376">
+        <v>1.47</v>
+      </c>
+      <c r="AL376">
+        <v>1.28</v>
+      </c>
+      <c r="AM376">
+        <v>1.47</v>
+      </c>
+      <c r="AN376">
+        <v>1.53</v>
+      </c>
+      <c r="AO376">
+        <v>1.33</v>
+      </c>
+      <c r="AP376">
+        <v>1.5</v>
+      </c>
+      <c r="AQ376">
+        <v>1.31</v>
+      </c>
+      <c r="AR376">
+        <v>1.53</v>
+      </c>
+      <c r="AS376">
+        <v>1.22</v>
+      </c>
+      <c r="AT376">
+        <v>2.75</v>
+      </c>
+      <c r="AU376">
+        <v>5</v>
+      </c>
+      <c r="AV376">
+        <v>2</v>
+      </c>
+      <c r="AW376">
+        <v>6</v>
+      </c>
+      <c r="AX376">
+        <v>8</v>
+      </c>
+      <c r="AY376">
+        <v>15</v>
+      </c>
+      <c r="AZ376">
+        <v>11</v>
+      </c>
+      <c r="BA376">
+        <v>3</v>
+      </c>
+      <c r="BB376">
+        <v>3</v>
+      </c>
+      <c r="BC376">
+        <v>6</v>
+      </c>
+      <c r="BD376">
+        <v>1.98</v>
+      </c>
+      <c r="BE376">
+        <v>6.5</v>
+      </c>
+      <c r="BF376">
+        <v>1.98</v>
+      </c>
+      <c r="BG376">
+        <v>1.28</v>
+      </c>
+      <c r="BH376">
+        <v>3.3</v>
+      </c>
+      <c r="BI376">
+        <v>1.49</v>
+      </c>
+      <c r="BJ376">
+        <v>2.4</v>
+      </c>
+      <c r="BK376">
+        <v>1.88</v>
+      </c>
+      <c r="BL376">
+        <v>1.92</v>
+      </c>
+      <c r="BM376">
+        <v>2.23</v>
+      </c>
+      <c r="BN376">
+        <v>1.57</v>
+      </c>
+      <c r="BO376">
+        <v>2.88</v>
+      </c>
+      <c r="BP376">
+        <v>1.35</v>
+      </c>
+    </row>
+    <row r="377" spans="1:68">
+      <c r="A377" s="1">
+        <v>376</v>
+      </c>
+      <c r="B377">
+        <v>7476938</v>
+      </c>
+      <c r="C377" t="s">
+        <v>68</v>
+      </c>
+      <c r="D377" t="s">
+        <v>69</v>
+      </c>
+      <c r="E377" s="2">
+        <v>45710.5</v>
+      </c>
+      <c r="F377">
+        <v>33</v>
+      </c>
+      <c r="G377" t="s">
+        <v>91</v>
+      </c>
+      <c r="H377" t="s">
+        <v>70</v>
+      </c>
+      <c r="I377">
+        <v>0</v>
+      </c>
+      <c r="J377">
+        <v>0</v>
+      </c>
+      <c r="K377">
+        <v>0</v>
+      </c>
+      <c r="L377">
+        <v>1</v>
+      </c>
+      <c r="M377">
+        <v>0</v>
+      </c>
+      <c r="N377">
+        <v>1</v>
+      </c>
+      <c r="O377" t="s">
+        <v>312</v>
+      </c>
+      <c r="P377" t="s">
+        <v>101</v>
+      </c>
+      <c r="Q377">
+        <v>3.25</v>
+      </c>
+      <c r="R377">
+        <v>2.25</v>
+      </c>
+      <c r="S377">
+        <v>3</v>
+      </c>
+      <c r="T377">
+        <v>1.36</v>
+      </c>
+      <c r="U377">
+        <v>3</v>
+      </c>
+      <c r="V377">
+        <v>2.63</v>
+      </c>
+      <c r="W377">
+        <v>1.44</v>
+      </c>
+      <c r="X377">
+        <v>7</v>
+      </c>
+      <c r="Y377">
+        <v>1.1</v>
+      </c>
+      <c r="Z377">
+        <v>2.78</v>
+      </c>
+      <c r="AA377">
+        <v>3.45</v>
+      </c>
+      <c r="AB377">
+        <v>2.39</v>
+      </c>
+      <c r="AC377">
+        <v>1.02</v>
+      </c>
+      <c r="AD377">
+        <v>10</v>
+      </c>
+      <c r="AE377">
+        <v>1.19</v>
+      </c>
+      <c r="AF377">
+        <v>3.78</v>
+      </c>
+      <c r="AG377">
+        <v>1.85</v>
+      </c>
+      <c r="AH377">
+        <v>1.89</v>
+      </c>
+      <c r="AI377">
+        <v>1.62</v>
+      </c>
+      <c r="AJ377">
+        <v>2.2</v>
+      </c>
+      <c r="AK377">
+        <v>1.55</v>
+      </c>
+      <c r="AL377">
+        <v>1.28</v>
+      </c>
+      <c r="AM377">
+        <v>1.42</v>
+      </c>
+      <c r="AN377">
+        <v>1.47</v>
+      </c>
+      <c r="AO377">
+        <v>1.13</v>
+      </c>
+      <c r="AP377">
+        <v>1.56</v>
+      </c>
+      <c r="AQ377">
+        <v>1.06</v>
+      </c>
+      <c r="AR377">
+        <v>1.39</v>
+      </c>
+      <c r="AS377">
+        <v>1.29</v>
+      </c>
+      <c r="AT377">
+        <v>2.68</v>
+      </c>
+      <c r="AU377">
+        <v>3</v>
+      </c>
+      <c r="AV377">
+        <v>3</v>
+      </c>
+      <c r="AW377">
+        <v>8</v>
+      </c>
+      <c r="AX377">
+        <v>2</v>
+      </c>
+      <c r="AY377">
+        <v>11</v>
+      </c>
+      <c r="AZ377">
+        <v>5</v>
+      </c>
+      <c r="BA377">
+        <v>7</v>
+      </c>
+      <c r="BB377">
+        <v>8</v>
+      </c>
+      <c r="BC377">
+        <v>15</v>
+      </c>
+      <c r="BD377">
+        <v>2.05</v>
+      </c>
+      <c r="BE377">
+        <v>6.5</v>
+      </c>
+      <c r="BF377">
+        <v>1.95</v>
+      </c>
+      <c r="BG377">
+        <v>1.25</v>
+      </c>
+      <c r="BH377">
+        <v>3.4</v>
+      </c>
+      <c r="BI377">
+        <v>1.44</v>
+      </c>
+      <c r="BJ377">
+        <v>2.55</v>
+      </c>
+      <c r="BK377">
+        <v>1.74</v>
+      </c>
+      <c r="BL377">
+        <v>1.96</v>
+      </c>
+      <c r="BM377">
+        <v>2.17</v>
+      </c>
+      <c r="BN377">
+        <v>1.6</v>
+      </c>
+      <c r="BO377">
+        <v>2.7</v>
+      </c>
+      <c r="BP377">
+        <v>1.38</v>
+      </c>
+    </row>
+    <row r="378" spans="1:68">
+      <c r="A378" s="1">
+        <v>377</v>
+      </c>
+      <c r="B378">
+        <v>7476929</v>
+      </c>
+      <c r="C378" t="s">
+        <v>68</v>
+      </c>
+      <c r="D378" t="s">
+        <v>69</v>
+      </c>
+      <c r="E378" s="2">
+        <v>45710.5</v>
+      </c>
+      <c r="F378">
+        <v>33</v>
+      </c>
+      <c r="G378" t="s">
+        <v>83</v>
+      </c>
+      <c r="H378" t="s">
+        <v>77</v>
+      </c>
+      <c r="I378">
+        <v>2</v>
+      </c>
+      <c r="J378">
+        <v>0</v>
+      </c>
+      <c r="K378">
+        <v>2</v>
+      </c>
+      <c r="L378">
+        <v>2</v>
+      </c>
+      <c r="M378">
+        <v>0</v>
+      </c>
+      <c r="N378">
+        <v>2</v>
+      </c>
+      <c r="O378" t="s">
+        <v>313</v>
+      </c>
+      <c r="P378" t="s">
+        <v>101</v>
+      </c>
+      <c r="Q378">
+        <v>2.63</v>
+      </c>
+      <c r="R378">
+        <v>2.1</v>
+      </c>
+      <c r="S378">
+        <v>4.5</v>
+      </c>
+      <c r="T378">
+        <v>1.44</v>
+      </c>
+      <c r="U378">
+        <v>2.63</v>
+      </c>
+      <c r="V378">
+        <v>3.25</v>
+      </c>
+      <c r="W378">
+        <v>1.33</v>
+      </c>
+      <c r="X378">
+        <v>9</v>
+      </c>
+      <c r="Y378">
+        <v>1.07</v>
+      </c>
+      <c r="Z378">
+        <v>1.78</v>
+      </c>
+      <c r="AA378">
+        <v>3.64</v>
+      </c>
+      <c r="AB378">
+        <v>4.3</v>
+      </c>
+      <c r="AC378">
+        <v>1.01</v>
+      </c>
+      <c r="AD378">
+        <v>8.6</v>
+      </c>
+      <c r="AE378">
+        <v>1.3</v>
+      </c>
+      <c r="AF378">
+        <v>2.98</v>
+      </c>
+      <c r="AG378">
+        <v>2</v>
+      </c>
+      <c r="AH378">
+        <v>1.75</v>
+      </c>
+      <c r="AI378">
+        <v>1.91</v>
+      </c>
+      <c r="AJ378">
+        <v>1.8</v>
+      </c>
+      <c r="AK378">
+        <v>1.24</v>
+      </c>
+      <c r="AL378">
+        <v>1.28</v>
+      </c>
+      <c r="AM378">
+        <v>1.84</v>
+      </c>
+      <c r="AN378">
+        <v>1.2</v>
+      </c>
+      <c r="AO378">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="AP378">
+        <v>1.31</v>
+      </c>
+      <c r="AQ378">
+        <v>0.76</v>
+      </c>
+      <c r="AR378">
+        <v>1.48</v>
+      </c>
+      <c r="AS378">
+        <v>1.12</v>
+      </c>
+      <c r="AT378">
+        <v>2.6</v>
+      </c>
+      <c r="AU378">
+        <v>5</v>
+      </c>
+      <c r="AV378">
+        <v>4</v>
+      </c>
+      <c r="AW378">
+        <v>4</v>
+      </c>
+      <c r="AX378">
+        <v>10</v>
+      </c>
+      <c r="AY378">
+        <v>9</v>
+      </c>
+      <c r="AZ378">
+        <v>14</v>
+      </c>
+      <c r="BA378">
+        <v>5</v>
+      </c>
+      <c r="BB378">
+        <v>4</v>
+      </c>
+      <c r="BC378">
+        <v>9</v>
+      </c>
+      <c r="BD378">
+        <v>1.56</v>
+      </c>
+      <c r="BE378">
+        <v>6.75</v>
+      </c>
+      <c r="BF378">
+        <v>2.65</v>
+      </c>
+      <c r="BG378">
+        <v>1.25</v>
+      </c>
+      <c r="BH378">
+        <v>3.45</v>
+      </c>
+      <c r="BI378">
+        <v>1.44</v>
+      </c>
+      <c r="BJ378">
+        <v>2.55</v>
+      </c>
+      <c r="BK378">
+        <v>1.71</v>
+      </c>
+      <c r="BL378">
+        <v>2</v>
+      </c>
+      <c r="BM378">
+        <v>2.08</v>
+      </c>
+      <c r="BN378">
+        <v>1.65</v>
+      </c>
+      <c r="BO378">
+        <v>2.65</v>
+      </c>
+      <c r="BP378">
+        <v>1.41</v>
+      </c>
+    </row>
+    <row r="379" spans="1:68">
+      <c r="A379" s="1">
+        <v>378</v>
+      </c>
+      <c r="B379">
+        <v>7476937</v>
+      </c>
+      <c r="C379" t="s">
+        <v>68</v>
+      </c>
+      <c r="D379" t="s">
+        <v>69</v>
+      </c>
+      <c r="E379" s="2">
+        <v>45710.5</v>
+      </c>
+      <c r="F379">
+        <v>33</v>
+      </c>
+      <c r="G379" t="s">
+        <v>90</v>
+      </c>
+      <c r="H379" t="s">
+        <v>79</v>
+      </c>
+      <c r="I379">
+        <v>1</v>
+      </c>
+      <c r="J379">
+        <v>0</v>
+      </c>
+      <c r="K379">
+        <v>1</v>
+      </c>
+      <c r="L379">
+        <v>2</v>
+      </c>
+      <c r="M379">
+        <v>1</v>
+      </c>
+      <c r="N379">
+        <v>3</v>
+      </c>
+      <c r="O379" t="s">
+        <v>314</v>
+      </c>
+      <c r="P379" t="s">
+        <v>211</v>
+      </c>
+      <c r="Q379">
+        <v>3</v>
+      </c>
+      <c r="R379">
+        <v>2.05</v>
+      </c>
+      <c r="S379">
+        <v>4</v>
+      </c>
+      <c r="T379">
+        <v>1.5</v>
+      </c>
+      <c r="U379">
+        <v>2.5</v>
+      </c>
+      <c r="V379">
+        <v>3.4</v>
+      </c>
+      <c r="W379">
+        <v>1.3</v>
+      </c>
+      <c r="X379">
+        <v>10</v>
+      </c>
+      <c r="Y379">
+        <v>1.06</v>
+      </c>
+      <c r="Z379">
+        <v>2.17</v>
+      </c>
+      <c r="AA379">
+        <v>3.33</v>
+      </c>
+      <c r="AB379">
+        <v>3.23</v>
+      </c>
+      <c r="AC379">
+        <v>1.02</v>
+      </c>
+      <c r="AD379">
+        <v>8.1</v>
+      </c>
+      <c r="AE379">
+        <v>1.33</v>
+      </c>
+      <c r="AF379">
+        <v>2.84</v>
+      </c>
+      <c r="AG379">
+        <v>2.13</v>
+      </c>
+      <c r="AH379">
+        <v>1.65</v>
+      </c>
+      <c r="AI379">
+        <v>1.91</v>
+      </c>
+      <c r="AJ379">
+        <v>1.8</v>
+      </c>
+      <c r="AK379">
+        <v>1.31</v>
+      </c>
+      <c r="AL379">
+        <v>1.31</v>
+      </c>
+      <c r="AM379">
+        <v>1.65</v>
+      </c>
+      <c r="AN379">
+        <v>1.86</v>
+      </c>
+      <c r="AO379">
+        <v>1.27</v>
+      </c>
+      <c r="AP379">
+        <v>1.93</v>
+      </c>
+      <c r="AQ379">
+        <v>1.19</v>
+      </c>
+      <c r="AR379">
+        <v>1.3</v>
+      </c>
+      <c r="AS379">
+        <v>1.2</v>
+      </c>
+      <c r="AT379">
+        <v>2.5</v>
+      </c>
+      <c r="AU379">
+        <v>4</v>
+      </c>
+      <c r="AV379">
+        <v>2</v>
+      </c>
+      <c r="AW379">
+        <v>7</v>
+      </c>
+      <c r="AX379">
+        <v>9</v>
+      </c>
+      <c r="AY379">
+        <v>14</v>
+      </c>
+      <c r="AZ379">
+        <v>15</v>
+      </c>
+      <c r="BA379">
+        <v>6</v>
+      </c>
+      <c r="BB379">
+        <v>5</v>
+      </c>
+      <c r="BC379">
+        <v>11</v>
+      </c>
+      <c r="BD379">
+        <v>1.74</v>
+      </c>
+      <c r="BE379">
+        <v>6.75</v>
+      </c>
+      <c r="BF379">
+        <v>2.35</v>
+      </c>
+      <c r="BG379">
+        <v>1.3</v>
+      </c>
+      <c r="BH379">
+        <v>3.15</v>
+      </c>
+      <c r="BI379">
+        <v>1.5</v>
+      </c>
+      <c r="BJ379">
+        <v>2.33</v>
+      </c>
+      <c r="BK379">
+        <v>1.8</v>
+      </c>
+      <c r="BL379">
+        <v>2</v>
+      </c>
+      <c r="BM379">
+        <v>2.28</v>
+      </c>
+      <c r="BN379">
+        <v>1.54</v>
+      </c>
+      <c r="BO379">
+        <v>2.9</v>
+      </c>
+      <c r="BP379">
+        <v>1.35</v>
+      </c>
+    </row>
+    <row r="380" spans="1:68">
+      <c r="A380" s="1">
+        <v>379</v>
+      </c>
+      <c r="B380">
+        <v>7476936</v>
+      </c>
+      <c r="C380" t="s">
+        <v>68</v>
+      </c>
+      <c r="D380" t="s">
+        <v>69</v>
+      </c>
+      <c r="E380" s="2">
+        <v>45710.5</v>
+      </c>
+      <c r="F380">
+        <v>33</v>
+      </c>
+      <c r="G380" t="s">
+        <v>93</v>
+      </c>
+      <c r="H380" t="s">
+        <v>80</v>
+      </c>
+      <c r="I380">
+        <v>0</v>
+      </c>
+      <c r="J380">
+        <v>0</v>
+      </c>
+      <c r="K380">
+        <v>0</v>
+      </c>
+      <c r="L380">
+        <v>2</v>
+      </c>
+      <c r="M380">
+        <v>1</v>
+      </c>
+      <c r="N380">
+        <v>3</v>
+      </c>
+      <c r="O380" t="s">
+        <v>315</v>
+      </c>
+      <c r="P380" t="s">
+        <v>296</v>
+      </c>
+      <c r="Q380">
+        <v>2.3</v>
+      </c>
+      <c r="R380">
+        <v>2.1</v>
+      </c>
+      <c r="S380">
+        <v>5.5</v>
+      </c>
+      <c r="T380">
+        <v>1.44</v>
+      </c>
+      <c r="U380">
+        <v>2.63</v>
+      </c>
+      <c r="V380">
+        <v>3.25</v>
+      </c>
+      <c r="W380">
+        <v>1.33</v>
+      </c>
+      <c r="X380">
+        <v>9</v>
+      </c>
+      <c r="Y380">
+        <v>1.07</v>
+      </c>
+      <c r="Z380">
+        <v>1.67</v>
+      </c>
+      <c r="AA380">
+        <v>3.82</v>
+      </c>
+      <c r="AB380">
+        <v>4.75</v>
+      </c>
+      <c r="AC380">
+        <v>1.05</v>
+      </c>
+      <c r="AD380">
+        <v>10</v>
+      </c>
+      <c r="AE380">
+        <v>1.36</v>
+      </c>
+      <c r="AF380">
+        <v>3.2</v>
+      </c>
+      <c r="AG380">
+        <v>1.87</v>
+      </c>
+      <c r="AH380">
+        <v>1.87</v>
+      </c>
+      <c r="AI380">
+        <v>2</v>
+      </c>
+      <c r="AJ380">
+        <v>1.73</v>
+      </c>
+      <c r="AK380">
+        <v>1.17</v>
+      </c>
+      <c r="AL380">
+        <v>1.2</v>
+      </c>
+      <c r="AM380">
+        <v>2.25</v>
+      </c>
+      <c r="AN380">
+        <v>1.87</v>
+      </c>
+      <c r="AO380">
+        <v>0.53</v>
+      </c>
+      <c r="AP380">
+        <v>1.94</v>
+      </c>
+      <c r="AQ380">
+        <v>0.5</v>
+      </c>
+      <c r="AR380">
+        <v>1.72</v>
+      </c>
+      <c r="AS380">
+        <v>1.19</v>
+      </c>
+      <c r="AT380">
+        <v>2.91</v>
+      </c>
+      <c r="AU380">
+        <v>6</v>
+      </c>
+      <c r="AV380">
+        <v>5</v>
+      </c>
+      <c r="AW380">
+        <v>7</v>
+      </c>
+      <c r="AX380">
+        <v>14</v>
+      </c>
+      <c r="AY380">
+        <v>15</v>
+      </c>
+      <c r="AZ380">
+        <v>19</v>
+      </c>
+      <c r="BA380">
+        <v>5</v>
+      </c>
+      <c r="BB380">
+        <v>8</v>
+      </c>
+      <c r="BC380">
+        <v>13</v>
+      </c>
+      <c r="BD380">
+        <v>1.46</v>
+      </c>
+      <c r="BE380">
+        <v>7</v>
+      </c>
+      <c r="BF380">
+        <v>2.95</v>
+      </c>
+      <c r="BG380">
+        <v>1.21</v>
+      </c>
+      <c r="BH380">
+        <v>3.8</v>
+      </c>
+      <c r="BI380">
+        <v>1.38</v>
+      </c>
+      <c r="BJ380">
+        <v>2.75</v>
+      </c>
+      <c r="BK380">
+        <v>1.64</v>
+      </c>
+      <c r="BL380">
+        <v>2.1</v>
+      </c>
+      <c r="BM380">
+        <v>1.98</v>
+      </c>
+      <c r="BN380">
+        <v>1.72</v>
+      </c>
+      <c r="BO380">
+        <v>2.48</v>
+      </c>
+      <c r="BP380">
+        <v>1.47</v>
+      </c>
+    </row>
+    <row r="381" spans="1:68">
+      <c r="A381" s="1">
+        <v>380</v>
+      </c>
+      <c r="B381">
+        <v>7476935</v>
+      </c>
+      <c r="C381" t="s">
+        <v>68</v>
+      </c>
+      <c r="D381" t="s">
+        <v>69</v>
+      </c>
+      <c r="E381" s="2">
+        <v>45710.5</v>
+      </c>
+      <c r="F381">
+        <v>33</v>
+      </c>
+      <c r="G381" t="s">
+        <v>89</v>
+      </c>
+      <c r="H381" t="s">
+        <v>73</v>
+      </c>
+      <c r="I381">
+        <v>0</v>
+      </c>
+      <c r="J381">
+        <v>1</v>
+      </c>
+      <c r="K381">
+        <v>1</v>
+      </c>
+      <c r="L381">
+        <v>0</v>
+      </c>
+      <c r="M381">
+        <v>3</v>
+      </c>
+      <c r="N381">
+        <v>3</v>
+      </c>
+      <c r="O381" t="s">
+        <v>101</v>
+      </c>
+      <c r="P381" t="s">
+        <v>454</v>
+      </c>
+      <c r="Q381">
+        <v>3.5</v>
+      </c>
+      <c r="R381">
+        <v>2.1</v>
+      </c>
+      <c r="S381">
+        <v>3.1</v>
+      </c>
+      <c r="T381">
+        <v>1.44</v>
+      </c>
+      <c r="U381">
+        <v>2.63</v>
+      </c>
+      <c r="V381">
+        <v>3</v>
+      </c>
+      <c r="W381">
+        <v>1.36</v>
+      </c>
+      <c r="X381">
+        <v>9</v>
+      </c>
+      <c r="Y381">
+        <v>1.07</v>
+      </c>
+      <c r="Z381">
+        <v>2.86</v>
+      </c>
+      <c r="AA381">
+        <v>3.36</v>
+      </c>
+      <c r="AB381">
+        <v>2.37</v>
+      </c>
+      <c r="AC381">
+        <v>1.02</v>
+      </c>
+      <c r="AD381">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="AE381">
+        <v>1.28</v>
+      </c>
+      <c r="AF381">
+        <v>3.08</v>
+      </c>
+      <c r="AG381">
+        <v>1.98</v>
+      </c>
+      <c r="AH381">
+        <v>1.77</v>
+      </c>
+      <c r="AI381">
+        <v>1.73</v>
+      </c>
+      <c r="AJ381">
+        <v>2</v>
+      </c>
+      <c r="AK381">
+        <v>1.54</v>
+      </c>
+      <c r="AL381">
+        <v>1.31</v>
+      </c>
+      <c r="AM381">
+        <v>1.4</v>
+      </c>
+      <c r="AN381">
+        <v>1.8</v>
+      </c>
+      <c r="AO381">
+        <v>0.79</v>
+      </c>
+      <c r="AP381">
+        <v>1.69</v>
+      </c>
+      <c r="AQ381">
+        <v>0.93</v>
+      </c>
+      <c r="AR381">
+        <v>1.24</v>
+      </c>
+      <c r="AS381">
+        <v>1.12</v>
+      </c>
+      <c r="AT381">
+        <v>2.36</v>
+      </c>
+      <c r="AU381">
+        <v>3</v>
+      </c>
+      <c r="AV381">
+        <v>5</v>
+      </c>
+      <c r="AW381">
+        <v>11</v>
+      </c>
+      <c r="AX381">
+        <v>6</v>
+      </c>
+      <c r="AY381">
+        <v>16</v>
+      </c>
+      <c r="AZ381">
+        <v>12</v>
+      </c>
+      <c r="BA381">
+        <v>5</v>
+      </c>
+      <c r="BB381">
+        <v>5</v>
+      </c>
+      <c r="BC381">
+        <v>10</v>
+      </c>
+      <c r="BD381">
+        <v>2.1</v>
+      </c>
+      <c r="BE381">
+        <v>6.5</v>
+      </c>
+      <c r="BF381">
+        <v>1.9</v>
+      </c>
+      <c r="BG381">
+        <v>1.26</v>
+      </c>
+      <c r="BH381">
+        <v>3.4</v>
+      </c>
+      <c r="BI381">
+        <v>1.44</v>
+      </c>
+      <c r="BJ381">
+        <v>2.55</v>
+      </c>
+      <c r="BK381">
+        <v>1.72</v>
+      </c>
+      <c r="BL381">
+        <v>1.98</v>
+      </c>
+      <c r="BM381">
+        <v>2.12</v>
+      </c>
+      <c r="BN381">
+        <v>1.63</v>
+      </c>
+      <c r="BO381">
+        <v>2.65</v>
+      </c>
+      <c r="BP381">
+        <v>1.41</v>
+      </c>
+    </row>
+    <row r="382" spans="1:68">
+      <c r="A382" s="1">
+        <v>381</v>
+      </c>
+      <c r="B382">
+        <v>7476927</v>
+      </c>
+      <c r="C382" t="s">
+        <v>68</v>
+      </c>
+      <c r="D382" t="s">
+        <v>69</v>
+      </c>
+      <c r="E382" s="2">
+        <v>45710.5</v>
+      </c>
+      <c r="F382">
+        <v>33</v>
+      </c>
+      <c r="G382" t="s">
+        <v>84</v>
+      </c>
+      <c r="H382" t="s">
+        <v>74</v>
+      </c>
+      <c r="I382">
+        <v>0</v>
+      </c>
+      <c r="J382">
+        <v>1</v>
+      </c>
+      <c r="K382">
+        <v>1</v>
+      </c>
+      <c r="L382">
+        <v>1</v>
+      </c>
+      <c r="M382">
+        <v>2</v>
+      </c>
+      <c r="N382">
+        <v>3</v>
+      </c>
+      <c r="O382" t="s">
+        <v>316</v>
+      </c>
+      <c r="P382" t="s">
+        <v>455</v>
+      </c>
+      <c r="Q382">
+        <v>4</v>
+      </c>
+      <c r="R382">
+        <v>2.25</v>
+      </c>
+      <c r="S382">
+        <v>2.63</v>
+      </c>
+      <c r="T382">
+        <v>1.36</v>
+      </c>
+      <c r="U382">
+        <v>3</v>
+      </c>
+      <c r="V382">
+        <v>2.63</v>
+      </c>
+      <c r="W382">
+        <v>1.44</v>
+      </c>
+      <c r="X382">
+        <v>7</v>
+      </c>
+      <c r="Y382">
+        <v>1.1</v>
+      </c>
+      <c r="Z382">
+        <v>3.77</v>
+      </c>
+      <c r="AA382">
+        <v>3.27</v>
+      </c>
+      <c r="AB382">
+        <v>2.01</v>
+      </c>
+      <c r="AC382">
+        <v>1.04</v>
+      </c>
+      <c r="AD382">
+        <v>12</v>
+      </c>
+      <c r="AE382">
+        <v>1.25</v>
+      </c>
+      <c r="AF382">
+        <v>3.75</v>
+      </c>
+      <c r="AG382">
+        <v>1.77</v>
+      </c>
+      <c r="AH382">
+        <v>1.98</v>
+      </c>
+      <c r="AI382">
+        <v>1.62</v>
+      </c>
+      <c r="AJ382">
+        <v>2.2</v>
+      </c>
+      <c r="AK382">
+        <v>1.8</v>
+      </c>
+      <c r="AL382">
+        <v>1.25</v>
+      </c>
+      <c r="AM382">
+        <v>1.3</v>
+      </c>
+      <c r="AN382">
+        <v>1.14</v>
+      </c>
+      <c r="AO382">
+        <v>1.69</v>
+      </c>
+      <c r="AP382">
+        <v>1.07</v>
+      </c>
+      <c r="AQ382">
+        <v>1.76</v>
+      </c>
+      <c r="AR382">
+        <v>1.2</v>
+      </c>
+      <c r="AS382">
+        <v>1.43</v>
+      </c>
+      <c r="AT382">
+        <v>2.63</v>
+      </c>
+      <c r="AU382">
+        <v>2</v>
+      </c>
+      <c r="AV382">
+        <v>3</v>
+      </c>
+      <c r="AW382">
+        <v>7</v>
+      </c>
+      <c r="AX382">
+        <v>5</v>
+      </c>
+      <c r="AY382">
+        <v>11</v>
+      </c>
+      <c r="AZ382">
+        <v>9</v>
+      </c>
+      <c r="BA382">
+        <v>4</v>
+      </c>
+      <c r="BB382">
+        <v>3</v>
+      </c>
+      <c r="BC382">
+        <v>7</v>
+      </c>
+      <c r="BD382">
+        <v>2.55</v>
+      </c>
+      <c r="BE382">
+        <v>6.75</v>
+      </c>
+      <c r="BF382">
+        <v>1.65</v>
+      </c>
+      <c r="BG382">
+        <v>1.23</v>
+      </c>
+      <c r="BH382">
+        <v>3.65</v>
+      </c>
+      <c r="BI382">
+        <v>1.41</v>
+      </c>
+      <c r="BJ382">
+        <v>2.65</v>
+      </c>
+      <c r="BK382">
+        <v>1.66</v>
+      </c>
+      <c r="BL382">
+        <v>2.07</v>
+      </c>
+      <c r="BM382">
+        <v>1.88</v>
+      </c>
+      <c r="BN382">
+        <v>1.92</v>
+      </c>
+      <c r="BO382">
+        <v>2.55</v>
+      </c>
+      <c r="BP382">
+        <v>1.43</v>
+      </c>
+    </row>
+    <row r="383" spans="1:68">
+      <c r="A383" s="1">
+        <v>382</v>
+      </c>
+      <c r="B383">
+        <v>7476928</v>
+      </c>
+      <c r="C383" t="s">
+        <v>68</v>
+      </c>
+      <c r="D383" t="s">
+        <v>69</v>
+      </c>
+      <c r="E383" s="2">
+        <v>45710.5</v>
+      </c>
+      <c r="F383">
+        <v>33</v>
+      </c>
+      <c r="G383" t="s">
+        <v>92</v>
+      </c>
+      <c r="H383" t="s">
+        <v>78</v>
+      </c>
+      <c r="I383">
+        <v>1</v>
+      </c>
+      <c r="J383">
+        <v>0</v>
+      </c>
+      <c r="K383">
+        <v>1</v>
+      </c>
+      <c r="L383">
+        <v>2</v>
+      </c>
+      <c r="M383">
+        <v>0</v>
+      </c>
+      <c r="N383">
+        <v>2</v>
+      </c>
+      <c r="O383" t="s">
+        <v>317</v>
+      </c>
+      <c r="P383" t="s">
+        <v>101</v>
+      </c>
+      <c r="Q383">
+        <v>2.5</v>
+      </c>
+      <c r="R383">
+        <v>2.2</v>
+      </c>
+      <c r="S383">
+        <v>4.5</v>
+      </c>
+      <c r="T383">
+        <v>1.4</v>
+      </c>
+      <c r="U383">
+        <v>2.75</v>
+      </c>
+      <c r="V383">
+        <v>2.75</v>
+      </c>
+      <c r="W383">
+        <v>1.4</v>
+      </c>
+      <c r="X383">
+        <v>8</v>
+      </c>
+      <c r="Y383">
+        <v>1.08</v>
+      </c>
+      <c r="Z383">
+        <v>1.83</v>
+      </c>
+      <c r="AA383">
+        <v>3.56</v>
+      </c>
+      <c r="AB383">
+        <v>4.1</v>
+      </c>
+      <c r="AC383">
+        <v>1.01</v>
+      </c>
+      <c r="AD383">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AE383">
+        <v>1.24</v>
+      </c>
+      <c r="AF383">
+        <v>3.36</v>
+      </c>
+      <c r="AG383">
+        <v>1.89</v>
+      </c>
+      <c r="AH383">
+        <v>1.85</v>
+      </c>
+      <c r="AI383">
+        <v>1.8</v>
+      </c>
+      <c r="AJ383">
+        <v>1.91</v>
+      </c>
+      <c r="AK383">
+        <v>1.2</v>
+      </c>
+      <c r="AL383">
+        <v>1.26</v>
+      </c>
+      <c r="AM383">
+        <v>1.99</v>
+      </c>
+      <c r="AN383">
+        <v>2.44</v>
+      </c>
+      <c r="AO383">
+        <v>1</v>
+      </c>
+      <c r="AP383">
+        <v>2.47</v>
+      </c>
+      <c r="AQ383">
+        <v>0.93</v>
+      </c>
+      <c r="AR383">
+        <v>1.43</v>
+      </c>
+      <c r="AS383">
+        <v>1.34</v>
+      </c>
+      <c r="AT383">
+        <v>2.77</v>
+      </c>
+      <c r="AU383">
+        <v>6</v>
+      </c>
+      <c r="AV383">
+        <v>4</v>
+      </c>
+      <c r="AW383">
+        <v>11</v>
+      </c>
+      <c r="AX383">
+        <v>2</v>
+      </c>
+      <c r="AY383">
+        <v>18</v>
+      </c>
+      <c r="AZ383">
+        <v>7</v>
+      </c>
+      <c r="BA383">
+        <v>3</v>
+      </c>
+      <c r="BB383">
+        <v>4</v>
+      </c>
+      <c r="BC383">
+        <v>7</v>
+      </c>
+      <c r="BD383">
+        <v>1.54</v>
+      </c>
+      <c r="BE383">
+        <v>6.4</v>
+      </c>
+      <c r="BF383">
+        <v>2.8</v>
+      </c>
+      <c r="BG383">
+        <v>1.41</v>
+      </c>
+      <c r="BH383">
+        <v>2.63</v>
+      </c>
+      <c r="BI383">
+        <v>1.71</v>
+      </c>
+      <c r="BJ383">
+        <v>2</v>
+      </c>
+      <c r="BK383">
+        <v>2</v>
+      </c>
+      <c r="BL383">
+        <v>1.8</v>
+      </c>
+      <c r="BM383">
+        <v>2.7</v>
+      </c>
+      <c r="BN383">
+        <v>1.38</v>
+      </c>
+      <c r="BO383">
+        <v>3.65</v>
+      </c>
+      <c r="BP383">
+        <v>1.23</v>
+      </c>
+    </row>
+    <row r="384" spans="1:68">
+      <c r="A384" s="1">
+        <v>383</v>
+      </c>
+      <c r="B384">
+        <v>7476933</v>
+      </c>
+      <c r="C384" t="s">
+        <v>68</v>
+      </c>
+      <c r="D384" t="s">
+        <v>69</v>
+      </c>
+      <c r="E384" s="2">
+        <v>45710.5</v>
+      </c>
+      <c r="F384">
+        <v>33</v>
+      </c>
+      <c r="G384" t="s">
+        <v>87</v>
+      </c>
+      <c r="H384" t="s">
+        <v>75</v>
+      </c>
+      <c r="I384">
+        <v>1</v>
+      </c>
+      <c r="J384">
+        <v>0</v>
+      </c>
+      <c r="K384">
+        <v>1</v>
+      </c>
+      <c r="L384">
+        <v>2</v>
+      </c>
+      <c r="M384">
+        <v>1</v>
+      </c>
+      <c r="N384">
+        <v>3</v>
+      </c>
+      <c r="O384" t="s">
+        <v>318</v>
+      </c>
+      <c r="P384" t="s">
+        <v>312</v>
+      </c>
+      <c r="Q384">
+        <v>3.1</v>
+      </c>
+      <c r="R384">
+        <v>2.25</v>
+      </c>
+      <c r="S384">
+        <v>3.2</v>
+      </c>
+      <c r="T384">
+        <v>1.33</v>
+      </c>
+      <c r="U384">
+        <v>3.25</v>
+      </c>
+      <c r="V384">
+        <v>2.63</v>
+      </c>
+      <c r="W384">
+        <v>1.44</v>
+      </c>
+      <c r="X384">
+        <v>6.5</v>
+      </c>
+      <c r="Y384">
+        <v>1.11</v>
+      </c>
+      <c r="Z384">
+        <v>2.51</v>
+      </c>
+      <c r="AA384">
+        <v>3.41</v>
+      </c>
+      <c r="AB384">
+        <v>2.64</v>
+      </c>
+      <c r="AC384">
+        <v>1.03</v>
+      </c>
+      <c r="AD384">
+        <v>13</v>
+      </c>
+      <c r="AE384">
+        <v>1.22</v>
+      </c>
+      <c r="AF384">
+        <v>4</v>
+      </c>
+      <c r="AG384">
+        <v>1.89</v>
+      </c>
+      <c r="AH384">
+        <v>1.85</v>
+      </c>
+      <c r="AI384">
+        <v>1.57</v>
+      </c>
+      <c r="AJ384">
+        <v>2.25</v>
+      </c>
+      <c r="AK384">
+        <v>1.5</v>
+      </c>
+      <c r="AL384">
+        <v>1.25</v>
+      </c>
+      <c r="AM384">
+        <v>1.53</v>
+      </c>
+      <c r="AN384">
+        <v>1.53</v>
+      </c>
+      <c r="AO384">
+        <v>1.07</v>
+      </c>
+      <c r="AP384">
+        <v>1.63</v>
+      </c>
+      <c r="AQ384">
+        <v>1</v>
+      </c>
+      <c r="AR384">
+        <v>1.41</v>
+      </c>
+      <c r="AS384">
+        <v>1.18</v>
+      </c>
+      <c r="AT384">
+        <v>2.59</v>
+      </c>
+      <c r="AU384">
+        <v>5</v>
+      </c>
+      <c r="AV384">
+        <v>5</v>
+      </c>
+      <c r="AW384">
+        <v>7</v>
+      </c>
+      <c r="AX384">
+        <v>6</v>
+      </c>
+      <c r="AY384">
+        <v>16</v>
+      </c>
+      <c r="AZ384">
+        <v>12</v>
+      </c>
+      <c r="BA384">
+        <v>7</v>
+      </c>
+      <c r="BB384">
+        <v>3</v>
+      </c>
+      <c r="BC384">
+        <v>10</v>
+      </c>
+      <c r="BD384">
+        <v>1.97</v>
+      </c>
+      <c r="BE384">
+        <v>6.75</v>
+      </c>
+      <c r="BF384">
+        <v>1.98</v>
+      </c>
+      <c r="BG384">
+        <v>1.18</v>
+      </c>
+      <c r="BH384">
+        <v>4</v>
+      </c>
+      <c r="BI384">
+        <v>1.34</v>
+      </c>
+      <c r="BJ384">
+        <v>2.9</v>
+      </c>
+      <c r="BK384">
+        <v>1.56</v>
+      </c>
+      <c r="BL384">
+        <v>2.23</v>
+      </c>
+      <c r="BM384">
+        <v>1.89</v>
+      </c>
+      <c r="BN384">
+        <v>1.8</v>
+      </c>
+      <c r="BO384">
+        <v>2.33</v>
+      </c>
+      <c r="BP384">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="385" spans="1:68">
+      <c r="A385" s="1">
+        <v>384</v>
+      </c>
+      <c r="B385">
+        <v>7476930</v>
+      </c>
+      <c r="C385" t="s">
+        <v>68</v>
+      </c>
+      <c r="D385" t="s">
+        <v>69</v>
+      </c>
+      <c r="E385" s="2">
+        <v>45710.5</v>
+      </c>
+      <c r="F385">
+        <v>33</v>
+      </c>
+      <c r="G385" t="s">
+        <v>82</v>
+      </c>
+      <c r="H385" t="s">
+        <v>76</v>
+      </c>
+      <c r="I385">
+        <v>0</v>
+      </c>
+      <c r="J385">
+        <v>0</v>
+      </c>
+      <c r="K385">
+        <v>0</v>
+      </c>
+      <c r="L385">
+        <v>0</v>
+      </c>
+      <c r="M385">
+        <v>0</v>
+      </c>
+      <c r="N385">
+        <v>0</v>
+      </c>
+      <c r="O385" t="s">
+        <v>101</v>
+      </c>
+      <c r="P385" t="s">
+        <v>101</v>
+      </c>
+      <c r="Q385">
+        <v>3.4</v>
+      </c>
+      <c r="R385">
+        <v>1.95</v>
+      </c>
+      <c r="S385">
+        <v>3.5</v>
+      </c>
+      <c r="T385">
+        <v>1.53</v>
+      </c>
+      <c r="U385">
+        <v>2.38</v>
+      </c>
+      <c r="V385">
+        <v>3.5</v>
+      </c>
+      <c r="W385">
+        <v>1.29</v>
+      </c>
+      <c r="X385">
+        <v>11</v>
+      </c>
+      <c r="Y385">
+        <v>1.05</v>
+      </c>
+      <c r="Z385">
+        <v>2.58</v>
+      </c>
+      <c r="AA385">
+        <v>3.21</v>
+      </c>
+      <c r="AB385">
+        <v>2.69</v>
+      </c>
+      <c r="AC385">
+        <v>1.03</v>
+      </c>
+      <c r="AD385">
+        <v>7.2</v>
+      </c>
+      <c r="AE385">
+        <v>1.39</v>
+      </c>
+      <c r="AF385">
+        <v>2.6</v>
+      </c>
+      <c r="AG385">
+        <v>2.3</v>
+      </c>
+      <c r="AH385">
+        <v>1.57</v>
+      </c>
+      <c r="AI385">
+        <v>2</v>
+      </c>
+      <c r="AJ385">
+        <v>1.73</v>
+      </c>
+      <c r="AK385">
+        <v>1.43</v>
+      </c>
+      <c r="AL385">
+        <v>1.33</v>
+      </c>
+      <c r="AM385">
+        <v>1.46</v>
+      </c>
+      <c r="AN385">
+        <v>0.67</v>
+      </c>
+      <c r="AO385">
+        <v>0.93</v>
+      </c>
+      <c r="AP385">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="AQ385">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="AR385">
+        <v>1.36</v>
+      </c>
+      <c r="AS385">
+        <v>1.05</v>
+      </c>
+      <c r="AT385">
+        <v>2.41</v>
+      </c>
+      <c r="AU385">
+        <v>6</v>
+      </c>
+      <c r="AV385">
+        <v>4</v>
+      </c>
+      <c r="AW385">
+        <v>10</v>
+      </c>
+      <c r="AX385">
+        <v>10</v>
+      </c>
+      <c r="AY385">
+        <v>16</v>
+      </c>
+      <c r="AZ385">
+        <v>14</v>
+      </c>
+      <c r="BA385">
+        <v>6</v>
+      </c>
+      <c r="BB385">
+        <v>3</v>
+      </c>
+      <c r="BC385">
+        <v>9</v>
+      </c>
+      <c r="BD385">
+        <v>1.97</v>
+      </c>
+      <c r="BE385">
+        <v>6.25</v>
+      </c>
+      <c r="BF385">
+        <v>2.05</v>
+      </c>
+      <c r="BG385">
+        <v>1.41</v>
+      </c>
+      <c r="BH385">
+        <v>2.65</v>
+      </c>
+      <c r="BI385">
+        <v>1.68</v>
+      </c>
+      <c r="BJ385">
+        <v>2.04</v>
+      </c>
+      <c r="BK385">
+        <v>1.92</v>
+      </c>
+      <c r="BL385">
+        <v>1.88</v>
+      </c>
+      <c r="BM385">
+        <v>2.65</v>
+      </c>
+      <c r="BN385">
+        <v>1.4</v>
+      </c>
+      <c r="BO385">
+        <v>3.55</v>
+      </c>
+      <c r="BP385">
+        <v>1.24</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/England EFL League Two_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/England EFL League Two_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2372" uniqueCount="456">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2396" uniqueCount="459">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -973,6 +973,12 @@
     <t>['23', '64']</t>
   </si>
   <si>
+    <t>['39']</t>
+  </si>
+  <si>
+    <t>['90', '90+3']</t>
+  </si>
+  <si>
     <t>['1', '9']</t>
   </si>
   <si>
@@ -1082,9 +1088,6 @@
   </si>
   <si>
     <t>['25', '51', '57', '67', '85', '90+4']</t>
-  </si>
-  <si>
-    <t>['39']</t>
   </si>
   <si>
     <t>['10', '34']</t>
@@ -1382,6 +1385,12 @@
   </si>
   <si>
     <t>['2', '61']</t>
+  </si>
+  <si>
+    <t>['45', '50']</t>
+  </si>
+  <si>
+    <t>['1', '79']</t>
   </si>
 </sst>
 </file>
@@ -1743,7 +1752,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP385"/>
+  <dimension ref="A1:BP389"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -2205,7 +2214,7 @@
         <v>95</v>
       </c>
       <c r="P3" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="Q3">
         <v>2.5</v>
@@ -2617,7 +2626,7 @@
         <v>97</v>
       </c>
       <c r="P5" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="Q5">
         <v>2.4</v>
@@ -2695,7 +2704,7 @@
         <v>0</v>
       </c>
       <c r="AP5">
-        <v>1.88</v>
+        <v>1.82</v>
       </c>
       <c r="AQ5">
         <v>0.8100000000000001</v>
@@ -2904,7 +2913,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ6">
-        <v>0.88</v>
+        <v>1</v>
       </c>
       <c r="AR6">
         <v>0</v>
@@ -3313,7 +3322,7 @@
         <v>0</v>
       </c>
       <c r="AP8">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AQ8">
         <v>0.75</v>
@@ -3441,7 +3450,7 @@
         <v>101</v>
       </c>
       <c r="P9" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="Q9">
         <v>2.75</v>
@@ -3647,7 +3656,7 @@
         <v>102</v>
       </c>
       <c r="P10" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="Q10">
         <v>2.63</v>
@@ -3728,7 +3737,7 @@
         <v>1.47</v>
       </c>
       <c r="AQ10">
-        <v>1</v>
+        <v>1.13</v>
       </c>
       <c r="AR10">
         <v>0</v>
@@ -3853,7 +3862,7 @@
         <v>101</v>
       </c>
       <c r="P11" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="Q11">
         <v>2.88</v>
@@ -4137,7 +4146,7 @@
         <v>0</v>
       </c>
       <c r="AP12">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="AQ12">
         <v>1.63</v>
@@ -4755,7 +4764,7 @@
         <v>0</v>
       </c>
       <c r="AP15">
-        <v>1.31</v>
+        <v>1.24</v>
       </c>
       <c r="AQ15">
         <v>1.31</v>
@@ -4883,7 +4892,7 @@
         <v>105</v>
       </c>
       <c r="P16" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="Q16">
         <v>2.88</v>
@@ -5295,7 +5304,7 @@
         <v>101</v>
       </c>
       <c r="P18" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="Q18">
         <v>3.4</v>
@@ -5501,7 +5510,7 @@
         <v>107</v>
       </c>
       <c r="P19" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="Q19">
         <v>3</v>
@@ -6325,7 +6334,7 @@
         <v>101</v>
       </c>
       <c r="P23" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="Q23">
         <v>3</v>
@@ -6406,7 +6415,7 @@
         <v>1.56</v>
       </c>
       <c r="AQ23">
-        <v>1.73</v>
+        <v>1.69</v>
       </c>
       <c r="AR23">
         <v>0</v>
@@ -6737,7 +6746,7 @@
         <v>109</v>
       </c>
       <c r="P25" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="Q25">
         <v>2.63</v>
@@ -6818,7 +6827,7 @@
         <v>1.94</v>
       </c>
       <c r="AQ25">
-        <v>1</v>
+        <v>1.13</v>
       </c>
       <c r="AR25">
         <v>0</v>
@@ -6943,7 +6952,7 @@
         <v>110</v>
       </c>
       <c r="P26" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="Q26">
         <v>2.38</v>
@@ -7227,10 +7236,10 @@
         <v>3</v>
       </c>
       <c r="AP27">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="AQ27">
-        <v>1.73</v>
+        <v>1.69</v>
       </c>
       <c r="AR27">
         <v>0.86</v>
@@ -7767,7 +7776,7 @@
         <v>112</v>
       </c>
       <c r="P30" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="Q30">
         <v>3</v>
@@ -7848,7 +7857,7 @@
         <v>1.69</v>
       </c>
       <c r="AQ30">
-        <v>0.88</v>
+        <v>1</v>
       </c>
       <c r="AR30">
         <v>0</v>
@@ -8669,7 +8678,7 @@
         <v>0</v>
       </c>
       <c r="AP34">
-        <v>1.88</v>
+        <v>1.82</v>
       </c>
       <c r="AQ34">
         <v>1.31</v>
@@ -9209,7 +9218,7 @@
         <v>101</v>
       </c>
       <c r="P37" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="Q37">
         <v>2.6</v>
@@ -9415,7 +9424,7 @@
         <v>117</v>
       </c>
       <c r="P38" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="Q38">
         <v>2.88</v>
@@ -9699,7 +9708,7 @@
         <v>3</v>
       </c>
       <c r="AP39">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AQ39">
         <v>1.06</v>
@@ -9827,7 +9836,7 @@
         <v>119</v>
       </c>
       <c r="P40" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="Q40">
         <v>3</v>
@@ -10239,7 +10248,7 @@
         <v>101</v>
       </c>
       <c r="P42" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="Q42">
         <v>3.75</v>
@@ -10651,7 +10660,7 @@
         <v>121</v>
       </c>
       <c r="P44" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="Q44">
         <v>2.75</v>
@@ -10857,7 +10866,7 @@
         <v>122</v>
       </c>
       <c r="P45" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="Q45">
         <v>2.63</v>
@@ -10935,7 +10944,7 @@
         <v>0</v>
       </c>
       <c r="AP45">
-        <v>1.31</v>
+        <v>1.24</v>
       </c>
       <c r="AQ45">
         <v>1.35</v>
@@ -11350,7 +11359,7 @@
         <v>2.25</v>
       </c>
       <c r="AQ47">
-        <v>1</v>
+        <v>1.13</v>
       </c>
       <c r="AR47">
         <v>1.5</v>
@@ -11475,7 +11484,7 @@
         <v>125</v>
       </c>
       <c r="P48" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="Q48">
         <v>3.5</v>
@@ -11556,7 +11565,7 @@
         <v>1.63</v>
       </c>
       <c r="AQ48">
-        <v>1</v>
+        <v>1.13</v>
       </c>
       <c r="AR48">
         <v>1.43</v>
@@ -11887,7 +11896,7 @@
         <v>127</v>
       </c>
       <c r="P50" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="Q50">
         <v>3.6</v>
@@ -12093,7 +12102,7 @@
         <v>103</v>
       </c>
       <c r="P51" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="Q51">
         <v>2.5</v>
@@ -12377,7 +12386,7 @@
         <v>2</v>
       </c>
       <c r="AP52">
-        <v>1.88</v>
+        <v>1.82</v>
       </c>
       <c r="AQ52">
         <v>0.76</v>
@@ -13616,7 +13625,7 @@
         <v>1.47</v>
       </c>
       <c r="AQ58">
-        <v>1.73</v>
+        <v>1.69</v>
       </c>
       <c r="AR58">
         <v>1.63</v>
@@ -13822,7 +13831,7 @@
         <v>1.94</v>
       </c>
       <c r="AQ59">
-        <v>0.88</v>
+        <v>1</v>
       </c>
       <c r="AR59">
         <v>1.79</v>
@@ -14771,7 +14780,7 @@
         <v>139</v>
       </c>
       <c r="P64" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="Q64">
         <v>3</v>
@@ -14852,7 +14861,7 @@
         <v>2.35</v>
       </c>
       <c r="AQ64">
-        <v>1</v>
+        <v>1.13</v>
       </c>
       <c r="AR64">
         <v>1.57</v>
@@ -15183,7 +15192,7 @@
         <v>141</v>
       </c>
       <c r="P66" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="Q66">
         <v>3.75</v>
@@ -15467,7 +15476,7 @@
         <v>2</v>
       </c>
       <c r="AP67">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AQ67">
         <v>0.5</v>
@@ -15801,7 +15810,7 @@
         <v>143</v>
       </c>
       <c r="P69" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="Q69">
         <v>3.2</v>
@@ -15879,7 +15888,7 @@
         <v>2</v>
       </c>
       <c r="AP69">
-        <v>1.31</v>
+        <v>1.24</v>
       </c>
       <c r="AQ69">
         <v>1.63</v>
@@ -16007,7 +16016,7 @@
         <v>144</v>
       </c>
       <c r="P70" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="Q70">
         <v>3.25</v>
@@ -16213,7 +16222,7 @@
         <v>145</v>
       </c>
       <c r="P71" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="Q71">
         <v>3</v>
@@ -16294,7 +16303,7 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="AQ71">
-        <v>1</v>
+        <v>1.13</v>
       </c>
       <c r="AR71">
         <v>1.35</v>
@@ -16419,7 +16428,7 @@
         <v>146</v>
       </c>
       <c r="P72" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="Q72">
         <v>4</v>
@@ -16831,7 +16840,7 @@
         <v>101</v>
       </c>
       <c r="P74" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="Q74">
         <v>2.63</v>
@@ -17037,7 +17046,7 @@
         <v>101</v>
       </c>
       <c r="P75" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="Q75">
         <v>3.4</v>
@@ -17118,7 +17127,7 @@
         <v>1.81</v>
       </c>
       <c r="AQ75">
-        <v>1.73</v>
+        <v>1.69</v>
       </c>
       <c r="AR75">
         <v>1.26</v>
@@ -17243,7 +17252,7 @@
         <v>101</v>
       </c>
       <c r="P76" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="Q76">
         <v>2.6</v>
@@ -17655,7 +17664,7 @@
         <v>149</v>
       </c>
       <c r="P78" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="Q78">
         <v>2.88</v>
@@ -18685,7 +18694,7 @@
         <v>153</v>
       </c>
       <c r="P83" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="Q83">
         <v>2.2</v>
@@ -18969,7 +18978,7 @@
         <v>1</v>
       </c>
       <c r="AP84">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="AQ84">
         <v>1.19</v>
@@ -19384,7 +19393,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ86">
-        <v>1</v>
+        <v>1.13</v>
       </c>
       <c r="AR86">
         <v>1.1</v>
@@ -19921,7 +19930,7 @@
         <v>157</v>
       </c>
       <c r="P89" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="Q89">
         <v>3.75</v>
@@ -20205,7 +20214,7 @@
         <v>0</v>
       </c>
       <c r="AP90">
-        <v>1.31</v>
+        <v>1.24</v>
       </c>
       <c r="AQ90">
         <v>0.93</v>
@@ -20333,7 +20342,7 @@
         <v>101</v>
       </c>
       <c r="P91" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="Q91">
         <v>2.75</v>
@@ -20539,7 +20548,7 @@
         <v>101</v>
       </c>
       <c r="P92" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="Q92">
         <v>3.4</v>
@@ -20617,10 +20626,10 @@
         <v>1.33</v>
       </c>
       <c r="AP92">
-        <v>1.88</v>
+        <v>1.82</v>
       </c>
       <c r="AQ92">
-        <v>1</v>
+        <v>1.13</v>
       </c>
       <c r="AR92">
         <v>1.26</v>
@@ -20745,7 +20754,7 @@
         <v>159</v>
       </c>
       <c r="P93" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="Q93">
         <v>2.75</v>
@@ -21029,7 +21038,7 @@
         <v>2</v>
       </c>
       <c r="AP94">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AQ94">
         <v>0.5600000000000001</v>
@@ -21157,7 +21166,7 @@
         <v>161</v>
       </c>
       <c r="P95" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="Q95">
         <v>2.5</v>
@@ -21363,7 +21372,7 @@
         <v>162</v>
       </c>
       <c r="P96" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="Q96">
         <v>4.5</v>
@@ -21647,7 +21656,7 @@
         <v>0.75</v>
       </c>
       <c r="AP97">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="AQ97">
         <v>0.9399999999999999</v>
@@ -22062,7 +22071,7 @@
         <v>0.75</v>
       </c>
       <c r="AQ99">
-        <v>1</v>
+        <v>1.13</v>
       </c>
       <c r="AR99">
         <v>1.37</v>
@@ -22187,7 +22196,7 @@
         <v>166</v>
       </c>
       <c r="P100" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="Q100">
         <v>2.75</v>
@@ -22268,7 +22277,7 @@
         <v>2.35</v>
       </c>
       <c r="AQ100">
-        <v>1</v>
+        <v>1.13</v>
       </c>
       <c r="AR100">
         <v>1.61</v>
@@ -22471,7 +22480,7 @@
         <v>0.75</v>
       </c>
       <c r="AP101">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AQ101">
         <v>1.56</v>
@@ -22599,7 +22608,7 @@
         <v>167</v>
       </c>
       <c r="P102" t="s">
-        <v>356</v>
+        <v>319</v>
       </c>
       <c r="Q102">
         <v>2.88</v>
@@ -22677,10 +22686,10 @@
         <v>0</v>
       </c>
       <c r="AP102">
-        <v>1.88</v>
+        <v>1.82</v>
       </c>
       <c r="AQ102">
-        <v>0.88</v>
+        <v>1</v>
       </c>
       <c r="AR102">
         <v>1.14</v>
@@ -22805,7 +22814,7 @@
         <v>101</v>
       </c>
       <c r="P103" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="Q103">
         <v>3</v>
@@ -23011,7 +23020,7 @@
         <v>168</v>
       </c>
       <c r="P104" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="Q104">
         <v>4</v>
@@ -23089,7 +23098,7 @@
         <v>1.5</v>
       </c>
       <c r="AP104">
-        <v>1.31</v>
+        <v>1.24</v>
       </c>
       <c r="AQ104">
         <v>1.06</v>
@@ -23423,7 +23432,7 @@
         <v>101</v>
       </c>
       <c r="P106" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="Q106">
         <v>3.6</v>
@@ -24865,7 +24874,7 @@
         <v>172</v>
       </c>
       <c r="P113" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="Q113">
         <v>2.6</v>
@@ -24946,7 +24955,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ113">
-        <v>1.73</v>
+        <v>1.69</v>
       </c>
       <c r="AR113">
         <v>1.34</v>
@@ -25071,7 +25080,7 @@
         <v>173</v>
       </c>
       <c r="P114" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="Q114">
         <v>2.4</v>
@@ -25895,7 +25904,7 @@
         <v>176</v>
       </c>
       <c r="P118" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="Q118">
         <v>2.5</v>
@@ -26101,7 +26110,7 @@
         <v>101</v>
       </c>
       <c r="P119" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="Q119">
         <v>3.4</v>
@@ -26179,10 +26188,10 @@
         <v>0.8</v>
       </c>
       <c r="AP119">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="AQ119">
-        <v>1</v>
+        <v>1.13</v>
       </c>
       <c r="AR119">
         <v>1.15</v>
@@ -26307,7 +26316,7 @@
         <v>94</v>
       </c>
       <c r="P120" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="Q120">
         <v>2.88</v>
@@ -26925,7 +26934,7 @@
         <v>178</v>
       </c>
       <c r="P123" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="Q123">
         <v>2.38</v>
@@ -27003,10 +27012,10 @@
         <v>0</v>
       </c>
       <c r="AP123">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AQ123">
-        <v>0.88</v>
+        <v>1</v>
       </c>
       <c r="AR123">
         <v>1.25</v>
@@ -27337,7 +27346,7 @@
         <v>101</v>
       </c>
       <c r="P125" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="Q125">
         <v>2.1</v>
@@ -27749,7 +27758,7 @@
         <v>180</v>
       </c>
       <c r="P127" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="Q127">
         <v>3.25</v>
@@ -27827,7 +27836,7 @@
         <v>0.8</v>
       </c>
       <c r="AP127">
-        <v>1.88</v>
+        <v>1.82</v>
       </c>
       <c r="AQ127">
         <v>0.9399999999999999</v>
@@ -27955,7 +27964,7 @@
         <v>101</v>
       </c>
       <c r="P128" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="Q128">
         <v>4.75</v>
@@ -28573,7 +28582,7 @@
         <v>182</v>
       </c>
       <c r="P131" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="Q131">
         <v>2.63</v>
@@ -28654,7 +28663,7 @@
         <v>1.93</v>
       </c>
       <c r="AQ131">
-        <v>1</v>
+        <v>1.13</v>
       </c>
       <c r="AR131">
         <v>1.51</v>
@@ -28779,7 +28788,7 @@
         <v>183</v>
       </c>
       <c r="P132" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="Q132">
         <v>3.5</v>
@@ -29191,7 +29200,7 @@
         <v>185</v>
       </c>
       <c r="P134" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="Q134">
         <v>4</v>
@@ -29397,7 +29406,7 @@
         <v>147</v>
       </c>
       <c r="P135" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="Q135">
         <v>2.6</v>
@@ -29603,7 +29612,7 @@
         <v>186</v>
       </c>
       <c r="P136" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="Q136">
         <v>3.6</v>
@@ -29684,7 +29693,7 @@
         <v>1.63</v>
       </c>
       <c r="AQ136">
-        <v>1.73</v>
+        <v>1.69</v>
       </c>
       <c r="AR136">
         <v>1.16</v>
@@ -29809,7 +29818,7 @@
         <v>187</v>
       </c>
       <c r="P137" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="Q137">
         <v>3</v>
@@ -29887,7 +29896,7 @@
         <v>1</v>
       </c>
       <c r="AP137">
-        <v>1.31</v>
+        <v>1.24</v>
       </c>
       <c r="AQ137">
         <v>0.5</v>
@@ -30221,7 +30230,7 @@
         <v>185</v>
       </c>
       <c r="P139" t="s">
-        <v>356</v>
+        <v>319</v>
       </c>
       <c r="Q139">
         <v>2.5</v>
@@ -30427,7 +30436,7 @@
         <v>189</v>
       </c>
       <c r="P140" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="Q140">
         <v>2.25</v>
@@ -30920,7 +30929,7 @@
         <v>1.47</v>
       </c>
       <c r="AQ142">
-        <v>0.88</v>
+        <v>1</v>
       </c>
       <c r="AR142">
         <v>1.27</v>
@@ -31251,7 +31260,7 @@
         <v>101</v>
       </c>
       <c r="P144" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="Q144">
         <v>2.25</v>
@@ -31329,7 +31338,7 @@
         <v>0.5</v>
       </c>
       <c r="AP144">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AQ144">
         <v>0.8100000000000001</v>
@@ -31869,7 +31878,7 @@
         <v>101</v>
       </c>
       <c r="P147" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="Q147">
         <v>3</v>
@@ -31947,7 +31956,7 @@
         <v>1.5</v>
       </c>
       <c r="AP147">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="AQ147">
         <v>1.56</v>
@@ -32153,10 +32162,10 @@
         <v>1.17</v>
       </c>
       <c r="AP148">
-        <v>1.88</v>
+        <v>1.82</v>
       </c>
       <c r="AQ148">
-        <v>1</v>
+        <v>1.13</v>
       </c>
       <c r="AR148">
         <v>1.26</v>
@@ -32693,7 +32702,7 @@
         <v>193</v>
       </c>
       <c r="P151" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="Q151">
         <v>2.4</v>
@@ -32899,7 +32908,7 @@
         <v>194</v>
       </c>
       <c r="P152" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="Q152">
         <v>4.5</v>
@@ -33105,7 +33114,7 @@
         <v>195</v>
       </c>
       <c r="P153" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="Q153">
         <v>2.75</v>
@@ -33517,7 +33526,7 @@
         <v>197</v>
       </c>
       <c r="P155" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="Q155">
         <v>3</v>
@@ -33804,7 +33813,7 @@
         <v>1.69</v>
       </c>
       <c r="AQ156">
-        <v>1</v>
+        <v>1.13</v>
       </c>
       <c r="AR156">
         <v>1.14</v>
@@ -33929,7 +33938,7 @@
         <v>198</v>
       </c>
       <c r="P157" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="Q157">
         <v>3.4</v>
@@ -34547,7 +34556,7 @@
         <v>200</v>
       </c>
       <c r="P160" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="Q160">
         <v>3.2</v>
@@ -34834,7 +34843,7 @@
         <v>1.07</v>
       </c>
       <c r="AQ161">
-        <v>1.73</v>
+        <v>1.69</v>
       </c>
       <c r="AR161">
         <v>1.36</v>
@@ -35243,7 +35252,7 @@
         <v>1</v>
       </c>
       <c r="AP163">
-        <v>1.31</v>
+        <v>1.24</v>
       </c>
       <c r="AQ163">
         <v>0.5600000000000001</v>
@@ -35371,7 +35380,7 @@
         <v>203</v>
       </c>
       <c r="P164" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="Q164">
         <v>2.4</v>
@@ -35783,7 +35792,7 @@
         <v>204</v>
       </c>
       <c r="P166" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="Q166">
         <v>2.88</v>
@@ -36067,7 +36076,7 @@
         <v>2.29</v>
       </c>
       <c r="AP167">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AQ167">
         <v>1.63</v>
@@ -36195,7 +36204,7 @@
         <v>206</v>
       </c>
       <c r="P168" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="Q168">
         <v>2.3</v>
@@ -36479,7 +36488,7 @@
         <v>0.86</v>
       </c>
       <c r="AP169">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="AQ169">
         <v>0.8100000000000001</v>
@@ -36607,7 +36616,7 @@
         <v>208</v>
       </c>
       <c r="P170" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="Q170">
         <v>2.5</v>
@@ -36894,7 +36903,7 @@
         <v>1.53</v>
       </c>
       <c r="AQ171">
-        <v>1</v>
+        <v>1.13</v>
       </c>
       <c r="AR171">
         <v>1.56</v>
@@ -37225,7 +37234,7 @@
         <v>101</v>
       </c>
       <c r="P173" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="Q173">
         <v>2.1</v>
@@ -37306,7 +37315,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ173">
-        <v>0.88</v>
+        <v>1</v>
       </c>
       <c r="AR173">
         <v>1.48</v>
@@ -37431,7 +37440,7 @@
         <v>148</v>
       </c>
       <c r="P174" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="Q174">
         <v>3.2</v>
@@ -37509,7 +37518,7 @@
         <v>1.33</v>
       </c>
       <c r="AP174">
-        <v>1.88</v>
+        <v>1.82</v>
       </c>
       <c r="AQ174">
         <v>1.5</v>
@@ -38461,7 +38470,7 @@
         <v>210</v>
       </c>
       <c r="P179" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="Q179">
         <v>2.3</v>
@@ -39363,7 +39372,7 @@
         <v>0.88</v>
       </c>
       <c r="AP183">
-        <v>1.31</v>
+        <v>1.24</v>
       </c>
       <c r="AQ183">
         <v>0.75</v>
@@ -39491,7 +39500,7 @@
         <v>185</v>
       </c>
       <c r="P184" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="Q184">
         <v>3.4</v>
@@ -39697,7 +39706,7 @@
         <v>215</v>
       </c>
       <c r="P185" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="Q185">
         <v>3.2</v>
@@ -39984,7 +39993,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ186">
-        <v>1</v>
+        <v>1.13</v>
       </c>
       <c r="AR186">
         <v>1.66</v>
@@ -40109,7 +40118,7 @@
         <v>217</v>
       </c>
       <c r="P187" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="Q187">
         <v>2.2</v>
@@ -40190,7 +40199,7 @@
         <v>2.25</v>
       </c>
       <c r="AQ187">
-        <v>0.88</v>
+        <v>1</v>
       </c>
       <c r="AR187">
         <v>1.62</v>
@@ -40393,7 +40402,7 @@
         <v>1.14</v>
       </c>
       <c r="AP188">
-        <v>1.88</v>
+        <v>1.82</v>
       </c>
       <c r="AQ188">
         <v>0.5</v>
@@ -40727,7 +40736,7 @@
         <v>101</v>
       </c>
       <c r="P190" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="Q190">
         <v>3.25</v>
@@ -40933,7 +40942,7 @@
         <v>148</v>
       </c>
       <c r="P191" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="Q191">
         <v>2.3</v>
@@ -41011,7 +41020,7 @@
         <v>0.86</v>
       </c>
       <c r="AP191">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AQ191">
         <v>0.76</v>
@@ -41139,7 +41148,7 @@
         <v>219</v>
       </c>
       <c r="P192" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="Q192">
         <v>2.4</v>
@@ -41426,7 +41435,7 @@
         <v>2.25</v>
       </c>
       <c r="AQ193">
-        <v>1.73</v>
+        <v>1.69</v>
       </c>
       <c r="AR193">
         <v>1.56</v>
@@ -42169,7 +42178,7 @@
         <v>101</v>
       </c>
       <c r="P197" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="Q197">
         <v>3.75</v>
@@ -42247,7 +42256,7 @@
         <v>1</v>
       </c>
       <c r="AP197">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="AQ197">
         <v>1.31</v>
@@ -42375,7 +42384,7 @@
         <v>221</v>
       </c>
       <c r="P198" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="Q198">
         <v>2.2</v>
@@ -42581,7 +42590,7 @@
         <v>122</v>
       </c>
       <c r="P199" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="Q199">
         <v>3.4</v>
@@ -42993,7 +43002,7 @@
         <v>222</v>
       </c>
       <c r="P201" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="Q201">
         <v>2.85</v>
@@ -43074,7 +43083,7 @@
         <v>1.63</v>
       </c>
       <c r="AQ201">
-        <v>0.88</v>
+        <v>1</v>
       </c>
       <c r="AR201">
         <v>1.24</v>
@@ -43199,7 +43208,7 @@
         <v>223</v>
       </c>
       <c r="P202" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="Q202">
         <v>1.8</v>
@@ -43611,7 +43620,7 @@
         <v>224</v>
       </c>
       <c r="P204" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="Q204">
         <v>3.55</v>
@@ -43689,7 +43698,7 @@
         <v>2.11</v>
       </c>
       <c r="AP204">
-        <v>1.88</v>
+        <v>1.82</v>
       </c>
       <c r="AQ204">
         <v>1.63</v>
@@ -44435,7 +44444,7 @@
         <v>228</v>
       </c>
       <c r="P208" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="Q208">
         <v>2.4</v>
@@ -44513,7 +44522,7 @@
         <v>1.11</v>
       </c>
       <c r="AP208">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="AQ208">
         <v>0.82</v>
@@ -44641,7 +44650,7 @@
         <v>229</v>
       </c>
       <c r="P209" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="Q209">
         <v>2.5</v>
@@ -44925,7 +44934,7 @@
         <v>1.14</v>
       </c>
       <c r="AP210">
-        <v>1.31</v>
+        <v>1.24</v>
       </c>
       <c r="AQ210">
         <v>0.9399999999999999</v>
@@ -45053,7 +45062,7 @@
         <v>231</v>
       </c>
       <c r="P211" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="Q211">
         <v>3.5</v>
@@ -45340,7 +45349,7 @@
         <v>1.81</v>
       </c>
       <c r="AQ212">
-        <v>1</v>
+        <v>1.13</v>
       </c>
       <c r="AR212">
         <v>1.19</v>
@@ -45546,7 +45555,7 @@
         <v>1.93</v>
       </c>
       <c r="AQ213">
-        <v>1.73</v>
+        <v>1.69</v>
       </c>
       <c r="AR213">
         <v>1.25</v>
@@ -45877,7 +45886,7 @@
         <v>101</v>
       </c>
       <c r="P215" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="Q215">
         <v>4.33</v>
@@ -46083,7 +46092,7 @@
         <v>234</v>
       </c>
       <c r="P216" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="Q216">
         <v>3</v>
@@ -46289,7 +46298,7 @@
         <v>235</v>
       </c>
       <c r="P217" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="Q217">
         <v>0</v>
@@ -46576,7 +46585,7 @@
         <v>1.56</v>
       </c>
       <c r="AQ218">
-        <v>1</v>
+        <v>1.13</v>
       </c>
       <c r="AR218">
         <v>1.22</v>
@@ -46701,7 +46710,7 @@
         <v>101</v>
       </c>
       <c r="P219" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="Q219">
         <v>3.2</v>
@@ -46985,7 +46994,7 @@
         <v>1.13</v>
       </c>
       <c r="AP220">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AQ220">
         <v>1.19</v>
@@ -47191,7 +47200,7 @@
         <v>1</v>
       </c>
       <c r="AP221">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="AQ221">
         <v>0.76</v>
@@ -47525,7 +47534,7 @@
         <v>101</v>
       </c>
       <c r="P223" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="Q223">
         <v>3.75</v>
@@ -47731,7 +47740,7 @@
         <v>101</v>
       </c>
       <c r="P224" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="Q224">
         <v>3.4</v>
@@ -48839,7 +48848,7 @@
         <v>2</v>
       </c>
       <c r="AP229">
-        <v>1.31</v>
+        <v>1.24</v>
       </c>
       <c r="AQ229">
         <v>1.63</v>
@@ -48967,7 +48976,7 @@
         <v>101</v>
       </c>
       <c r="P230" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="Q230">
         <v>2.5</v>
@@ -49251,7 +49260,7 @@
         <v>1.1</v>
       </c>
       <c r="AP231">
-        <v>1.88</v>
+        <v>1.82</v>
       </c>
       <c r="AQ231">
         <v>0.82</v>
@@ -49379,7 +49388,7 @@
         <v>240</v>
       </c>
       <c r="P232" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="Q232">
         <v>2.4</v>
@@ -49460,7 +49469,7 @@
         <v>1.53</v>
       </c>
       <c r="AQ232">
-        <v>0.88</v>
+        <v>1</v>
       </c>
       <c r="AR232">
         <v>1.34</v>
@@ -49585,7 +49594,7 @@
         <v>241</v>
       </c>
       <c r="P233" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="Q233">
         <v>2.88</v>
@@ -49663,7 +49672,7 @@
         <v>0.89</v>
       </c>
       <c r="AP233">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AQ233">
         <v>0.93</v>
@@ -50284,7 +50293,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ236">
-        <v>1</v>
+        <v>1.13</v>
       </c>
       <c r="AR236">
         <v>1.41</v>
@@ -50696,7 +50705,7 @@
         <v>1.94</v>
       </c>
       <c r="AQ238">
-        <v>1</v>
+        <v>1.13</v>
       </c>
       <c r="AR238">
         <v>1.85</v>
@@ -50821,7 +50830,7 @@
         <v>245</v>
       </c>
       <c r="P239" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="Q239">
         <v>4.5</v>
@@ -51027,7 +51036,7 @@
         <v>101</v>
       </c>
       <c r="P240" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="Q240">
         <v>3.75</v>
@@ -51233,7 +51242,7 @@
         <v>101</v>
       </c>
       <c r="P241" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="Q241">
         <v>5.5</v>
@@ -51314,7 +51323,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ241">
-        <v>1.73</v>
+        <v>1.69</v>
       </c>
       <c r="AR241">
         <v>1.17</v>
@@ -51439,7 +51448,7 @@
         <v>246</v>
       </c>
       <c r="P242" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="Q242">
         <v>2.88</v>
@@ -51645,7 +51654,7 @@
         <v>101</v>
       </c>
       <c r="P243" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="Q243">
         <v>3.5</v>
@@ -52135,7 +52144,7 @@
         <v>1.6</v>
       </c>
       <c r="AP245">
-        <v>1.88</v>
+        <v>1.82</v>
       </c>
       <c r="AQ245">
         <v>1.35</v>
@@ -52263,7 +52272,7 @@
         <v>248</v>
       </c>
       <c r="P246" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="Q246">
         <v>2.38</v>
@@ -52469,7 +52478,7 @@
         <v>101</v>
       </c>
       <c r="P247" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="Q247">
         <v>2.6</v>
@@ -53293,7 +53302,7 @@
         <v>252</v>
       </c>
       <c r="P251" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="Q251">
         <v>2.25</v>
@@ -53705,7 +53714,7 @@
         <v>254</v>
       </c>
       <c r="P253" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="Q253">
         <v>2.1</v>
@@ -53783,7 +53792,7 @@
         <v>0.82</v>
       </c>
       <c r="AP253">
-        <v>1.31</v>
+        <v>1.24</v>
       </c>
       <c r="AQ253">
         <v>0.8100000000000001</v>
@@ -54323,7 +54332,7 @@
         <v>114</v>
       </c>
       <c r="P256" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="Q256">
         <v>2.88</v>
@@ -54401,7 +54410,7 @@
         <v>0.75</v>
       </c>
       <c r="AP256">
-        <v>1.31</v>
+        <v>1.24</v>
       </c>
       <c r="AQ256">
         <v>0.9399999999999999</v>
@@ -54610,7 +54619,7 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="AQ257">
-        <v>0.88</v>
+        <v>1</v>
       </c>
       <c r="AR257">
         <v>1.34</v>
@@ -54813,7 +54822,7 @@
         <v>0.73</v>
       </c>
       <c r="AP258">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="AQ258">
         <v>0.5600000000000001</v>
@@ -56383,7 +56392,7 @@
         <v>259</v>
       </c>
       <c r="P266" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="Q266">
         <v>3.6</v>
@@ -56461,7 +56470,7 @@
         <v>1.42</v>
       </c>
       <c r="AP266">
-        <v>1.88</v>
+        <v>1.82</v>
       </c>
       <c r="AQ266">
         <v>1.63</v>
@@ -57001,7 +57010,7 @@
         <v>261</v>
       </c>
       <c r="P269" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="Q269">
         <v>2.75</v>
@@ -57207,7 +57216,7 @@
         <v>262</v>
       </c>
       <c r="P270" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="Q270">
         <v>2.4</v>
@@ -57288,7 +57297,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ270">
-        <v>1</v>
+        <v>1.13</v>
       </c>
       <c r="AR270">
         <v>1.45</v>
@@ -57413,7 +57422,7 @@
         <v>101</v>
       </c>
       <c r="P271" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="Q271">
         <v>4</v>
@@ -57619,7 +57628,7 @@
         <v>263</v>
       </c>
       <c r="P272" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="Q272">
         <v>3.1</v>
@@ -58031,7 +58040,7 @@
         <v>184</v>
       </c>
       <c r="P274" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="Q274">
         <v>3.25</v>
@@ -58112,7 +58121,7 @@
         <v>1.94</v>
       </c>
       <c r="AQ274">
-        <v>1.73</v>
+        <v>1.69</v>
       </c>
       <c r="AR274">
         <v>1.79</v>
@@ -58237,7 +58246,7 @@
         <v>265</v>
       </c>
       <c r="P275" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="Q275">
         <v>3.4</v>
@@ -58318,7 +58327,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ275">
-        <v>1</v>
+        <v>1.13</v>
       </c>
       <c r="AR275">
         <v>1.43</v>
@@ -58443,7 +58452,7 @@
         <v>266</v>
       </c>
       <c r="P276" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="Q276">
         <v>2.88</v>
@@ -58649,7 +58658,7 @@
         <v>267</v>
       </c>
       <c r="P277" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="Q277">
         <v>3.1</v>
@@ -58855,7 +58864,7 @@
         <v>101</v>
       </c>
       <c r="P278" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="Q278">
         <v>3.1</v>
@@ -58933,7 +58942,7 @@
         <v>1.6</v>
       </c>
       <c r="AP278">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AQ278">
         <v>1.5</v>
@@ -59061,7 +59070,7 @@
         <v>128</v>
       </c>
       <c r="P279" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="Q279">
         <v>5</v>
@@ -59679,7 +59688,7 @@
         <v>101</v>
       </c>
       <c r="P282" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="Q282">
         <v>2.6</v>
@@ -59760,7 +59769,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ282">
-        <v>0.88</v>
+        <v>1</v>
       </c>
       <c r="AR282">
         <v>1.6</v>
@@ -59963,7 +59972,7 @@
         <v>0.82</v>
       </c>
       <c r="AP283">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="AQ283">
         <v>0.75</v>
@@ -60503,7 +60512,7 @@
         <v>101</v>
       </c>
       <c r="P286" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="Q286">
         <v>2.5</v>
@@ -60709,7 +60718,7 @@
         <v>270</v>
       </c>
       <c r="P287" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="Q287">
         <v>2.75</v>
@@ -61533,7 +61542,7 @@
         <v>101</v>
       </c>
       <c r="P291" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="Q291">
         <v>4</v>
@@ -61611,7 +61620,7 @@
         <v>1.5</v>
       </c>
       <c r="AP291">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AQ291">
         <v>1.76</v>
@@ -61820,7 +61829,7 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="AQ292">
-        <v>1</v>
+        <v>1.13</v>
       </c>
       <c r="AR292">
         <v>1.32</v>
@@ -62151,7 +62160,7 @@
         <v>101</v>
       </c>
       <c r="P294" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="Q294">
         <v>4</v>
@@ -62357,7 +62366,7 @@
         <v>274</v>
       </c>
       <c r="P295" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="Q295">
         <v>2</v>
@@ -62563,7 +62572,7 @@
         <v>101</v>
       </c>
       <c r="P296" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="Q296">
         <v>2.75</v>
@@ -62644,7 +62653,7 @@
         <v>1.81</v>
       </c>
       <c r="AQ296">
-        <v>1</v>
+        <v>1.13</v>
       </c>
       <c r="AR296">
         <v>1.45</v>
@@ -62975,7 +62984,7 @@
         <v>276</v>
       </c>
       <c r="P298" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="Q298">
         <v>2.38</v>
@@ -63181,7 +63190,7 @@
         <v>101</v>
       </c>
       <c r="P299" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="Q299">
         <v>2.88</v>
@@ -63259,7 +63268,7 @@
         <v>0.91</v>
       </c>
       <c r="AP299">
-        <v>1.31</v>
+        <v>1.24</v>
       </c>
       <c r="AQ299">
         <v>1.19</v>
@@ -63387,7 +63396,7 @@
         <v>101</v>
       </c>
       <c r="P300" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="Q300">
         <v>3.6</v>
@@ -64211,7 +64220,7 @@
         <v>278</v>
       </c>
       <c r="P304" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="Q304">
         <v>4</v>
@@ -64704,7 +64713,7 @@
         <v>2.47</v>
       </c>
       <c r="AQ306">
-        <v>1.73</v>
+        <v>1.69</v>
       </c>
       <c r="AR306">
         <v>1.4</v>
@@ -64910,7 +64919,7 @@
         <v>1.81</v>
       </c>
       <c r="AQ307">
-        <v>0.88</v>
+        <v>1</v>
       </c>
       <c r="AR307">
         <v>1.21</v>
@@ -65525,7 +65534,7 @@
         <v>1</v>
       </c>
       <c r="AP310">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="AQ310">
         <v>0.9399999999999999</v>
@@ -65653,7 +65662,7 @@
         <v>282</v>
       </c>
       <c r="P311" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="Q311">
         <v>3.75</v>
@@ -65731,7 +65740,7 @@
         <v>1.5</v>
       </c>
       <c r="AP311">
-        <v>1.88</v>
+        <v>1.82</v>
       </c>
       <c r="AQ311">
         <v>1.19</v>
@@ -65859,7 +65868,7 @@
         <v>195</v>
       </c>
       <c r="P312" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="Q312">
         <v>2.63</v>
@@ -67095,7 +67104,7 @@
         <v>283</v>
       </c>
       <c r="P318" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="Q318">
         <v>3.4</v>
@@ -67382,7 +67391,7 @@
         <v>1.53</v>
       </c>
       <c r="AQ319">
-        <v>1.73</v>
+        <v>1.69</v>
       </c>
       <c r="AR319">
         <v>1.37</v>
@@ -68743,7 +68752,7 @@
         <v>290</v>
       </c>
       <c r="P326" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="Q326">
         <v>3.75</v>
@@ -68949,7 +68958,7 @@
         <v>291</v>
       </c>
       <c r="P327" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="Q327">
         <v>3.75</v>
@@ -69027,7 +69036,7 @@
         <v>1.64</v>
       </c>
       <c r="AP327">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AQ327">
         <v>1.63</v>
@@ -69233,7 +69242,7 @@
         <v>1.31</v>
       </c>
       <c r="AP328">
-        <v>1.88</v>
+        <v>1.82</v>
       </c>
       <c r="AQ328">
         <v>1.06</v>
@@ -69442,7 +69451,7 @@
         <v>1.93</v>
       </c>
       <c r="AQ329">
-        <v>0.88</v>
+        <v>1</v>
       </c>
       <c r="AR329">
         <v>1.33</v>
@@ -69567,7 +69576,7 @@
         <v>293</v>
       </c>
       <c r="P330" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="Q330">
         <v>2.63</v>
@@ -69773,7 +69782,7 @@
         <v>260</v>
       </c>
       <c r="P331" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="Q331">
         <v>3.5</v>
@@ -69851,7 +69860,7 @@
         <v>1.08</v>
       </c>
       <c r="AP331">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="AQ331">
         <v>1.19</v>
@@ -70185,7 +70194,7 @@
         <v>294</v>
       </c>
       <c r="P333" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="Q333">
         <v>4</v>
@@ -70266,7 +70275,7 @@
         <v>0.75</v>
       </c>
       <c r="AQ333">
-        <v>1</v>
+        <v>1.13</v>
       </c>
       <c r="AR333">
         <v>1.34</v>
@@ -70803,7 +70812,7 @@
         <v>101</v>
       </c>
       <c r="P336" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="Q336">
         <v>2.63</v>
@@ -70881,7 +70890,7 @@
         <v>1.36</v>
       </c>
       <c r="AP336">
-        <v>1.31</v>
+        <v>1.24</v>
       </c>
       <c r="AQ336">
         <v>1.56</v>
@@ -71090,7 +71099,7 @@
         <v>2.25</v>
       </c>
       <c r="AQ337">
-        <v>1</v>
+        <v>1.13</v>
       </c>
       <c r="AR337">
         <v>1.4</v>
@@ -71215,7 +71224,7 @@
         <v>296</v>
       </c>
       <c r="P338" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="Q338">
         <v>3.1</v>
@@ -71421,7 +71430,7 @@
         <v>297</v>
       </c>
       <c r="P339" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="Q339">
         <v>3</v>
@@ -71833,7 +71842,7 @@
         <v>299</v>
       </c>
       <c r="P341" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="Q341">
         <v>3</v>
@@ -72039,7 +72048,7 @@
         <v>300</v>
       </c>
       <c r="P342" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="Q342">
         <v>3.1</v>
@@ -72532,7 +72541,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ344">
-        <v>1.73</v>
+        <v>1.69</v>
       </c>
       <c r="AR344">
         <v>1.55</v>
@@ -72657,7 +72666,7 @@
         <v>101</v>
       </c>
       <c r="P345" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="Q345">
         <v>1.91</v>
@@ -74589,10 +74598,10 @@
         <v>1.17</v>
       </c>
       <c r="AP354">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="AQ354">
-        <v>1</v>
+        <v>1.13</v>
       </c>
       <c r="AR354">
         <v>1.52</v>
@@ -75210,7 +75219,7 @@
         <v>2.47</v>
       </c>
       <c r="AQ357">
-        <v>0.88</v>
+        <v>1</v>
       </c>
       <c r="AR357">
         <v>1.44</v>
@@ -75335,7 +75344,7 @@
         <v>178</v>
       </c>
       <c r="P358" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="Q358">
         <v>2.45</v>
@@ -75747,7 +75756,7 @@
         <v>206</v>
       </c>
       <c r="P360" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="Q360">
         <v>2.3</v>
@@ -76159,7 +76168,7 @@
         <v>205</v>
       </c>
       <c r="P362" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="Q362">
         <v>3.5</v>
@@ -76237,7 +76246,7 @@
         <v>1</v>
       </c>
       <c r="AP362">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="AQ362">
         <v>0.93</v>
@@ -76443,10 +76452,10 @@
         <v>1.15</v>
       </c>
       <c r="AP363">
-        <v>1.31</v>
+        <v>1.24</v>
       </c>
       <c r="AQ363">
-        <v>1</v>
+        <v>1.13</v>
       </c>
       <c r="AR363">
         <v>1.51</v>
@@ -76652,7 +76661,7 @@
         <v>1.69</v>
       </c>
       <c r="AQ364">
-        <v>1</v>
+        <v>1.13</v>
       </c>
       <c r="AR364">
         <v>1.22</v>
@@ -76858,7 +76867,7 @@
         <v>0.75</v>
       </c>
       <c r="AQ365">
-        <v>0.88</v>
+        <v>1</v>
       </c>
       <c r="AR365">
         <v>1.39</v>
@@ -77267,7 +77276,7 @@
         <v>1.38</v>
       </c>
       <c r="AP367">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AQ367">
         <v>1.35</v>
@@ -77601,7 +77610,7 @@
         <v>309</v>
       </c>
       <c r="P369" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="Q369">
         <v>3.25</v>
@@ -77679,7 +77688,7 @@
         <v>0.64</v>
       </c>
       <c r="AP369">
-        <v>1.88</v>
+        <v>1.82</v>
       </c>
       <c r="AQ369">
         <v>0.5600000000000001</v>
@@ -78837,7 +78846,7 @@
         <v>101</v>
       </c>
       <c r="P375" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="Q375">
         <v>5.5</v>
@@ -78918,7 +78927,7 @@
         <v>0.75</v>
       </c>
       <c r="AQ375">
-        <v>1.73</v>
+        <v>1.69</v>
       </c>
       <c r="AR375">
         <v>1.41</v>
@@ -79043,7 +79052,7 @@
         <v>218</v>
       </c>
       <c r="P376" t="s">
-        <v>356</v>
+        <v>319</v>
       </c>
       <c r="Q376">
         <v>3.5</v>
@@ -79533,7 +79542,7 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="AP378">
-        <v>1.31</v>
+        <v>1.24</v>
       </c>
       <c r="AQ378">
         <v>0.76</v>
@@ -80073,7 +80082,7 @@
         <v>101</v>
       </c>
       <c r="P381" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="Q381">
         <v>3.5</v>
@@ -80279,7 +80288,7 @@
         <v>316</v>
       </c>
       <c r="P382" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="Q382">
         <v>4</v>
@@ -80772,7 +80781,7 @@
         <v>1.63</v>
       </c>
       <c r="AQ384">
-        <v>1</v>
+        <v>1.13</v>
       </c>
       <c r="AR384">
         <v>1.41</v>
@@ -81054,6 +81063,830 @@
       </c>
       <c r="BP385">
         <v>1.24</v>
+      </c>
+    </row>
+    <row r="386" spans="1:68">
+      <c r="A386" s="1">
+        <v>385</v>
+      </c>
+      <c r="B386">
+        <v>7476806</v>
+      </c>
+      <c r="C386" t="s">
+        <v>68</v>
+      </c>
+      <c r="D386" t="s">
+        <v>69</v>
+      </c>
+      <c r="E386" s="2">
+        <v>45713.69791666666</v>
+      </c>
+      <c r="F386">
+        <v>22</v>
+      </c>
+      <c r="G386" t="s">
+        <v>80</v>
+      </c>
+      <c r="H386" t="s">
+        <v>84</v>
+      </c>
+      <c r="I386">
+        <v>0</v>
+      </c>
+      <c r="J386">
+        <v>0</v>
+      </c>
+      <c r="K386">
+        <v>0</v>
+      </c>
+      <c r="L386">
+        <v>0</v>
+      </c>
+      <c r="M386">
+        <v>1</v>
+      </c>
+      <c r="N386">
+        <v>1</v>
+      </c>
+      <c r="O386" t="s">
+        <v>101</v>
+      </c>
+      <c r="P386" t="s">
+        <v>178</v>
+      </c>
+      <c r="Q386">
+        <v>2.75</v>
+      </c>
+      <c r="R386">
+        <v>2.1</v>
+      </c>
+      <c r="S386">
+        <v>4</v>
+      </c>
+      <c r="T386">
+        <v>1.4</v>
+      </c>
+      <c r="U386">
+        <v>2.75</v>
+      </c>
+      <c r="V386">
+        <v>3</v>
+      </c>
+      <c r="W386">
+        <v>1.36</v>
+      </c>
+      <c r="X386">
+        <v>9</v>
+      </c>
+      <c r="Y386">
+        <v>1.07</v>
+      </c>
+      <c r="Z386">
+        <v>2.19</v>
+      </c>
+      <c r="AA386">
+        <v>3.28</v>
+      </c>
+      <c r="AB386">
+        <v>3.23</v>
+      </c>
+      <c r="AC386">
+        <v>1.05</v>
+      </c>
+      <c r="AD386">
+        <v>11</v>
+      </c>
+      <c r="AE386">
+        <v>1.33</v>
+      </c>
+      <c r="AF386">
+        <v>3.25</v>
+      </c>
+      <c r="AG386">
+        <v>1.92</v>
+      </c>
+      <c r="AH386">
+        <v>1.82</v>
+      </c>
+      <c r="AI386">
+        <v>1.8</v>
+      </c>
+      <c r="AJ386">
+        <v>1.91</v>
+      </c>
+      <c r="AK386">
+        <v>1.33</v>
+      </c>
+      <c r="AL386">
+        <v>1.25</v>
+      </c>
+      <c r="AM386">
+        <v>1.75</v>
+      </c>
+      <c r="AN386">
+        <v>1.25</v>
+      </c>
+      <c r="AO386">
+        <v>0.88</v>
+      </c>
+      <c r="AP386">
+        <v>1.18</v>
+      </c>
+      <c r="AQ386">
+        <v>1</v>
+      </c>
+      <c r="AR386">
+        <v>1.52</v>
+      </c>
+      <c r="AS386">
+        <v>1.33</v>
+      </c>
+      <c r="AT386">
+        <v>2.85</v>
+      </c>
+      <c r="AU386">
+        <v>3</v>
+      </c>
+      <c r="AV386">
+        <v>6</v>
+      </c>
+      <c r="AW386">
+        <v>16</v>
+      </c>
+      <c r="AX386">
+        <v>5</v>
+      </c>
+      <c r="AY386">
+        <v>25</v>
+      </c>
+      <c r="AZ386">
+        <v>12</v>
+      </c>
+      <c r="BA386">
+        <v>5</v>
+      </c>
+      <c r="BB386">
+        <v>1</v>
+      </c>
+      <c r="BC386">
+        <v>6</v>
+      </c>
+      <c r="BD386">
+        <v>1.79</v>
+      </c>
+      <c r="BE386">
+        <v>6.75</v>
+      </c>
+      <c r="BF386">
+        <v>2.23</v>
+      </c>
+      <c r="BG386">
+        <v>1.25</v>
+      </c>
+      <c r="BH386">
+        <v>3.45</v>
+      </c>
+      <c r="BI386">
+        <v>1.45</v>
+      </c>
+      <c r="BJ386">
+        <v>2.55</v>
+      </c>
+      <c r="BK386">
+        <v>1.73</v>
+      </c>
+      <c r="BL386">
+        <v>1.98</v>
+      </c>
+      <c r="BM386">
+        <v>2.1</v>
+      </c>
+      <c r="BN386">
+        <v>1.64</v>
+      </c>
+      <c r="BO386">
+        <v>2.65</v>
+      </c>
+      <c r="BP386">
+        <v>1.41</v>
+      </c>
+    </row>
+    <row r="387" spans="1:68">
+      <c r="A387" s="1">
+        <v>386</v>
+      </c>
+      <c r="B387">
+        <v>7476847</v>
+      </c>
+      <c r="C387" t="s">
+        <v>68</v>
+      </c>
+      <c r="D387" t="s">
+        <v>69</v>
+      </c>
+      <c r="E387" s="2">
+        <v>45713.69791666666</v>
+      </c>
+      <c r="F387">
+        <v>26</v>
+      </c>
+      <c r="G387" t="s">
+        <v>76</v>
+      </c>
+      <c r="H387" t="s">
+        <v>75</v>
+      </c>
+      <c r="I387">
+        <v>1</v>
+      </c>
+      <c r="J387">
+        <v>1</v>
+      </c>
+      <c r="K387">
+        <v>2</v>
+      </c>
+      <c r="L387">
+        <v>1</v>
+      </c>
+      <c r="M387">
+        <v>2</v>
+      </c>
+      <c r="N387">
+        <v>3</v>
+      </c>
+      <c r="O387" t="s">
+        <v>319</v>
+      </c>
+      <c r="P387" t="s">
+        <v>457</v>
+      </c>
+      <c r="Q387">
+        <v>3.25</v>
+      </c>
+      <c r="R387">
+        <v>2.05</v>
+      </c>
+      <c r="S387">
+        <v>3.5</v>
+      </c>
+      <c r="T387">
+        <v>1.44</v>
+      </c>
+      <c r="U387">
+        <v>2.63</v>
+      </c>
+      <c r="V387">
+        <v>3.4</v>
+      </c>
+      <c r="W387">
+        <v>1.3</v>
+      </c>
+      <c r="X387">
+        <v>10</v>
+      </c>
+      <c r="Y387">
+        <v>1.06</v>
+      </c>
+      <c r="Z387">
+        <v>2.61</v>
+      </c>
+      <c r="AA387">
+        <v>3.31</v>
+      </c>
+      <c r="AB387">
+        <v>2.61</v>
+      </c>
+      <c r="AC387">
+        <v>1.07</v>
+      </c>
+      <c r="AD387">
+        <v>8</v>
+      </c>
+      <c r="AE387">
+        <v>1.38</v>
+      </c>
+      <c r="AF387">
+        <v>3</v>
+      </c>
+      <c r="AG387">
+        <v>2.13</v>
+      </c>
+      <c r="AH387">
+        <v>1.65</v>
+      </c>
+      <c r="AI387">
+        <v>1.83</v>
+      </c>
+      <c r="AJ387">
+        <v>1.83</v>
+      </c>
+      <c r="AK387">
+        <v>1.42</v>
+      </c>
+      <c r="AL387">
+        <v>1.28</v>
+      </c>
+      <c r="AM387">
+        <v>1.5</v>
+      </c>
+      <c r="AN387">
+        <v>1.33</v>
+      </c>
+      <c r="AO387">
+        <v>1</v>
+      </c>
+      <c r="AP387">
+        <v>1.25</v>
+      </c>
+      <c r="AQ387">
+        <v>1.13</v>
+      </c>
+      <c r="AR387">
+        <v>1.35</v>
+      </c>
+      <c r="AS387">
+        <v>1.19</v>
+      </c>
+      <c r="AT387">
+        <v>2.54</v>
+      </c>
+      <c r="AU387">
+        <v>4</v>
+      </c>
+      <c r="AV387">
+        <v>7</v>
+      </c>
+      <c r="AW387">
+        <v>12</v>
+      </c>
+      <c r="AX387">
+        <v>7</v>
+      </c>
+      <c r="AY387">
+        <v>20</v>
+      </c>
+      <c r="AZ387">
+        <v>16</v>
+      </c>
+      <c r="BA387">
+        <v>4</v>
+      </c>
+      <c r="BB387">
+        <v>4</v>
+      </c>
+      <c r="BC387">
+        <v>8</v>
+      </c>
+      <c r="BD387">
+        <v>1.85</v>
+      </c>
+      <c r="BE387">
+        <v>6.75</v>
+      </c>
+      <c r="BF387">
+        <v>2.15</v>
+      </c>
+      <c r="BG387">
+        <v>1.24</v>
+      </c>
+      <c r="BH387">
+        <v>3.55</v>
+      </c>
+      <c r="BI387">
+        <v>1.43</v>
+      </c>
+      <c r="BJ387">
+        <v>2.55</v>
+      </c>
+      <c r="BK387">
+        <v>1.71</v>
+      </c>
+      <c r="BL387">
+        <v>2</v>
+      </c>
+      <c r="BM387">
+        <v>2.1</v>
+      </c>
+      <c r="BN387">
+        <v>1.64</v>
+      </c>
+      <c r="BO387">
+        <v>2.65</v>
+      </c>
+      <c r="BP387">
+        <v>1.41</v>
+      </c>
+    </row>
+    <row r="388" spans="1:68">
+      <c r="A388" s="1">
+        <v>387</v>
+      </c>
+      <c r="B388">
+        <v>7476845</v>
+      </c>
+      <c r="C388" t="s">
+        <v>68</v>
+      </c>
+      <c r="D388" t="s">
+        <v>69</v>
+      </c>
+      <c r="E388" s="2">
+        <v>45713.69791666666</v>
+      </c>
+      <c r="F388">
+        <v>26</v>
+      </c>
+      <c r="G388" t="s">
+        <v>83</v>
+      </c>
+      <c r="H388" t="s">
+        <v>92</v>
+      </c>
+      <c r="I388">
+        <v>0</v>
+      </c>
+      <c r="J388">
+        <v>0</v>
+      </c>
+      <c r="K388">
+        <v>0</v>
+      </c>
+      <c r="L388">
+        <v>0</v>
+      </c>
+      <c r="M388">
+        <v>1</v>
+      </c>
+      <c r="N388">
+        <v>1</v>
+      </c>
+      <c r="O388" t="s">
+        <v>101</v>
+      </c>
+      <c r="P388" t="s">
+        <v>349</v>
+      </c>
+      <c r="Q388">
+        <v>3.1</v>
+      </c>
+      <c r="R388">
+        <v>2.05</v>
+      </c>
+      <c r="S388">
+        <v>3.6</v>
+      </c>
+      <c r="T388">
+        <v>1.44</v>
+      </c>
+      <c r="U388">
+        <v>2.63</v>
+      </c>
+      <c r="V388">
+        <v>3.25</v>
+      </c>
+      <c r="W388">
+        <v>1.33</v>
+      </c>
+      <c r="X388">
+        <v>9</v>
+      </c>
+      <c r="Y388">
+        <v>1.07</v>
+      </c>
+      <c r="Z388">
+        <v>2.4</v>
+      </c>
+      <c r="AA388">
+        <v>3.25</v>
+      </c>
+      <c r="AB388">
+        <v>2.9</v>
+      </c>
+      <c r="AC388">
+        <v>1.06</v>
+      </c>
+      <c r="AD388">
+        <v>9.5</v>
+      </c>
+      <c r="AE388">
+        <v>1.35</v>
+      </c>
+      <c r="AF388">
+        <v>3.2</v>
+      </c>
+      <c r="AG388">
+        <v>2.05</v>
+      </c>
+      <c r="AH388">
+        <v>1.7</v>
+      </c>
+      <c r="AI388">
+        <v>1.83</v>
+      </c>
+      <c r="AJ388">
+        <v>1.83</v>
+      </c>
+      <c r="AK388">
+        <v>1.55</v>
+      </c>
+      <c r="AL388">
+        <v>1.28</v>
+      </c>
+      <c r="AM388">
+        <v>1.42</v>
+      </c>
+      <c r="AN388">
+        <v>1.31</v>
+      </c>
+      <c r="AO388">
+        <v>1</v>
+      </c>
+      <c r="AP388">
+        <v>1.24</v>
+      </c>
+      <c r="AQ388">
+        <v>1.13</v>
+      </c>
+      <c r="AR388">
+        <v>1.47</v>
+      </c>
+      <c r="AS388">
+        <v>1.28</v>
+      </c>
+      <c r="AT388">
+        <v>2.75</v>
+      </c>
+      <c r="AU388">
+        <v>2</v>
+      </c>
+      <c r="AV388">
+        <v>4</v>
+      </c>
+      <c r="AW388">
+        <v>3</v>
+      </c>
+      <c r="AX388">
+        <v>12</v>
+      </c>
+      <c r="AY388">
+        <v>6</v>
+      </c>
+      <c r="AZ388">
+        <v>20</v>
+      </c>
+      <c r="BA388">
+        <v>1</v>
+      </c>
+      <c r="BB388">
+        <v>5</v>
+      </c>
+      <c r="BC388">
+        <v>6</v>
+      </c>
+      <c r="BD388">
+        <v>2.05</v>
+      </c>
+      <c r="BE388">
+        <v>8</v>
+      </c>
+      <c r="BF388">
+        <v>2</v>
+      </c>
+      <c r="BG388">
+        <v>1.21</v>
+      </c>
+      <c r="BH388">
+        <v>3.75</v>
+      </c>
+      <c r="BI388">
+        <v>1.41</v>
+      </c>
+      <c r="BJ388">
+        <v>2.68</v>
+      </c>
+      <c r="BK388">
+        <v>1.69</v>
+      </c>
+      <c r="BL388">
+        <v>2.09</v>
+      </c>
+      <c r="BM388">
+        <v>2.11</v>
+      </c>
+      <c r="BN388">
+        <v>1.68</v>
+      </c>
+      <c r="BO388">
+        <v>2.67</v>
+      </c>
+      <c r="BP388">
+        <v>1.42</v>
+      </c>
+    </row>
+    <row r="389" spans="1:68">
+      <c r="A389" s="1">
+        <v>388</v>
+      </c>
+      <c r="B389">
+        <v>7476834</v>
+      </c>
+      <c r="C389" t="s">
+        <v>68</v>
+      </c>
+      <c r="D389" t="s">
+        <v>69</v>
+      </c>
+      <c r="E389" s="2">
+        <v>45713.69791666666</v>
+      </c>
+      <c r="F389">
+        <v>25</v>
+      </c>
+      <c r="G389" t="s">
+        <v>73</v>
+      </c>
+      <c r="H389" t="s">
+        <v>81</v>
+      </c>
+      <c r="I389">
+        <v>0</v>
+      </c>
+      <c r="J389">
+        <v>1</v>
+      </c>
+      <c r="K389">
+        <v>1</v>
+      </c>
+      <c r="L389">
+        <v>2</v>
+      </c>
+      <c r="M389">
+        <v>2</v>
+      </c>
+      <c r="N389">
+        <v>4</v>
+      </c>
+      <c r="O389" t="s">
+        <v>320</v>
+      </c>
+      <c r="P389" t="s">
+        <v>458</v>
+      </c>
+      <c r="Q389">
+        <v>4</v>
+      </c>
+      <c r="R389">
+        <v>2.2</v>
+      </c>
+      <c r="S389">
+        <v>2.63</v>
+      </c>
+      <c r="T389">
+        <v>1.4</v>
+      </c>
+      <c r="U389">
+        <v>2.75</v>
+      </c>
+      <c r="V389">
+        <v>2.75</v>
+      </c>
+      <c r="W389">
+        <v>1.4</v>
+      </c>
+      <c r="X389">
+        <v>8</v>
+      </c>
+      <c r="Y389">
+        <v>1.08</v>
+      </c>
+      <c r="Z389">
+        <v>3.53</v>
+      </c>
+      <c r="AA389">
+        <v>3.32</v>
+      </c>
+      <c r="AB389">
+        <v>2.06</v>
+      </c>
+      <c r="AC389">
+        <v>1.05</v>
+      </c>
+      <c r="AD389">
+        <v>9</v>
+      </c>
+      <c r="AE389">
+        <v>1.28</v>
+      </c>
+      <c r="AF389">
+        <v>3.55</v>
+      </c>
+      <c r="AG389">
+        <v>1.77</v>
+      </c>
+      <c r="AH389">
+        <v>1.98</v>
+      </c>
+      <c r="AI389">
+        <v>1.73</v>
+      </c>
+      <c r="AJ389">
+        <v>2</v>
+      </c>
+      <c r="AK389">
+        <v>1.8</v>
+      </c>
+      <c r="AL389">
+        <v>1.25</v>
+      </c>
+      <c r="AM389">
+        <v>1.25</v>
+      </c>
+      <c r="AN389">
+        <v>1.88</v>
+      </c>
+      <c r="AO389">
+        <v>1.73</v>
+      </c>
+      <c r="AP389">
+        <v>1.82</v>
+      </c>
+      <c r="AQ389">
+        <v>1.69</v>
+      </c>
+      <c r="AR389">
+        <v>1.38</v>
+      </c>
+      <c r="AS389">
+        <v>1.37</v>
+      </c>
+      <c r="AT389">
+        <v>2.75</v>
+      </c>
+      <c r="AU389">
+        <v>5</v>
+      </c>
+      <c r="AV389">
+        <v>3</v>
+      </c>
+      <c r="AW389">
+        <v>10</v>
+      </c>
+      <c r="AX389">
+        <v>9</v>
+      </c>
+      <c r="AY389">
+        <v>16</v>
+      </c>
+      <c r="AZ389">
+        <v>15</v>
+      </c>
+      <c r="BA389">
+        <v>3</v>
+      </c>
+      <c r="BB389">
+        <v>5</v>
+      </c>
+      <c r="BC389">
+        <v>8</v>
+      </c>
+      <c r="BD389">
+        <v>2.5</v>
+      </c>
+      <c r="BE389">
+        <v>6.75</v>
+      </c>
+      <c r="BF389">
+        <v>1.65</v>
+      </c>
+      <c r="BG389">
+        <v>1.24</v>
+      </c>
+      <c r="BH389">
+        <v>3.55</v>
+      </c>
+      <c r="BI389">
+        <v>1.44</v>
+      </c>
+      <c r="BJ389">
+        <v>2.55</v>
+      </c>
+      <c r="BK389">
+        <v>1.7</v>
+      </c>
+      <c r="BL389">
+        <v>2.02</v>
+      </c>
+      <c r="BM389">
+        <v>2.07</v>
+      </c>
+      <c r="BN389">
+        <v>1.67</v>
+      </c>
+      <c r="BO389">
+        <v>2.65</v>
+      </c>
+      <c r="BP389">
+        <v>1.42</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/England EFL League Two_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/England EFL League Two_20242025.xlsx
@@ -81223,13 +81223,13 @@
         <v>12</v>
       </c>
       <c r="BA386">
+        <v>4</v>
+      </c>
+      <c r="BB386">
+        <v>1</v>
+      </c>
+      <c r="BC386">
         <v>5</v>
-      </c>
-      <c r="BB386">
-        <v>1</v>
-      </c>
-      <c r="BC386">
-        <v>6</v>
       </c>
       <c r="BD386">
         <v>1.79</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/England EFL League Two_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/England EFL League Two_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2396" uniqueCount="459">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2402" uniqueCount="459">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -1752,7 +1752,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP389"/>
+  <dimension ref="A1:BP390"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -2498,7 +2498,7 @@
         <v>0</v>
       </c>
       <c r="AP4">
-        <v>1.75</v>
+        <v>1.65</v>
       </c>
       <c r="AQ4">
         <v>1.35</v>
@@ -3325,7 +3325,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ8">
-        <v>0.75</v>
+        <v>0.88</v>
       </c>
       <c r="AR8">
         <v>0</v>
@@ -8063,7 +8063,7 @@
         <v>1.47</v>
       </c>
       <c r="AQ31">
-        <v>0.75</v>
+        <v>0.88</v>
       </c>
       <c r="AR31">
         <v>1.62</v>
@@ -9090,7 +9090,7 @@
         <v>3</v>
       </c>
       <c r="AP36">
-        <v>1.75</v>
+        <v>1.65</v>
       </c>
       <c r="AQ36">
         <v>1.63</v>
@@ -12180,7 +12180,7 @@
         <v>1</v>
       </c>
       <c r="AP51">
-        <v>1.75</v>
+        <v>1.65</v>
       </c>
       <c r="AQ51">
         <v>0.9399999999999999</v>
@@ -13419,7 +13419,7 @@
         <v>2.47</v>
       </c>
       <c r="AQ57">
-        <v>0.75</v>
+        <v>0.88</v>
       </c>
       <c r="AR57">
         <v>1.74</v>
@@ -16921,7 +16921,7 @@
         <v>1.56</v>
       </c>
       <c r="AQ74">
-        <v>0.75</v>
+        <v>0.88</v>
       </c>
       <c r="AR74">
         <v>1.69</v>
@@ -18360,7 +18360,7 @@
         <v>1</v>
       </c>
       <c r="AP81">
-        <v>1.75</v>
+        <v>1.65</v>
       </c>
       <c r="AQ81">
         <v>0.8100000000000001</v>
@@ -25158,7 +25158,7 @@
         <v>0.25</v>
       </c>
       <c r="AP114">
-        <v>1.75</v>
+        <v>1.65</v>
       </c>
       <c r="AQ114">
         <v>0.93</v>
@@ -25573,7 +25573,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ116">
-        <v>0.75</v>
+        <v>0.88</v>
       </c>
       <c r="AR116">
         <v>1.85</v>
@@ -27424,7 +27424,7 @@
         <v>0.2</v>
       </c>
       <c r="AP125">
-        <v>1.75</v>
+        <v>1.65</v>
       </c>
       <c r="AQ125">
         <v>0.82</v>
@@ -27633,7 +27633,7 @@
         <v>2.25</v>
       </c>
       <c r="AQ126">
-        <v>0.75</v>
+        <v>0.88</v>
       </c>
       <c r="AR126">
         <v>1.5</v>
@@ -30517,7 +30517,7 @@
         <v>2.35</v>
       </c>
       <c r="AQ140">
-        <v>0.75</v>
+        <v>0.88</v>
       </c>
       <c r="AR140">
         <v>1.55</v>
@@ -32368,7 +32368,7 @@
         <v>2</v>
       </c>
       <c r="AP149">
-        <v>1.75</v>
+        <v>1.65</v>
       </c>
       <c r="AQ149">
         <v>1.63</v>
@@ -35667,7 +35667,7 @@
         <v>1.81</v>
       </c>
       <c r="AQ165">
-        <v>0.75</v>
+        <v>0.88</v>
       </c>
       <c r="AR165">
         <v>1.4</v>
@@ -37724,7 +37724,7 @@
         <v>0.67</v>
       </c>
       <c r="AP175">
-        <v>1.75</v>
+        <v>1.65</v>
       </c>
       <c r="AQ175">
         <v>1.19</v>
@@ -39375,7 +39375,7 @@
         <v>1.24</v>
       </c>
       <c r="AQ183">
-        <v>0.75</v>
+        <v>0.88</v>
       </c>
       <c r="AR183">
         <v>1.45</v>
@@ -39578,7 +39578,7 @@
         <v>0.67</v>
       </c>
       <c r="AP184">
-        <v>1.75</v>
+        <v>1.65</v>
       </c>
       <c r="AQ184">
         <v>1.31</v>
@@ -50290,7 +50290,7 @@
         <v>1.38</v>
       </c>
       <c r="AP236">
-        <v>1.75</v>
+        <v>1.65</v>
       </c>
       <c r="AQ236">
         <v>1.13</v>
@@ -50499,7 +50499,7 @@
         <v>1.93</v>
       </c>
       <c r="AQ237">
-        <v>0.75</v>
+        <v>0.88</v>
       </c>
       <c r="AR237">
         <v>1.18</v>
@@ -57091,7 +57091,7 @@
         <v>1.81</v>
       </c>
       <c r="AQ269">
-        <v>0.75</v>
+        <v>0.88</v>
       </c>
       <c r="AR269">
         <v>1.12</v>
@@ -58324,7 +58324,7 @@
         <v>0.91</v>
       </c>
       <c r="AP275">
-        <v>1.75</v>
+        <v>1.65</v>
       </c>
       <c r="AQ275">
         <v>1.13</v>
@@ -59975,7 +59975,7 @@
         <v>1.18</v>
       </c>
       <c r="AQ283">
-        <v>0.75</v>
+        <v>0.88</v>
       </c>
       <c r="AR283">
         <v>1.46</v>
@@ -60590,7 +60590,7 @@
         <v>0.83</v>
       </c>
       <c r="AP286">
-        <v>1.75</v>
+        <v>1.65</v>
       </c>
       <c r="AQ286">
         <v>0.76</v>
@@ -65122,7 +65122,7 @@
         <v>1.46</v>
       </c>
       <c r="AP308">
-        <v>1.75</v>
+        <v>1.65</v>
       </c>
       <c r="AQ308">
         <v>1.56</v>
@@ -65949,7 +65949,7 @@
         <v>1.53</v>
       </c>
       <c r="AQ312">
-        <v>0.75</v>
+        <v>0.88</v>
       </c>
       <c r="AR312">
         <v>1.34</v>
@@ -67803,7 +67803,7 @@
         <v>1.94</v>
       </c>
       <c r="AQ321">
-        <v>0.75</v>
+        <v>0.88</v>
       </c>
       <c r="AR321">
         <v>1.74</v>
@@ -68830,7 +68830,7 @@
         <v>1.62</v>
       </c>
       <c r="AP326">
-        <v>1.75</v>
+        <v>1.65</v>
       </c>
       <c r="AQ326">
         <v>1.76</v>
@@ -73156,7 +73156,7 @@
         <v>1</v>
       </c>
       <c r="AP347">
-        <v>1.75</v>
+        <v>1.65</v>
       </c>
       <c r="AQ347">
         <v>0.9399999999999999</v>
@@ -74189,7 +74189,7 @@
         <v>1.63</v>
       </c>
       <c r="AQ352">
-        <v>0.75</v>
+        <v>0.88</v>
       </c>
       <c r="AR352">
         <v>1.3</v>
@@ -74807,7 +74807,7 @@
         <v>1.69</v>
       </c>
       <c r="AQ355">
-        <v>0.75</v>
+        <v>0.88</v>
       </c>
       <c r="AR355">
         <v>1.24</v>
@@ -75010,7 +75010,7 @@
         <v>1.08</v>
       </c>
       <c r="AP356">
-        <v>1.75</v>
+        <v>1.65</v>
       </c>
       <c r="AQ356">
         <v>0.93</v>
@@ -81887,6 +81887,212 @@
       </c>
       <c r="BP389">
         <v>1.42</v>
+      </c>
+    </row>
+    <row r="390" spans="1:68">
+      <c r="A390" s="1">
+        <v>389</v>
+      </c>
+      <c r="B390">
+        <v>7476940</v>
+      </c>
+      <c r="C390" t="s">
+        <v>68</v>
+      </c>
+      <c r="D390" t="s">
+        <v>69</v>
+      </c>
+      <c r="E390" s="2">
+        <v>45715.70833333334</v>
+      </c>
+      <c r="F390">
+        <v>34</v>
+      </c>
+      <c r="G390" t="s">
+        <v>72</v>
+      </c>
+      <c r="H390" t="s">
+        <v>82</v>
+      </c>
+      <c r="I390">
+        <v>0</v>
+      </c>
+      <c r="J390">
+        <v>1</v>
+      </c>
+      <c r="K390">
+        <v>1</v>
+      </c>
+      <c r="L390">
+        <v>0</v>
+      </c>
+      <c r="M390">
+        <v>1</v>
+      </c>
+      <c r="N390">
+        <v>1</v>
+      </c>
+      <c r="O390" t="s">
+        <v>101</v>
+      </c>
+      <c r="P390" t="s">
+        <v>286</v>
+      </c>
+      <c r="Q390">
+        <v>2.5</v>
+      </c>
+      <c r="R390">
+        <v>2.1</v>
+      </c>
+      <c r="S390">
+        <v>5</v>
+      </c>
+      <c r="T390">
+        <v>1.44</v>
+      </c>
+      <c r="U390">
+        <v>2.63</v>
+      </c>
+      <c r="V390">
+        <v>3.25</v>
+      </c>
+      <c r="W390">
+        <v>1.33</v>
+      </c>
+      <c r="X390">
+        <v>10</v>
+      </c>
+      <c r="Y390">
+        <v>1.06</v>
+      </c>
+      <c r="Z390">
+        <v>2.01</v>
+      </c>
+      <c r="AA390">
+        <v>3.45</v>
+      </c>
+      <c r="AB390">
+        <v>3.53</v>
+      </c>
+      <c r="AC390">
+        <v>1.06</v>
+      </c>
+      <c r="AD390">
+        <v>9.5</v>
+      </c>
+      <c r="AE390">
+        <v>1.38</v>
+      </c>
+      <c r="AF390">
+        <v>3</v>
+      </c>
+      <c r="AG390">
+        <v>1.75</v>
+      </c>
+      <c r="AH390">
+        <v>1.95</v>
+      </c>
+      <c r="AI390">
+        <v>2</v>
+      </c>
+      <c r="AJ390">
+        <v>1.73</v>
+      </c>
+      <c r="AK390">
+        <v>1.22</v>
+      </c>
+      <c r="AL390">
+        <v>1.25</v>
+      </c>
+      <c r="AM390">
+        <v>2</v>
+      </c>
+      <c r="AN390">
+        <v>1.75</v>
+      </c>
+      <c r="AO390">
+        <v>0.75</v>
+      </c>
+      <c r="AP390">
+        <v>1.65</v>
+      </c>
+      <c r="AQ390">
+        <v>0.88</v>
+      </c>
+      <c r="AR390">
+        <v>1.41</v>
+      </c>
+      <c r="AS390">
+        <v>1.22</v>
+      </c>
+      <c r="AT390">
+        <v>2.63</v>
+      </c>
+      <c r="AU390">
+        <v>7</v>
+      </c>
+      <c r="AV390">
+        <v>2</v>
+      </c>
+      <c r="AW390">
+        <v>13</v>
+      </c>
+      <c r="AX390">
+        <v>6</v>
+      </c>
+      <c r="AY390">
+        <v>26</v>
+      </c>
+      <c r="AZ390">
+        <v>8</v>
+      </c>
+      <c r="BA390">
+        <v>4</v>
+      </c>
+      <c r="BB390">
+        <v>1</v>
+      </c>
+      <c r="BC390">
+        <v>5</v>
+      </c>
+      <c r="BD390">
+        <v>1.58</v>
+      </c>
+      <c r="BE390">
+        <v>6.75</v>
+      </c>
+      <c r="BF390">
+        <v>2.65</v>
+      </c>
+      <c r="BG390">
+        <v>1.3</v>
+      </c>
+      <c r="BH390">
+        <v>3.1</v>
+      </c>
+      <c r="BI390">
+        <v>1.53</v>
+      </c>
+      <c r="BJ390">
+        <v>2.32</v>
+      </c>
+      <c r="BK390">
+        <v>1.85</v>
+      </c>
+      <c r="BL390">
+        <v>1.83</v>
+      </c>
+      <c r="BM390">
+        <v>2.35</v>
+      </c>
+      <c r="BN390">
+        <v>1.5</v>
+      </c>
+      <c r="BO390">
+        <v>3.05</v>
+      </c>
+      <c r="BP390">
+        <v>1.32</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/England EFL League Two_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/England EFL League Two_20242025.xlsx
@@ -100791,31 +100791,31 @@
         <v>2.84</v>
       </c>
       <c r="AU480">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AV480">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AW480">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AX480">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AY480">
-        <v>-1</v>
+        <v>12</v>
       </c>
       <c r="AZ480">
-        <v>-1</v>
+        <v>18</v>
       </c>
       <c r="BA480">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="BB480">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="BC480">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="BD480">
         <v>1.51</v>
@@ -101203,31 +101203,31 @@
         <v>2.88</v>
       </c>
       <c r="AU482">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AV482">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AW482">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AX482">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AY482">
-        <v>-1</v>
+        <v>13</v>
       </c>
       <c r="AZ482">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="BA482">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="BB482">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="BC482">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="BD482">
         <v>1.87</v>
@@ -101409,31 +101409,31 @@
         <v>2.71</v>
       </c>
       <c r="AU483">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AV483">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AW483">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AX483">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AY483">
-        <v>-1</v>
+        <v>18</v>
       </c>
       <c r="AZ483">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="BA483">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="BB483">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="BC483">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="BD483">
         <v>1.93</v>
@@ -101615,31 +101615,31 @@
         <v>2.56</v>
       </c>
       <c r="AU484">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AV484">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AW484">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AX484">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AY484">
-        <v>-1</v>
+        <v>22</v>
       </c>
       <c r="AZ484">
-        <v>-1</v>
+        <v>13</v>
       </c>
       <c r="BA484">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="BB484">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="BC484">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="BD484">
         <v>2</v>
@@ -102027,31 +102027,31 @@
         <v>2.63</v>
       </c>
       <c r="AU486">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AV486">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AW486">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AX486">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AY486">
-        <v>-1</v>
+        <v>13</v>
       </c>
       <c r="AZ486">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="BA486">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="BB486">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="BC486">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="BD486">
         <v>1.81</v>
@@ -103057,31 +103057,31 @@
         <v>2.49</v>
       </c>
       <c r="AU491">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AV491">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AW491">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AX491">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AY491">
-        <v>-1</v>
+        <v>21</v>
       </c>
       <c r="AZ491">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="BA491">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="BB491">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="BC491">
-        <v>-1</v>
+        <v>12</v>
       </c>
       <c r="BD491">
         <v>1.53</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/England EFL League Two_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/England EFL League Two_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3008" uniqueCount="533">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3014" uniqueCount="533">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -1974,7 +1974,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP491"/>
+  <dimension ref="A1:BP492"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -2308,7 +2308,7 @@
         <v>0</v>
       </c>
       <c r="AP2">
-        <v>1.68</v>
+        <v>1.65</v>
       </c>
       <c r="AQ2">
         <v>1.1</v>
@@ -8694,7 +8694,7 @@
         <v>1</v>
       </c>
       <c r="AP33">
-        <v>1.68</v>
+        <v>1.65</v>
       </c>
       <c r="AQ33">
         <v>1.35</v>
@@ -12814,7 +12814,7 @@
         <v>0</v>
       </c>
       <c r="AP53">
-        <v>1.68</v>
+        <v>1.65</v>
       </c>
       <c r="AQ53">
         <v>1.6</v>
@@ -16934,7 +16934,7 @@
         <v>0</v>
       </c>
       <c r="AP73">
-        <v>1.68</v>
+        <v>1.65</v>
       </c>
       <c r="AQ73">
         <v>0.9</v>
@@ -25174,7 +25174,7 @@
         <v>1.5</v>
       </c>
       <c r="AP113">
-        <v>1.68</v>
+        <v>1.65</v>
       </c>
       <c r="AQ113">
         <v>1.55</v>
@@ -26204,7 +26204,7 @@
         <v>2.2</v>
       </c>
       <c r="AP118">
-        <v>1.68</v>
+        <v>1.65</v>
       </c>
       <c r="AQ118">
         <v>1.57</v>
@@ -33002,7 +33002,7 @@
         <v>0.6</v>
       </c>
       <c r="AP151">
-        <v>1.68</v>
+        <v>1.65</v>
       </c>
       <c r="AQ151">
         <v>1.3</v>
@@ -37534,7 +37534,7 @@
         <v>0.5</v>
       </c>
       <c r="AP173">
-        <v>1.68</v>
+        <v>1.65</v>
       </c>
       <c r="AQ173">
         <v>0.86</v>
@@ -42066,7 +42066,7 @@
         <v>1</v>
       </c>
       <c r="AP195">
-        <v>1.68</v>
+        <v>1.65</v>
       </c>
       <c r="AQ195">
         <v>0.95</v>
@@ -45980,7 +45980,7 @@
         <v>1</v>
       </c>
       <c r="AP214">
-        <v>1.68</v>
+        <v>1.65</v>
       </c>
       <c r="AQ214">
         <v>0.65</v>
@@ -52160,7 +52160,7 @@
         <v>1.44</v>
       </c>
       <c r="AP244">
-        <v>1.68</v>
+        <v>1.65</v>
       </c>
       <c r="AQ244">
         <v>1.25</v>
@@ -58752,7 +58752,7 @@
         <v>1.25</v>
       </c>
       <c r="AP276">
-        <v>1.68</v>
+        <v>1.65</v>
       </c>
       <c r="AQ276">
         <v>0.9</v>
@@ -66580,7 +66580,7 @@
         <v>1.71</v>
       </c>
       <c r="AP314">
-        <v>1.68</v>
+        <v>1.65</v>
       </c>
       <c r="AQ314">
         <v>1.62</v>
@@ -68640,7 +68640,7 @@
         <v>1.54</v>
       </c>
       <c r="AP324">
-        <v>1.68</v>
+        <v>1.65</v>
       </c>
       <c r="AQ324">
         <v>1.4</v>
@@ -72142,7 +72142,7 @@
         <v>1.71</v>
       </c>
       <c r="AP341">
-        <v>1.68</v>
+        <v>1.65</v>
       </c>
       <c r="AQ341">
         <v>1.7</v>
@@ -82854,7 +82854,7 @@
         <v>1.35</v>
       </c>
       <c r="AP393">
-        <v>1.68</v>
+        <v>1.65</v>
       </c>
       <c r="AQ393">
         <v>1.33</v>
@@ -89446,7 +89446,7 @@
         <v>0.76</v>
       </c>
       <c r="AP425">
-        <v>1.68</v>
+        <v>1.65</v>
       </c>
       <c r="AQ425">
         <v>0.62</v>
@@ -94390,7 +94390,7 @@
         <v>0.74</v>
       </c>
       <c r="AP449">
-        <v>1.68</v>
+        <v>1.65</v>
       </c>
       <c r="AQ449">
         <v>0.71</v>
@@ -99952,7 +99952,7 @@
         <v>0.79</v>
       </c>
       <c r="AP476">
-        <v>1.68</v>
+        <v>1.65</v>
       </c>
       <c r="AQ476">
         <v>0.75</v>
@@ -103121,6 +103121,212 @@
       </c>
       <c r="BP491">
         <v>1.42</v>
+      </c>
+    </row>
+    <row r="492" spans="1:68">
+      <c r="A492" s="1">
+        <v>491</v>
+      </c>
+      <c r="B492">
+        <v>7477098</v>
+      </c>
+      <c r="C492" t="s">
+        <v>68</v>
+      </c>
+      <c r="D492" t="s">
+        <v>69</v>
+      </c>
+      <c r="E492" s="2">
+        <v>45755.65625</v>
+      </c>
+      <c r="F492">
+        <v>25</v>
+      </c>
+      <c r="G492" t="s">
+        <v>70</v>
+      </c>
+      <c r="H492" t="s">
+        <v>76</v>
+      </c>
+      <c r="I492">
+        <v>0</v>
+      </c>
+      <c r="J492">
+        <v>1</v>
+      </c>
+      <c r="K492">
+        <v>1</v>
+      </c>
+      <c r="L492">
+        <v>1</v>
+      </c>
+      <c r="M492">
+        <v>1</v>
+      </c>
+      <c r="N492">
+        <v>2</v>
+      </c>
+      <c r="O492" t="s">
+        <v>211</v>
+      </c>
+      <c r="P492" t="s">
+        <v>283</v>
+      </c>
+      <c r="Q492">
+        <v>2.75</v>
+      </c>
+      <c r="R492">
+        <v>2.1</v>
+      </c>
+      <c r="S492">
+        <v>4</v>
+      </c>
+      <c r="T492">
+        <v>1.4</v>
+      </c>
+      <c r="U492">
+        <v>2.75</v>
+      </c>
+      <c r="V492">
+        <v>3</v>
+      </c>
+      <c r="W492">
+        <v>1.36</v>
+      </c>
+      <c r="X492">
+        <v>9</v>
+      </c>
+      <c r="Y492">
+        <v>1.07</v>
+      </c>
+      <c r="Z492">
+        <v>1.82</v>
+      </c>
+      <c r="AA492">
+        <v>3.47</v>
+      </c>
+      <c r="AB492">
+        <v>4.3</v>
+      </c>
+      <c r="AC492">
+        <v>1.05</v>
+      </c>
+      <c r="AD492">
+        <v>10</v>
+      </c>
+      <c r="AE492">
+        <v>1.33</v>
+      </c>
+      <c r="AF492">
+        <v>3.25</v>
+      </c>
+      <c r="AG492">
+        <v>1.95</v>
+      </c>
+      <c r="AH492">
+        <v>1.79</v>
+      </c>
+      <c r="AI492">
+        <v>1.8</v>
+      </c>
+      <c r="AJ492">
+        <v>1.91</v>
+      </c>
+      <c r="AK492">
+        <v>1.3</v>
+      </c>
+      <c r="AL492">
+        <v>1.25</v>
+      </c>
+      <c r="AM492">
+        <v>1.78</v>
+      </c>
+      <c r="AN492">
+        <v>1.68</v>
+      </c>
+      <c r="AO492">
+        <v>0.9</v>
+      </c>
+      <c r="AP492">
+        <v>1.65</v>
+      </c>
+      <c r="AQ492">
+        <v>0.9</v>
+      </c>
+      <c r="AR492">
+        <v>1.78</v>
+      </c>
+      <c r="AS492">
+        <v>1.13</v>
+      </c>
+      <c r="AT492">
+        <v>2.91</v>
+      </c>
+      <c r="AU492">
+        <v>2</v>
+      </c>
+      <c r="AV492">
+        <v>3</v>
+      </c>
+      <c r="AW492">
+        <v>11</v>
+      </c>
+      <c r="AX492">
+        <v>4</v>
+      </c>
+      <c r="AY492">
+        <v>17</v>
+      </c>
+      <c r="AZ492">
+        <v>8</v>
+      </c>
+      <c r="BA492">
+        <v>3</v>
+      </c>
+      <c r="BB492">
+        <v>1</v>
+      </c>
+      <c r="BC492">
+        <v>4</v>
+      </c>
+      <c r="BD492">
+        <v>1.63</v>
+      </c>
+      <c r="BE492">
+        <v>6.7</v>
+      </c>
+      <c r="BF492">
+        <v>2.92</v>
+      </c>
+      <c r="BG492">
+        <v>1.22</v>
+      </c>
+      <c r="BH492">
+        <v>3.5</v>
+      </c>
+      <c r="BI492">
+        <v>1.44</v>
+      </c>
+      <c r="BJ492">
+        <v>2.51</v>
+      </c>
+      <c r="BK492">
+        <v>1.77</v>
+      </c>
+      <c r="BL492">
+        <v>1.95</v>
+      </c>
+      <c r="BM492">
+        <v>2.27</v>
+      </c>
+      <c r="BN492">
+        <v>1.53</v>
+      </c>
+      <c r="BO492">
+        <v>2.97</v>
+      </c>
+      <c r="BP492">
+        <v>1.3</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/England EFL League Two_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/England EFL League Two_20242025.xlsx
@@ -101842,10 +101842,10 @@
         <v>5</v>
       </c>
       <c r="BB485">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BC485">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="BD485">
         <v>1.35</v>
